--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G18">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G23">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G32">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>5.99</v>
+        <v>2.29</v>
       </c>
       <c r="O37">
-        <v>4.88</v>
+        <v>3.96</v>
       </c>
       <c r="P37">
-        <v>1.55</v>
+        <v>3.07</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,16 +6379,16 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.29</v>
+        <v>4.06</v>
       </c>
       <c r="O38">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>3.07</v>
+        <v>1.94</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,16 +6542,16 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.06</v>
+        <v>2.23</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="P39">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,16 +6705,16 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC39">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.23</v>
+        <v>2.59</v>
       </c>
       <c r="O40">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="P40">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,16 +6868,16 @@
         <v>0</v>
       </c>
       <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>1.97</v>
+      </c>
+      <c r="AD40">
         <v>1.8</v>
-      </c>
-      <c r="AB40">
-        <v>1.9</v>
-      </c>
-      <c r="AC40">
-        <v>0</v>
-      </c>
-      <c r="AD40">
-        <v>0</v>
       </c>
       <c r="AE40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>4.11</v>
+        <v>5.99</v>
       </c>
       <c r="O41">
-        <v>3.94</v>
+        <v>4.88</v>
       </c>
       <c r="P41">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7040,7 +7040,7 @@
         <v>1.95</v>
       </c>
       <c r="AD41">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.59</v>
+        <v>4.11</v>
       </c>
       <c r="O42">
         <v>3.94</v>
       </c>
       <c r="P42">
-        <v>2.66</v>
+        <v>1.93</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7200,10 +7200,10 @@
         <v>0</v>
       </c>
       <c r="AC42">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AD42">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE42">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G21">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G23">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G32">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.29</v>
+        <v>4.06</v>
       </c>
       <c r="O37">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="P37">
-        <v>3.07</v>
+        <v>1.94</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,16 +6379,16 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.06</v>
+        <v>2.23</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="P38">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,16 +6542,16 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.23</v>
+        <v>2.59</v>
       </c>
       <c r="O39">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="P39">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,16 +6705,16 @@
         <v>0</v>
       </c>
       <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>1.97</v>
+      </c>
+      <c r="AD39">
         <v>1.8</v>
-      </c>
-      <c r="AB39">
-        <v>1.9</v>
-      </c>
-      <c r="AC39">
-        <v>0</v>
-      </c>
-      <c r="AD39">
-        <v>0</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.59</v>
+        <v>5.99</v>
       </c>
       <c r="O40">
-        <v>3.94</v>
+        <v>4.88</v>
       </c>
       <c r="P40">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6874,10 +6874,10 @@
         <v>0</v>
       </c>
       <c r="AC40">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AD40">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>5.99</v>
+        <v>4.11</v>
       </c>
       <c r="O41">
-        <v>4.88</v>
+        <v>3.94</v>
       </c>
       <c r="P41">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7040,7 +7040,7 @@
         <v>1.95</v>
       </c>
       <c r="AD41">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.11</v>
+        <v>2.29</v>
       </c>
       <c r="O42">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="P42">
-        <v>1.93</v>
+        <v>3.07</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,16 +7194,16 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE42">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="O63">
-        <v>6.46</v>
+        <v>4.28</v>
       </c>
       <c r="P63">
-        <v>9.5</v>
+        <v>4.49</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10623,10 +10623,10 @@
         <v>0</v>
       </c>
       <c r="AC63">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AD63">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AE63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.86</v>
+        <v>1.3</v>
       </c>
       <c r="O64">
-        <v>3.86</v>
+        <v>6.46</v>
       </c>
       <c r="P64">
-        <v>2.37</v>
+        <v>9.5</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10786,10 +10786,10 @@
         <v>0</v>
       </c>
       <c r="AC64">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AD64">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AE64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="O65">
-        <v>4.09</v>
+        <v>3.86</v>
       </c>
       <c r="P65">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10949,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AD65">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AE65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.74</v>
+        <v>2.69</v>
       </c>
       <c r="O66">
-        <v>4.28</v>
+        <v>4.09</v>
       </c>
       <c r="P66">
-        <v>4.49</v>
+        <v>2.41</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11112,10 +11112,10 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AD66">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AE66">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G21">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G23">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G29">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G32">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G34">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.9</v>
+        <v>2.59</v>
       </c>
       <c r="O36">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="P36">
-        <v>4.22</v>
+        <v>2.66</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,16 +6216,16 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>4.06</v>
+        <v>5.99</v>
       </c>
       <c r="O37">
-        <v>3.94</v>
+        <v>4.88</v>
       </c>
       <c r="P37">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6385,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="AC37">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AD37">
         <v>1.75</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.23</v>
+        <v>4.11</v>
       </c>
       <c r="O38">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>3.5</v>
+        <v>1.93</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,16 +6542,16 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.59</v>
+        <v>2.29</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="P39">
-        <v>2.66</v>
+        <v>3.07</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,16 +6705,16 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC39">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>5.99</v>
+        <v>1.9</v>
       </c>
       <c r="O40">
-        <v>4.88</v>
+        <v>3.97</v>
       </c>
       <c r="P40">
-        <v>1.55</v>
+        <v>4.22</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,16 +6868,16 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC40">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>4.11</v>
+        <v>2.23</v>
       </c>
       <c r="O41">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="P41">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,16 +7031,16 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC41">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.29</v>
+        <v>4.06</v>
       </c>
       <c r="O42">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="P42">
-        <v>3.07</v>
+        <v>1.94</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,16 +7194,16 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE42">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G54">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G62">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="O65">
-        <v>3.86</v>
+        <v>4.09</v>
       </c>
       <c r="P65">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10949,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AD65">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AE65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="O66">
-        <v>4.09</v>
+        <v>3.86</v>
       </c>
       <c r="P66">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11112,10 +11112,10 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AD66">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AE66">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G23">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,49 +6829,49 @@
         </is>
       </c>
       <c r="N40">
+        <v>2.23</v>
+      </c>
+      <c r="O40">
+        <v>3.58</v>
+      </c>
+      <c r="P40">
+        <v>3.5</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>1.8</v>
+      </c>
+      <c r="AB40">
         <v>1.9</v>
-      </c>
-      <c r="O40">
-        <v>3.97</v>
-      </c>
-      <c r="P40">
-        <v>4.22</v>
-      </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
-      <c r="R40">
-        <v>0</v>
-      </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
-      <c r="T40">
-        <v>0</v>
-      </c>
-      <c r="U40">
-        <v>0</v>
-      </c>
-      <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
-      <c r="X40">
-        <v>0</v>
-      </c>
-      <c r="Y40">
-        <v>0</v>
-      </c>
-      <c r="Z40">
-        <v>0</v>
-      </c>
-      <c r="AA40">
-        <v>1.71</v>
-      </c>
-      <c r="AB40">
-        <v>2</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.23</v>
+        <v>4.06</v>
       </c>
       <c r="O41">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="P41">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,16 +7031,16 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.06</v>
+        <v>1.9</v>
       </c>
       <c r="O42">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="P42">
-        <v>1.94</v>
+        <v>4.22</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,16 +7194,16 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC42">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE42">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.3</v>
+        <v>2.69</v>
       </c>
       <c r="O64">
-        <v>6.46</v>
+        <v>4.09</v>
       </c>
       <c r="P64">
-        <v>9.5</v>
+        <v>2.41</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10786,10 +10786,10 @@
         <v>0</v>
       </c>
       <c r="AC64">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AD64">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AE64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="O65">
-        <v>4.09</v>
+        <v>3.86</v>
       </c>
       <c r="P65">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10949,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AD65">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AE65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.86</v>
+        <v>1.3</v>
       </c>
       <c r="O66">
-        <v>3.86</v>
+        <v>6.46</v>
       </c>
       <c r="P66">
-        <v>2.37</v>
+        <v>9.5</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11112,10 +11112,10 @@
         <v>0</v>
       </c>
       <c r="AC66">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AD66">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="AE66">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU71"/>
+  <dimension ref="A1:AU69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8906,22 +8906,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G60">
@@ -10205,27 +10205,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10368,27 +10368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10460,10 +10460,10 @@
         <v>0</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.74</v>
+        <v>2.86</v>
       </c>
       <c r="O63">
-        <v>4.28</v>
+        <v>3.86</v>
       </c>
       <c r="P63">
-        <v>4.49</v>
+        <v>2.37</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10626,7 +10626,7 @@
         <v>2.15</v>
       </c>
       <c r="AD63">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.69</v>
+        <v>1.3</v>
       </c>
       <c r="O64">
-        <v>4.09</v>
+        <v>6.46</v>
       </c>
       <c r="P64">
-        <v>2.41</v>
+        <v>9.5</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10786,10 +10786,10 @@
         <v>0</v>
       </c>
       <c r="AC64">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AD64">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AE64">
         <v>0</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.86</v>
+        <v>1.86</v>
       </c>
       <c r="O65">
-        <v>3.86</v>
+        <v>4.15</v>
       </c>
       <c r="P65">
-        <v>2.37</v>
+        <v>3.98</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10949,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="AC65">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD65">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AE65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-10-14 21:30:00</t>
+          <t>2026-10-14 22:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.3</v>
+        <v>2.11</v>
       </c>
       <c r="O66">
-        <v>6.46</v>
+        <v>3.77</v>
       </c>
       <c r="P66">
-        <v>9.5</v>
+        <v>3.44</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,16 +11106,16 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC66">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD66">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-10-14 21:30:00</t>
+          <t>2026-10-14 22:30:00</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="O67">
-        <v>4.15</v>
+        <v>4.9</v>
       </c>
       <c r="P67">
-        <v>3.98</v>
+        <v>6.57</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11275,10 +11275,10 @@
         <v>0</v>
       </c>
       <c r="AC67">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD67">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AE67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:00</t>
+          <t>2026-10-14 23:30:00</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.11</v>
+        <v>1.98</v>
       </c>
       <c r="O68">
-        <v>3.77</v>
+        <v>3.94</v>
       </c>
       <c r="P68">
-        <v>3.44</v>
+        <v>3.67</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,7 +11432,7 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB68">
         <v>2.25</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:00</t>
+          <t>2026-10-14 23:30:00</t>
         </is>
       </c>
     </row>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.48</v>
+        <v>1.97</v>
       </c>
       <c r="O69">
-        <v>4.9</v>
+        <v>4.13</v>
       </c>
       <c r="P69">
-        <v>6.57</v>
+        <v>3.55</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11601,10 +11601,10 @@
         <v>0</v>
       </c>
       <c r="AC69">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AD69">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AE69">
         <v>0</v>
@@ -11659,332 +11659,6 @@
         <v>0</v>
       </c>
       <c r="AU69" t="inlineStr">
-        <is>
-          <t>2026-10-14 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N70">
-        <v>1.98</v>
-      </c>
-      <c r="O70">
-        <v>3.94</v>
-      </c>
-      <c r="P70">
-        <v>3.67</v>
-      </c>
-      <c r="Q70">
-        <v>0</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>0</v>
-      </c>
-      <c r="T70">
-        <v>0</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-      <c r="V70">
-        <v>0</v>
-      </c>
-      <c r="W70">
-        <v>0</v>
-      </c>
-      <c r="X70">
-        <v>0</v>
-      </c>
-      <c r="Y70">
-        <v>0</v>
-      </c>
-      <c r="Z70">
-        <v>0</v>
-      </c>
-      <c r="AA70">
-        <v>1.55</v>
-      </c>
-      <c r="AB70">
-        <v>2.25</v>
-      </c>
-      <c r="AC70">
-        <v>0</v>
-      </c>
-      <c r="AD70">
-        <v>0</v>
-      </c>
-      <c r="AE70">
-        <v>0</v>
-      </c>
-      <c r="AF70">
-        <v>0</v>
-      </c>
-      <c r="AG70">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>0</v>
-      </c>
-      <c r="AK70">
-        <v>0</v>
-      </c>
-      <c r="AL70">
-        <v>0</v>
-      </c>
-      <c r="AM70">
-        <v>-1</v>
-      </c>
-      <c r="AN70">
-        <v>-1</v>
-      </c>
-      <c r="AO70">
-        <v>-1</v>
-      </c>
-      <c r="AP70">
-        <v>-1</v>
-      </c>
-      <c r="AQ70">
-        <v>0</v>
-      </c>
-      <c r="AR70">
-        <v>0</v>
-      </c>
-      <c r="AS70">
-        <v>0</v>
-      </c>
-      <c r="AT70">
-        <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>2026-10-14 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N71">
-        <v>1.97</v>
-      </c>
-      <c r="O71">
-        <v>4.13</v>
-      </c>
-      <c r="P71">
-        <v>3.55</v>
-      </c>
-      <c r="Q71">
-        <v>0</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>0</v>
-      </c>
-      <c r="T71">
-        <v>0</v>
-      </c>
-      <c r="U71">
-        <v>0</v>
-      </c>
-      <c r="V71">
-        <v>0</v>
-      </c>
-      <c r="W71">
-        <v>0</v>
-      </c>
-      <c r="X71">
-        <v>0</v>
-      </c>
-      <c r="Y71">
-        <v>0</v>
-      </c>
-      <c r="Z71">
-        <v>0</v>
-      </c>
-      <c r="AA71">
-        <v>0</v>
-      </c>
-      <c r="AB71">
-        <v>0</v>
-      </c>
-      <c r="AC71">
-        <v>1.9</v>
-      </c>
-      <c r="AD71">
-        <v>1.77</v>
-      </c>
-      <c r="AE71">
-        <v>0</v>
-      </c>
-      <c r="AF71">
-        <v>0</v>
-      </c>
-      <c r="AG71">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ71">
-        <v>0</v>
-      </c>
-      <c r="AK71">
-        <v>0</v>
-      </c>
-      <c r="AL71">
-        <v>0</v>
-      </c>
-      <c r="AM71">
-        <v>-1</v>
-      </c>
-      <c r="AN71">
-        <v>-1</v>
-      </c>
-      <c r="AO71">
-        <v>-1</v>
-      </c>
-      <c r="AP71">
-        <v>-1</v>
-      </c>
-      <c r="AQ71">
-        <v>0</v>
-      </c>
-      <c r="AR71">
-        <v>0</v>
-      </c>
-      <c r="AS71">
-        <v>0</v>
-      </c>
-      <c r="AT71">
-        <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
         <is>
           <t>2026-10-14 23:30:00</t>
         </is>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.85</v>
+        <v>2.19</v>
       </c>
       <c r="O47">
-        <v>4.11</v>
+        <v>3.84</v>
       </c>
       <c r="P47">
-        <v>4.07</v>
+        <v>3.18</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,16 +8009,16 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC47">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.48</v>
+        <v>1.85</v>
       </c>
       <c r="O48">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
       <c r="P48">
-        <v>2.62</v>
+        <v>4.07</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8178,10 +8178,10 @@
         <v>0</v>
       </c>
       <c r="AC48">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AD48">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AE48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="O49">
-        <v>3.86</v>
+        <v>4.09</v>
       </c>
       <c r="P49">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,16 +8335,16 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AD49">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AE49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G50">
@@ -8462,10 +8462,10 @@
         <v>2.1</v>
       </c>
       <c r="O50">
-        <v>4.12</v>
+        <v>3.86</v>
       </c>
       <c r="P50">
-        <v>3.21</v>
+        <v>3.4</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,16 +8498,16 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC50">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AD50">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AE50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="O51">
-        <v>5.05</v>
+        <v>4.12</v>
       </c>
       <c r="P51">
-        <v>5.83</v>
+        <v>3.21</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AD51">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.19</v>
+        <v>1.51</v>
       </c>
       <c r="O52">
-        <v>3.84</v>
+        <v>5.05</v>
       </c>
       <c r="P52">
-        <v>3.18</v>
+        <v>5.83</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,16 +8824,16 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE52">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G60">

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU69"/>
+  <dimension ref="A1:AU61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.59</v>
+        <v>5.99</v>
       </c>
       <c r="O36">
-        <v>3.94</v>
+        <v>4.88</v>
       </c>
       <c r="P36">
-        <v>2.66</v>
+        <v>1.55</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6222,10 +6222,10 @@
         <v>0</v>
       </c>
       <c r="AC36">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AD36">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>5.99</v>
+        <v>4.11</v>
       </c>
       <c r="O37">
-        <v>4.88</v>
+        <v>3.94</v>
       </c>
       <c r="P37">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6388,7 +6388,7 @@
         <v>1.95</v>
       </c>
       <c r="AD37">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.11</v>
+        <v>2.29</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="P38">
-        <v>1.93</v>
+        <v>3.07</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,16 +6542,16 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC38">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="O39">
-        <v>3.96</v>
+        <v>3.58</v>
       </c>
       <c r="P39">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB39">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.23</v>
+        <v>4.06</v>
       </c>
       <c r="O40">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="P40">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,16 +6868,16 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB40">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>4.06</v>
+        <v>1.9</v>
       </c>
       <c r="O41">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="P41">
-        <v>1.94</v>
+        <v>4.22</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,16 +7031,16 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC41">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.9</v>
+        <v>2.59</v>
       </c>
       <c r="O42">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="P42">
-        <v>4.22</v>
+        <v>2.66</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,16 +7194,16 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE42">
         <v>0</v>
@@ -8901,27 +8901,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8993,10 +8993,10 @@
         <v>0</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 21:30:00</t>
         </is>
       </c>
     </row>
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9156,10 +9156,10 @@
         <v>0</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 21:30:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 21:30:00</t>
         </is>
       </c>
     </row>
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>6.46</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9482,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 21:30:00</t>
         </is>
       </c>
     </row>
@@ -9553,27 +9553,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 22:30:00</t>
         </is>
       </c>
     </row>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9808,10 +9808,10 @@
         <v>0</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 22:30:00</t>
         </is>
       </c>
     </row>
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9971,10 +9971,10 @@
         <v>0</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 23:30:00</t>
         </is>
       </c>
     </row>
@@ -10042,27 +10042,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10134,10 +10134,10 @@
         <v>0</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 23:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="O61">
-        <v>4.28</v>
+        <v>3.94</v>
       </c>
       <c r="P61">
-        <v>4.49</v>
+        <v>3.67</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10291,16 +10291,16 @@
         <v>0</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC61">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD61">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -10355,1310 +10355,6 @@
         <v>0</v>
       </c>
       <c r="AU61" t="inlineStr">
-        <is>
-          <t>2026-10-14 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Chicago Fire</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Philadelphia Union</t>
-        </is>
-      </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>0</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N62">
-        <v>2.69</v>
-      </c>
-      <c r="O62">
-        <v>4.09</v>
-      </c>
-      <c r="P62">
-        <v>2.41</v>
-      </c>
-      <c r="Q62">
-        <v>0</v>
-      </c>
-      <c r="R62">
-        <v>0</v>
-      </c>
-      <c r="S62">
-        <v>0</v>
-      </c>
-      <c r="T62">
-        <v>0</v>
-      </c>
-      <c r="U62">
-        <v>0</v>
-      </c>
-      <c r="V62">
-        <v>0</v>
-      </c>
-      <c r="W62">
-        <v>0</v>
-      </c>
-      <c r="X62">
-        <v>0</v>
-      </c>
-      <c r="Y62">
-        <v>0</v>
-      </c>
-      <c r="Z62">
-        <v>0</v>
-      </c>
-      <c r="AA62">
-        <v>0</v>
-      </c>
-      <c r="AB62">
-        <v>0</v>
-      </c>
-      <c r="AC62">
-        <v>1.9</v>
-      </c>
-      <c r="AD62">
-        <v>1.78</v>
-      </c>
-      <c r="AE62">
-        <v>0</v>
-      </c>
-      <c r="AF62">
-        <v>0</v>
-      </c>
-      <c r="AG62">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>0</v>
-      </c>
-      <c r="AK62">
-        <v>0</v>
-      </c>
-      <c r="AL62">
-        <v>0</v>
-      </c>
-      <c r="AM62">
-        <v>-1</v>
-      </c>
-      <c r="AN62">
-        <v>-1</v>
-      </c>
-      <c r="AO62">
-        <v>-1</v>
-      </c>
-      <c r="AP62">
-        <v>-1</v>
-      </c>
-      <c r="AQ62">
-        <v>0</v>
-      </c>
-      <c r="AR62">
-        <v>0</v>
-      </c>
-      <c r="AS62">
-        <v>0</v>
-      </c>
-      <c r="AT62">
-        <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>2026-10-14 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Vancouver Whitecaps</t>
-        </is>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>0</v>
-      </c>
-      <c r="K63">
-        <v>0</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N63">
-        <v>2.86</v>
-      </c>
-      <c r="O63">
-        <v>3.86</v>
-      </c>
-      <c r="P63">
-        <v>2.37</v>
-      </c>
-      <c r="Q63">
-        <v>0</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
-        <v>0</v>
-      </c>
-      <c r="T63">
-        <v>0</v>
-      </c>
-      <c r="U63">
-        <v>0</v>
-      </c>
-      <c r="V63">
-        <v>0</v>
-      </c>
-      <c r="W63">
-        <v>0</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>0</v>
-      </c>
-      <c r="Z63">
-        <v>0</v>
-      </c>
-      <c r="AA63">
-        <v>0</v>
-      </c>
-      <c r="AB63">
-        <v>0</v>
-      </c>
-      <c r="AC63">
-        <v>2.15</v>
-      </c>
-      <c r="AD63">
-        <v>1.61</v>
-      </c>
-      <c r="AE63">
-        <v>0</v>
-      </c>
-      <c r="AF63">
-        <v>0</v>
-      </c>
-      <c r="AG63">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>0</v>
-      </c>
-      <c r="AK63">
-        <v>0</v>
-      </c>
-      <c r="AL63">
-        <v>0</v>
-      </c>
-      <c r="AM63">
-        <v>-1</v>
-      </c>
-      <c r="AN63">
-        <v>-1</v>
-      </c>
-      <c r="AO63">
-        <v>-1</v>
-      </c>
-      <c r="AP63">
-        <v>-1</v>
-      </c>
-      <c r="AQ63">
-        <v>0</v>
-      </c>
-      <c r="AR63">
-        <v>0</v>
-      </c>
-      <c r="AS63">
-        <v>0</v>
-      </c>
-      <c r="AT63">
-        <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>2026-10-14 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Nashville SC</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Sporting KC</t>
-        </is>
-      </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
-      <c r="H64">
-        <v>0</v>
-      </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>0</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N64">
-        <v>1.3</v>
-      </c>
-      <c r="O64">
-        <v>6.46</v>
-      </c>
-      <c r="P64">
-        <v>9.5</v>
-      </c>
-      <c r="Q64">
-        <v>0</v>
-      </c>
-      <c r="R64">
-        <v>0</v>
-      </c>
-      <c r="S64">
-        <v>0</v>
-      </c>
-      <c r="T64">
-        <v>0</v>
-      </c>
-      <c r="U64">
-        <v>0</v>
-      </c>
-      <c r="V64">
-        <v>0</v>
-      </c>
-      <c r="W64">
-        <v>0</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
-      </c>
-      <c r="Y64">
-        <v>0</v>
-      </c>
-      <c r="Z64">
-        <v>0</v>
-      </c>
-      <c r="AA64">
-        <v>0</v>
-      </c>
-      <c r="AB64">
-        <v>0</v>
-      </c>
-      <c r="AC64">
-        <v>1.82</v>
-      </c>
-      <c r="AD64">
-        <v>1.87</v>
-      </c>
-      <c r="AE64">
-        <v>0</v>
-      </c>
-      <c r="AF64">
-        <v>0</v>
-      </c>
-      <c r="AG64">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>0</v>
-      </c>
-      <c r="AK64">
-        <v>0</v>
-      </c>
-      <c r="AL64">
-        <v>0</v>
-      </c>
-      <c r="AM64">
-        <v>-1</v>
-      </c>
-      <c r="AN64">
-        <v>-1</v>
-      </c>
-      <c r="AO64">
-        <v>-1</v>
-      </c>
-      <c r="AP64">
-        <v>-1</v>
-      </c>
-      <c r="AQ64">
-        <v>0</v>
-      </c>
-      <c r="AR64">
-        <v>0</v>
-      </c>
-      <c r="AS64">
-        <v>0</v>
-      </c>
-      <c r="AT64">
-        <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>2026-10-14 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Real Salt Lake</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>SJ Earthquakes</t>
-        </is>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65">
-        <v>0</v>
-      </c>
-      <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>0</v>
-      </c>
-      <c r="K65">
-        <v>0</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N65">
-        <v>1.86</v>
-      </c>
-      <c r="O65">
-        <v>4.15</v>
-      </c>
-      <c r="P65">
-        <v>3.98</v>
-      </c>
-      <c r="Q65">
-        <v>0</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
-        <v>0</v>
-      </c>
-      <c r="T65">
-        <v>0</v>
-      </c>
-      <c r="U65">
-        <v>0</v>
-      </c>
-      <c r="V65">
-        <v>0</v>
-      </c>
-      <c r="W65">
-        <v>0</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>0</v>
-      </c>
-      <c r="Z65">
-        <v>0</v>
-      </c>
-      <c r="AA65">
-        <v>0</v>
-      </c>
-      <c r="AB65">
-        <v>0</v>
-      </c>
-      <c r="AC65">
-        <v>2.05</v>
-      </c>
-      <c r="AD65">
-        <v>1.66</v>
-      </c>
-      <c r="AE65">
-        <v>0</v>
-      </c>
-      <c r="AF65">
-        <v>0</v>
-      </c>
-      <c r="AG65">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>0</v>
-      </c>
-      <c r="AK65">
-        <v>0</v>
-      </c>
-      <c r="AL65">
-        <v>0</v>
-      </c>
-      <c r="AM65">
-        <v>-1</v>
-      </c>
-      <c r="AN65">
-        <v>-1</v>
-      </c>
-      <c r="AO65">
-        <v>-1</v>
-      </c>
-      <c r="AP65">
-        <v>-1</v>
-      </c>
-      <c r="AQ65">
-        <v>0</v>
-      </c>
-      <c r="AR65">
-        <v>0</v>
-      </c>
-      <c r="AS65">
-        <v>0</v>
-      </c>
-      <c r="AT65">
-        <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>2026-10-14 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Colorado Rapids</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Minnesota United</t>
-        </is>
-      </c>
-      <c r="G66">
-        <v>0</v>
-      </c>
-      <c r="H66">
-        <v>0</v>
-      </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>0</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N66">
-        <v>2.11</v>
-      </c>
-      <c r="O66">
-        <v>3.77</v>
-      </c>
-      <c r="P66">
-        <v>3.44</v>
-      </c>
-      <c r="Q66">
-        <v>0</v>
-      </c>
-      <c r="R66">
-        <v>0</v>
-      </c>
-      <c r="S66">
-        <v>0</v>
-      </c>
-      <c r="T66">
-        <v>0</v>
-      </c>
-      <c r="U66">
-        <v>0</v>
-      </c>
-      <c r="V66">
-        <v>0</v>
-      </c>
-      <c r="W66">
-        <v>0</v>
-      </c>
-      <c r="X66">
-        <v>0</v>
-      </c>
-      <c r="Y66">
-        <v>0</v>
-      </c>
-      <c r="Z66">
-        <v>0</v>
-      </c>
-      <c r="AA66">
-        <v>1.57</v>
-      </c>
-      <c r="AB66">
-        <v>2.25</v>
-      </c>
-      <c r="AC66">
-        <v>0</v>
-      </c>
-      <c r="AD66">
-        <v>0</v>
-      </c>
-      <c r="AE66">
-        <v>0</v>
-      </c>
-      <c r="AF66">
-        <v>0</v>
-      </c>
-      <c r="AG66">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>0</v>
-      </c>
-      <c r="AK66">
-        <v>0</v>
-      </c>
-      <c r="AL66">
-        <v>0</v>
-      </c>
-      <c r="AM66">
-        <v>-1</v>
-      </c>
-      <c r="AN66">
-        <v>-1</v>
-      </c>
-      <c r="AO66">
-        <v>-1</v>
-      </c>
-      <c r="AP66">
-        <v>-1</v>
-      </c>
-      <c r="AQ66">
-        <v>0</v>
-      </c>
-      <c r="AR66">
-        <v>0</v>
-      </c>
-      <c r="AS66">
-        <v>0</v>
-      </c>
-      <c r="AT66">
-        <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>2026-10-14 22:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>0</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N67">
-        <v>1.48</v>
-      </c>
-      <c r="O67">
-        <v>4.9</v>
-      </c>
-      <c r="P67">
-        <v>6.57</v>
-      </c>
-      <c r="Q67">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>0</v>
-      </c>
-      <c r="S67">
-        <v>0</v>
-      </c>
-      <c r="T67">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>0</v>
-      </c>
-      <c r="V67">
-        <v>0</v>
-      </c>
-      <c r="W67">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>0</v>
-      </c>
-      <c r="Y67">
-        <v>0</v>
-      </c>
-      <c r="Z67">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>0</v>
-      </c>
-      <c r="AB67">
-        <v>0</v>
-      </c>
-      <c r="AC67">
-        <v>2.25</v>
-      </c>
-      <c r="AD67">
-        <v>1.55</v>
-      </c>
-      <c r="AE67">
-        <v>0</v>
-      </c>
-      <c r="AF67">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ67">
-        <v>0</v>
-      </c>
-      <c r="AK67">
-        <v>0</v>
-      </c>
-      <c r="AL67">
-        <v>0</v>
-      </c>
-      <c r="AM67">
-        <v>-1</v>
-      </c>
-      <c r="AN67">
-        <v>-1</v>
-      </c>
-      <c r="AO67">
-        <v>-1</v>
-      </c>
-      <c r="AP67">
-        <v>-1</v>
-      </c>
-      <c r="AQ67">
-        <v>0</v>
-      </c>
-      <c r="AR67">
-        <v>0</v>
-      </c>
-      <c r="AS67">
-        <v>0</v>
-      </c>
-      <c r="AT67">
-        <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>2026-10-14 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Houston Dynamo</t>
-        </is>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N68">
-        <v>1.98</v>
-      </c>
-      <c r="O68">
-        <v>3.94</v>
-      </c>
-      <c r="P68">
-        <v>3.67</v>
-      </c>
-      <c r="Q68">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>0</v>
-      </c>
-      <c r="S68">
-        <v>0</v>
-      </c>
-      <c r="T68">
-        <v>0</v>
-      </c>
-      <c r="U68">
-        <v>0</v>
-      </c>
-      <c r="V68">
-        <v>0</v>
-      </c>
-      <c r="W68">
-        <v>0</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
-      </c>
-      <c r="Y68">
-        <v>0</v>
-      </c>
-      <c r="Z68">
-        <v>0</v>
-      </c>
-      <c r="AA68">
-        <v>1.55</v>
-      </c>
-      <c r="AB68">
-        <v>2.25</v>
-      </c>
-      <c r="AC68">
-        <v>0</v>
-      </c>
-      <c r="AD68">
-        <v>0</v>
-      </c>
-      <c r="AE68">
-        <v>0</v>
-      </c>
-      <c r="AF68">
-        <v>0</v>
-      </c>
-      <c r="AG68">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>0</v>
-      </c>
-      <c r="AK68">
-        <v>0</v>
-      </c>
-      <c r="AL68">
-        <v>0</v>
-      </c>
-      <c r="AM68">
-        <v>-1</v>
-      </c>
-      <c r="AN68">
-        <v>-1</v>
-      </c>
-      <c r="AO68">
-        <v>-1</v>
-      </c>
-      <c r="AP68">
-        <v>-1</v>
-      </c>
-      <c r="AQ68">
-        <v>0</v>
-      </c>
-      <c r="AR68">
-        <v>0</v>
-      </c>
-      <c r="AS68">
-        <v>0</v>
-      </c>
-      <c r="AT68">
-        <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>2026-10-14 23:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Portland Timbers</t>
-        </is>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69">
-        <v>0</v>
-      </c>
-      <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>0</v>
-      </c>
-      <c r="K69">
-        <v>0</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N69">
-        <v>1.97</v>
-      </c>
-      <c r="O69">
-        <v>4.13</v>
-      </c>
-      <c r="P69">
-        <v>3.55</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-      <c r="T69">
-        <v>0</v>
-      </c>
-      <c r="U69">
-        <v>0</v>
-      </c>
-      <c r="V69">
-        <v>0</v>
-      </c>
-      <c r="W69">
-        <v>0</v>
-      </c>
-      <c r="X69">
-        <v>0</v>
-      </c>
-      <c r="Y69">
-        <v>0</v>
-      </c>
-      <c r="Z69">
-        <v>0</v>
-      </c>
-      <c r="AA69">
-        <v>0</v>
-      </c>
-      <c r="AB69">
-        <v>0</v>
-      </c>
-      <c r="AC69">
-        <v>1.9</v>
-      </c>
-      <c r="AD69">
-        <v>1.77</v>
-      </c>
-      <c r="AE69">
-        <v>0</v>
-      </c>
-      <c r="AF69">
-        <v>0</v>
-      </c>
-      <c r="AG69">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>0</v>
-      </c>
-      <c r="AK69">
-        <v>0</v>
-      </c>
-      <c r="AL69">
-        <v>0</v>
-      </c>
-      <c r="AM69">
-        <v>-1</v>
-      </c>
-      <c r="AN69">
-        <v>-1</v>
-      </c>
-      <c r="AO69">
-        <v>-1</v>
-      </c>
-      <c r="AP69">
-        <v>-1</v>
-      </c>
-      <c r="AQ69">
-        <v>0</v>
-      </c>
-      <c r="AR69">
-        <v>0</v>
-      </c>
-      <c r="AS69">
-        <v>0</v>
-      </c>
-      <c r="AT69">
-        <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
         <is>
           <t>2026-10-14 23:30:00</t>
         </is>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU61"/>
+  <dimension ref="A1:AU68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G8">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G9">
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00:00</t>
+          <t>2026-10-14 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2060,22 +2060,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G12">
@@ -2261,69 +2261,69 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N12">
+        <v>2.2</v>
+      </c>
+      <c r="O12">
+        <v>3.3</v>
+      </c>
+      <c r="P12">
+        <v>2.85</v>
+      </c>
+      <c r="Q12">
+        <v>2.8</v>
+      </c>
+      <c r="R12">
+        <v>2.1</v>
+      </c>
+      <c r="S12">
+        <v>1.36</v>
+      </c>
+      <c r="T12">
+        <v>2.88</v>
+      </c>
+      <c r="U12">
+        <v>2.62</v>
+      </c>
+      <c r="V12">
+        <v>1.44</v>
+      </c>
+      <c r="W12">
+        <v>1.1</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.26</v>
+      </c>
+      <c r="Z12">
+        <v>3.88</v>
+      </c>
+      <c r="AA12">
+        <v>1.74</v>
+      </c>
+      <c r="AB12">
+        <v>2.04</v>
+      </c>
+      <c r="AC12">
+        <v>2.7</v>
+      </c>
+      <c r="AD12">
+        <v>1.29</v>
+      </c>
+      <c r="AE12">
+        <v>1.11</v>
+      </c>
+      <c r="AF12">
+        <v>1.65</v>
+      </c>
+      <c r="AG12">
         <v>2.05</v>
       </c>
-      <c r="O12">
-        <v>3.1</v>
-      </c>
-      <c r="P12">
-        <v>3.25</v>
-      </c>
-      <c r="Q12">
-        <v>2.7</v>
-      </c>
-      <c r="R12">
-        <v>1.86</v>
-      </c>
-      <c r="S12">
-        <v>1.49</v>
-      </c>
-      <c r="T12">
-        <v>2.34</v>
-      </c>
-      <c r="U12">
-        <v>3.6</v>
-      </c>
-      <c r="V12">
-        <v>1.25</v>
-      </c>
-      <c r="W12">
-        <v>1.03</v>
-      </c>
-      <c r="X12">
-        <v>1.05</v>
-      </c>
-      <c r="Y12">
-        <v>1.38</v>
-      </c>
-      <c r="Z12">
-        <v>2.62</v>
-      </c>
-      <c r="AA12">
-        <v>1.94</v>
-      </c>
-      <c r="AB12">
-        <v>1.53</v>
-      </c>
-      <c r="AC12">
-        <v>4.1</v>
-      </c>
-      <c r="AD12">
-        <v>1.13</v>
-      </c>
-      <c r="AE12">
-        <v>1.02</v>
-      </c>
-      <c r="AF12">
-        <v>1.91</v>
-      </c>
-      <c r="AG12">
-        <v>1.76</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AK12">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00:00</t>
+          <t>2026-10-14 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,68 +2424,68 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2544,27 +2544,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2636,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-14 13:00:00</t>
+          <t>2026-10-14 13:45:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2962,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="AC16">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-14 13:45:00</t>
+          <t>2026-10-14 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G17">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G31">
@@ -5478,27 +5478,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-10-14 14:00:00</t>
+          <t>2026-10-14 15:45:00</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G33">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>5.99</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-14 15:45:00</t>
+          <t>2026-10-14 16:00:00</t>
         </is>
       </c>
     </row>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>5.99</v>
+        <v>4.11</v>
       </c>
       <c r="O36">
-        <v>4.88</v>
+        <v>3.94</v>
       </c>
       <c r="P36">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6225,7 +6225,7 @@
         <v>1.95</v>
       </c>
       <c r="AD36">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>4.11</v>
+        <v>2.29</v>
       </c>
       <c r="O37">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="P37">
-        <v>1.93</v>
+        <v>3.07</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,16 +6379,16 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="O38">
-        <v>3.96</v>
+        <v>3.58</v>
       </c>
       <c r="P38">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AB38">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.23</v>
+        <v>4.06</v>
       </c>
       <c r="O39">
-        <v>3.58</v>
+        <v>3.94</v>
       </c>
       <c r="P39">
-        <v>3.5</v>
+        <v>1.94</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,16 +6705,16 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.06</v>
+        <v>1.9</v>
       </c>
       <c r="O40">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="P40">
-        <v>1.94</v>
+        <v>4.22</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,16 +6868,16 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC40">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.9</v>
+        <v>2.59</v>
       </c>
       <c r="O41">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="P41">
-        <v>4.22</v>
+        <v>2.66</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,16 +7031,16 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE41">
         <v>0</v>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7200,10 +7200,10 @@
         <v>0</v>
       </c>
       <c r="AC42">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE42">
         <v>0</v>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-14 16:00:00</t>
+          <t>2026-10-14 17:00:00</t>
         </is>
       </c>
     </row>
@@ -7434,27 +7434,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-14 17:00:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G45">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-10-14 20:00:00</t>
+          <t>2026-10-14 20:30:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7846,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="O47">
-        <v>3.84</v>
+        <v>4.11</v>
       </c>
       <c r="P47">
-        <v>3.18</v>
+        <v>4.07</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,16 +8009,16 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,55 +8133,55 @@
         </is>
       </c>
       <c r="N48">
+        <v>2.48</v>
+      </c>
+      <c r="O48">
+        <v>4.09</v>
+      </c>
+      <c r="P48">
+        <v>2.62</v>
+      </c>
+      <c r="Q48">
+        <v>0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>1.83</v>
+      </c>
+      <c r="AD48">
         <v>1.85</v>
-      </c>
-      <c r="O48">
-        <v>4.11</v>
-      </c>
-      <c r="P48">
-        <v>4.07</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
-        <v>0</v>
-      </c>
-      <c r="AB48">
-        <v>0</v>
-      </c>
-      <c r="AC48">
-        <v>2.15</v>
-      </c>
-      <c r="AD48">
-        <v>1.62</v>
       </c>
       <c r="AE48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="O49">
-        <v>4.09</v>
+        <v>3.86</v>
       </c>
       <c r="P49">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,16 +8335,16 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC49">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AD49">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AE49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G50">
@@ -8462,10 +8462,10 @@
         <v>2.1</v>
       </c>
       <c r="O50">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="P50">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,16 +8498,16 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD50">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AE50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.1</v>
+        <v>1.51</v>
       </c>
       <c r="O51">
-        <v>4.12</v>
+        <v>5.05</v>
       </c>
       <c r="P51">
-        <v>3.21</v>
+        <v>5.83</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AD51">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8830,10 +8830,10 @@
         <v>0</v>
       </c>
       <c r="AC52">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-10-14 20:30:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -8901,27 +8901,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G53">
@@ -8944,17 +8944,17 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N53">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8993,10 +8993,10 @@
         <v>0</v>
       </c>
       <c r="AC53">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD53">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-10-14 21:30:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G54">
@@ -9107,17 +9107,17 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N54">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9156,10 +9156,10 @@
         <v>0</v>
       </c>
       <c r="AC54">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-14 21:30:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,27 +9227,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G55">
@@ -9270,17 +9270,17 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N55">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="AC55">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD55">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-14 21:30:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G56">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N56">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9482,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="AC56">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-10-14 21:30:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9553,27 +9553,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9639,10 +9639,10 @@
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB57">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,17 +9759,17 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9808,10 +9808,10 @@
         <v>0</v>
       </c>
       <c r="AC58">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD58">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -9879,27 +9879,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9971,10 +9971,10 @@
         <v>0</v>
       </c>
       <c r="AC59">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD59">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-10-14 23:30:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="O60">
-        <v>4.13</v>
+        <v>4.28</v>
       </c>
       <c r="P60">
-        <v>3.55</v>
+        <v>4.49</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10134,10 +10134,10 @@
         <v>0</v>
       </c>
       <c r="AC60">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AD60">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AE60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-10-14 23:30:00</t>
+          <t>2026-10-14 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,156 +10205,1297 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N61">
+        <v>2.69</v>
+      </c>
+      <c r="O61">
+        <v>4.09</v>
+      </c>
+      <c r="P61">
+        <v>2.41</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+      <c r="AB61">
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <v>1.9</v>
+      </c>
+      <c r="AD61">
+        <v>1.78</v>
+      </c>
+      <c r="AE61">
+        <v>0</v>
+      </c>
+      <c r="AF61">
+        <v>0</v>
+      </c>
+      <c r="AG61">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>0</v>
+      </c>
+      <c r="AK61">
+        <v>0</v>
+      </c>
+      <c r="AL61">
+        <v>0</v>
+      </c>
+      <c r="AM61">
+        <v>-1</v>
+      </c>
+      <c r="AN61">
+        <v>-1</v>
+      </c>
+      <c r="AO61">
+        <v>-1</v>
+      </c>
+      <c r="AP61">
+        <v>-1</v>
+      </c>
+      <c r="AQ61">
+        <v>0</v>
+      </c>
+      <c r="AR61">
+        <v>0</v>
+      </c>
+      <c r="AS61">
+        <v>0</v>
+      </c>
+      <c r="AT61">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>St. Louis City</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N62">
+        <v>2.86</v>
+      </c>
+      <c r="O62">
+        <v>3.86</v>
+      </c>
+      <c r="P62">
+        <v>2.37</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+      <c r="AB62">
+        <v>0</v>
+      </c>
+      <c r="AC62">
+        <v>2.15</v>
+      </c>
+      <c r="AD62">
+        <v>1.61</v>
+      </c>
+      <c r="AE62">
+        <v>0</v>
+      </c>
+      <c r="AF62">
+        <v>0</v>
+      </c>
+      <c r="AG62">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>0</v>
+      </c>
+      <c r="AK62">
+        <v>0</v>
+      </c>
+      <c r="AL62">
+        <v>0</v>
+      </c>
+      <c r="AM62">
+        <v>-1</v>
+      </c>
+      <c r="AN62">
+        <v>-1</v>
+      </c>
+      <c r="AO62">
+        <v>-1</v>
+      </c>
+      <c r="AP62">
+        <v>-1</v>
+      </c>
+      <c r="AQ62">
+        <v>0</v>
+      </c>
+      <c r="AR62">
+        <v>0</v>
+      </c>
+      <c r="AS62">
+        <v>0</v>
+      </c>
+      <c r="AT62">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Sporting KC</t>
+        </is>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N63">
+        <v>1.3</v>
+      </c>
+      <c r="O63">
+        <v>6.46</v>
+      </c>
+      <c r="P63">
+        <v>9.5</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>1.82</v>
+      </c>
+      <c r="AD63">
+        <v>1.87</v>
+      </c>
+      <c r="AE63">
+        <v>0</v>
+      </c>
+      <c r="AF63">
+        <v>0</v>
+      </c>
+      <c r="AG63">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>0</v>
+      </c>
+      <c r="AK63">
+        <v>0</v>
+      </c>
+      <c r="AL63">
+        <v>0</v>
+      </c>
+      <c r="AM63">
+        <v>-1</v>
+      </c>
+      <c r="AN63">
+        <v>-1</v>
+      </c>
+      <c r="AO63">
+        <v>-1</v>
+      </c>
+      <c r="AP63">
+        <v>-1</v>
+      </c>
+      <c r="AQ63">
+        <v>0</v>
+      </c>
+      <c r="AR63">
+        <v>0</v>
+      </c>
+      <c r="AS63">
+        <v>0</v>
+      </c>
+      <c r="AT63">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>2026-10-14 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N64">
+        <v>2.11</v>
+      </c>
+      <c r="O64">
+        <v>3.77</v>
+      </c>
+      <c r="P64">
+        <v>3.44</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>1.57</v>
+      </c>
+      <c r="AB64">
+        <v>2.25</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>0</v>
+      </c>
+      <c r="AE64">
+        <v>0</v>
+      </c>
+      <c r="AF64">
+        <v>0</v>
+      </c>
+      <c r="AG64">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
+        <v>0</v>
+      </c>
+      <c r="AK64">
+        <v>0</v>
+      </c>
+      <c r="AL64">
+        <v>0</v>
+      </c>
+      <c r="AM64">
+        <v>-1</v>
+      </c>
+      <c r="AN64">
+        <v>-1</v>
+      </c>
+      <c r="AO64">
+        <v>-1</v>
+      </c>
+      <c r="AP64">
+        <v>-1</v>
+      </c>
+      <c r="AQ64">
+        <v>0</v>
+      </c>
+      <c r="AR64">
+        <v>0</v>
+      </c>
+      <c r="AS64">
+        <v>0</v>
+      </c>
+      <c r="AT64">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N65">
+        <v>1.86</v>
+      </c>
+      <c r="O65">
+        <v>4.15</v>
+      </c>
+      <c r="P65">
+        <v>3.98</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>0</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>2.05</v>
+      </c>
+      <c r="AD65">
+        <v>1.66</v>
+      </c>
+      <c r="AE65">
+        <v>0</v>
+      </c>
+      <c r="AF65">
+        <v>0</v>
+      </c>
+      <c r="AG65">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>0</v>
+      </c>
+      <c r="AK65">
+        <v>0</v>
+      </c>
+      <c r="AL65">
+        <v>0</v>
+      </c>
+      <c r="AM65">
+        <v>-1</v>
+      </c>
+      <c r="AN65">
+        <v>-1</v>
+      </c>
+      <c r="AO65">
+        <v>-1</v>
+      </c>
+      <c r="AP65">
+        <v>-1</v>
+      </c>
+      <c r="AQ65">
+        <v>0</v>
+      </c>
+      <c r="AR65">
+        <v>0</v>
+      </c>
+      <c r="AS65">
+        <v>0</v>
+      </c>
+      <c r="AT65">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>2026-10-14 22:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N66">
+        <v>1.48</v>
+      </c>
+      <c r="O66">
+        <v>4.9</v>
+      </c>
+      <c r="P66">
+        <v>6.57</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>0</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+      <c r="AA66">
+        <v>0</v>
+      </c>
+      <c r="AB66">
+        <v>0</v>
+      </c>
+      <c r="AC66">
+        <v>2.25</v>
+      </c>
+      <c r="AD66">
+        <v>1.55</v>
+      </c>
+      <c r="AE66">
+        <v>0</v>
+      </c>
+      <c r="AF66">
+        <v>0</v>
+      </c>
+      <c r="AG66">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>0</v>
+      </c>
+      <c r="AK66">
+        <v>0</v>
+      </c>
+      <c r="AL66">
+        <v>0</v>
+      </c>
+      <c r="AM66">
+        <v>-1</v>
+      </c>
+      <c r="AN66">
+        <v>-1</v>
+      </c>
+      <c r="AO66">
+        <v>-1</v>
+      </c>
+      <c r="AP66">
+        <v>-1</v>
+      </c>
+      <c r="AQ66">
+        <v>0</v>
+      </c>
+      <c r="AR66">
+        <v>0</v>
+      </c>
+      <c r="AS66">
+        <v>0</v>
+      </c>
+      <c r="AT66">
+        <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>2026-10-14 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N67">
+        <v>1.97</v>
+      </c>
+      <c r="O67">
+        <v>4.13</v>
+      </c>
+      <c r="P67">
+        <v>3.55</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>0</v>
+      </c>
+      <c r="Y67">
+        <v>0</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>0</v>
+      </c>
+      <c r="AB67">
+        <v>0</v>
+      </c>
+      <c r="AC67">
+        <v>1.9</v>
+      </c>
+      <c r="AD67">
+        <v>1.77</v>
+      </c>
+      <c r="AE67">
+        <v>0</v>
+      </c>
+      <c r="AF67">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ67">
+        <v>0</v>
+      </c>
+      <c r="AK67">
+        <v>0</v>
+      </c>
+      <c r="AL67">
+        <v>0</v>
+      </c>
+      <c r="AM67">
+        <v>-1</v>
+      </c>
+      <c r="AN67">
+        <v>-1</v>
+      </c>
+      <c r="AO67">
+        <v>-1</v>
+      </c>
+      <c r="AP67">
+        <v>-1</v>
+      </c>
+      <c r="AQ67">
+        <v>0</v>
+      </c>
+      <c r="AR67">
+        <v>0</v>
+      </c>
+      <c r="AS67">
+        <v>0</v>
+      </c>
+      <c r="AT67">
+        <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>2026-10-14 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>San Diego</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Houston Dynamo</t>
         </is>
       </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
-      <c r="H61">
-        <v>0</v>
-      </c>
-      <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>0</v>
-      </c>
-      <c r="K61">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61" t="inlineStr">
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N61">
+      <c r="N68">
         <v>1.98</v>
       </c>
-      <c r="O61">
+      <c r="O68">
         <v>3.94</v>
       </c>
-      <c r="P61">
+      <c r="P68">
         <v>3.67</v>
       </c>
-      <c r="Q61">
-        <v>0</v>
-      </c>
-      <c r="R61">
-        <v>0</v>
-      </c>
-      <c r="S61">
-        <v>0</v>
-      </c>
-      <c r="T61">
-        <v>0</v>
-      </c>
-      <c r="U61">
-        <v>0</v>
-      </c>
-      <c r="V61">
-        <v>0</v>
-      </c>
-      <c r="W61">
-        <v>0</v>
-      </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>0</v>
-      </c>
-      <c r="Z61">
-        <v>0</v>
-      </c>
-      <c r="AA61">
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>0</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+      <c r="AA68">
         <v>1.55</v>
       </c>
-      <c r="AB61">
+      <c r="AB68">
         <v>2.25</v>
       </c>
-      <c r="AC61">
-        <v>0</v>
-      </c>
-      <c r="AD61">
-        <v>0</v>
-      </c>
-      <c r="AE61">
-        <v>0</v>
-      </c>
-      <c r="AF61">
-        <v>0</v>
-      </c>
-      <c r="AG61">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>0</v>
-      </c>
-      <c r="AK61">
-        <v>0</v>
-      </c>
-      <c r="AL61">
-        <v>0</v>
-      </c>
-      <c r="AM61">
-        <v>-1</v>
-      </c>
-      <c r="AN61">
-        <v>-1</v>
-      </c>
-      <c r="AO61">
-        <v>-1</v>
-      </c>
-      <c r="AP61">
-        <v>-1</v>
-      </c>
-      <c r="AQ61">
-        <v>0</v>
-      </c>
-      <c r="AR61">
-        <v>0</v>
-      </c>
-      <c r="AS61">
-        <v>0</v>
-      </c>
-      <c r="AT61">
-        <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
+      <c r="AC68">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>0</v>
+      </c>
+      <c r="AE68">
+        <v>0</v>
+      </c>
+      <c r="AF68">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>0</v>
+      </c>
+      <c r="AK68">
+        <v>0</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>-1</v>
+      </c>
+      <c r="AN68">
+        <v>-1</v>
+      </c>
+      <c r="AO68">
+        <v>-1</v>
+      </c>
+      <c r="AP68">
+        <v>-1</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
         <is>
           <t>2026-10-14 23:30:00</t>
         </is>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="Q33">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2600,40 +2600,40 @@
         <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC14">
         <v>1.94</v>
@@ -2642,13 +2642,13 @@
         <v>1.8</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,40 +2763,40 @@
         <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC15">
         <v>2.25</v>
@@ -2805,13 +2805,13 @@
         <v>1.58</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Q31">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.43</v>
+        <v>2.95</v>
       </c>
       <c r="O25">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P25">
-        <v>5.6</v>
+        <v>2.07</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="O26">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P26">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.65</v>
+        <v>1.49</v>
       </c>
       <c r="O27">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="P27">
-        <v>2.14</v>
+        <v>5.1</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="O28">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>5.1</v>
+        <v>2.43</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P29">
-        <v>2.43</v>
+        <v>3.35</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="O30">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P30">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O31">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P31">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q42">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.65</v>
+        <v>1.49</v>
       </c>
       <c r="O26">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="P26">
-        <v>2.14</v>
+        <v>5.1</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.49</v>
+        <v>2.4</v>
       </c>
       <c r="O27">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>5.1</v>
+        <v>2.43</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P28">
-        <v>2.43</v>
+        <v>3.35</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="O29">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P29">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="O30">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P30">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.43</v>
+        <v>2.65</v>
       </c>
       <c r="O31">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>5.6</v>
+        <v>2.14</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -6023,40 +6023,40 @@
         <v>1.55</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AC35">
         <v>1.95</v>
@@ -6065,13 +6065,13 @@
         <v>1.75</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6186,40 +6186,40 @@
         <v>1.93</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC36">
         <v>1.95</v>
@@ -6228,13 +6228,13 @@
         <v>1.77</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,34 +6349,34 @@
         <v>3.07</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA37">
         <v>1.63</v>
@@ -6385,19 +6385,19 @@
         <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,34 +6512,34 @@
         <v>3.5</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA38">
         <v>1.8</v>
@@ -6548,19 +6548,19 @@
         <v>1.9</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,40 +6675,40 @@
         <v>1.94</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC39">
         <v>1.98</v>
@@ -6717,13 +6717,13 @@
         <v>1.75</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,34 +6838,34 @@
         <v>4.22</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA40">
         <v>1.71</v>
@@ -6874,19 +6874,19 @@
         <v>2</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,40 +7001,40 @@
         <v>2.66</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC41">
         <v>1.97</v>
@@ -7043,13 +7043,13 @@
         <v>1.8</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>5.99</v>
+        <v>2.29</v>
       </c>
       <c r="O35">
-        <v>4.88</v>
+        <v>3.96</v>
       </c>
       <c r="P35">
-        <v>1.55</v>
+        <v>3.07</v>
       </c>
       <c r="Q35">
-        <v>7.8</v>
+        <v>2.47</v>
       </c>
       <c r="R35">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>3.22</v>
+      </c>
+      <c r="U35">
+        <v>2.52</v>
+      </c>
+      <c r="V35">
+        <v>1.49</v>
+      </c>
+      <c r="W35">
+        <v>1.09</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
         <v>1.18</v>
       </c>
-      <c r="T35">
-        <v>4.4</v>
-      </c>
-      <c r="U35">
-        <v>1.91</v>
-      </c>
-      <c r="V35">
-        <v>1.79</v>
-      </c>
-      <c r="W35">
-        <v>1.2</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.06</v>
-      </c>
       <c r="Z35">
-        <v>7</v>
+        <v>4.15</v>
       </c>
       <c r="AA35">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB35">
-        <v>2.86</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>1.95</v>
+        <v>2.68</v>
       </c>
       <c r="AD35">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AF35">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>3.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.05</v>
+        <v>1.73</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>4.11</v>
+        <v>2.23</v>
       </c>
       <c r="O36">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="P36">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="Q36">
-        <v>3.88</v>
+        <v>3.02</v>
       </c>
       <c r="R36">
-        <v>2.62</v>
+        <v>2.11</v>
       </c>
       <c r="S36">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="U36">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="V36">
-        <v>1.79</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
+        <v>1.23</v>
+      </c>
+      <c r="Z36">
+        <v>3.64</v>
+      </c>
+      <c r="AA36">
+        <v>1.8</v>
+      </c>
+      <c r="AB36">
+        <v>1.9</v>
+      </c>
+      <c r="AC36">
+        <v>2.98</v>
+      </c>
+      <c r="AD36">
+        <v>1.33</v>
+      </c>
+      <c r="AE36">
         <v>1.08</v>
       </c>
-      <c r="Z36">
-        <v>6.5</v>
-      </c>
-      <c r="AA36">
-        <v>1.4</v>
-      </c>
-      <c r="AB36">
-        <v>3</v>
-      </c>
-      <c r="AC36">
-        <v>1.95</v>
-      </c>
-      <c r="AD36">
-        <v>1.77</v>
-      </c>
-      <c r="AE36">
-        <v>1.3</v>
-      </c>
       <c r="AF36">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AG36">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AK36">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.29</v>
+        <v>2.59</v>
       </c>
       <c r="O37">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="P37">
-        <v>3.07</v>
+        <v>2.66</v>
       </c>
       <c r="Q37">
-        <v>2.47</v>
+        <v>2.71</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>3.22</v>
+        <v>4.2</v>
       </c>
       <c r="U37">
-        <v>2.52</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="W37">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z37">
-        <v>4.15</v>
+        <v>6</v>
       </c>
       <c r="AA37">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AB37">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AC37">
-        <v>2.68</v>
+        <v>1.97</v>
       </c>
       <c r="AD37">
+        <v>1.8</v>
+      </c>
+      <c r="AE37">
+        <v>1.29</v>
+      </c>
+      <c r="AF37">
         <v>1.4</v>
       </c>
-      <c r="AE37">
-        <v>1.13</v>
-      </c>
-      <c r="AF37">
-        <v>1.6</v>
-      </c>
       <c r="AG37">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.23</v>
+        <v>5.99</v>
       </c>
       <c r="O38">
-        <v>3.58</v>
+        <v>4.88</v>
       </c>
       <c r="P38">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q38">
-        <v>3.02</v>
+        <v>7.8</v>
       </c>
       <c r="R38">
-        <v>2.11</v>
+        <v>2.67</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="T38">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="U38">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="V38">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="Z38">
-        <v>3.64</v>
+        <v>7</v>
       </c>
       <c r="AA38">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AB38">
-        <v>1.9</v>
+        <v>2.86</v>
       </c>
       <c r="AC38">
-        <v>2.98</v>
+        <v>1.95</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AE38">
-        <v>1.08</v>
+        <v>1.36</v>
       </c>
       <c r="AF38">
         <v>1.65</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.44</v>
+        <v>3.2</v>
       </c>
       <c r="AK38">
-        <v>1.43</v>
+        <v>1.05</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.06</v>
+        <v>1.9</v>
       </c>
       <c r="O39">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="P39">
-        <v>1.94</v>
+        <v>4.22</v>
       </c>
       <c r="Q39">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="R39">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="T39">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="U39">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z39">
-        <v>5.65</v>
+        <v>4.3</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AB39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC39">
-        <v>1.98</v>
+        <v>2.66</v>
       </c>
       <c r="AD39">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AE39">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AG39">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.9</v>
+        <v>4.11</v>
       </c>
       <c r="O40">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="P40">
-        <v>4.22</v>
+        <v>1.93</v>
       </c>
       <c r="Q40">
-        <v>2.15</v>
+        <v>3.88</v>
       </c>
       <c r="R40">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="S40">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="T40">
+        <v>4.1</v>
+      </c>
+      <c r="U40">
+        <v>2.07</v>
+      </c>
+      <c r="V40">
+        <v>1.79</v>
+      </c>
+      <c r="W40">
+        <v>1.17</v>
+      </c>
+      <c r="X40">
+        <v>1.02</v>
+      </c>
+      <c r="Y40">
+        <v>1.08</v>
+      </c>
+      <c r="Z40">
+        <v>6.5</v>
+      </c>
+      <c r="AA40">
+        <v>1.4</v>
+      </c>
+      <c r="AB40">
         <v>3</v>
       </c>
-      <c r="U40">
-        <v>2.4</v>
-      </c>
-      <c r="V40">
-        <v>1.5</v>
-      </c>
-      <c r="W40">
-        <v>1.12</v>
-      </c>
-      <c r="X40">
-        <v>1.03</v>
-      </c>
-      <c r="Y40">
-        <v>1.17</v>
-      </c>
-      <c r="Z40">
-        <v>4.3</v>
-      </c>
-      <c r="AA40">
-        <v>1.71</v>
-      </c>
-      <c r="AB40">
-        <v>2</v>
-      </c>
       <c r="AC40">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="AD40">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AE40">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AF40">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.98</v>
       </c>
       <c r="AK40">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.59</v>
+        <v>4.06</v>
       </c>
       <c r="O41">
         <v>3.94</v>
       </c>
       <c r="P41">
-        <v>2.66</v>
+        <v>1.94</v>
       </c>
       <c r="Q41">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="R41">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="S41">
         <v>1.2</v>
       </c>
       <c r="T41">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U41">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="V41">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="W41">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X41">
         <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z41">
-        <v>6</v>
+        <v>5.65</v>
       </c>
       <c r="AA41">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB41">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC41">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AD41">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE41">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG41">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC44">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>5.99</v>
+        <v>4.11</v>
       </c>
       <c r="O38">
-        <v>4.88</v>
+        <v>3.94</v>
       </c>
       <c r="P38">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="Q38">
-        <v>7.8</v>
+        <v>3.88</v>
       </c>
       <c r="R38">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="S38">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="U38">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="V38">
         <v>1.79</v>
       </c>
       <c r="W38">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA38">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AC38">
         <v>1.95</v>
       </c>
       <c r="AD38">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE38">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF38">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>3.2</v>
+        <v>1.98</v>
       </c>
       <c r="AK38">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="O40">
         <v>3.94</v>
       </c>
       <c r="P40">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q40">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="R40">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="S40">
         <v>1.2</v>
@@ -6850,13 +6850,13 @@
         <v>4.1</v>
       </c>
       <c r="U40">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="V40">
         <v>1.79</v>
       </c>
       <c r="W40">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X40">
         <v>1.02</v>
@@ -6865,7 +6865,7 @@
         <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>6.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA40">
         <v>1.4</v>
@@ -6874,19 +6874,19 @@
         <v>3</v>
       </c>
       <c r="AC40">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD40">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE40">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG40">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.98</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>4.06</v>
+        <v>5.99</v>
       </c>
       <c r="O41">
-        <v>3.94</v>
+        <v>4.88</v>
       </c>
       <c r="P41">
-        <v>1.94</v>
+        <v>1.55</v>
       </c>
       <c r="Q41">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="R41">
-        <v>2.48</v>
+        <v>2.67</v>
       </c>
       <c r="S41">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T41">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U41">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="V41">
         <v>1.79</v>
       </c>
       <c r="W41">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z41">
-        <v>5.65</v>
+        <v>7</v>
       </c>
       <c r="AA41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB41">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AC41">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AD41">
         <v>1.75</v>
       </c>
       <c r="AE41">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AF41">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="AK41">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AL41">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -647,31 +647,31 @@
         <v>3.7</v>
       </c>
       <c r="R2">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S2">
         <v>1.34</v>
       </c>
       <c r="T2">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="U2">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="V2">
         <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y2">
         <v>1.29</v>
       </c>
       <c r="Z2">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA2">
         <v>1.93</v>
@@ -680,13 +680,13 @@
         <v>1.83</v>
       </c>
       <c r="AC2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
         <v>1.82</v>
@@ -708,7 +708,7 @@
         <v>1.88</v>
       </c>
       <c r="AK2">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="N3">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
         <v>2.05</v>
@@ -810,16 +810,16 @@
         <v>3.75</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S3">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
         <v>2.66</v>
       </c>
       <c r="U3">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="V3">
         <v>1.33</v>
@@ -855,7 +855,7 @@
         <v>1.75</v>
       </c>
       <c r="AG3">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.11</v>
+        <v>4.06</v>
       </c>
       <c r="O38">
         <v>3.94</v>
       </c>
       <c r="P38">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q38">
-        <v>3.88</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="S38">
         <v>1.2</v>
@@ -6524,13 +6524,13 @@
         <v>4.1</v>
       </c>
       <c r="U38">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="V38">
         <v>1.79</v>
       </c>
       <c r="W38">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X38">
         <v>1.02</v>
@@ -6539,7 +6539,7 @@
         <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>6.5</v>
+        <v>5.65</v>
       </c>
       <c r="AA38">
         <v>1.4</v>
@@ -6548,19 +6548,19 @@
         <v>3</v>
       </c>
       <c r="AC38">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD38">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AE38">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF38">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG38">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.98</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.06</v>
+        <v>4.11</v>
       </c>
       <c r="O40">
         <v>3.94</v>
       </c>
       <c r="P40">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q40">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="R40">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="S40">
         <v>1.2</v>
@@ -6850,13 +6850,13 @@
         <v>4.1</v>
       </c>
       <c r="U40">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="V40">
         <v>1.79</v>
       </c>
       <c r="W40">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X40">
         <v>1.02</v>
@@ -6865,7 +6865,7 @@
         <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>5.65</v>
+        <v>6.5</v>
       </c>
       <c r="AA40">
         <v>1.4</v>
@@ -6874,35 +6874,35 @@
         <v>3</v>
       </c>
       <c r="AC40">
+        <v>1.95</v>
+      </c>
+      <c r="AD40">
+        <v>1.77</v>
+      </c>
+      <c r="AE40">
+        <v>1.3</v>
+      </c>
+      <c r="AF40">
+        <v>1.4</v>
+      </c>
+      <c r="AG40">
+        <v>2.9</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.98</v>
       </c>
-      <c r="AD40">
-        <v>1.75</v>
-      </c>
-      <c r="AE40">
-        <v>1.31</v>
-      </c>
-      <c r="AF40">
-        <v>1.36</v>
-      </c>
-      <c r="AG40">
-        <v>3</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.2</v>
-      </c>
       <c r="AK40">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AL40">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -1459,22 +1459,22 @@
         <v>1.63</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1483,16 +1483,16 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1504,10 +1504,10 @@
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
         <v>0</v>
@@ -2111,28 +2111,28 @@
         <v>3.25</v>
       </c>
       <c r="Q11">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R11">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S11">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T11">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="V11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.38</v>
@@ -2141,22 +2141,22 @@
         <v>2.62</v>
       </c>
       <c r="AA11">
-        <v>1.94</v>
+        <v>2.29</v>
       </c>
       <c r="AB11">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC11">
         <v>4.1</v>
       </c>
       <c r="AD11">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG11">
         <v>1.76</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S4">
         <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U4">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z4">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="AA4">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC4">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF4">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="O8">
-        <v>4.65</v>
+        <v>3.98</v>
       </c>
       <c r="P8">
-        <v>7.85</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2268,16 +2268,16 @@
         <v>2.2</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>2.85</v>
       </c>
       <c r="Q12">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R12">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2286,37 +2286,37 @@
         <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>3.88</v>
+        <v>4.35</v>
       </c>
       <c r="AA12">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="AB12">
-        <v>2.04</v>
+        <v>2.31</v>
       </c>
       <c r="AC12">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF12">
         <v>1.65</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AK12">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>3.8</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>2.87</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q23">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
+        <v>2.88</v>
+      </c>
+      <c r="U23">
+        <v>2.9</v>
+      </c>
+      <c r="V23">
+        <v>1.36</v>
+      </c>
+      <c r="W23">
+        <v>1.06</v>
+      </c>
+      <c r="X23">
+        <v>1.04</v>
+      </c>
+      <c r="Y23">
+        <v>1.29</v>
+      </c>
+      <c r="Z23">
         <v>3</v>
       </c>
-      <c r="U23">
-        <v>2.61</v>
-      </c>
-      <c r="V23">
-        <v>1.39</v>
-      </c>
-      <c r="W23">
-        <v>1.08</v>
-      </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
-      <c r="Y23">
-        <v>1.23</v>
-      </c>
-      <c r="Z23">
-        <v>3.42</v>
-      </c>
       <c r="AA23">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="AB23">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AC23">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="AD23">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AG23">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK23">
         <v>1.36</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O32">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="P32">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>3.81</v>
+        <v>4.6</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5854,61 +5854,61 @@
         <v>2.24</v>
       </c>
       <c r="O34">
-        <v>3.65</v>
+        <v>3.82</v>
       </c>
       <c r="P34">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.48</v>
+        <v>4.6</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P42">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.69</v>
+        <v>2.38</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="O46">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="P46">
-        <v>3.18</v>
+        <v>2.87</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X46">
         <v>0</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA46">
         <v>1.55</v>
       </c>
       <c r="AB46">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="O47">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="P47">
-        <v>4.07</v>
+        <v>3.5</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X47">
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC47">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD47">
         <v>1.62</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="O48">
-        <v>4.09</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC48">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="AD48">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="O49">
-        <v>3.86</v>
+        <v>4.6</v>
       </c>
       <c r="P49">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA49">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AB49">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="AC49">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="AD49">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O50">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="P50">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC50">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD50">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.51</v>
+        <v>2.25</v>
       </c>
       <c r="O51">
-        <v>5.05</v>
+        <v>3.92</v>
       </c>
       <c r="P51">
-        <v>5.83</v>
+        <v>2.87</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X51">
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>6.14</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC51">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AD51">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O67">
-        <v>4.13</v>
+        <v>3.94</v>
       </c>
       <c r="P67">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,16 +11269,16 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC67">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AE67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="O68">
-        <v>3.94</v>
+        <v>4.13</v>
       </c>
       <c r="P68">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,16 +11432,16 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB68">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE68">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>3.98</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>14.4</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
-        <v>6.85</v>
+        <v>4</v>
       </c>
       <c r="P14">
-        <v>1.25</v>
+        <v>1.93</v>
       </c>
       <c r="Q14">
-        <v>8.65</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
+        <v>2.45</v>
+      </c>
+      <c r="S14">
+        <v>1.17</v>
+      </c>
+      <c r="T14">
+        <v>4</v>
+      </c>
+      <c r="U14">
+        <v>2.09</v>
+      </c>
+      <c r="V14">
+        <v>1.69</v>
+      </c>
+      <c r="W14">
+        <v>1.17</v>
+      </c>
+      <c r="X14">
+        <v>1.02</v>
+      </c>
+      <c r="Y14">
+        <v>1.1</v>
+      </c>
+      <c r="Z14">
+        <v>5.35</v>
+      </c>
+      <c r="AA14">
+        <v>1.44</v>
+      </c>
+      <c r="AB14">
+        <v>2.62</v>
+      </c>
+      <c r="AC14">
+        <v>1.98</v>
+      </c>
+      <c r="AD14">
+        <v>1.81</v>
+      </c>
+      <c r="AE14">
+        <v>1.29</v>
+      </c>
+      <c r="AF14">
+        <v>1.36</v>
+      </c>
+      <c r="AG14">
         <v>2.88</v>
       </c>
-      <c r="S14">
-        <v>1.2</v>
-      </c>
-      <c r="T14">
-        <v>4.33</v>
-      </c>
-      <c r="U14">
-        <v>1.91</v>
-      </c>
-      <c r="V14">
-        <v>1.8</v>
-      </c>
-      <c r="W14">
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.22</v>
       </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.07</v>
-      </c>
-      <c r="Z14">
-        <v>7</v>
-      </c>
-      <c r="AA14">
-        <v>1.36</v>
-      </c>
-      <c r="AB14">
-        <v>3.2</v>
-      </c>
-      <c r="AC14">
-        <v>1.94</v>
-      </c>
-      <c r="AD14">
-        <v>1.8</v>
-      </c>
-      <c r="AE14">
-        <v>1.35</v>
-      </c>
-      <c r="AF14">
-        <v>1.67</v>
-      </c>
-      <c r="AG14">
-        <v>2.15</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.12</v>
-      </c>
       <c r="AK14">
-        <v>1.06</v>
+        <v>1.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.35</v>
+        <v>9.5</v>
       </c>
       <c r="O15">
-        <v>3.82</v>
+        <v>6.5</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>1.26</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="R15">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="S15">
+        <v>1.2</v>
+      </c>
+      <c r="T15">
+        <v>4.33</v>
+      </c>
+      <c r="U15">
+        <v>1.91</v>
+      </c>
+      <c r="V15">
+        <v>1.8</v>
+      </c>
+      <c r="W15">
         <v>1.22</v>
       </c>
-      <c r="T15">
-        <v>4</v>
-      </c>
-      <c r="U15">
-        <v>2.09</v>
-      </c>
-      <c r="V15">
-        <v>1.74</v>
-      </c>
-      <c r="W15">
-        <v>1.19</v>
-      </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z15">
-        <v>5.35</v>
+        <v>7.5</v>
       </c>
       <c r="AA15">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB15">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="AC15">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD15">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="AE15">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AF15">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AK15">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.4</v>
+        <v>1.74</v>
       </c>
       <c r="O32">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA32">
+        <v>1.8</v>
+      </c>
+      <c r="AB32">
         <v>2</v>
       </c>
-      <c r="AB32">
-        <v>1.8</v>
-      </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="O33">
+        <v>3.82</v>
+      </c>
+      <c r="P33">
+        <v>2.95</v>
+      </c>
+      <c r="Q33">
+        <v>2.8</v>
+      </c>
+      <c r="R33">
+        <v>2.38</v>
+      </c>
+      <c r="S33">
+        <v>1.22</v>
+      </c>
+      <c r="T33">
         <v>3.8</v>
       </c>
-      <c r="P33">
-        <v>4.6</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="O34">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="P34">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="U34">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="V34">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA34">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC34">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AE34">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,37 +6014,37 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="O35">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="Q35">
         <v>2.47</v>
       </c>
       <c r="R35">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="V35">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
         <v>1.18</v>
@@ -6053,16 +6053,16 @@
         <v>4.15</v>
       </c>
       <c r="AA35">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC35">
         <v>2.68</v>
       </c>
       <c r="AD35">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE35">
         <v>1.13</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK35">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.23</v>
+        <v>2.56</v>
       </c>
       <c r="O36">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="P36">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q36">
         <v>3.02</v>
@@ -6192,13 +6192,13 @@
         <v>2.11</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
         <v>3.05</v>
       </c>
       <c r="U36">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="V36">
         <v>1.45</v>
@@ -6207,25 +6207,25 @@
         <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
-        <v>3.64</v>
+        <v>3.81</v>
       </c>
       <c r="AA36">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AB36">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC36">
-        <v>2.98</v>
+        <v>2.83</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE36">
         <v>1.08</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="O37">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="P37">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="Q37">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="R37">
         <v>2.62</v>
@@ -6364,10 +6364,10 @@
         <v>2</v>
       </c>
       <c r="V37">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6376,7 +6376,7 @@
         <v>1.07</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AA37">
         <v>1.44</v>
@@ -6385,10 +6385,10 @@
         <v>2.75</v>
       </c>
       <c r="AC37">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AD37">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE37">
         <v>1.29</v>
@@ -6397,7 +6397,7 @@
         <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.06</v>
+        <v>3.1</v>
       </c>
       <c r="O38">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="P38">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q38">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R38">
         <v>2.48</v>
@@ -6521,13 +6521,13 @@
         <v>1.2</v>
       </c>
       <c r="T38">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U38">
         <v>2.03</v>
       </c>
       <c r="V38">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="W38">
         <v>1.18</v>
@@ -6548,13 +6548,13 @@
         <v>3</v>
       </c>
       <c r="AC38">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AD38">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE38">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AF38">
         <v>1.36</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AK38">
         <v>1.33</v>
@@ -6666,25 +6666,25 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="O39">
-        <v>3.97</v>
+        <v>4.05</v>
       </c>
       <c r="P39">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="Q39">
         <v>2.15</v>
       </c>
       <c r="R39">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S39">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U39">
         <v>2.4</v>
@@ -6693,10 +6693,10 @@
         <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.17</v>
@@ -6705,22 +6705,22 @@
         <v>4.3</v>
       </c>
       <c r="AA39">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB39">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AC39">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="AD39">
         <v>1.47</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF39">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG39">
         <v>2.15</v>
@@ -6739,7 +6739,7 @@
         <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>4.11</v>
+        <v>3.55</v>
       </c>
       <c r="O40">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="P40">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="Q40">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="R40">
         <v>2.62</v>
@@ -6847,13 +6847,13 @@
         <v>1.2</v>
       </c>
       <c r="T40">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U40">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="V40">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W40">
         <v>1.17</v>
@@ -6871,13 +6871,13 @@
         <v>1.4</v>
       </c>
       <c r="AB40">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AC40">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AD40">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AE40">
         <v>1.3</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.98</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
         <v>1.25</v>
@@ -6992,16 +6992,16 @@
         </is>
       </c>
       <c r="N41">
-        <v>5.99</v>
+        <v>8</v>
       </c>
       <c r="O41">
-        <v>4.88</v>
+        <v>5.75</v>
       </c>
       <c r="P41">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="Q41">
-        <v>7.8</v>
+        <v>7.91</v>
       </c>
       <c r="R41">
         <v>2.67</v>
@@ -7013,7 +7013,7 @@
         <v>4.4</v>
       </c>
       <c r="U41">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V41">
         <v>1.79</v>
@@ -7028,22 +7028,22 @@
         <v>1.06</v>
       </c>
       <c r="Z41">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA41">
         <v>1.36</v>
       </c>
       <c r="AB41">
-        <v>2.86</v>
+        <v>3.17</v>
       </c>
       <c r="AC41">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AD41">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AE41">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF41">
         <v>1.65</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="AK41">
         <v>1.05</v>
@@ -7158,40 +7158,40 @@
         <v>4.6</v>
       </c>
       <c r="O42">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P42">
         <v>1.65</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA42">
         <v>1.72</v>
@@ -7200,19 +7200,19 @@
         <v>2.1</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,31 +7807,31 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="O46">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="Q46">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R46">
         <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U46">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="V46">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W46">
         <v>1.13</v>
@@ -7846,22 +7846,22 @@
         <v>5</v>
       </c>
       <c r="AA46">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB46">
         <v>2.35</v>
       </c>
       <c r="AC46">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AD46">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AE46">
         <v>1.18</v>
       </c>
       <c r="AF46">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG46">
         <v>2.45</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK46">
         <v>1.7</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="O47">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="P47">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="Q47">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="R47">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="S47">
+        <v>1.18</v>
+      </c>
+      <c r="T47">
+        <v>4.6</v>
+      </c>
+      <c r="U47">
+        <v>1.83</v>
+      </c>
+      <c r="V47">
+        <v>1.79</v>
+      </c>
+      <c r="W47">
         <v>1.22</v>
       </c>
-      <c r="T47">
-        <v>4.1</v>
-      </c>
-      <c r="U47">
-        <v>2.07</v>
-      </c>
-      <c r="V47">
-        <v>1.65</v>
-      </c>
-      <c r="W47">
-        <v>1.18</v>
-      </c>
       <c r="X47">
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Z47">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AA47">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AB47">
+        <v>3.3</v>
+      </c>
+      <c r="AC47">
+        <v>1.8</v>
+      </c>
+      <c r="AD47">
+        <v>1.94</v>
+      </c>
+      <c r="AE47">
+        <v>1.4</v>
+      </c>
+      <c r="AF47">
+        <v>1.4</v>
+      </c>
+      <c r="AG47">
+        <v>2.68</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>1.16</v>
+      </c>
+      <c r="AK47">
         <v>2.5</v>
-      </c>
-      <c r="AC47">
-        <v>2.12</v>
-      </c>
-      <c r="AD47">
-        <v>1.62</v>
-      </c>
-      <c r="AE47">
-        <v>1.23</v>
-      </c>
-      <c r="AF47">
-        <v>1.44</v>
-      </c>
-      <c r="AG47">
-        <v>2.5</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.23</v>
-      </c>
-      <c r="AK47">
-        <v>1.95</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q48">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="S48">
+        <v>1.14</v>
+      </c>
+      <c r="T48">
+        <v>4.33</v>
+      </c>
+      <c r="U48">
+        <v>2.03</v>
+      </c>
+      <c r="V48">
+        <v>1.8</v>
+      </c>
+      <c r="W48">
         <v>1.22</v>
       </c>
-      <c r="T48">
-        <v>3.8</v>
-      </c>
-      <c r="U48">
-        <v>2.15</v>
-      </c>
-      <c r="V48">
-        <v>1.6</v>
-      </c>
-      <c r="W48">
-        <v>1.13</v>
-      </c>
       <c r="X48">
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z48">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="AA48">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AB48">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AC48">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="AD48">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF48">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AG48">
-        <v>2.45</v>
+        <v>2.96</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="O49">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="P49">
-        <v>5</v>
+        <v>2.87</v>
       </c>
       <c r="Q49">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="R49">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="S49">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T49">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="U49">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="V49">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="W49">
         <v>1.22</v>
@@ -8329,31 +8329,31 @@
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z49">
-        <v>8</v>
+        <v>6.14</v>
       </c>
       <c r="AA49">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB49">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AC49">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD49">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AE49">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AF49">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG49">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AK49">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O50">
         <v>4</v>
       </c>
       <c r="P50">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q50">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="S50">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="U50">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="V50">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="W50">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA50">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AB50">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="AC50">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AD50">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AE50">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF50">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG50">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK50">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="O51">
-        <v>3.92</v>
+        <v>3.85</v>
       </c>
       <c r="P51">
         <v>2.87</v>
       </c>
       <c r="Q51">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R51">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="V51">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="W51">
+        <v>1.13</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>1.15</v>
+      </c>
+      <c r="Z51">
+        <v>5</v>
+      </c>
+      <c r="AA51">
+        <v>1.55</v>
+      </c>
+      <c r="AB51">
+        <v>2.35</v>
+      </c>
+      <c r="AC51">
+        <v>2.34</v>
+      </c>
+      <c r="AD51">
+        <v>1.58</v>
+      </c>
+      <c r="AE51">
+        <v>1.18</v>
+      </c>
+      <c r="AF51">
+        <v>1.5</v>
+      </c>
+      <c r="AG51">
+        <v>2.45</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
         <v>1.22</v>
       </c>
-      <c r="X51">
-        <v>0</v>
-      </c>
-      <c r="Y51">
-        <v>1.11</v>
-      </c>
-      <c r="Z51">
-        <v>6.14</v>
-      </c>
-      <c r="AA51">
-        <v>1.33</v>
-      </c>
-      <c r="AB51">
-        <v>3.1</v>
-      </c>
-      <c r="AC51">
-        <v>1.83</v>
-      </c>
-      <c r="AD51">
-        <v>1.83</v>
-      </c>
-      <c r="AE51">
-        <v>1.31</v>
-      </c>
-      <c r="AF51">
-        <v>1.33</v>
-      </c>
-      <c r="AG51">
-        <v>3.1</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.23</v>
-      </c>
       <c r="AK51">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="O66">
-        <v>4.9</v>
+        <v>3.94</v>
       </c>
       <c r="P66">
-        <v>6.57</v>
+        <v>3.67</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,16 +11106,16 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC66">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD66">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE66">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="O67">
-        <v>3.94</v>
+        <v>4.13</v>
       </c>
       <c r="P67">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,16 +11269,16 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.97</v>
+        <v>1.48</v>
       </c>
       <c r="O68">
-        <v>4.13</v>
+        <v>4.9</v>
       </c>
       <c r="P68">
-        <v>3.55</v>
+        <v>6.57</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11438,10 +11438,10 @@
         <v>0</v>
       </c>
       <c r="AC68">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD68">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AE68">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -967,7 +967,7 @@
         <v>3.8</v>
       </c>
       <c r="P4">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -991,7 +991,7 @@
         <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
         <v>1.16</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>1.48</v>
       </c>
       <c r="O8">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="P8">
         <v>5.5</v>
@@ -1806,7 +1806,7 @@
         <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
         <v>1.22</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
         <v>1.36</v>
@@ -5528,10 +5528,10 @@
         <v>1.74</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>4.6</v>
+        <v>4.27</v>
       </c>
       <c r="Q32">
         <v>2.28</v>
@@ -5582,7 +5582,7 @@
         <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="P33">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="Q33">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="U33">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="V33">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA33">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB33">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC33">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="O34">
-        <v>3.38</v>
+        <v>3.82</v>
       </c>
       <c r="P34">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.81</v>
+        <v>2.15</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="Z34">
-        <v>3.28</v>
+        <v>5.3</v>
       </c>
       <c r="AA34">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AB34">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AC34">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD34">
+        <v>1.62</v>
+      </c>
+      <c r="AE34">
         <v>1.26</v>
       </c>
-      <c r="AE34">
-        <v>1.05</v>
-      </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="P35">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q35">
-        <v>2.47</v>
+        <v>2.68</v>
       </c>
       <c r="R35">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="S35">
+        <v>1.2</v>
+      </c>
+      <c r="T35">
+        <v>4.2</v>
+      </c>
+      <c r="U35">
+        <v>2</v>
+      </c>
+      <c r="V35">
+        <v>1.73</v>
+      </c>
+      <c r="W35">
+        <v>1.18</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.07</v>
+      </c>
+      <c r="Z35">
+        <v>5.8</v>
+      </c>
+      <c r="AA35">
+        <v>1.44</v>
+      </c>
+      <c r="AB35">
+        <v>2.75</v>
+      </c>
+      <c r="AC35">
+        <v>1.99</v>
+      </c>
+      <c r="AD35">
+        <v>1.76</v>
+      </c>
+      <c r="AE35">
         <v>1.29</v>
       </c>
-      <c r="T35">
-        <v>3.3</v>
-      </c>
-      <c r="U35">
-        <v>2.4</v>
-      </c>
-      <c r="V35">
-        <v>1.5</v>
-      </c>
-      <c r="W35">
-        <v>1.08</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.18</v>
-      </c>
-      <c r="Z35">
-        <v>4.15</v>
-      </c>
-      <c r="AA35">
-        <v>1.72</v>
-      </c>
-      <c r="AB35">
-        <v>2.1</v>
-      </c>
-      <c r="AC35">
-        <v>2.68</v>
-      </c>
-      <c r="AD35">
-        <v>1.43</v>
-      </c>
-      <c r="AE35">
-        <v>1.13</v>
-      </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AG35">
-        <v>2.3</v>
+        <v>2.89</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="O36">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="P36">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
-        <v>3.02</v>
+        <v>2.47</v>
       </c>
       <c r="R36">
-        <v>2.11</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="V36">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>3.81</v>
+        <v>4.15</v>
       </c>
       <c r="AA36">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AB36">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="AD36">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF36">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P37">
-        <v>2.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q37">
-        <v>2.68</v>
+        <v>3.65</v>
       </c>
       <c r="R37">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="S37">
         <v>1.2</v>
@@ -6361,10 +6361,10 @@
         <v>4.2</v>
       </c>
       <c r="U37">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="V37">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="W37">
         <v>1.18</v>
@@ -6373,31 +6373,31 @@
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC37">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AD37">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE37">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="AF37">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG37">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="AK37">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P38">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="Q38">
-        <v>3.65</v>
+        <v>2.15</v>
       </c>
       <c r="R38">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
+        <v>1.3</v>
+      </c>
+      <c r="T38">
+        <v>3.05</v>
+      </c>
+      <c r="U38">
+        <v>2.4</v>
+      </c>
+      <c r="V38">
+        <v>1.5</v>
+      </c>
+      <c r="W38">
+        <v>1.14</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
+        <v>1.17</v>
+      </c>
+      <c r="Z38">
+        <v>4.3</v>
+      </c>
+      <c r="AA38">
+        <v>1.69</v>
+      </c>
+      <c r="AB38">
+        <v>2.13</v>
+      </c>
+      <c r="AC38">
+        <v>2.71</v>
+      </c>
+      <c r="AD38">
+        <v>1.47</v>
+      </c>
+      <c r="AE38">
+        <v>1.15</v>
+      </c>
+      <c r="AF38">
+        <v>1.67</v>
+      </c>
+      <c r="AG38">
+        <v>2.15</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.2</v>
       </c>
-      <c r="T38">
-        <v>4.2</v>
-      </c>
-      <c r="U38">
-        <v>2.03</v>
-      </c>
-      <c r="V38">
-        <v>1.82</v>
-      </c>
-      <c r="W38">
-        <v>1.18</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.08</v>
-      </c>
-      <c r="Z38">
-        <v>5.65</v>
-      </c>
-      <c r="AA38">
-        <v>1.4</v>
-      </c>
-      <c r="AB38">
-        <v>3</v>
-      </c>
-      <c r="AC38">
-        <v>1.91</v>
-      </c>
-      <c r="AD38">
-        <v>1.77</v>
-      </c>
-      <c r="AE38">
-        <v>1.34</v>
-      </c>
-      <c r="AF38">
-        <v>1.36</v>
-      </c>
-      <c r="AG38">
-        <v>3</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.8</v>
-      </c>
       <c r="AK38">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.61</v>
+        <v>3.55</v>
       </c>
       <c r="O39">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P39">
+        <v>1.83</v>
+      </c>
+      <c r="Q39">
+        <v>3.7</v>
+      </c>
+      <c r="R39">
+        <v>2.62</v>
+      </c>
+      <c r="S39">
+        <v>1.2</v>
+      </c>
+      <c r="T39">
         <v>4.2</v>
       </c>
-      <c r="Q39">
-        <v>2.15</v>
-      </c>
-      <c r="R39">
-        <v>2.4</v>
-      </c>
-      <c r="S39">
+      <c r="U39">
+        <v>2</v>
+      </c>
+      <c r="V39">
+        <v>1.78</v>
+      </c>
+      <c r="W39">
+        <v>1.17</v>
+      </c>
+      <c r="X39">
+        <v>1.02</v>
+      </c>
+      <c r="Y39">
+        <v>1.08</v>
+      </c>
+      <c r="Z39">
+        <v>6.5</v>
+      </c>
+      <c r="AA39">
+        <v>1.4</v>
+      </c>
+      <c r="AB39">
+        <v>2.94</v>
+      </c>
+      <c r="AC39">
+        <v>2.04</v>
+      </c>
+      <c r="AD39">
+        <v>1.83</v>
+      </c>
+      <c r="AE39">
         <v>1.3</v>
       </c>
-      <c r="T39">
-        <v>3.05</v>
-      </c>
-      <c r="U39">
-        <v>2.4</v>
-      </c>
-      <c r="V39">
-        <v>1.5</v>
-      </c>
-      <c r="W39">
-        <v>1.14</v>
-      </c>
-      <c r="X39">
-        <v>1.01</v>
-      </c>
-      <c r="Y39">
+      <c r="AF39">
+        <v>1.4</v>
+      </c>
+      <c r="AG39">
+        <v>2.9</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.17</v>
       </c>
-      <c r="Z39">
-        <v>4.3</v>
-      </c>
-      <c r="AA39">
-        <v>1.69</v>
-      </c>
-      <c r="AB39">
-        <v>2.13</v>
-      </c>
-      <c r="AC39">
-        <v>2.71</v>
-      </c>
-      <c r="AD39">
-        <v>1.47</v>
-      </c>
-      <c r="AE39">
-        <v>1.15</v>
-      </c>
-      <c r="AF39">
-        <v>1.67</v>
-      </c>
-      <c r="AG39">
-        <v>2.15</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.2</v>
-      </c>
       <c r="AK39">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="O40">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="P40">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="Q40">
-        <v>3.7</v>
+        <v>7.91</v>
       </c>
       <c r="R40">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="S40">
+        <v>1.18</v>
+      </c>
+      <c r="T40">
+        <v>4.4</v>
+      </c>
+      <c r="U40">
+        <v>1.92</v>
+      </c>
+      <c r="V40">
+        <v>1.79</v>
+      </c>
+      <c r="W40">
         <v>1.2</v>
       </c>
-      <c r="T40">
-        <v>4.2</v>
-      </c>
-      <c r="U40">
-        <v>2</v>
-      </c>
-      <c r="V40">
-        <v>1.78</v>
-      </c>
-      <c r="W40">
-        <v>1.17</v>
-      </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z40">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB40">
-        <v>2.94</v>
+        <v>3.17</v>
       </c>
       <c r="AC40">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="AD40">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AE40">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AF40">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.17</v>
+        <v>3.19</v>
       </c>
       <c r="AK40">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>8</v>
+        <v>2.56</v>
       </c>
       <c r="O41">
-        <v>5.75</v>
+        <v>3.44</v>
       </c>
       <c r="P41">
+        <v>2.55</v>
+      </c>
+      <c r="Q41">
+        <v>3.02</v>
+      </c>
+      <c r="R41">
+        <v>2.11</v>
+      </c>
+      <c r="S41">
         <v>1.33</v>
       </c>
-      <c r="Q41">
-        <v>7.91</v>
-      </c>
-      <c r="R41">
-        <v>2.67</v>
-      </c>
-      <c r="S41">
-        <v>1.18</v>
-      </c>
       <c r="T41">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="U41">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="V41">
-        <v>1.79</v>
+        <v>1.45</v>
       </c>
       <c r="W41">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="Z41">
-        <v>7.5</v>
+        <v>3.81</v>
       </c>
       <c r="AA41">
-        <v>1.36</v>
+        <v>1.84</v>
       </c>
       <c r="AB41">
-        <v>3.17</v>
+        <v>1.97</v>
       </c>
       <c r="AC41">
-        <v>1.97</v>
+        <v>2.83</v>
       </c>
       <c r="AD41">
-        <v>1.89</v>
+        <v>1.37</v>
       </c>
       <c r="AE41">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="AF41">
         <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>3.19</v>
+        <v>1.44</v>
       </c>
       <c r="AK41">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>4.6</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P42">
         <v>1.65</v>
@@ -7194,10 +7194,10 @@
         <v>4.2</v>
       </c>
       <c r="AA42">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AB42">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
         <v>2.49</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="O44">
         <v>3.5</v>
       </c>
       <c r="P44">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,10 +7644,10 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="O45">
-        <v>4.27</v>
+        <v>4</v>
       </c>
       <c r="P45">
         <v>5</v>
@@ -7816,10 +7816,10 @@
         <v>3.4</v>
       </c>
       <c r="Q46">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="S46">
         <v>1.22</v>
@@ -7828,13 +7828,13 @@
         <v>3.8</v>
       </c>
       <c r="U46">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V46">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W46">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA46">
         <v>1.57</v>
@@ -7852,16 +7852,16 @@
         <v>2.35</v>
       </c>
       <c r="AC46">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AD46">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AE46">
         <v>1.18</v>
       </c>
       <c r="AF46">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG46">
         <v>2.45</v>
@@ -7880,7 +7880,7 @@
         <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>5</v>
       </c>
       <c r="Q47">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="R47">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="S47">
         <v>1.18</v>
@@ -7991,7 +7991,7 @@
         <v>4.6</v>
       </c>
       <c r="U47">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V47">
         <v>1.79</v>
@@ -8009,25 +8009,25 @@
         <v>8</v>
       </c>
       <c r="AA47">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AB47">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AC47">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD47">
         <v>1.94</v>
       </c>
       <c r="AE47">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AF47">
         <v>1.4</v>
       </c>
       <c r="AG47">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK47">
         <v>2.5</v>
@@ -8136,7 +8136,7 @@
         <v>2</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
         <v>3.1</v>
@@ -8145,22 +8145,22 @@
         <v>2.38</v>
       </c>
       <c r="R48">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="S48">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T48">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U48">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="V48">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="W48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X48">
         <v>0</v>
@@ -8169,28 +8169,28 @@
         <v>1.07</v>
       </c>
       <c r="Z48">
-        <v>7.5</v>
+        <v>6.29</v>
       </c>
       <c r="AA48">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AB48">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AC48">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AD48">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AE48">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF48">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG48">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,46 +8296,46 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O49">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="P49">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="R49">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="S49">
         <v>1.2</v>
       </c>
       <c r="T49">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U49">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V49">
         <v>1.75</v>
       </c>
       <c r="W49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z49">
-        <v>6.14</v>
+        <v>6.16</v>
       </c>
       <c r="AA49">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AB49">
         <v>3.1</v>
@@ -8344,10 +8344,10 @@
         <v>1.83</v>
       </c>
       <c r="AD49">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AE49">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AF49">
         <v>1.33</v>
@@ -8471,7 +8471,7 @@
         <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="S50">
         <v>1.22</v>
@@ -8480,10 +8480,10 @@
         <v>4.1</v>
       </c>
       <c r="U50">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="V50">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W50">
         <v>1.18</v>
@@ -8495,7 +8495,7 @@
         <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="AA50">
         <v>1.5</v>
@@ -8504,7 +8504,7 @@
         <v>2.5</v>
       </c>
       <c r="AC50">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AD50">
         <v>1.62</v>
@@ -8640,10 +8640,10 @@
         <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U51">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V51">
         <v>1.62</v>
@@ -8658,19 +8658,19 @@
         <v>1.15</v>
       </c>
       <c r="Z51">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA51">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB51">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC51">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD51">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE51">
         <v>1.18</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
         <v>1.7</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.74</v>
+        <v>2.47</v>
       </c>
       <c r="O60">
-        <v>4.28</v>
+        <v>3.75</v>
       </c>
       <c r="P60">
-        <v>4.49</v>
+        <v>2.58</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AC60">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AD60">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="O61">
-        <v>4.09</v>
+        <v>4.02</v>
       </c>
       <c r="P61">
-        <v>2.41</v>
+        <v>3.92</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X61">
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC61">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AD61">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="O62">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X62">
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC62">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AD62">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O63">
-        <v>6.46</v>
+        <v>5.75</v>
       </c>
       <c r="P63">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X63">
         <v>0</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AC63">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AD63">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="O64">
-        <v>3.77</v>
+        <v>3.73</v>
       </c>
       <c r="P64">
-        <v>3.44</v>
+        <v>3.26</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
         <v>0</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="AA64">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB64">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="O65">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>3.98</v>
+        <v>3.48</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X65">
         <v>0</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AC65">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AD65">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11070,61 +11070,61 @@
         <v>1.98</v>
       </c>
       <c r="O66">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X66">
         <v>0</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="AA66">
+        <v>1.57</v>
+      </c>
+      <c r="AB66">
+        <v>2.35</v>
+      </c>
+      <c r="AC66">
+        <v>2.47</v>
+      </c>
+      <c r="AD66">
         <v>1.55</v>
       </c>
-      <c r="AB66">
-        <v>2.25</v>
-      </c>
-      <c r="AC66">
-        <v>0</v>
-      </c>
-      <c r="AD66">
-        <v>0</v>
-      </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="O67">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="P67">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X67">
         <v>0</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC67">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD67">
         <v>1.77</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="O68">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P68">
-        <v>6.57</v>
+        <v>6.78</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X68">
         <v>0</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC68">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AD68">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU68"/>
+  <dimension ref="A1:AU69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,7 +979,7 @@
         <v>1.3</v>
       </c>
       <c r="T4">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U4">
         <v>2.4</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="O9">
         <v>4.2</v>
@@ -4224,7 +4224,7 @@
         <v>1.95</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
         <v>3.25</v>
@@ -4236,7 +4236,7 @@
         <v>2.2</v>
       </c>
       <c r="S24">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
         <v>2.89</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="O32">
+        <v>3.82</v>
+      </c>
+      <c r="P32">
+        <v>2.76</v>
+      </c>
+      <c r="Q32">
+        <v>2.8</v>
+      </c>
+      <c r="R32">
+        <v>2.38</v>
+      </c>
+      <c r="S32">
+        <v>1.25</v>
+      </c>
+      <c r="T32">
         <v>3.8</v>
       </c>
-      <c r="P32">
-        <v>4.27</v>
-      </c>
-      <c r="Q32">
-        <v>2.28</v>
-      </c>
-      <c r="R32">
-        <v>2.23</v>
-      </c>
-      <c r="S32">
-        <v>1.35</v>
-      </c>
-      <c r="T32">
-        <v>2.87</v>
-      </c>
       <c r="U32">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="V32">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="Z32">
-        <v>3.78</v>
+        <v>5.3</v>
       </c>
       <c r="AA32">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AC32">
-        <v>2.83</v>
+        <v>2.12</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,58 +5688,58 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.4</v>
+        <v>1.74</v>
       </c>
       <c r="O33">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>2.76</v>
+        <v>4.27</v>
       </c>
       <c r="Q33">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
-        <v>2.82</v>
+        <v>3.22</v>
       </c>
       <c r="U33">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
+        <v>1.08</v>
+      </c>
+      <c r="X33">
         <v>1.03</v>
       </c>
-      <c r="X33">
-        <v>1.01</v>
-      </c>
       <c r="Y33">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z33">
-        <v>3.28</v>
+        <v>3.78</v>
       </c>
       <c r="AA33">
+        <v>1.8</v>
+      </c>
+      <c r="AB33">
         <v>2</v>
       </c>
-      <c r="AB33">
-        <v>1.83</v>
-      </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AD33">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
         <v>1.7</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="O34">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="P34">
         <v>2.76</v>
       </c>
       <c r="Q34">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="U34">
-        <v>2.15</v>
+        <v>2.81</v>
       </c>
       <c r="V34">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>5.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA34">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AB34">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC34">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AE34">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="AF34">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7481,43 +7481,43 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="O44">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA44">
         <v>1.8</v>
@@ -7526,19 +7526,19 @@
         <v>2</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.46</v>
+        <v>2.96</v>
       </c>
       <c r="O45">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P45">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-10-14 20:30:00</t>
+          <t>2026-10-14 20:00:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.95</v>
+        <v>1.46</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="Q46">
-        <v>2.44</v>
+        <v>1.97</v>
       </c>
       <c r="R46">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V46">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA46">
         <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC46">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AD46">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AE46">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF46">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.44</v>
+        <v>2.28</v>
       </c>
       <c r="O47">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="P47">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="Q47">
-        <v>1.86</v>
+        <v>2.6</v>
       </c>
       <c r="R47">
-        <v>2.98</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
+        <v>1.25</v>
+      </c>
+      <c r="T47">
+        <v>3.75</v>
+      </c>
+      <c r="U47">
+        <v>2.2</v>
+      </c>
+      <c r="V47">
+        <v>1.62</v>
+      </c>
+      <c r="W47">
+        <v>1.13</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>1.15</v>
+      </c>
+      <c r="Z47">
+        <v>5.1</v>
+      </c>
+      <c r="AA47">
+        <v>1.57</v>
+      </c>
+      <c r="AB47">
+        <v>2.45</v>
+      </c>
+      <c r="AC47">
+        <v>2.36</v>
+      </c>
+      <c r="AD47">
+        <v>1.6</v>
+      </c>
+      <c r="AE47">
         <v>1.18</v>
       </c>
-      <c r="T47">
-        <v>4.6</v>
-      </c>
-      <c r="U47">
-        <v>1.85</v>
-      </c>
-      <c r="V47">
-        <v>1.79</v>
-      </c>
-      <c r="W47">
-        <v>1.22</v>
-      </c>
-      <c r="X47">
-        <v>0</v>
-      </c>
-      <c r="Y47">
-        <v>1.06</v>
-      </c>
-      <c r="Z47">
-        <v>8</v>
-      </c>
-      <c r="AA47">
-        <v>1.32</v>
-      </c>
-      <c r="AB47">
-        <v>3.4</v>
-      </c>
-      <c r="AC47">
-        <v>1.81</v>
-      </c>
-      <c r="AD47">
-        <v>1.94</v>
-      </c>
-      <c r="AE47">
-        <v>1.43</v>
-      </c>
       <c r="AF47">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG47">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O48">
+        <v>3.5</v>
+      </c>
+      <c r="P48">
+        <v>3.4</v>
+      </c>
+      <c r="Q48">
+        <v>2.44</v>
+      </c>
+      <c r="R48">
+        <v>2.56</v>
+      </c>
+      <c r="S48">
+        <v>1.22</v>
+      </c>
+      <c r="T48">
         <v>3.8</v>
       </c>
-      <c r="P48">
-        <v>3.1</v>
-      </c>
-      <c r="Q48">
-        <v>2.38</v>
-      </c>
-      <c r="R48">
-        <v>2.67</v>
-      </c>
-      <c r="S48">
-        <v>1.2</v>
-      </c>
-      <c r="T48">
-        <v>4.2</v>
-      </c>
       <c r="U48">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="V48">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="W48">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X48">
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z48">
-        <v>6.29</v>
+        <v>5.2</v>
       </c>
       <c r="AA48">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="AB48">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="AC48">
-        <v>2.02</v>
+        <v>2.33</v>
       </c>
       <c r="AD48">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AE48">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AF48">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG48">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,80 +8296,80 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="O49">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="P49">
+        <v>5.25</v>
+      </c>
+      <c r="Q49">
+        <v>1.86</v>
+      </c>
+      <c r="R49">
+        <v>2.98</v>
+      </c>
+      <c r="S49">
+        <v>1.18</v>
+      </c>
+      <c r="T49">
+        <v>4.6</v>
+      </c>
+      <c r="U49">
+        <v>1.85</v>
+      </c>
+      <c r="V49">
+        <v>1.79</v>
+      </c>
+      <c r="W49">
+        <v>1.22</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>1.06</v>
+      </c>
+      <c r="Z49">
+        <v>8</v>
+      </c>
+      <c r="AA49">
+        <v>1.32</v>
+      </c>
+      <c r="AB49">
+        <v>3.4</v>
+      </c>
+      <c r="AC49">
+        <v>1.81</v>
+      </c>
+      <c r="AD49">
+        <v>1.94</v>
+      </c>
+      <c r="AE49">
+        <v>1.43</v>
+      </c>
+      <c r="AF49">
+        <v>1.4</v>
+      </c>
+      <c r="AG49">
+        <v>2.7</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49">
+        <v>1.18</v>
+      </c>
+      <c r="AK49">
         <v>2.5</v>
-      </c>
-      <c r="Q49">
-        <v>2.66</v>
-      </c>
-      <c r="R49">
-        <v>2.64</v>
-      </c>
-      <c r="S49">
-        <v>1.2</v>
-      </c>
-      <c r="T49">
-        <v>4.2</v>
-      </c>
-      <c r="U49">
-        <v>2</v>
-      </c>
-      <c r="V49">
-        <v>1.75</v>
-      </c>
-      <c r="W49">
-        <v>1.2</v>
-      </c>
-      <c r="X49">
-        <v>0</v>
-      </c>
-      <c r="Y49">
-        <v>1.12</v>
-      </c>
-      <c r="Z49">
-        <v>6.16</v>
-      </c>
-      <c r="AA49">
-        <v>1.43</v>
-      </c>
-      <c r="AB49">
-        <v>3.1</v>
-      </c>
-      <c r="AC49">
-        <v>1.83</v>
-      </c>
-      <c r="AD49">
-        <v>1.81</v>
-      </c>
-      <c r="AE49">
-        <v>1.34</v>
-      </c>
-      <c r="AF49">
-        <v>1.33</v>
-      </c>
-      <c r="AG49">
-        <v>3.1</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49">
-        <v>1.23</v>
-      </c>
-      <c r="AK49">
-        <v>1.57</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,80 +8459,80 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O50">
         <v>4</v>
       </c>
       <c r="P50">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="S50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U50">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V50">
+        <v>1.76</v>
+      </c>
+      <c r="W50">
+        <v>1.2</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>1.07</v>
+      </c>
+      <c r="Z50">
+        <v>6.29</v>
+      </c>
+      <c r="AA50">
+        <v>1.41</v>
+      </c>
+      <c r="AB50">
+        <v>2.88</v>
+      </c>
+      <c r="AC50">
+        <v>2.02</v>
+      </c>
+      <c r="AD50">
+        <v>1.83</v>
+      </c>
+      <c r="AE50">
+        <v>1.34</v>
+      </c>
+      <c r="AF50">
+        <v>1.36</v>
+      </c>
+      <c r="AG50">
+        <v>2.9</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.25</v>
+      </c>
+      <c r="AK50">
         <v>1.67</v>
-      </c>
-      <c r="W50">
-        <v>1.18</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>1.13</v>
-      </c>
-      <c r="Z50">
-        <v>5.44</v>
-      </c>
-      <c r="AA50">
-        <v>1.5</v>
-      </c>
-      <c r="AB50">
-        <v>2.5</v>
-      </c>
-      <c r="AC50">
-        <v>2.21</v>
-      </c>
-      <c r="AD50">
-        <v>1.62</v>
-      </c>
-      <c r="AE50">
-        <v>1.23</v>
-      </c>
-      <c r="AF50">
-        <v>1.44</v>
-      </c>
-      <c r="AG50">
-        <v>2.5</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.23</v>
-      </c>
-      <c r="AK50">
-        <v>1.95</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O51">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="P51">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="Q51">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R51">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="U51">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="V51">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X51">
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z51">
-        <v>5.1</v>
+        <v>6.16</v>
       </c>
       <c r="AA51">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AB51">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="AC51">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="AD51">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AE51">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="AF51">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AG51">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-10-14 21:00:00</t>
+          <t>2026-10-14 20:30:00</t>
         </is>
       </c>
     </row>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G53">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G57">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N59">
@@ -10042,27 +10042,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X60">
         <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE60">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF60">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK60">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-10-14 21:30:00</t>
+          <t>2026-10-14 21:00:00</t>
         </is>
       </c>
     </row>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,80 +10252,80 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.75</v>
+        <v>2.47</v>
       </c>
       <c r="O61">
-        <v>4.02</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>3.92</v>
+        <v>2.58</v>
       </c>
       <c r="Q61">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="R61">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
+        <v>1.18</v>
+      </c>
+      <c r="T61">
+        <v>4.6</v>
+      </c>
+      <c r="U61">
+        <v>2</v>
+      </c>
+      <c r="V61">
+        <v>1.73</v>
+      </c>
+      <c r="W61">
+        <v>1.2</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>1.07</v>
+      </c>
+      <c r="Z61">
+        <v>5.88</v>
+      </c>
+      <c r="AA61">
+        <v>1.4</v>
+      </c>
+      <c r="AB61">
+        <v>2.72</v>
+      </c>
+      <c r="AC61">
+        <v>2.08</v>
+      </c>
+      <c r="AD61">
+        <v>1.76</v>
+      </c>
+      <c r="AE61">
+        <v>1.33</v>
+      </c>
+      <c r="AF61">
+        <v>1.3</v>
+      </c>
+      <c r="AG61">
+        <v>3.2</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
         <v>1.25</v>
       </c>
-      <c r="T61">
-        <v>3.9</v>
-      </c>
-      <c r="U61">
-        <v>2.27</v>
-      </c>
-      <c r="V61">
-        <v>1.61</v>
-      </c>
-      <c r="W61">
-        <v>1.15</v>
-      </c>
-      <c r="X61">
-        <v>0</v>
-      </c>
-      <c r="Y61">
-        <v>1.17</v>
-      </c>
-      <c r="Z61">
-        <v>5.09</v>
-      </c>
-      <c r="AA61">
-        <v>1.55</v>
-      </c>
-      <c r="AB61">
-        <v>2.3</v>
-      </c>
-      <c r="AC61">
-        <v>2.35</v>
-      </c>
-      <c r="AD61">
-        <v>1.6</v>
-      </c>
-      <c r="AE61">
-        <v>1.24</v>
-      </c>
-      <c r="AF61">
-        <v>1.53</v>
-      </c>
-      <c r="AG61">
-        <v>2.38</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.22</v>
-      </c>
       <c r="AK61">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>4.02</v>
       </c>
       <c r="P62">
+        <v>3.92</v>
+      </c>
+      <c r="Q62">
+        <v>2.25</v>
+      </c>
+      <c r="R62">
+        <v>2.4</v>
+      </c>
+      <c r="S62">
+        <v>1.25</v>
+      </c>
+      <c r="T62">
+        <v>3.9</v>
+      </c>
+      <c r="U62">
+        <v>2.27</v>
+      </c>
+      <c r="V62">
+        <v>1.61</v>
+      </c>
+      <c r="W62">
+        <v>1.15</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>1.17</v>
+      </c>
+      <c r="Z62">
+        <v>5.09</v>
+      </c>
+      <c r="AA62">
+        <v>1.55</v>
+      </c>
+      <c r="AB62">
         <v>2.3</v>
       </c>
-      <c r="Q62">
-        <v>3</v>
-      </c>
-      <c r="R62">
-        <v>2.45</v>
-      </c>
-      <c r="S62">
-        <v>1.22</v>
-      </c>
-      <c r="T62">
-        <v>3.8</v>
-      </c>
-      <c r="U62">
-        <v>2.15</v>
-      </c>
-      <c r="V62">
-        <v>1.62</v>
-      </c>
-      <c r="W62">
-        <v>1.17</v>
-      </c>
-      <c r="X62">
-        <v>0</v>
-      </c>
-      <c r="Y62">
-        <v>1.13</v>
-      </c>
-      <c r="Z62">
-        <v>5.5</v>
-      </c>
-      <c r="AA62">
-        <v>1.5</v>
-      </c>
-      <c r="AB62">
-        <v>2.55</v>
-      </c>
       <c r="AC62">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AD62">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE62">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AF62">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG62">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
+        <v>2.6</v>
+      </c>
+      <c r="O63">
+        <v>3.6</v>
+      </c>
+      <c r="P63">
+        <v>2.3</v>
+      </c>
+      <c r="Q63">
+        <v>3</v>
+      </c>
+      <c r="R63">
+        <v>2.45</v>
+      </c>
+      <c r="S63">
+        <v>1.2</v>
+      </c>
+      <c r="T63">
+        <v>4</v>
+      </c>
+      <c r="U63">
+        <v>2.15</v>
+      </c>
+      <c r="V63">
+        <v>1.62</v>
+      </c>
+      <c r="W63">
+        <v>1.17</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>1.13</v>
+      </c>
+      <c r="Z63">
+        <v>5.5</v>
+      </c>
+      <c r="AA63">
+        <v>1.47</v>
+      </c>
+      <c r="AB63">
+        <v>2.5</v>
+      </c>
+      <c r="AC63">
+        <v>2.12</v>
+      </c>
+      <c r="AD63">
+        <v>1.62</v>
+      </c>
+      <c r="AE63">
+        <v>1.22</v>
+      </c>
+      <c r="AF63">
+        <v>1.44</v>
+      </c>
+      <c r="AG63">
+        <v>2.62</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.25</v>
       </c>
-      <c r="O63">
-        <v>5.75</v>
-      </c>
-      <c r="P63">
-        <v>7.5</v>
-      </c>
-      <c r="Q63">
-        <v>1.65</v>
-      </c>
-      <c r="R63">
-        <v>2.8</v>
-      </c>
-      <c r="S63">
-        <v>1.18</v>
-      </c>
-      <c r="T63">
-        <v>4.4</v>
-      </c>
-      <c r="U63">
-        <v>1.85</v>
-      </c>
-      <c r="V63">
-        <v>1.85</v>
-      </c>
-      <c r="W63">
-        <v>1.22</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>1.07</v>
-      </c>
-      <c r="Z63">
-        <v>7.5</v>
-      </c>
-      <c r="AA63">
-        <v>1.33</v>
-      </c>
-      <c r="AB63">
-        <v>3.32</v>
-      </c>
-      <c r="AC63">
-        <v>1.87</v>
-      </c>
-      <c r="AD63">
-        <v>1.97</v>
-      </c>
-      <c r="AE63">
-        <v>1.39</v>
-      </c>
-      <c r="AF63">
-        <v>1.6</v>
-      </c>
-      <c r="AG63">
-        <v>2.2</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.12</v>
-      </c>
       <c r="AK63">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.19</v>
+        <v>1.25</v>
       </c>
       <c r="O64">
-        <v>3.73</v>
+        <v>5.75</v>
       </c>
       <c r="P64">
-        <v>3.26</v>
+        <v>7.5</v>
       </c>
       <c r="Q64">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="R64">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="S64">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T64">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="U64">
-        <v>2.34</v>
+        <v>1.85</v>
       </c>
       <c r="V64">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="W64">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X64">
         <v>0</v>
       </c>
       <c r="Y64">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="Z64">
-        <v>4.84</v>
+        <v>7.5</v>
       </c>
       <c r="AA64">
+        <v>1.33</v>
+      </c>
+      <c r="AB64">
+        <v>3.32</v>
+      </c>
+      <c r="AC64">
+        <v>1.87</v>
+      </c>
+      <c r="AD64">
+        <v>1.97</v>
+      </c>
+      <c r="AE64">
+        <v>1.39</v>
+      </c>
+      <c r="AF64">
         <v>1.6</v>
       </c>
-      <c r="AB64">
-        <v>2.35</v>
-      </c>
-      <c r="AC64">
-        <v>2.46</v>
-      </c>
-      <c r="AD64">
-        <v>1.56</v>
-      </c>
-      <c r="AE64">
-        <v>1.22</v>
-      </c>
-      <c r="AF64">
-        <v>1.53</v>
-      </c>
       <c r="AG64">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AK64">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-10-14 22:30:00</t>
+          <t>2026-10-14 21:30:00</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.9</v>
+        <v>2.19</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="P65">
-        <v>3.48</v>
+        <v>3.26</v>
       </c>
       <c r="Q65">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="R65">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="S65">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U65">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="V65">
+        <v>1.57</v>
+      </c>
+      <c r="W65">
+        <v>1.14</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>1.19</v>
+      </c>
+      <c r="Z65">
+        <v>4.75</v>
+      </c>
+      <c r="AA65">
+        <v>1.62</v>
+      </c>
+      <c r="AB65">
+        <v>2.31</v>
+      </c>
+      <c r="AC65">
+        <v>2.5</v>
+      </c>
+      <c r="AD65">
+        <v>1.54</v>
+      </c>
+      <c r="AE65">
+        <v>1.21</v>
+      </c>
+      <c r="AF65">
+        <v>1.5</v>
+      </c>
+      <c r="AG65">
+        <v>2.4</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>1.29</v>
+      </c>
+      <c r="AK65">
         <v>1.7</v>
-      </c>
-      <c r="W65">
-        <v>1.18</v>
-      </c>
-      <c r="X65">
-        <v>0</v>
-      </c>
-      <c r="Y65">
-        <v>1.14</v>
-      </c>
-      <c r="Z65">
-        <v>5.63</v>
-      </c>
-      <c r="AA65">
-        <v>1.48</v>
-      </c>
-      <c r="AB65">
-        <v>2.64</v>
-      </c>
-      <c r="AC65">
-        <v>2.19</v>
-      </c>
-      <c r="AD65">
-        <v>1.69</v>
-      </c>
-      <c r="AE65">
-        <v>1.28</v>
-      </c>
-      <c r="AF65">
-        <v>1.44</v>
-      </c>
-      <c r="AG65">
-        <v>2.64</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.3</v>
-      </c>
-      <c r="AK65">
-        <v>1.85</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P66">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="Q66">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="R66">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T66">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U66">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="V66">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="W66">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X66">
         <v>0</v>
       </c>
       <c r="Y66">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z66">
-        <v>4.82</v>
+        <v>5.63</v>
       </c>
       <c r="AA66">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AB66">
-        <v>2.35</v>
+        <v>2.64</v>
       </c>
       <c r="AC66">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
       <c r="AD66">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AE66">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AF66">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AG66">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK66">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-10-14 23:30:00</t>
+          <t>2026-10-14 22:30:00</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="O67">
-        <v>4.08</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="Q67">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="R67">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="S67">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T67">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="U67">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="V67">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="W67">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X67">
         <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z67">
-        <v>7</v>
+        <v>4.82</v>
       </c>
       <c r="AA67">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB67">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="AC67">
-        <v>1.95</v>
+        <v>2.47</v>
       </c>
       <c r="AD67">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AE67">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AF67">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AG67">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,141 +11361,304 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N68">
+        <v>1.8</v>
+      </c>
+      <c r="O68">
+        <v>4.08</v>
+      </c>
+      <c r="P68">
+        <v>3.68</v>
+      </c>
+      <c r="Q68">
+        <v>2.3</v>
+      </c>
+      <c r="R68">
+        <v>2.5</v>
+      </c>
+      <c r="S68">
+        <v>1.17</v>
+      </c>
+      <c r="T68">
+        <v>4.5</v>
+      </c>
+      <c r="U68">
+        <v>2</v>
+      </c>
+      <c r="V68">
+        <v>1.73</v>
+      </c>
+      <c r="W68">
+        <v>1.2</v>
+      </c>
+      <c r="X68">
+        <v>0</v>
+      </c>
+      <c r="Y68">
+        <v>1.08</v>
+      </c>
+      <c r="Z68">
+        <v>7</v>
+      </c>
+      <c r="AA68">
+        <v>1.4</v>
+      </c>
+      <c r="AB68">
+        <v>2.87</v>
+      </c>
+      <c r="AC68">
+        <v>1.95</v>
+      </c>
+      <c r="AD68">
+        <v>1.77</v>
+      </c>
+      <c r="AE68">
+        <v>1.33</v>
+      </c>
+      <c r="AF68">
+        <v>1.38</v>
+      </c>
+      <c r="AG68">
+        <v>2.8</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>1.25</v>
+      </c>
+      <c r="AK68">
+        <v>1.83</v>
+      </c>
+      <c r="AL68">
+        <v>0</v>
+      </c>
+      <c r="AM68">
+        <v>-1</v>
+      </c>
+      <c r="AN68">
+        <v>-1</v>
+      </c>
+      <c r="AO68">
+        <v>-1</v>
+      </c>
+      <c r="AP68">
+        <v>-1</v>
+      </c>
+      <c r="AQ68">
+        <v>0</v>
+      </c>
+      <c r="AR68">
+        <v>0</v>
+      </c>
+      <c r="AS68">
+        <v>0</v>
+      </c>
+      <c r="AT68">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>2026-10-14 23:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr">
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N68">
-        <v>1.42</v>
-      </c>
-      <c r="O68">
-        <v>4.8</v>
-      </c>
-      <c r="P68">
-        <v>6.78</v>
-      </c>
-      <c r="Q68">
-        <v>1.89</v>
-      </c>
-      <c r="R68">
-        <v>2.66</v>
-      </c>
-      <c r="S68">
+      <c r="N69">
+        <v>1.4</v>
+      </c>
+      <c r="O69">
+        <v>4.33</v>
+      </c>
+      <c r="P69">
+        <v>6</v>
+      </c>
+      <c r="Q69">
+        <v>1.88</v>
+      </c>
+      <c r="R69">
+        <v>2.69</v>
+      </c>
+      <c r="S69">
         <v>1.25</v>
       </c>
-      <c r="T68">
-        <v>3.5</v>
-      </c>
-      <c r="U68">
-        <v>2.35</v>
-      </c>
-      <c r="V68">
+      <c r="T69">
+        <v>3.48</v>
+      </c>
+      <c r="U69">
+        <v>2.32</v>
+      </c>
+      <c r="V69">
+        <v>1.59</v>
+      </c>
+      <c r="W69">
+        <v>1.12</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>1.18</v>
+      </c>
+      <c r="Z69">
+        <v>4.92</v>
+      </c>
+      <c r="AA69">
         <v>1.57</v>
       </c>
-      <c r="W68">
-        <v>1.14</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
-      </c>
-      <c r="Y68">
-        <v>1.18</v>
-      </c>
-      <c r="Z68">
-        <v>4.78</v>
-      </c>
-      <c r="AA68">
-        <v>1.59</v>
-      </c>
-      <c r="AB68">
-        <v>2.4</v>
-      </c>
-      <c r="AC68">
-        <v>2.47</v>
-      </c>
-      <c r="AD68">
-        <v>1.52</v>
-      </c>
-      <c r="AE68">
-        <v>1.21</v>
-      </c>
-      <c r="AF68">
+      <c r="AB69">
+        <v>2.43</v>
+      </c>
+      <c r="AC69">
+        <v>2.38</v>
+      </c>
+      <c r="AD69">
+        <v>1.54</v>
+      </c>
+      <c r="AE69">
+        <v>1.17</v>
+      </c>
+      <c r="AF69">
         <v>1.7</v>
       </c>
-      <c r="AG68">
-        <v>2</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
+      <c r="AG69">
+        <v>2.05</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
         <v>1.11</v>
       </c>
-      <c r="AK68">
+      <c r="AK69">
         <v>2.7</v>
       </c>
-      <c r="AL68">
-        <v>0</v>
-      </c>
-      <c r="AM68">
-        <v>-1</v>
-      </c>
-      <c r="AN68">
-        <v>-1</v>
-      </c>
-      <c r="AO68">
-        <v>-1</v>
-      </c>
-      <c r="AP68">
-        <v>-1</v>
-      </c>
-      <c r="AQ68">
-        <v>0</v>
-      </c>
-      <c r="AR68">
-        <v>0</v>
-      </c>
-      <c r="AS68">
-        <v>0</v>
-      </c>
-      <c r="AT68">
-        <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
+      <c r="AL69">
+        <v>0</v>
+      </c>
+      <c r="AM69">
+        <v>-1</v>
+      </c>
+      <c r="AN69">
+        <v>-1</v>
+      </c>
+      <c r="AO69">
+        <v>-1</v>
+      </c>
+      <c r="AP69">
+        <v>-1</v>
+      </c>
+      <c r="AQ69">
+        <v>0</v>
+      </c>
+      <c r="AR69">
+        <v>0</v>
+      </c>
+      <c r="AS69">
+        <v>0</v>
+      </c>
+      <c r="AT69">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
         <is>
           <t>2026-10-14 23:30:00</t>
         </is>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -970,7 +970,7 @@
         <v>4.8</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R4">
         <v>2.3</v>
@@ -982,43 +982,43 @@
         <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="V4">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
         <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>4.05</v>
+        <v>4.02</v>
       </c>
       <c r="AA4">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB4">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AC4">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="AD4">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE4">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF4">
         <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1779,61 +1779,61 @@
         <v>1.4</v>
       </c>
       <c r="O9">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P9">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q9">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="U9">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="V9">
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="AA9">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB9">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC9">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AD9">
         <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG9">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AK9">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>2.2</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
         <v>2.85</v>
@@ -2304,19 +2304,19 @@
         <v>4.35</v>
       </c>
       <c r="AA12">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AB12">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="AC12">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
         <v>1.65</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK12">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="O20">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q20">
         <v>2.26</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="O21">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="P21">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>2.1</v>
       </c>
       <c r="O22">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P22">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Q22">
         <v>2.5</v>
@@ -3925,7 +3925,7 @@
         <v>1.2</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
         <v>1.08</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.8</v>
+        <v>1.95</v>
       </c>
       <c r="O23">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>2.25</v>
+        <v>3.25</v>
       </c>
       <c r="Q23">
-        <v>3.58</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
+        <v>1.3</v>
+      </c>
+      <c r="T23">
+        <v>2.89</v>
+      </c>
+      <c r="U23">
+        <v>2.43</v>
+      </c>
+      <c r="V23">
+        <v>1.47</v>
+      </c>
+      <c r="W23">
+        <v>1.07</v>
+      </c>
+      <c r="X23">
+        <v>1.01</v>
+      </c>
+      <c r="Y23">
+        <v>1.22</v>
+      </c>
+      <c r="Z23">
+        <v>3.9</v>
+      </c>
+      <c r="AA23">
+        <v>1.71</v>
+      </c>
+      <c r="AB23">
+        <v>1.97</v>
+      </c>
+      <c r="AC23">
+        <v>2.88</v>
+      </c>
+      <c r="AD23">
         <v>1.36</v>
       </c>
-      <c r="T23">
-        <v>2.88</v>
-      </c>
-      <c r="U23">
-        <v>2.9</v>
-      </c>
-      <c r="V23">
-        <v>1.36</v>
-      </c>
-      <c r="W23">
-        <v>1.06</v>
-      </c>
-      <c r="X23">
-        <v>1.04</v>
-      </c>
-      <c r="Y23">
-        <v>1.29</v>
-      </c>
-      <c r="Z23">
-        <v>3</v>
-      </c>
-      <c r="AA23">
-        <v>2.01</v>
-      </c>
-      <c r="AB23">
-        <v>1.69</v>
-      </c>
-      <c r="AC23">
-        <v>3.8</v>
-      </c>
-      <c r="AD23">
-        <v>1.22</v>
-      </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,80 +4221,80 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P24">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="Q24">
-        <v>2.5</v>
+        <v>3.58</v>
       </c>
       <c r="R24">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T24">
-        <v>2.89</v>
+        <v>2.59</v>
       </c>
       <c r="U24">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="V24">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W24">
         <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
+        <v>1.29</v>
+      </c>
+      <c r="Z24">
+        <v>3</v>
+      </c>
+      <c r="AA24">
+        <v>2.01</v>
+      </c>
+      <c r="AB24">
+        <v>1.69</v>
+      </c>
+      <c r="AC24">
+        <v>3.8</v>
+      </c>
+      <c r="AD24">
         <v>1.22</v>
       </c>
-      <c r="Z24">
-        <v>3.9</v>
-      </c>
-      <c r="AA24">
-        <v>1.71</v>
-      </c>
-      <c r="AB24">
-        <v>1.97</v>
-      </c>
-      <c r="AC24">
-        <v>2.88</v>
-      </c>
-      <c r="AD24">
+      <c r="AE24">
+        <v>1.03</v>
+      </c>
+      <c r="AF24">
+        <v>1.79</v>
+      </c>
+      <c r="AG24">
+        <v>1.95</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>1.33</v>
+      </c>
+      <c r="AK24">
         <v>1.36</v>
-      </c>
-      <c r="AE24">
-        <v>1.11</v>
-      </c>
-      <c r="AF24">
-        <v>1.62</v>
-      </c>
-      <c r="AG24">
-        <v>2.15</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.25</v>
-      </c>
-      <c r="AK24">
-        <v>1.73</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5525,16 +5525,16 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="O32">
         <v>3.82</v>
       </c>
       <c r="P32">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="Q32">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R32">
         <v>2.38</v>
@@ -5549,19 +5549,19 @@
         <v>2.15</v>
       </c>
       <c r="V32">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W32">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
         <v>1.09</v>
       </c>
       <c r="Z32">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA32">
         <v>1.5</v>
@@ -5570,13 +5570,13 @@
         <v>2.62</v>
       </c>
       <c r="AC32">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AD32">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE32">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF32">
         <v>1.44</v>
@@ -5598,7 +5598,7 @@
         <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="P33">
-        <v>4.27</v>
+        <v>4.05</v>
       </c>
       <c r="Q33">
         <v>2.28</v>
@@ -5703,19 +5703,19 @@
         <v>2.23</v>
       </c>
       <c r="S33">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U33">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="V33">
         <v>1.47</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
         <v>1.03</v>
@@ -5745,7 +5745,7 @@
         <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="O34">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>2.76</v>
+        <v>2.97</v>
       </c>
       <c r="Q34">
         <v>3</v>
@@ -5866,34 +5866,34 @@
         <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
         <v>2.82</v>
       </c>
       <c r="U34">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
+        <v>1.04</v>
+      </c>
+      <c r="X34">
         <v>1.03</v>
       </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z34">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA34">
         <v>2</v>
       </c>
       <c r="AB34">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC34">
         <v>3.2</v>
@@ -5902,13 +5902,13 @@
         <v>1.26</v>
       </c>
       <c r="AE34">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK34">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>4.6</v>
       </c>
       <c r="O42">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="P42">
         <v>1.65</v>
@@ -7170,16 +7170,16 @@
         <v>2.34</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="U42">
         <v>2.38</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W42">
         <v>1.09</v>
@@ -7188,22 +7188,22 @@
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA42">
         <v>1.63</v>
       </c>
       <c r="AB42">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="AC42">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AD42">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE42">
         <v>1.14</v>
@@ -7212,7 +7212,7 @@
         <v>1.64</v>
       </c>
       <c r="AG42">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>2.75</v>
       </c>
       <c r="Q47">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="R47">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S47">
         <v>1.25</v>
@@ -7991,10 +7991,10 @@
         <v>3.75</v>
       </c>
       <c r="U47">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V47">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W47">
         <v>1.13</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK48">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         <v>5.25</v>
       </c>
       <c r="Q49">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R49">
         <v>2.98</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK49">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O50">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P50">
         <v>3.1</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O51">
         <v>3.92</v>
       </c>
       <c r="P51">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
         <v>2.66</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK51">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,7 +8794,7 @@
         <v>3.5</v>
       </c>
       <c r="Q52">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R52">
         <v>2.6</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10255,16 +10255,16 @@
         <v>2.47</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>4.02</v>
       </c>
       <c r="P61">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q61">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="S61">
         <v>1.18</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK61">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10421,10 +10421,10 @@
         <v>4.02</v>
       </c>
       <c r="P62">
-        <v>3.92</v>
+        <v>4.02</v>
       </c>
       <c r="Q62">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="R62">
         <v>2.4</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK62">
         <v>1.91</v>
@@ -10750,7 +10750,7 @@
         <v>7.5</v>
       </c>
       <c r="Q64">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="R64">
         <v>2.8</v>
@@ -10762,10 +10762,10 @@
         <v>4.4</v>
       </c>
       <c r="U64">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="V64">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="W64">
         <v>1.22</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="O65">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="Q65">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="R65">
         <v>2.47</v>
@@ -10925,10 +10925,10 @@
         <v>3.6</v>
       </c>
       <c r="U65">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="V65">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W65">
         <v>1.14</v>
@@ -10937,25 +10937,25 @@
         <v>0</v>
       </c>
       <c r="Y65">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z65">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="AA65">
         <v>1.62</v>
       </c>
       <c r="AB65">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AC65">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AD65">
         <v>1.54</v>
       </c>
       <c r="AE65">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF65">
         <v>1.5</v>
@@ -11076,10 +11076,10 @@
         <v>3.48</v>
       </c>
       <c r="Q66">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="R66">
-        <v>2.59</v>
+        <v>2.41</v>
       </c>
       <c r="S66">
         <v>1.2</v>
@@ -11118,7 +11118,7 @@
         <v>1.69</v>
       </c>
       <c r="AE66">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF66">
         <v>1.41</v>
@@ -11601,7 +11601,7 @@
         <v>2.43</v>
       </c>
       <c r="AC69">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AD69">
         <v>1.54</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>2.2</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>2.85</v>
@@ -2286,10 +2286,10 @@
         <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
         <v>1.11</v>
@@ -2298,10 +2298,10 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="AA12">
         <v>1.61</v>
@@ -2316,7 +2316,7 @@
         <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
         <v>1.65</v>
@@ -2597,10 +2597,10 @@
         <v>4</v>
       </c>
       <c r="P14">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="Q14">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R14">
         <v>2.45</v>
@@ -2633,13 +2633,13 @@
         <v>1.44</v>
       </c>
       <c r="AB14">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AC14">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AD14">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AE14">
         <v>1.29</v>
@@ -2664,7 +2664,7 @@
         <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="O15">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="P15">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q15">
-        <v>8.880000000000001</v>
+        <v>6.47</v>
       </c>
       <c r="R15">
         <v>2.88</v>
@@ -2778,7 +2778,7 @@
         <v>1.91</v>
       </c>
       <c r="V15">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W15">
         <v>1.22</v>
@@ -2787,10 +2787,10 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z15">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>1.4</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK15">
         <v>1.06</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="O19">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q19">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R19">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="V19">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z19">
-        <v>4.95</v>
+        <v>4.37</v>
       </c>
       <c r="AA19">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AB19">
-        <v>2.41</v>
+        <v>2.21</v>
       </c>
       <c r="AC19">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AD19">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF19">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AG19">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O20">
         <v>3.8</v>
       </c>
       <c r="P20">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="Q20">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="R20">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="S20">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="T20">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="V20">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="W20">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z20">
-        <v>5.15</v>
+        <v>6.05</v>
       </c>
       <c r="AA20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB20">
-        <v>2.42</v>
+        <v>2.82</v>
       </c>
       <c r="AC20">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AD20">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AE20">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AF20">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK20">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O21">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="Q21">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R21">
-        <v>2.41</v>
+        <v>2.56</v>
       </c>
       <c r="S21">
         <v>1.19</v>
       </c>
       <c r="T21">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="V21">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X21">
         <v>1.02</v>
@@ -3768,13 +3768,13 @@
         <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>5.5</v>
+        <v>5.51</v>
       </c>
       <c r="AA21">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AB21">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AC21">
         <v>2.04</v>
@@ -3786,10 +3786,10 @@
         <v>1.25</v>
       </c>
       <c r="AF21">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.95</v>
+        <v>3.17</v>
       </c>
       <c r="O25">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P25">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.49</v>
+        <v>2.01</v>
       </c>
       <c r="O26">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="P26">
-        <v>5.1</v>
+        <v>3.06</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="O27">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P27">
-        <v>2.43</v>
+        <v>3.55</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.76</v>
+        <v>1.42</v>
       </c>
       <c r="O28">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="P28">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="O29">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="P29">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="O30">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="P30">
-        <v>5.6</v>
+        <v>7.55</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.65</v>
+        <v>3.16</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P31">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.36</v>
+        <v>1.79</v>
       </c>
       <c r="O32">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="P32">
-        <v>2.57</v>
+        <v>4.05</v>
       </c>
       <c r="Q32">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="R32">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="U32">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="V32">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
+        <v>1.19</v>
+      </c>
+      <c r="Z32">
+        <v>3.78</v>
+      </c>
+      <c r="AA32">
+        <v>1.8</v>
+      </c>
+      <c r="AB32">
+        <v>2</v>
+      </c>
+      <c r="AC32">
+        <v>2.83</v>
+      </c>
+      <c r="AD32">
+        <v>1.33</v>
+      </c>
+      <c r="AE32">
         <v>1.09</v>
       </c>
-      <c r="Z32">
-        <v>5.4</v>
-      </c>
-      <c r="AA32">
-        <v>1.5</v>
-      </c>
-      <c r="AB32">
-        <v>2.62</v>
-      </c>
-      <c r="AC32">
-        <v>2.17</v>
-      </c>
-      <c r="AD32">
-        <v>1.64</v>
-      </c>
-      <c r="AE32">
-        <v>1.22</v>
-      </c>
       <c r="AF32">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.24</v>
       </c>
       <c r="AK32">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.79</v>
+        <v>2.36</v>
       </c>
       <c r="O33">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="P33">
-        <v>4.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q33">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="R33">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="U33">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="W33">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="Z33">
-        <v>3.78</v>
+        <v>5.4</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AC33">
-        <v>2.83</v>
+        <v>2.17</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.24</v>
       </c>
       <c r="AK33">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6017,13 +6017,13 @@
         <v>2.3</v>
       </c>
       <c r="O35">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="P35">
-        <v>2.87</v>
+        <v>2.48</v>
       </c>
       <c r="Q35">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="R35">
         <v>2.62</v>
@@ -6056,10 +6056,10 @@
         <v>1.44</v>
       </c>
       <c r="AB35">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AC35">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="AD35">
         <v>1.76</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AK35">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>4.15</v>
       </c>
       <c r="AA36">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB36">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC36">
         <v>2.68</v>
@@ -6349,7 +6349,7 @@
         <v>1.95</v>
       </c>
       <c r="Q37">
-        <v>3.65</v>
+        <v>3.26</v>
       </c>
       <c r="R37">
         <v>2.48</v>
@@ -6382,13 +6382,13 @@
         <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="AC37">
         <v>1.91</v>
       </c>
       <c r="AD37">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AE37">
         <v>1.34</v>
@@ -6413,7 +6413,7 @@
         <v>1.8</v>
       </c>
       <c r="AK37">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O38">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="P38">
         <v>4.2</v>
       </c>
       <c r="Q38">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="R38">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
         <v>1.3</v>
@@ -6542,13 +6542,13 @@
         <v>4.3</v>
       </c>
       <c r="AA38">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AB38">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="AC38">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="AD38">
         <v>1.47</v>
@@ -6576,7 +6576,7 @@
         <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P39">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q39">
         <v>3.7</v>
       </c>
       <c r="R39">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6708,13 +6708,13 @@
         <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="AC39">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD39">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AE39">
         <v>1.3</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O40">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="P40">
         <v>1.33</v>
       </c>
       <c r="Q40">
-        <v>7.91</v>
+        <v>5.7</v>
       </c>
       <c r="R40">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="S40">
         <v>1.18</v>
@@ -6871,7 +6871,7 @@
         <v>1.36</v>
       </c>
       <c r="AB40">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="AC40">
         <v>1.97</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O41">
         <v>3.44</v>
@@ -7668,7 +7668,7 @@
         <v>2</v>
       </c>
       <c r="V45">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="W45">
         <v>1.22</v>
@@ -7683,22 +7683,22 @@
         <v>7</v>
       </c>
       <c r="AA45">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AB45">
-        <v>2.81</v>
+        <v>3.25</v>
       </c>
       <c r="AC45">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AD45">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AE45">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF45">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG45">
         <v>2.88</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK45">
         <v>1.29</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK47">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8206,7 +8206,7 @@
         <v>1.19</v>
       </c>
       <c r="AK48">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK49">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK51">
         <v>1.59</v>
@@ -8794,7 +8794,7 @@
         <v>3.5</v>
       </c>
       <c r="Q52">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R52">
         <v>2.6</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="O61">
         <v>4.02</v>
@@ -10261,10 +10261,10 @@
         <v>2.5</v>
       </c>
       <c r="Q61">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="R61">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
         <v>1.18</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AK61">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10418,16 +10418,16 @@
         <v>1.8</v>
       </c>
       <c r="O62">
-        <v>4.02</v>
+        <v>3.94</v>
       </c>
       <c r="P62">
-        <v>4.02</v>
+        <v>3.9</v>
       </c>
       <c r="Q62">
         <v>2.23</v>
       </c>
       <c r="R62">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
         <v>1.25</v>
@@ -10436,13 +10436,13 @@
         <v>3.9</v>
       </c>
       <c r="U62">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="V62">
         <v>1.61</v>
       </c>
       <c r="W62">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X62">
         <v>0</v>
@@ -10451,16 +10451,16 @@
         <v>1.17</v>
       </c>
       <c r="Z62">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
       <c r="AA62">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AB62">
         <v>2.3</v>
       </c>
       <c r="AC62">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AD62">
         <v>1.6</v>
@@ -10472,7 +10472,7 @@
         <v>1.53</v>
       </c>
       <c r="AG62">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.18</v>
       </c>
       <c r="AK62">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10762,10 +10762,10 @@
         <v>4.4</v>
       </c>
       <c r="U64">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="V64">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="W64">
         <v>1.22</v>
@@ -10913,7 +10913,7 @@
         <v>3</v>
       </c>
       <c r="Q65">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="R65">
         <v>2.47</v>
@@ -11076,10 +11076,10 @@
         <v>3.48</v>
       </c>
       <c r="Q66">
-        <v>2.28</v>
+        <v>2.43</v>
       </c>
       <c r="R66">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="S66">
         <v>1.2</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -982,10 +982,10 @@
         <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="V4">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
         <v>1.12</v>
@@ -997,19 +997,19 @@
         <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="AA4">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB4">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AC4">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="AD4">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE4">
         <v>1.15</v>
@@ -1034,7 +1034,7 @@
         <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>1.63</v>
       </c>
       <c r="Q7">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="R7">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S7">
         <v>1.4</v>
@@ -1486,13 +1486,13 @@
         <v>1.4</v>
       </c>
       <c r="Z7">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AA7">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AB7">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1504,10 +1504,10 @@
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AG7">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         <v>1.08</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
         <v>1.2</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>2.1</v>
+      </c>
+      <c r="O18">
+        <v>3.75</v>
+      </c>
+      <c r="P18">
         <v>2.75</v>
       </c>
-      <c r="O18">
-        <v>3.5</v>
-      </c>
-      <c r="P18">
-        <v>2.32</v>
-      </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="O19">
         <v>3.5</v>
       </c>
       <c r="P19">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q19">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>2.13</v>
+        <v>2.8</v>
       </c>
       <c r="R20">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U20">
-        <v>2.07</v>
+        <v>2.44</v>
       </c>
       <c r="V20">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="W20">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="Z20">
-        <v>6.05</v>
+        <v>4.37</v>
       </c>
       <c r="AA20">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB20">
-        <v>2.82</v>
+        <v>2.21</v>
       </c>
       <c r="AC20">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="AD20">
-        <v>1.76</v>
+        <v>1.46</v>
       </c>
       <c r="AE20">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AF20">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AG20">
-        <v>2.73</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>2.03</v>
+        <v>1.49</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q21">
-        <v>2.46</v>
+        <v>2.13</v>
       </c>
       <c r="R21">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="S21">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="T21">
         <v>4</v>
       </c>
       <c r="U21">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="V21">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W21">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>5.51</v>
+        <v>6.05</v>
       </c>
       <c r="AA21">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="AC21">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AD21">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AE21">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF21">
         <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK21">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O22">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Q22">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R22">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="S22">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T22">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U22">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="V22">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>5.7</v>
+        <v>5.51</v>
       </c>
       <c r="AA22">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AB22">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AC22">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AD22">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE22">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF22">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK22">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4248,7 +4248,7 @@
         <v>1.36</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
         <v>1.04</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="O32">
         <v>3.78</v>
@@ -5691,7 +5691,7 @@
         <v>2.36</v>
       </c>
       <c r="O33">
-        <v>3.82</v>
+        <v>3.48</v>
       </c>
       <c r="P33">
         <v>2.57</v>
@@ -5736,7 +5736,7 @@
         <v>2.17</v>
       </c>
       <c r="AD33">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE33">
         <v>1.22</v>
@@ -5860,7 +5860,7 @@
         <v>2.97</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
         <v>2.1</v>
@@ -5899,7 +5899,7 @@
         <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
         <v>1.07</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>4.6</v>
       </c>
       <c r="O42">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="P42">
         <v>1.65</v>
@@ -7327,10 +7327,10 @@
         <v>1.82</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -7339,10 +7339,10 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W43">
         <v>0</v>
@@ -7357,25 +7357,25 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7816,10 +7816,10 @@
         <v>5</v>
       </c>
       <c r="Q46">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="R46">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="S46">
         <v>1.29</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G54">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G58">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>JS El Biar</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G59">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS El Biar</t>
         </is>
       </c>
       <c r="G60">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N60">

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O4">
         <v>3.8</v>
@@ -991,7 +991,7 @@
         <v>1.12</v>
       </c>
       <c r="X4">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
         <v>1.17</v>
@@ -1003,7 +1003,7 @@
         <v>1.67</v>
       </c>
       <c r="AB4">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
         <v>2.66</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="O8">
         <v>3.95</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="O13">
         <v>4</v>
       </c>
       <c r="P13">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>2.75</v>
       </c>
       <c r="Q18">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R18">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="S18">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T18">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V18">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W18">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>5.7</v>
+        <v>6.05</v>
       </c>
       <c r="AA18">
         <v>1.35</v>
       </c>
       <c r="AB18">
-        <v>2.74</v>
+        <v>3.07</v>
       </c>
       <c r="AC18">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AD18">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AE18">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AF18">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG18">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q20">
         <v>2.8</v>
@@ -3590,7 +3590,7 @@
         <v>3.5</v>
       </c>
       <c r="U20">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="V20">
         <v>1.53</v>
@@ -3599,7 +3599,7 @@
         <v>1.12</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
         <v>1.19</v>
@@ -3608,10 +3608,10 @@
         <v>4.37</v>
       </c>
       <c r="AA20">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC20">
         <v>2.46</v>
@@ -3623,10 +3623,10 @@
         <v>1.15</v>
       </c>
       <c r="AF20">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AG20">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O21">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P21">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
         <v>2.13</v>
@@ -3774,7 +3774,7 @@
         <v>1.4</v>
       </c>
       <c r="AB21">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="AC21">
         <v>2.02</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P22">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q22">
         <v>2.46</v>
@@ -3934,10 +3934,10 @@
         <v>5.51</v>
       </c>
       <c r="AA22">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB22">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AC22">
         <v>2.04</v>
@@ -4061,7 +4061,7 @@
         <v>1.95</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
         <v>3.25</v>
@@ -4097,10 +4097,10 @@
         <v>3.9</v>
       </c>
       <c r="AA23">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AC23">
         <v>2.88</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="O24">
         <v>3.1</v>
@@ -5528,7 +5528,7 @@
         <v>1.74</v>
       </c>
       <c r="O32">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
         <v>4.05</v>
@@ -5564,10 +5564,10 @@
         <v>3.78</v>
       </c>
       <c r="AA32">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC32">
         <v>2.83</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="O33">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="Q33">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="R33">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
         <v>1.25</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P34">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S34">
         <v>1.35</v>
@@ -5890,10 +5890,10 @@
         <v>3.34</v>
       </c>
       <c r="AA34">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB34">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AC34">
         <v>3.2</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7188,25 +7188,25 @@
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA42">
         <v>1.63</v>
       </c>
       <c r="AB42">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AC42">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="AD42">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF42">
         <v>1.64</v>
@@ -7228,7 +7228,7 @@
         <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7484,10 +7484,10 @@
         <v>2.69</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P44">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q44">
         <v>3.28</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P46">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="Q46">
         <v>1.91</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="O48">
         <v>3.5</v>
@@ -8341,10 +8341,10 @@
         <v>3.4</v>
       </c>
       <c r="AC49">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AD49">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AE49">
         <v>1.43</v>
@@ -8631,10 +8631,10 @@
         <v>2.7</v>
       </c>
       <c r="Q51">
-        <v>2.66</v>
+        <v>2.36</v>
       </c>
       <c r="R51">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="S51">
         <v>1.2</v>
@@ -8667,10 +8667,10 @@
         <v>2.83</v>
       </c>
       <c r="AC51">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AD51">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AE51">
         <v>1.34</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="O61">
-        <v>4.02</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q61">
         <v>2.9</v>
@@ -10297,10 +10297,10 @@
         <v>2.72</v>
       </c>
       <c r="AC61">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="AD61">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AE61">
         <v>1.33</v>
@@ -10433,7 +10433,7 @@
         <v>1.25</v>
       </c>
       <c r="T62">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U62">
         <v>2.25</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK62">
         <v>1.85</v>
@@ -10584,7 +10584,7 @@
         <v>3.6</v>
       </c>
       <c r="P63">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -10762,7 +10762,7 @@
         <v>4.4</v>
       </c>
       <c r="U64">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="V64">
         <v>1.85</v>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK67">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11396,7 +11396,7 @@
         <v>1.8</v>
       </c>
       <c r="O68">
-        <v>4.08</v>
+        <v>3.8</v>
       </c>
       <c r="P68">
         <v>3.68</v>
@@ -11447,7 +11447,7 @@
         <v>1.33</v>
       </c>
       <c r="AF68">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG68">
         <v>2.8</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -2277,7 +2277,7 @@
         <v>2.62</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2304,13 +2304,13 @@
         <v>4.05</v>
       </c>
       <c r="AA12">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AB12">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="AC12">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK12">
         <v>1.67</v>
@@ -2434,7 +2434,7 @@
         <v>4</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2594,16 +2594,16 @@
         <v>3.3</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P14">
         <v>1.83</v>
       </c>
       <c r="Q14">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
         <v>1.17</v>
@@ -2612,10 +2612,10 @@
         <v>4</v>
       </c>
       <c r="U14">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="V14">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W14">
         <v>1.17</v>
@@ -2624,16 +2624,16 @@
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z14">
-        <v>5.35</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>1.44</v>
       </c>
       <c r="AB14">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="AC14">
         <v>1.99</v>
@@ -2642,7 +2642,7 @@
         <v>1.78</v>
       </c>
       <c r="AE14">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF14">
         <v>1.36</v>
@@ -2760,7 +2760,7 @@
         <v>6.55</v>
       </c>
       <c r="P15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q15">
         <v>6.47</v>
@@ -2787,19 +2787,19 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z15">
         <v>7</v>
       </c>
       <c r="AA15">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="AC15">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AD15">
         <v>1.9</v>
@@ -2808,7 +2808,7 @@
         <v>1.36</v>
       </c>
       <c r="AF15">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
         <v>2.15</v>
@@ -3258,13 +3258,13 @@
         <v>2.62</v>
       </c>
       <c r="S18">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V18">
         <v>1.75</v>
@@ -3282,19 +3282,19 @@
         <v>6.05</v>
       </c>
       <c r="AA18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="AC18">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AD18">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AE18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF18">
         <v>1.33</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="R19">
         <v>2.37</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AK19">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O20">
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="Q20">
         <v>2.8</v>
@@ -3605,7 +3605,7 @@
         <v>1.19</v>
       </c>
       <c r="Z20">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="AA20">
         <v>1.6</v>
@@ -3620,7 +3620,7 @@
         <v>1.46</v>
       </c>
       <c r="AE20">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
         <v>1.55</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
         <v>1.53</v>
@@ -3732,34 +3732,34 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="O21">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="R21">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="S21">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="U21">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="V21">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="W21">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3768,7 +3768,7 @@
         <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="AA21">
         <v>1.4</v>
@@ -3777,19 +3777,19 @@
         <v>2.88</v>
       </c>
       <c r="AC21">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AD21">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF21">
         <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK21">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O22">
         <v>3.55</v>
@@ -3904,10 +3904,10 @@
         <v>2.94</v>
       </c>
       <c r="Q22">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R22">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
         <v>1.19</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="O24">
         <v>3.1</v>
@@ -5537,7 +5537,7 @@
         <v>2.28</v>
       </c>
       <c r="R32">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="S32">
         <v>1.3</v>
@@ -5555,7 +5555,7 @@
         <v>1.11</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
         <v>1.19</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK32">
         <v>2.02</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="O33">
         <v>3.7</v>
       </c>
       <c r="P33">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="Q33">
         <v>2.54</v>
@@ -5727,10 +5727,10 @@
         <v>5.4</v>
       </c>
       <c r="AA33">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB33">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AC33">
         <v>2.17</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="O34">
         <v>3.35</v>
@@ -5860,7 +5860,7 @@
         <v>3.1</v>
       </c>
       <c r="Q34">
-        <v>2.57</v>
+        <v>2.9</v>
       </c>
       <c r="R34">
         <v>2.06</v>
@@ -5890,10 +5890,10 @@
         <v>3.34</v>
       </c>
       <c r="AA34">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC34">
         <v>3.2</v>
@@ -5924,7 +5924,7 @@
         <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O35">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="P35">
-        <v>2.48</v>
+        <v>2.87</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
@@ -6047,22 +6047,22 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>1.44</v>
       </c>
       <c r="AB35">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AC35">
         <v>2.11</v>
       </c>
       <c r="AD35">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE35">
         <v>1.29</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK35">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,34 +6177,34 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O36">
         <v>3.6</v>
       </c>
       <c r="P36">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="Q36">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="R36">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U36">
         <v>2.4</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X36">
         <v>1.01</v>
@@ -6213,22 +6213,22 @@
         <v>1.18</v>
       </c>
       <c r="Z36">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="AA36">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AB36">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AC36">
         <v>2.68</v>
       </c>
       <c r="AD36">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE36">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
         <v>1.6</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O37">
         <v>4</v>
@@ -6367,7 +6367,7 @@
         <v>1.82</v>
       </c>
       <c r="W37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6376,22 +6376,22 @@
         <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>5.65</v>
+        <v>7</v>
       </c>
       <c r="AA37">
         <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="AC37">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AD37">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AE37">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF37">
         <v>1.36</v>
@@ -6413,7 +6413,7 @@
         <v>1.8</v>
       </c>
       <c r="AK37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6515,7 +6515,7 @@
         <v>2.24</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S38">
         <v>1.3</v>
@@ -6536,25 +6536,25 @@
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA38">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB38">
         <v>2.3</v>
       </c>
       <c r="AC38">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AD38">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE38">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF38">
         <v>1.67</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6678,7 +6678,7 @@
         <v>3.7</v>
       </c>
       <c r="R39">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6690,7 +6690,7 @@
         <v>2</v>
       </c>
       <c r="V39">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W39">
         <v>1.17</v>
@@ -6702,7 +6702,7 @@
         <v>1.08</v>
       </c>
       <c r="Z39">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA39">
         <v>1.4</v>
@@ -6711,10 +6711,10 @@
         <v>2.91</v>
       </c>
       <c r="AC39">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD39">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AE39">
         <v>1.3</v>
@@ -6838,7 +6838,7 @@
         <v>1.33</v>
       </c>
       <c r="Q40">
-        <v>5.7</v>
+        <v>7.84</v>
       </c>
       <c r="R40">
         <v>2.88</v>
@@ -6850,7 +6850,7 @@
         <v>4.4</v>
       </c>
       <c r="U40">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="V40">
         <v>1.79</v>
@@ -6862,7 +6862,7 @@
         <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z40">
         <v>7.5</v>
@@ -6871,16 +6871,16 @@
         <v>1.36</v>
       </c>
       <c r="AB40">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="AC40">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AD40">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AE40">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AF40">
         <v>1.65</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="AK40">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7004,7 +7004,7 @@
         <v>3.02</v>
       </c>
       <c r="R41">
-        <v>2.11</v>
+        <v>2.31</v>
       </c>
       <c r="S41">
         <v>1.33</v>
@@ -7013,7 +7013,7 @@
         <v>3.05</v>
       </c>
       <c r="U41">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="V41">
         <v>1.45</v>
@@ -7022,34 +7022,34 @@
         <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="AA41">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AB41">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AC41">
-        <v>2.83</v>
+        <v>2.91</v>
       </c>
       <c r="AD41">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AE41">
         <v>1.08</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG41">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AK41">
         <v>1.43</v>
@@ -7164,7 +7164,7 @@
         <v>1.65</v>
       </c>
       <c r="Q42">
-        <v>4.88</v>
+        <v>4.17</v>
       </c>
       <c r="R42">
         <v>2.34</v>
@@ -7197,13 +7197,13 @@
         <v>1.63</v>
       </c>
       <c r="AB42">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AC42">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD42">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE42">
         <v>1.17</v>
@@ -7228,7 +7228,7 @@
         <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="O47">
         <v>3.85</v>
@@ -8009,7 +8009,7 @@
         <v>5.1</v>
       </c>
       <c r="AA47">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB47">
         <v>2.45</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK47">
         <v>1.62</v>
@@ -8335,7 +8335,7 @@
         <v>8</v>
       </c>
       <c r="AA49">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AB49">
         <v>3.4</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK49">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8628,7 +8628,7 @@
         <v>3.92</v>
       </c>
       <c r="P51">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q51">
         <v>2.36</v>
@@ -8667,19 +8667,19 @@
         <v>2.83</v>
       </c>
       <c r="AC51">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AD51">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AE51">
         <v>1.34</v>
       </c>
       <c r="AF51">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG51">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8791,13 +8791,13 @@
         <v>4</v>
       </c>
       <c r="P52">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q52">
         <v>2.2</v>
       </c>
       <c r="R52">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8821,22 +8821,22 @@
         <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="AA52">
         <v>1.5</v>
       </c>
       <c r="AB52">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="AC52">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AD52">
         <v>1.62</v>
       </c>
       <c r="AE52">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF52">
         <v>1.44</v>
@@ -10291,7 +10291,7 @@
         <v>5.88</v>
       </c>
       <c r="AA61">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB61">
         <v>2.72</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O62">
         <v>3.94</v>
@@ -10454,10 +10454,10 @@
         <v>5.07</v>
       </c>
       <c r="AA62">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB62">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AC62">
         <v>2.31</v>
@@ -10584,13 +10584,13 @@
         <v>3.6</v>
       </c>
       <c r="P63">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q63">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="S63">
         <v>1.2</v>
@@ -10602,34 +10602,34 @@
         <v>2.15</v>
       </c>
       <c r="V63">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W63">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X63">
         <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z63">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="AA63">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB63">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="AC63">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AD63">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE63">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AF63">
         <v>1.44</v>
@@ -11230,19 +11230,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="O67">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q67">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="R67">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="S67">
         <v>1.25</v>
@@ -11266,7 +11266,7 @@
         <v>1.15</v>
       </c>
       <c r="Z67">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="AA67">
         <v>1.57</v>
@@ -11275,7 +11275,7 @@
         <v>2.35</v>
       </c>
       <c r="AC67">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="AD67">
         <v>1.55</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O68">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="P68">
-        <v>3.68</v>
+        <v>3.19</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -11417,7 +11417,7 @@
         <v>2</v>
       </c>
       <c r="V68">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W68">
         <v>1.2</v>
@@ -11426,25 +11426,25 @@
         <v>0</v>
       </c>
       <c r="Y68">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z68">
-        <v>7</v>
+        <v>6.23</v>
       </c>
       <c r="AA68">
         <v>1.4</v>
       </c>
       <c r="AB68">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AC68">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AD68">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AE68">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF68">
         <v>1.4</v>
@@ -11466,7 +11466,7 @@
         <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL68">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -807,7 +807,7 @@
         <v>2.05</v>
       </c>
       <c r="Q3">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R3">
         <v>2.13</v>
@@ -816,7 +816,7 @@
         <v>1.37</v>
       </c>
       <c r="T3">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="U3">
         <v>3</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,37 +2591,37 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="O14">
-        <v>3.95</v>
+        <v>6.55</v>
       </c>
       <c r="P14">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>3.5</v>
+        <v>6.47</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="S14">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U14">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="V14">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="W14">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.08</v>
@@ -2630,25 +2630,25 @@
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB14">
-        <v>2.61</v>
+        <v>2.84</v>
       </c>
       <c r="AC14">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AD14">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AE14">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF14">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AG14">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK14">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,37 +2754,37 @@
         </is>
       </c>
       <c r="N15">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="O15">
-        <v>6.55</v>
+        <v>3.95</v>
       </c>
       <c r="P15">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q15">
-        <v>6.47</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T15">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="V15">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="W15">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
         <v>1.08</v>
@@ -2793,25 +2793,25 @@
         <v>7</v>
       </c>
       <c r="AA15">
+        <v>1.44</v>
+      </c>
+      <c r="AB15">
+        <v>2.61</v>
+      </c>
+      <c r="AC15">
+        <v>1.99</v>
+      </c>
+      <c r="AD15">
+        <v>1.78</v>
+      </c>
+      <c r="AE15">
+        <v>1.3</v>
+      </c>
+      <c r="AF15">
         <v>1.36</v>
       </c>
-      <c r="AB15">
-        <v>2.84</v>
-      </c>
-      <c r="AC15">
-        <v>1.86</v>
-      </c>
-      <c r="AD15">
-        <v>1.9</v>
-      </c>
-      <c r="AE15">
-        <v>1.36</v>
-      </c>
-      <c r="AF15">
-        <v>1.67</v>
-      </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.17</v>
+        <v>1.76</v>
       </c>
       <c r="O25">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P25">
-        <v>1.91</v>
+        <v>3.35</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.01</v>
+        <v>2.4</v>
       </c>
       <c r="O26">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P26">
-        <v>3.06</v>
+        <v>2.43</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.76</v>
+        <v>2.95</v>
       </c>
       <c r="O27">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P27">
-        <v>3.55</v>
+        <v>2.07</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="O28">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="P28">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="O29">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="P29">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="O30">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="P30">
-        <v>7.55</v>
+        <v>5.1</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="O31">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="Q35">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="R35">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>4.2</v>
+        <v>3.22</v>
       </c>
       <c r="U35">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="V35">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="W35">
+        <v>1.1</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
         <v>1.18</v>
       </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.11</v>
-      </c>
       <c r="Z35">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA35">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AB35">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="AC35">
-        <v>2.11</v>
+        <v>2.68</v>
       </c>
       <c r="AD35">
+        <v>1.47</v>
+      </c>
+      <c r="AE35">
+        <v>1.14</v>
+      </c>
+      <c r="AF35">
+        <v>1.6</v>
+      </c>
+      <c r="AG35">
+        <v>2.3</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>1.26</v>
+      </c>
+      <c r="AK35">
         <v>1.75</v>
-      </c>
-      <c r="AE35">
-        <v>1.29</v>
-      </c>
-      <c r="AF35">
-        <v>1.4</v>
-      </c>
-      <c r="AG35">
-        <v>2.89</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.33</v>
-      </c>
-      <c r="AK35">
-        <v>1.72</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O36">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="Q36">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="S36">
+        <v>1.2</v>
+      </c>
+      <c r="T36">
+        <v>4.2</v>
+      </c>
+      <c r="U36">
+        <v>2</v>
+      </c>
+      <c r="V36">
+        <v>1.73</v>
+      </c>
+      <c r="W36">
+        <v>1.18</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.11</v>
+      </c>
+      <c r="Z36">
+        <v>6</v>
+      </c>
+      <c r="AA36">
+        <v>1.44</v>
+      </c>
+      <c r="AB36">
+        <v>2.8</v>
+      </c>
+      <c r="AC36">
+        <v>2.11</v>
+      </c>
+      <c r="AD36">
+        <v>1.75</v>
+      </c>
+      <c r="AE36">
+        <v>1.29</v>
+      </c>
+      <c r="AF36">
+        <v>1.4</v>
+      </c>
+      <c r="AG36">
+        <v>2.89</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.33</v>
       </c>
-      <c r="T36">
-        <v>3.22</v>
-      </c>
-      <c r="U36">
-        <v>2.4</v>
-      </c>
-      <c r="V36">
-        <v>1.51</v>
-      </c>
-      <c r="W36">
-        <v>1.1</v>
-      </c>
-      <c r="X36">
-        <v>1.01</v>
-      </c>
-      <c r="Y36">
-        <v>1.18</v>
-      </c>
-      <c r="Z36">
-        <v>4.5</v>
-      </c>
-      <c r="AA36">
-        <v>1.71</v>
-      </c>
-      <c r="AB36">
-        <v>2.17</v>
-      </c>
-      <c r="AC36">
-        <v>2.68</v>
-      </c>
-      <c r="AD36">
-        <v>1.47</v>
-      </c>
-      <c r="AE36">
-        <v>1.14</v>
-      </c>
-      <c r="AF36">
-        <v>1.6</v>
-      </c>
-      <c r="AG36">
-        <v>2.3</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.26</v>
-      </c>
       <c r="AK36">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7505,7 +7505,7 @@
         <v>2.32</v>
       </c>
       <c r="V44">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W44">
         <v>1.12</v>
@@ -7520,10 +7520,10 @@
         <v>3.98</v>
       </c>
       <c r="AA44">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AB44">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC44">
         <v>2.56</v>
@@ -7653,28 +7653,28 @@
         <v>1.95</v>
       </c>
       <c r="Q45">
-        <v>3.32</v>
+        <v>3.52</v>
       </c>
       <c r="R45">
         <v>2.5</v>
       </c>
       <c r="S45">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T45">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U45">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V45">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="W45">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45">
         <v>1.07</v>
@@ -7683,25 +7683,25 @@
         <v>7</v>
       </c>
       <c r="AA45">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AB45">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="AC45">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AD45">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AE45">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AF45">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG45">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK45">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -810,7 +810,7 @@
         <v>4.3</v>
       </c>
       <c r="R3">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
         <v>1.37</v>
@@ -819,10 +819,10 @@
         <v>2.85</v>
       </c>
       <c r="U3">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>2.12</v>
       </c>
       <c r="R4">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="S4">
         <v>1.3</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="O8">
         <v>3.95</v>
       </c>
       <c r="P8">
-        <v>5.5</v>
+        <v>5.58</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1797,7 +1797,7 @@
         <v>3.17</v>
       </c>
       <c r="U9">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
         <v>1.44</v>
@@ -1821,10 +1821,10 @@
         <v>1.94</v>
       </c>
       <c r="AC9">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE9">
         <v>1.08</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK9">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2338,7 +2338,7 @@
         <v>1.34</v>
       </c>
       <c r="AK12">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,37 +2591,37 @@
         </is>
       </c>
       <c r="N14">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
-        <v>6.55</v>
+        <v>3.95</v>
       </c>
       <c r="P14">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q14">
-        <v>6.47</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T14">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U14">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="V14">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="W14">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
         <v>1.08</v>
@@ -2630,25 +2630,25 @@
         <v>7</v>
       </c>
       <c r="AA14">
+        <v>1.44</v>
+      </c>
+      <c r="AB14">
+        <v>2.61</v>
+      </c>
+      <c r="AC14">
+        <v>1.99</v>
+      </c>
+      <c r="AD14">
+        <v>1.78</v>
+      </c>
+      <c r="AE14">
+        <v>1.3</v>
+      </c>
+      <c r="AF14">
         <v>1.36</v>
       </c>
-      <c r="AB14">
-        <v>2.84</v>
-      </c>
-      <c r="AC14">
-        <v>1.86</v>
-      </c>
-      <c r="AD14">
-        <v>1.9</v>
-      </c>
-      <c r="AE14">
-        <v>1.36</v>
-      </c>
-      <c r="AF14">
-        <v>1.67</v>
-      </c>
       <c r="AG14">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,37 +2754,37 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="O15">
-        <v>3.95</v>
+        <v>6.55</v>
       </c>
       <c r="P15">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>6.47</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="S15">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U15">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="V15">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
         <v>1.08</v>
@@ -2793,25 +2793,25 @@
         <v>7</v>
       </c>
       <c r="AA15">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.61</v>
+        <v>2.84</v>
       </c>
       <c r="AC15">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AD15">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AE15">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF15">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>2.88</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AK15">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3249,7 +3249,7 @@
         <v>3.75</v>
       </c>
       <c r="P18">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -3270,7 +3270,7 @@
         <v>1.75</v>
       </c>
       <c r="W18">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,10 +3282,10 @@
         <v>6.05</v>
       </c>
       <c r="AA18">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AB18">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AC18">
         <v>1.86</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK18">
         <v>1.67</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O19">
         <v>3.4</v>
@@ -3421,7 +3421,7 @@
         <v>2.37</v>
       </c>
       <c r="S19">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T19">
         <v>3.4</v>
@@ -3433,7 +3433,7 @@
         <v>1.51</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3575,7 +3575,7 @@
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q20">
         <v>2.8</v>
@@ -3590,13 +3590,13 @@
         <v>3.5</v>
       </c>
       <c r="U20">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="V20">
         <v>1.53</v>
       </c>
       <c r="W20">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
         <v>1.02</v>
@@ -3608,10 +3608,10 @@
         <v>4.3</v>
       </c>
       <c r="AA20">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AB20">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC20">
         <v>2.46</v>
@@ -3623,7 +3623,7 @@
         <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
         <v>2.3</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
         <v>1.53</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O21">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P21">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q21">
         <v>2.14</v>
@@ -3771,7 +3771,7 @@
         <v>5.95</v>
       </c>
       <c r="AA21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB21">
         <v>2.88</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
         <v>1.97</v>
@@ -3904,25 +3904,25 @@
         <v>2.94</v>
       </c>
       <c r="Q22">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S22">
         <v>1.19</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="U22">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W22">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3937,7 +3937,7 @@
         <v>1.4</v>
       </c>
       <c r="AB22">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AC22">
         <v>2.04</v>
@@ -3949,7 +3949,7 @@
         <v>1.25</v>
       </c>
       <c r="AF22">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AG22">
         <v>2.75</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AK22">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4070,19 +4070,19 @@
         <v>2.5</v>
       </c>
       <c r="R23">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T23">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U23">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="V23">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
         <v>1.07</v>
@@ -4115,7 +4115,7 @@
         <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK23">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4239,10 +4239,10 @@
         <v>1.42</v>
       </c>
       <c r="T24">
-        <v>2.59</v>
+        <v>2.88</v>
       </c>
       <c r="U24">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="V24">
         <v>1.36</v>
@@ -4257,7 +4257,7 @@
         <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AA24">
         <v>2.01</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
+        <v>1.25</v>
+      </c>
+      <c r="AK24">
         <v>1.33</v>
-      </c>
-      <c r="AK24">
-        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="O25">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P25">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="Q25">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="R25">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="S25">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T25">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="U25">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="V25">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="W25">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Z25">
-        <v>8.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA25">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AB25">
-        <v>3.82</v>
+        <v>2.7</v>
       </c>
       <c r="AC25">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AD25">
-        <v>2.32</v>
+        <v>1.72</v>
       </c>
       <c r="AE25">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AF25">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="AG25">
-        <v>3.65</v>
+        <v>2.21</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK25">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="O26">
+        <v>4.5</v>
+      </c>
+      <c r="P26">
+        <v>4.7</v>
+      </c>
+      <c r="Q26">
+        <v>1.62</v>
+      </c>
+      <c r="R26">
+        <v>3.04</v>
+      </c>
+      <c r="S26">
+        <v>1.09</v>
+      </c>
+      <c r="T26">
+        <v>5.55</v>
+      </c>
+      <c r="U26">
+        <v>1.69</v>
+      </c>
+      <c r="V26">
+        <v>2.06</v>
+      </c>
+      <c r="W26">
+        <v>1.31</v>
+      </c>
+      <c r="X26">
+        <v>1</v>
+      </c>
+      <c r="Y26">
+        <v>1.01</v>
+      </c>
+      <c r="Z26">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AA26">
+        <v>1.19</v>
+      </c>
+      <c r="AB26">
+        <v>3.76</v>
+      </c>
+      <c r="AC26">
+        <v>1.6</v>
+      </c>
+      <c r="AD26">
+        <v>2.23</v>
+      </c>
+      <c r="AE26">
+        <v>1.51</v>
+      </c>
+      <c r="AF26">
+        <v>1.45</v>
+      </c>
+      <c r="AG26">
+        <v>2.56</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.08</v>
+      </c>
+      <c r="AK26">
         <v>3.6</v>
-      </c>
-      <c r="P26">
-        <v>2.43</v>
-      </c>
-      <c r="Q26">
-        <v>2.5</v>
-      </c>
-      <c r="R26">
-        <v>2.48</v>
-      </c>
-      <c r="S26">
-        <v>1.17</v>
-      </c>
-      <c r="T26">
-        <v>4.1</v>
-      </c>
-      <c r="U26">
-        <v>1.91</v>
-      </c>
-      <c r="V26">
-        <v>1.8</v>
-      </c>
-      <c r="W26">
-        <v>1.22</v>
-      </c>
-      <c r="X26">
-        <v>1.01</v>
-      </c>
-      <c r="Y26">
-        <v>1.06</v>
-      </c>
-      <c r="Z26">
-        <v>6.1</v>
-      </c>
-      <c r="AA26">
-        <v>1.33</v>
-      </c>
-      <c r="AB26">
-        <v>3.25</v>
-      </c>
-      <c r="AC26">
-        <v>1.92</v>
-      </c>
-      <c r="AD26">
-        <v>1.81</v>
-      </c>
-      <c r="AE26">
-        <v>1.3</v>
-      </c>
-      <c r="AF26">
-        <v>1.33</v>
-      </c>
-      <c r="AG26">
-        <v>3.02</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.21</v>
-      </c>
-      <c r="AK26">
-        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,65 +4873,65 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="O28">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="P28">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="Q28">
         <v>1.77</v>
       </c>
       <c r="R28">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="S28">
         <v>1.17</v>
       </c>
       <c r="T28">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="U28">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="V28">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="W28">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Z28">
-        <v>5.75</v>
+        <v>7.3</v>
       </c>
       <c r="AA28">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AB28">
+        <v>3.28</v>
+      </c>
+      <c r="AC28">
+        <v>1.74</v>
+      </c>
+      <c r="AD28">
+        <v>2.01</v>
+      </c>
+      <c r="AE28">
+        <v>1.41</v>
+      </c>
+      <c r="AF28">
+        <v>1.41</v>
+      </c>
+      <c r="AG28">
         <v>2.7</v>
       </c>
-      <c r="AC28">
-        <v>1.97</v>
-      </c>
-      <c r="AD28">
-        <v>1.72</v>
-      </c>
-      <c r="AE28">
-        <v>1.27</v>
-      </c>
-      <c r="AF28">
-        <v>1.59</v>
-      </c>
-      <c r="AG28">
-        <v>2.21</v>
-      </c>
       <c r="AH28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AK28">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="O29">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>4.7</v>
+        <v>2.43</v>
       </c>
       <c r="Q29">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
-        <v>3.04</v>
+        <v>2.48</v>
       </c>
       <c r="S29">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="T29">
-        <v>5.55</v>
+        <v>4.1</v>
       </c>
       <c r="U29">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="V29">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="W29">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Z29">
-        <v>8.300000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="AA29">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AB29">
-        <v>3.76</v>
+        <v>3.25</v>
       </c>
       <c r="AC29">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AD29">
-        <v>2.23</v>
+        <v>1.81</v>
       </c>
       <c r="AE29">
-        <v>1.51</v>
+        <v>1.3</v>
       </c>
       <c r="AF29">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AG29">
-        <v>2.56</v>
+        <v>3.02</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="O30">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P30">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q30">
-        <v>1.77</v>
+        <v>2.14</v>
       </c>
       <c r="R30">
-        <v>2.81</v>
+        <v>2.93</v>
       </c>
       <c r="S30">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T30">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="U30">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="V30">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="W30">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Z30">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="AA30">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AB30">
-        <v>3.28</v>
+        <v>3.82</v>
       </c>
       <c r="AC30">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AD30">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="AE30">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AF30">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AG30">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK30">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.74</v>
+        <v>2.36</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="P32">
-        <v>4.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q32">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="R32">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U32">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="V32">
+        <v>1.64</v>
+      </c>
+      <c r="W32">
+        <v>1.13</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.09</v>
+      </c>
+      <c r="Z32">
+        <v>5.4</v>
+      </c>
+      <c r="AA32">
         <v>1.47</v>
       </c>
-      <c r="W32">
-        <v>1.11</v>
-      </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
-      <c r="Y32">
-        <v>1.19</v>
-      </c>
-      <c r="Z32">
-        <v>3.78</v>
-      </c>
-      <c r="AA32">
-        <v>1.75</v>
-      </c>
       <c r="AB32">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AC32">
-        <v>2.83</v>
+        <v>2.17</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.14</v>
+        <v>1.46</v>
       </c>
       <c r="AK32">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.39</v>
+        <v>1.74</v>
       </c>
       <c r="O33">
+        <v>3.8</v>
+      </c>
+      <c r="P33">
         <v>3.7</v>
       </c>
-      <c r="P33">
-        <v>2.57</v>
-      </c>
       <c r="Q33">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="R33">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="S33">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="U33">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="V33">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
+        <v>1.19</v>
+      </c>
+      <c r="Z33">
+        <v>3.78</v>
+      </c>
+      <c r="AA33">
+        <v>1.76</v>
+      </c>
+      <c r="AB33">
+        <v>1.99</v>
+      </c>
+      <c r="AC33">
+        <v>2.83</v>
+      </c>
+      <c r="AD33">
+        <v>1.33</v>
+      </c>
+      <c r="AE33">
         <v>1.09</v>
       </c>
-      <c r="Z33">
-        <v>5.4</v>
-      </c>
-      <c r="AA33">
-        <v>1.47</v>
-      </c>
-      <c r="AB33">
-        <v>2.63</v>
-      </c>
-      <c r="AC33">
-        <v>2.17</v>
-      </c>
-      <c r="AD33">
-        <v>1.63</v>
-      </c>
-      <c r="AE33">
-        <v>1.22</v>
-      </c>
       <c r="AF33">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5857,28 +5857,28 @@
         <v>3.35</v>
       </c>
       <c r="P34">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="R34">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
         <v>2.82</v>
       </c>
       <c r="U34">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
         <v>1.03</v>
@@ -5893,7 +5893,7 @@
         <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AC34">
         <v>3.2</v>
@@ -5902,7 +5902,7 @@
         <v>1.33</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
         <v>1.75</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O42">
         <v>4.05</v>
@@ -7164,25 +7164,25 @@
         <v>1.65</v>
       </c>
       <c r="Q42">
-        <v>4.17</v>
+        <v>4.88</v>
       </c>
       <c r="R42">
         <v>2.34</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="U42">
         <v>2.38</v>
       </c>
       <c r="V42">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
         <v>1.03</v>
@@ -7197,22 +7197,22 @@
         <v>1.63</v>
       </c>
       <c r="AB42">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="AD42">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE42">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
         <v>1.64</v>
       </c>
       <c r="AG42">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7816,28 +7816,28 @@
         <v>4.65</v>
       </c>
       <c r="Q46">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="R46">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
         <v>1.29</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="V46">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
         <v>1.14</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK46">
         <v>2.4</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="O47">
         <v>3.85</v>
@@ -7991,10 +7991,10 @@
         <v>3.75</v>
       </c>
       <c r="U47">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V47">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W47">
         <v>1.13</v>
@@ -8003,31 +8003,31 @@
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z47">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA47">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB47">
         <v>2.45</v>
       </c>
       <c r="AC47">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AD47">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE47">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF47">
         <v>1.5</v>
       </c>
       <c r="AG47">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
         <v>1.62</v>
@@ -8133,31 +8133,31 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q48">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="R48">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T48">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="V48">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W48">
         <v>1.17</v>
@@ -8166,31 +8166,31 @@
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z48">
-        <v>5.2</v>
+        <v>5.54</v>
       </c>
       <c r="AA48">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AB48">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC48">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="AD48">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AE48">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AF48">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG48">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,22 +8305,22 @@
         <v>5.25</v>
       </c>
       <c r="Q49">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="R49">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="S49">
         <v>1.18</v>
       </c>
       <c r="T49">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="U49">
         <v>1.85</v>
       </c>
       <c r="V49">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="W49">
         <v>1.22</v>
@@ -8338,22 +8338,22 @@
         <v>1.33</v>
       </c>
       <c r="AB49">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="AC49">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AD49">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AE49">
         <v>1.43</v>
       </c>
       <c r="AF49">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG49">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O50">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q50">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S50">
         <v>1.2</v>
@@ -8480,10 +8480,10 @@
         <v>4.2</v>
       </c>
       <c r="U50">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="V50">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W50">
         <v>1.2</v>
@@ -8492,25 +8492,25 @@
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z50">
-        <v>6.29</v>
+        <v>6.36</v>
       </c>
       <c r="AA50">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB50">
         <v>2.88</v>
       </c>
       <c r="AC50">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD50">
         <v>1.83</v>
       </c>
       <c r="AE50">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF50">
         <v>1.36</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK50">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8628,7 +8628,7 @@
         <v>3.92</v>
       </c>
       <c r="P51">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
         <v>2.36</v>
@@ -8637,7 +8637,7 @@
         <v>2.42</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T51">
         <v>4.2</v>
@@ -8649,7 +8649,7 @@
         <v>1.75</v>
       </c>
       <c r="W51">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X51">
         <v>0</v>
@@ -8664,16 +8664,16 @@
         <v>1.43</v>
       </c>
       <c r="AB51">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AC51">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AD51">
         <v>1.81</v>
       </c>
       <c r="AE51">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AF51">
         <v>1.36</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8788,10 +8788,10 @@
         <v>1.92</v>
       </c>
       <c r="O52">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P52">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q52">
         <v>2.2</v>
@@ -8803,7 +8803,7 @@
         <v>1.22</v>
       </c>
       <c r="T52">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U52">
         <v>2.1</v>
@@ -8812,34 +8812,34 @@
         <v>1.67</v>
       </c>
       <c r="W52">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z52">
         <v>5.38</v>
       </c>
       <c r="AA52">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB52">
         <v>2.63</v>
       </c>
       <c r="AC52">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="AD52">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE52">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF52">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG52">
         <v>2.5</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="O61">
         <v>3.6</v>
@@ -10267,16 +10267,16 @@
         <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="U61">
         <v>2</v>
       </c>
       <c r="V61">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W61">
         <v>1.2</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z61">
         <v>5.88</v>
@@ -10294,7 +10294,7 @@
         <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="AC61">
         <v>2.11</v>
@@ -10303,13 +10303,13 @@
         <v>1.72</v>
       </c>
       <c r="AE61">
+        <v>1.29</v>
+      </c>
+      <c r="AF61">
         <v>1.33</v>
       </c>
-      <c r="AF61">
-        <v>1.3</v>
-      </c>
       <c r="AG61">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,7 +10424,7 @@
         <v>3.9</v>
       </c>
       <c r="Q62">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="R62">
         <v>2.5</v>
@@ -10442,7 +10442,7 @@
         <v>1.61</v>
       </c>
       <c r="W62">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X62">
         <v>0</v>
@@ -10454,7 +10454,7 @@
         <v>5.07</v>
       </c>
       <c r="AA62">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB62">
         <v>2.4</v>
@@ -10469,7 +10469,7 @@
         <v>1.24</v>
       </c>
       <c r="AF62">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
         <v>2.4</v>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
         <v>1.85</v>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O63">
         <v>3.6</v>
       </c>
       <c r="P63">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="Q63">
-        <v>3.16</v>
+        <v>2.74</v>
       </c>
       <c r="R63">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="S63">
         <v>1.2</v>
@@ -10599,10 +10599,10 @@
         <v>4</v>
       </c>
       <c r="U63">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V63">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W63">
         <v>1.18</v>
@@ -10611,25 +10611,25 @@
         <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z63">
-        <v>5.33</v>
+        <v>5.47</v>
       </c>
       <c r="AA63">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB63">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="AC63">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="AD63">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE63">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF63">
         <v>1.44</v>
@@ -10651,7 +10651,7 @@
         <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10744,22 +10744,22 @@
         <v>1.25</v>
       </c>
       <c r="O64">
-        <v>5.75</v>
+        <v>7.36</v>
       </c>
       <c r="P64">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q64">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R64">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="S64">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="T64">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="U64">
         <v>1.94</v>
@@ -10768,37 +10768,37 @@
         <v>1.85</v>
       </c>
       <c r="W64">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X64">
         <v>0</v>
       </c>
       <c r="Y64">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z64">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA64">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AB64">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="AC64">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AD64">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AE64">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF64">
         <v>1.6</v>
       </c>
       <c r="AG64">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK64">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10907,7 +10907,7 @@
         <v>2</v>
       </c>
       <c r="O65">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P65">
         <v>3</v>
@@ -10922,7 +10922,7 @@
         <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U65">
         <v>2.37</v>
@@ -10946,7 +10946,7 @@
         <v>1.62</v>
       </c>
       <c r="AB65">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC65">
         <v>2.33</v>
@@ -10958,10 +10958,10 @@
         <v>1.22</v>
       </c>
       <c r="AF65">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG65">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11076,10 +11076,10 @@
         <v>3.48</v>
       </c>
       <c r="Q66">
-        <v>2.43</v>
+        <v>2.28</v>
       </c>
       <c r="R66">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="S66">
         <v>1.2</v>
@@ -11103,13 +11103,13 @@
         <v>1.14</v>
       </c>
       <c r="Z66">
-        <v>5.63</v>
+        <v>6</v>
       </c>
       <c r="AA66">
         <v>1.48</v>
       </c>
       <c r="AB66">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AC66">
         <v>2.19</v>
@@ -11121,10 +11121,10 @@
         <v>1.29</v>
       </c>
       <c r="AF66">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG66">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11233,22 +11233,22 @@
         <v>2.1</v>
       </c>
       <c r="O67">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="P67">
         <v>3</v>
       </c>
       <c r="Q67">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="R67">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S67">
         <v>1.25</v>
       </c>
       <c r="T67">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U67">
         <v>2.25</v>
@@ -11257,7 +11257,7 @@
         <v>1.57</v>
       </c>
       <c r="W67">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>5</v>
       </c>
       <c r="AA67">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB67">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC67">
         <v>2.48</v>
@@ -11281,13 +11281,13 @@
         <v>1.55</v>
       </c>
       <c r="AE67">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF67">
         <v>1.47</v>
       </c>
       <c r="AG67">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="O68">
         <v>3.96</v>
@@ -11402,7 +11402,7 @@
         <v>3.19</v>
       </c>
       <c r="Q68">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="R68">
         <v>2.5</v>
@@ -11417,7 +11417,7 @@
         <v>2</v>
       </c>
       <c r="V68">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="W68">
         <v>1.2</v>
@@ -11426,25 +11426,25 @@
         <v>0</v>
       </c>
       <c r="Y68">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z68">
-        <v>6.23</v>
+        <v>6.42</v>
       </c>
       <c r="AA68">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB68">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AC68">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AD68">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AE68">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF68">
         <v>1.4</v>
@@ -11574,7 +11574,7 @@
         <v>1.25</v>
       </c>
       <c r="T69">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="U69">
         <v>2.32</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
         <v>2.25</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>1.53</v>
       </c>
       <c r="O8">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P8">
         <v>5.58</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3252,10 +3252,10 @@
         <v>2.87</v>
       </c>
       <c r="Q18">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
         <v>1.17</v>
@@ -3264,10 +3264,10 @@
         <v>4</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="V18">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="W18">
         <v>1.18</v>
@@ -3288,7 +3288,7 @@
         <v>2.88</v>
       </c>
       <c r="AC18">
-        <v>1.86</v>
+        <v>1.69</v>
       </c>
       <c r="AD18">
         <v>1.81</v>
@@ -3297,10 +3297,10 @@
         <v>1.33</v>
       </c>
       <c r="AF18">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AG18">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>2.5</v>
       </c>
       <c r="Q20">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="R20">
         <v>2.3</v>
@@ -3642,7 +3642,7 @@
         <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>1.7</v>
       </c>
       <c r="O21">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P21">
         <v>3.7</v>
@@ -3934,7 +3934,7 @@
         <v>5.51</v>
       </c>
       <c r="AA22">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AB22">
         <v>2.59</v>
@@ -4266,10 +4266,10 @@
         <v>1.69</v>
       </c>
       <c r="AC24">
-        <v>3.8</v>
+        <v>3.63</v>
       </c>
       <c r="AD24">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
         <v>1.03</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O32">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="Q32">
         <v>2.54</v>
@@ -5564,7 +5564,7 @@
         <v>5.4</v>
       </c>
       <c r="AA32">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB32">
         <v>2.63</v>
@@ -5694,7 +5694,7 @@
         <v>3.8</v>
       </c>
       <c r="P33">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q33">
         <v>2.36</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
         <v>2.89</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O42">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q42">
         <v>4.88</v>
@@ -7490,10 +7490,10 @@
         <v>2.18</v>
       </c>
       <c r="Q44">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="R44">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
         <v>1.3</v>
@@ -7535,10 +7535,10 @@
         <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG44">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7680,7 +7680,7 @@
         <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>7</v>
+        <v>5.35</v>
       </c>
       <c r="AA45">
         <v>1.39</v>
@@ -7701,7 +7701,7 @@
         <v>1.39</v>
       </c>
       <c r="AG45">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>1.13</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
         <v>1.14</v>
@@ -7864,7 +7864,7 @@
         <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O47">
         <v>3.85</v>
@@ -7994,7 +7994,7 @@
         <v>2.2</v>
       </c>
       <c r="V47">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W47">
         <v>1.13</v>
@@ -8003,22 +8003,22 @@
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z47">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="AA47">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB47">
         <v>2.45</v>
       </c>
       <c r="AC47">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AD47">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AE47">
         <v>1.2</v>
@@ -8027,7 +8027,7 @@
         <v>1.5</v>
       </c>
       <c r="AG47">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>2.41</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S48">
         <v>1.2</v>
@@ -8305,7 +8305,7 @@
         <v>5.25</v>
       </c>
       <c r="Q49">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="R49">
         <v>2.75</v>
@@ -8314,7 +8314,7 @@
         <v>1.18</v>
       </c>
       <c r="T49">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="U49">
         <v>1.85</v>
@@ -8344,7 +8344,7 @@
         <v>1.83</v>
       </c>
       <c r="AD49">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AE49">
         <v>1.43</v>
@@ -8353,7 +8353,7 @@
         <v>1.36</v>
       </c>
       <c r="AG49">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8468,10 +8468,10 @@
         <v>3.25</v>
       </c>
       <c r="Q50">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R50">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="S50">
         <v>1.2</v>
@@ -8480,10 +8480,10 @@
         <v>4.2</v>
       </c>
       <c r="U50">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W50">
         <v>1.2</v>
@@ -8495,7 +8495,7 @@
         <v>1.06</v>
       </c>
       <c r="Z50">
-        <v>6.36</v>
+        <v>6.32</v>
       </c>
       <c r="AA50">
         <v>1.4</v>
@@ -8664,22 +8664,22 @@
         <v>1.43</v>
       </c>
       <c r="AB51">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AC51">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AD51">
         <v>1.81</v>
       </c>
       <c r="AE51">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AF51">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG51">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8791,10 +8791,10 @@
         <v>3.9</v>
       </c>
       <c r="P52">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q52">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R52">
         <v>2.59</v>
@@ -8812,7 +8812,7 @@
         <v>1.67</v>
       </c>
       <c r="W52">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
         <v>0</v>
@@ -8830,19 +8830,19 @@
         <v>2.63</v>
       </c>
       <c r="AC52">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="AD52">
         <v>1.63</v>
       </c>
       <c r="AE52">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF52">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>2.9</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S61">
         <v>1.2</v>
@@ -10276,7 +10276,7 @@
         <v>2</v>
       </c>
       <c r="V61">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W61">
         <v>1.2</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z61">
         <v>5.88</v>
@@ -10294,7 +10294,7 @@
         <v>1.44</v>
       </c>
       <c r="AB61">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="AC61">
         <v>2.11</v>
@@ -10309,7 +10309,7 @@
         <v>1.33</v>
       </c>
       <c r="AG61">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O62">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="P62">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q62">
         <v>2.26</v>
@@ -10439,7 +10439,7 @@
         <v>2.25</v>
       </c>
       <c r="V62">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W62">
         <v>1.13</v>
@@ -10451,7 +10451,7 @@
         <v>1.17</v>
       </c>
       <c r="Z62">
-        <v>5.07</v>
+        <v>5.04</v>
       </c>
       <c r="AA62">
         <v>1.5</v>
@@ -10460,10 +10460,10 @@
         <v>2.4</v>
       </c>
       <c r="AC62">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="AD62">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE62">
         <v>1.24</v>
@@ -10472,7 +10472,7 @@
         <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10599,7 +10599,7 @@
         <v>4</v>
       </c>
       <c r="U63">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V63">
         <v>1.65</v>
@@ -10623,13 +10623,13 @@
         <v>2.63</v>
       </c>
       <c r="AC63">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AD63">
         <v>1.66</v>
       </c>
       <c r="AE63">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AF63">
         <v>1.44</v>
@@ -10747,7 +10747,7 @@
         <v>7.36</v>
       </c>
       <c r="P64">
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="Q64">
         <v>1.55</v>
@@ -10765,7 +10765,7 @@
         <v>1.94</v>
       </c>
       <c r="V64">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W64">
         <v>1.25</v>
@@ -10774,10 +10774,10 @@
         <v>0</v>
       </c>
       <c r="Y64">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z64">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="AA64">
         <v>1.29</v>
@@ -10786,19 +10786,19 @@
         <v>3.5</v>
       </c>
       <c r="AC64">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AD64">
         <v>2.07</v>
       </c>
       <c r="AE64">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF64">
         <v>1.6</v>
       </c>
       <c r="AG64">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         <v>2.38</v>
       </c>
       <c r="AC65">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD65">
         <v>1.54</v>
@@ -10958,10 +10958,10 @@
         <v>1.22</v>
       </c>
       <c r="AF65">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG65">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>2.28</v>
       </c>
       <c r="R66">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S66">
         <v>1.2</v>
@@ -11094,7 +11094,7 @@
         <v>1.7</v>
       </c>
       <c r="W66">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X66">
         <v>0</v>
@@ -11103,13 +11103,13 @@
         <v>1.14</v>
       </c>
       <c r="Z66">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AA66">
         <v>1.48</v>
       </c>
       <c r="AB66">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AC66">
         <v>2.19</v>
@@ -11118,13 +11118,13 @@
         <v>1.69</v>
       </c>
       <c r="AE66">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF66">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG66">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11239,10 +11239,10 @@
         <v>3</v>
       </c>
       <c r="Q67">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="R67">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S67">
         <v>1.25</v>
@@ -11263,7 +11263,7 @@
         <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z67">
         <v>5</v>
@@ -11281,13 +11281,13 @@
         <v>1.55</v>
       </c>
       <c r="AE67">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AF67">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AG67">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O68">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="P68">
         <v>3.19</v>
@@ -11601,10 +11601,10 @@
         <v>2.43</v>
       </c>
       <c r="AC69">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AD69">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE69">
         <v>1.17</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="O8">
         <v>4.2</v>
@@ -1782,28 +1782,28 @@
         <v>4</v>
       </c>
       <c r="P9">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
         <v>3.17</v>
       </c>
       <c r="U9">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V9">
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
         <v>1.03</v>
@@ -1830,10 +1830,10 @@
         <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2606,13 +2606,13 @@
         <v>2.5</v>
       </c>
       <c r="S14">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="T14">
         <v>4</v>
       </c>
       <c r="U14">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="V14">
         <v>1.7</v>
@@ -2630,16 +2630,16 @@
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB14">
         <v>2.61</v>
       </c>
       <c r="AC14">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AD14">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE14">
         <v>1.3</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
         <v>1.23</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>10.5</v>
+        <v>8.75</v>
       </c>
       <c r="O15">
-        <v>6.55</v>
+        <v>6.3</v>
       </c>
       <c r="P15">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Q15">
-        <v>6.47</v>
+        <v>6.28</v>
       </c>
       <c r="R15">
         <v>2.88</v>
@@ -2772,22 +2772,22 @@
         <v>1.2</v>
       </c>
       <c r="T15">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U15">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V15">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z15">
         <v>7</v>
@@ -2796,16 +2796,16 @@
         <v>1.36</v>
       </c>
       <c r="AB15">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="AC15">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AD15">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AE15">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF15">
         <v>1.67</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK15">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>1.74</v>
       </c>
       <c r="V18">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W18">
         <v>1.18</v>
@@ -3297,7 +3297,7 @@
         <v>1.33</v>
       </c>
       <c r="AF18">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AG18">
         <v>2.5</v>
@@ -3415,10 +3415,10 @@
         <v>2.15</v>
       </c>
       <c r="Q19">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="R19">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="S19">
         <v>1.26</v>
@@ -3427,7 +3427,7 @@
         <v>3.4</v>
       </c>
       <c r="U19">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="V19">
         <v>1.51</v>
@@ -3442,7 +3442,7 @@
         <v>1.16</v>
       </c>
       <c r="Z19">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA19">
         <v>1.63</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="O20">
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q20">
-        <v>3.01</v>
+        <v>2.83</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
         <v>1.25</v>
@@ -3602,22 +3602,22 @@
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z20">
         <v>4.3</v>
       </c>
       <c r="AA20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC20">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AD20">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE20">
         <v>1.14</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>3.9</v>
       </c>
       <c r="P21">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
         <v>2.14</v>
@@ -3750,10 +3750,10 @@
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="V21">
         <v>1.68</v>
@@ -4230,7 +4230,7 @@
         <v>2.25</v>
       </c>
       <c r="Q24">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="R24">
         <v>2.02</v>
@@ -4254,10 +4254,10 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z24">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AA24">
         <v>2.01</v>
@@ -4275,7 +4275,7 @@
         <v>1.03</v>
       </c>
       <c r="AF24">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG24">
         <v>1.95</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="O25">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="P25">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="Q25">
         <v>1.77</v>
@@ -4399,16 +4399,16 @@
         <v>2.89</v>
       </c>
       <c r="S25">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T25">
         <v>4</v>
       </c>
       <c r="U25">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="V25">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W25">
         <v>1.17</v>
@@ -4429,19 +4429,19 @@
         <v>2.7</v>
       </c>
       <c r="AC25">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AD25">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE25">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF25">
         <v>1.59</v>
       </c>
       <c r="AG25">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="O26">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="P26">
-        <v>4.7</v>
+        <v>6.9</v>
       </c>
       <c r="Q26">
         <v>1.62</v>
@@ -4571,10 +4571,10 @@
         <v>1.69</v>
       </c>
       <c r="V26">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="W26">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X26">
         <v>1</v>
@@ -4595,7 +4595,7 @@
         <v>1.6</v>
       </c>
       <c r="AD26">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AE26">
         <v>1.51</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK26">
         <v>3.6</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="O27">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="Q27">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="R27">
         <v>2.53</v>
@@ -4731,13 +4731,13 @@
         <v>4.8</v>
       </c>
       <c r="U27">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V27">
         <v>1.93</v>
       </c>
       <c r="W27">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X27">
         <v>1.01</v>
@@ -4758,16 +4758,16 @@
         <v>1.74</v>
       </c>
       <c r="AD27">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE27">
         <v>1.41</v>
       </c>
       <c r="AF27">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AG27">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,19 +4873,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="O28">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="P28">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Q28">
         <v>1.77</v>
       </c>
       <c r="R28">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="S28">
         <v>1.17</v>
@@ -4894,10 +4894,10 @@
         <v>4.6</v>
       </c>
       <c r="U28">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V28">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="W28">
         <v>1.25</v>
@@ -4912,22 +4912,22 @@
         <v>7.3</v>
       </c>
       <c r="AA28">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB28">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AC28">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AD28">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AE28">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF28">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG28">
         <v>2.7</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="Q29">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R29">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="S29">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T29">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="U29">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V29">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="W29">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z29">
-        <v>6.1</v>
+        <v>5.95</v>
       </c>
       <c r="AA29">
+        <v>1.34</v>
+      </c>
+      <c r="AB29">
+        <v>3.1</v>
+      </c>
+      <c r="AC29">
+        <v>1.94</v>
+      </c>
+      <c r="AD29">
+        <v>1.79</v>
+      </c>
+      <c r="AE29">
         <v>1.33</v>
       </c>
-      <c r="AB29">
-        <v>3.25</v>
-      </c>
-      <c r="AC29">
-        <v>1.92</v>
-      </c>
-      <c r="AD29">
-        <v>1.81</v>
-      </c>
-      <c r="AE29">
-        <v>1.3</v>
-      </c>
       <c r="AF29">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG29">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK29">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="O30">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="P30">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q30">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R30">
         <v>2.93</v>
@@ -5229,7 +5229,7 @@
         <v>1.3</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y30">
         <v>1.01</v>
@@ -5247,16 +5247,16 @@
         <v>1.57</v>
       </c>
       <c r="AD30">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AE30">
         <v>1.53</v>
       </c>
       <c r="AF30">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AG30">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P31">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="Q31">
         <v>3.35</v>
@@ -5407,7 +5407,7 @@
         <v>3.2</v>
       </c>
       <c r="AC31">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AD31">
         <v>1.98</v>
@@ -5419,7 +5419,7 @@
         <v>1.28</v>
       </c>
       <c r="AG31">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.73</v>
       </c>
       <c r="AK31">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="O32">
         <v>3.8</v>
       </c>
       <c r="P32">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="U32">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
+        <v>1.19</v>
+      </c>
+      <c r="Z32">
+        <v>3.78</v>
+      </c>
+      <c r="AA32">
+        <v>1.76</v>
+      </c>
+      <c r="AB32">
+        <v>1.99</v>
+      </c>
+      <c r="AC32">
+        <v>2.83</v>
+      </c>
+      <c r="AD32">
+        <v>1.33</v>
+      </c>
+      <c r="AE32">
         <v>1.09</v>
       </c>
-      <c r="Z32">
-        <v>5.4</v>
-      </c>
-      <c r="AA32">
-        <v>1.5</v>
-      </c>
-      <c r="AB32">
-        <v>2.63</v>
-      </c>
-      <c r="AC32">
-        <v>2.17</v>
-      </c>
-      <c r="AD32">
-        <v>1.64</v>
-      </c>
-      <c r="AE32">
-        <v>1.22</v>
-      </c>
       <c r="AF32">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.74</v>
+        <v>2.4</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>4.2</v>
+        <v>2.57</v>
       </c>
       <c r="Q33">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="R33">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T33">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="U33">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="V33">
+        <v>1.64</v>
+      </c>
+      <c r="W33">
+        <v>1.13</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.09</v>
+      </c>
+      <c r="Z33">
+        <v>5.4</v>
+      </c>
+      <c r="AA33">
         <v>1.47</v>
       </c>
-      <c r="W33">
-        <v>1.08</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
-      <c r="Y33">
-        <v>1.19</v>
-      </c>
-      <c r="Z33">
-        <v>3.78</v>
-      </c>
-      <c r="AA33">
-        <v>1.76</v>
-      </c>
       <c r="AB33">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="AC33">
-        <v>2.83</v>
+        <v>2.17</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AK33">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O34">
         <v>3.4</v>
       </c>
       <c r="P34">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="Q34">
-        <v>2.89</v>
+        <v>2.57</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
         <v>1.36</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P35">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="Q35">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="S35">
+        <v>1.2</v>
+      </c>
+      <c r="T35">
+        <v>4.2</v>
+      </c>
+      <c r="U35">
+        <v>2</v>
+      </c>
+      <c r="V35">
+        <v>1.74</v>
+      </c>
+      <c r="W35">
+        <v>1.18</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.11</v>
+      </c>
+      <c r="Z35">
+        <v>6</v>
+      </c>
+      <c r="AA35">
+        <v>1.44</v>
+      </c>
+      <c r="AB35">
+        <v>2.8</v>
+      </c>
+      <c r="AC35">
+        <v>2.11</v>
+      </c>
+      <c r="AD35">
+        <v>1.73</v>
+      </c>
+      <c r="AE35">
+        <v>1.29</v>
+      </c>
+      <c r="AF35">
+        <v>1.4</v>
+      </c>
+      <c r="AG35">
+        <v>2.89</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.33</v>
       </c>
-      <c r="T35">
-        <v>3.22</v>
-      </c>
-      <c r="U35">
-        <v>2.4</v>
-      </c>
-      <c r="V35">
-        <v>1.51</v>
-      </c>
-      <c r="W35">
-        <v>1.1</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.18</v>
-      </c>
-      <c r="Z35">
-        <v>4.5</v>
-      </c>
-      <c r="AA35">
-        <v>1.71</v>
-      </c>
-      <c r="AB35">
-        <v>2.17</v>
-      </c>
-      <c r="AC35">
-        <v>2.68</v>
-      </c>
-      <c r="AD35">
-        <v>1.47</v>
-      </c>
-      <c r="AE35">
-        <v>1.14</v>
-      </c>
-      <c r="AF35">
-        <v>1.6</v>
-      </c>
-      <c r="AG35">
-        <v>2.3</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.26</v>
-      </c>
       <c r="AK35">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O36">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="Q36">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="R36">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
+        <v>1.29</v>
+      </c>
+      <c r="T36">
+        <v>3.3</v>
+      </c>
+      <c r="U36">
+        <v>2.4</v>
+      </c>
+      <c r="V36">
+        <v>1.5</v>
+      </c>
+      <c r="W36">
+        <v>1.1</v>
+      </c>
+      <c r="X36">
+        <v>1.01</v>
+      </c>
+      <c r="Y36">
         <v>1.2</v>
       </c>
-      <c r="T36">
+      <c r="Z36">
         <v>4.2</v>
       </c>
-      <c r="U36">
-        <v>2</v>
-      </c>
-      <c r="V36">
-        <v>1.73</v>
-      </c>
-      <c r="W36">
-        <v>1.18</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.11</v>
-      </c>
-      <c r="Z36">
-        <v>6</v>
-      </c>
       <c r="AA36">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AB36">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="AC36">
-        <v>2.11</v>
+        <v>2.68</v>
       </c>
       <c r="AD36">
+        <v>1.47</v>
+      </c>
+      <c r="AE36">
+        <v>1.14</v>
+      </c>
+      <c r="AF36">
+        <v>1.6</v>
+      </c>
+      <c r="AG36">
+        <v>2.3</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.26</v>
+      </c>
+      <c r="AK36">
         <v>1.75</v>
-      </c>
-      <c r="AE36">
-        <v>1.29</v>
-      </c>
-      <c r="AF36">
-        <v>1.4</v>
-      </c>
-      <c r="AG36">
-        <v>2.89</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.33</v>
-      </c>
-      <c r="AK36">
-        <v>1.72</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
         <v>4</v>
@@ -6352,7 +6352,7 @@
         <v>3.26</v>
       </c>
       <c r="R37">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
         <v>1.2</v>
@@ -6361,7 +6361,7 @@
         <v>4.2</v>
       </c>
       <c r="U37">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="V37">
         <v>1.82</v>
@@ -6385,10 +6385,10 @@
         <v>3</v>
       </c>
       <c r="AC37">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD37">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AE37">
         <v>1.33</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
         <v>1.3</v>
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="O38">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P38">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="Q38">
         <v>2.24</v>
@@ -6530,10 +6530,10 @@
         <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
         <v>1.18</v>
@@ -6542,7 +6542,7 @@
         <v>4.5</v>
       </c>
       <c r="AA38">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB38">
         <v>2.3</v>
@@ -6557,7 +6557,7 @@
         <v>1.18</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
         <v>2.15</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
         <v>2.27</v>
@@ -6675,7 +6675,7 @@
         <v>1.87</v>
       </c>
       <c r="Q39">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="R39">
         <v>2.47</v>
@@ -6705,10 +6705,10 @@
         <v>7</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB39">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="AC39">
         <v>1.95</v>
@@ -6717,7 +6717,7 @@
         <v>1.8</v>
       </c>
       <c r="AE39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF39">
         <v>1.4</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
+        <v>1.83</v>
+      </c>
+      <c r="AK39">
         <v>1.25</v>
-      </c>
-      <c r="AK39">
-        <v>1.22</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="O40">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="P40">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Q40">
-        <v>7.84</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="R40">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="S40">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T40">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U40">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V40">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="W40">
         <v>1.2</v>
@@ -6868,10 +6868,10 @@
         <v>7.5</v>
       </c>
       <c r="AA40">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AB40">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AC40">
         <v>1.87</v>
@@ -6902,7 +6902,7 @@
         <v>3.31</v>
       </c>
       <c r="AK40">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="O41">
         <v>3.44</v>
@@ -7004,16 +7004,16 @@
         <v>3.02</v>
       </c>
       <c r="R41">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U41">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="V41">
         <v>1.45</v>
@@ -7031,10 +7031,10 @@
         <v>3.7</v>
       </c>
       <c r="AA41">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AB41">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC41">
         <v>2.91</v>
@@ -7043,7 +7043,7 @@
         <v>1.33</v>
       </c>
       <c r="AE41">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
         <v>1.67</v>
@@ -7158,10 +7158,10 @@
         <v>4.6</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P42">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q42">
         <v>4.88</v>
@@ -7179,10 +7179,10 @@
         <v>2.38</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
         <v>1.03</v>
@@ -7653,10 +7653,10 @@
         <v>1.95</v>
       </c>
       <c r="Q45">
-        <v>3.52</v>
+        <v>3.56</v>
       </c>
       <c r="R45">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S45">
         <v>1.22</v>
@@ -7668,7 +7668,7 @@
         <v>2.1</v>
       </c>
       <c r="V45">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W45">
         <v>1.18</v>
@@ -7680,28 +7680,28 @@
         <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="AA45">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB45">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AC45">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AD45">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE45">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF45">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG45">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK45">
         <v>1.3</v>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="O47">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="P47">
         <v>2.75</v>
@@ -8012,7 +8012,7 @@
         <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC47">
         <v>2.36</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O48">
         <v>3.75</v>
@@ -8302,7 +8302,7 @@
         <v>4.5</v>
       </c>
       <c r="P49">
-        <v>5.25</v>
+        <v>5.32</v>
       </c>
       <c r="Q49">
         <v>1.92</v>
@@ -8335,7 +8335,7 @@
         <v>8</v>
       </c>
       <c r="AA49">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB49">
         <v>3.38</v>
@@ -8353,7 +8353,7 @@
         <v>1.36</v>
       </c>
       <c r="AG49">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>3.92</v>
       </c>
       <c r="P51">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Q51">
         <v>2.36</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="O52">
         <v>3.9</v>
       </c>
       <c r="P52">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q52">
         <v>2.38</v>
@@ -8800,19 +8800,19 @@
         <v>2.59</v>
       </c>
       <c r="S52">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T52">
         <v>4</v>
       </c>
       <c r="U52">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V52">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W52">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X52">
         <v>0</v>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O61">
         <v>3.6</v>
@@ -10418,7 +10418,7 @@
         <v>1.91</v>
       </c>
       <c r="O62">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
         <v>3.65</v>
@@ -10466,7 +10466,7 @@
         <v>1.59</v>
       </c>
       <c r="AE62">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AF62">
         <v>1.44</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
+        <v>2.37</v>
+      </c>
+      <c r="O63">
+        <v>3.5</v>
+      </c>
+      <c r="P63">
         <v>2.45</v>
-      </c>
-      <c r="O63">
-        <v>3.6</v>
-      </c>
-      <c r="P63">
-        <v>2.43</v>
       </c>
       <c r="Q63">
         <v>2.74</v>
@@ -10614,7 +10614,7 @@
         <v>1.15</v>
       </c>
       <c r="Z63">
-        <v>5.47</v>
+        <v>4.95</v>
       </c>
       <c r="AA63">
         <v>1.47</v>
@@ -10626,10 +10626,10 @@
         <v>2.13</v>
       </c>
       <c r="AD63">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE63">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AF63">
         <v>1.44</v>
@@ -10651,7 +10651,7 @@
         <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10765,7 +10765,7 @@
         <v>1.94</v>
       </c>
       <c r="V64">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="W64">
         <v>1.25</v>
@@ -10795,7 +10795,7 @@
         <v>1.41</v>
       </c>
       <c r="AF64">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG64">
         <v>2.2</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="O65">
         <v>3.7</v>
@@ -10946,7 +10946,7 @@
         <v>1.62</v>
       </c>
       <c r="AB65">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC65">
         <v>2.34</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O67">
         <v>3.68</v>
@@ -11257,7 +11257,7 @@
         <v>1.57</v>
       </c>
       <c r="W67">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X67">
         <v>0</v>
@@ -11266,7 +11266,7 @@
         <v>1.18</v>
       </c>
       <c r="Z67">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA67">
         <v>1.53</v>
@@ -11414,7 +11414,7 @@
         <v>4.5</v>
       </c>
       <c r="U68">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V68">
         <v>1.8</v>
@@ -11583,7 +11583,7 @@
         <v>1.59</v>
       </c>
       <c r="W69">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X69">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -816,7 +816,7 @@
         <v>1.37</v>
       </c>
       <c r="T3">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="U3">
         <v>2.75</v>
@@ -828,7 +828,7 @@
         <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
         <v>1.27</v>
@@ -846,7 +846,7 @@
         <v>3.42</v>
       </c>
       <c r="AD3">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE3">
         <v>1.04</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q4">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
         <v>1.3</v>
@@ -982,10 +982,10 @@
         <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="V4">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W4">
         <v>1.12</v>
@@ -997,28 +997,28 @@
         <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>4.06</v>
+        <v>3.97</v>
       </c>
       <c r="AA4">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AC4">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="AD4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG4">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
+        <v>1.83</v>
+      </c>
+      <c r="O6">
+        <v>3.7</v>
+      </c>
+      <c r="P6">
+        <v>3.3</v>
+      </c>
+      <c r="Q6">
+        <v>2.4</v>
+      </c>
+      <c r="R6">
+        <v>2.45</v>
+      </c>
+      <c r="S6">
+        <v>1.19</v>
+      </c>
+      <c r="T6">
+        <v>3.85</v>
+      </c>
+      <c r="U6">
+        <v>2.06</v>
+      </c>
+      <c r="V6">
+        <v>1.69</v>
+      </c>
+      <c r="W6">
+        <v>1.15</v>
+      </c>
+      <c r="X6">
+        <v>1.02</v>
+      </c>
+      <c r="Y6">
+        <v>1.08</v>
+      </c>
+      <c r="Z6">
+        <v>5.45</v>
+      </c>
+      <c r="AA6">
+        <v>1.39</v>
+      </c>
+      <c r="AB6">
+        <v>2.59</v>
+      </c>
+      <c r="AC6">
+        <v>2.09</v>
+      </c>
+      <c r="AD6">
+        <v>1.68</v>
+      </c>
+      <c r="AE6">
+        <v>1.24</v>
+      </c>
+      <c r="AF6">
+        <v>1.4</v>
+      </c>
+      <c r="AG6">
+        <v>2.73</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.21</v>
+      </c>
+      <c r="AK6">
         <v>1.79</v>
-      </c>
-      <c r="O6">
-        <v>3.75</v>
-      </c>
-      <c r="P6">
-        <v>3.55</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>0</v>
-      </c>
-      <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1616,10 +1616,10 @@
         <v>1.49</v>
       </c>
       <c r="O8">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P8">
-        <v>5.58</v>
+        <v>4.99</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1779,10 +1779,10 @@
         <v>1.4</v>
       </c>
       <c r="O9">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P9">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="Q9">
         <v>1.87</v>
@@ -1791,7 +1791,7 @@
         <v>2.38</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
         <v>3.17</v>
@@ -1809,16 +1809,16 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.69</v>
+        <v>4.1</v>
       </c>
       <c r="AA9">
         <v>1.74</v>
       </c>
       <c r="AB9">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AC9">
         <v>2.88</v>
@@ -1833,7 +1833,7 @@
         <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
         <v>2.85</v>
       </c>
       <c r="Q10">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
         <v>1.3</v>
@@ -1966,7 +1966,7 @@
         <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
         <v>1</v>
@@ -1978,10 +1978,10 @@
         <v>3.42</v>
       </c>
       <c r="AA10">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC10">
         <v>2.88</v>
@@ -2012,7 +2012,7 @@
         <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.22</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="O13">
         <v>3.9</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q13">
         <v>2.16</v>
@@ -2449,10 +2449,10 @@
         <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W13">
         <v>1.15</v>
@@ -2461,10 +2461,10 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z13">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA13">
         <v>1.5</v>
@@ -2473,10 +2473,10 @@
         <v>2.63</v>
       </c>
       <c r="AC13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AD13">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE13">
         <v>1.25</v>
@@ -3246,28 +3246,28 @@
         <v>2.1</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="Q18">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S18">
         <v>1.17</v>
       </c>
       <c r="T18">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="U18">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="V18">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W18">
         <v>1.18</v>
@@ -3276,31 +3276,31 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>6.05</v>
+        <v>5.85</v>
       </c>
       <c r="AA18">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC18">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="AD18">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AE18">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG18">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,31 +3406,31 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O19">
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
         <v>1.26</v>
       </c>
       <c r="T19">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U19">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="W19">
         <v>1.1</v>
@@ -3439,16 +3439,16 @@
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="AA19">
         <v>1.63</v>
       </c>
       <c r="AB19">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AC19">
         <v>2.52</v>
@@ -3460,10 +3460,10 @@
         <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.51</v>
+        <v>1.09</v>
       </c>
       <c r="AK19">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>2.62</v>
       </c>
       <c r="Q20">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="R20">
         <v>2.25</v>
@@ -3614,7 +3614,7 @@
         <v>2.14</v>
       </c>
       <c r="AC20">
-        <v>2.49</v>
+        <v>2.15</v>
       </c>
       <c r="AD20">
         <v>1.45</v>
@@ -3626,7 +3626,7 @@
         <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3738,22 +3738,22 @@
         <v>3.9</v>
       </c>
       <c r="P21">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="R21">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="U21">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="V21">
         <v>1.68</v>
@@ -3765,25 +3765,25 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>5.95</v>
+        <v>5.59</v>
       </c>
       <c r="AA21">
         <v>1.36</v>
       </c>
       <c r="AB21">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AC21">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AD21">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AE21">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
         <v>1.4</v>
@@ -3901,7 +3901,7 @@
         <v>3.55</v>
       </c>
       <c r="P22">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="Q22">
         <v>2.46</v>
@@ -3931,7 +3931,7 @@
         <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>5.51</v>
+        <v>3.6</v>
       </c>
       <c r="AA22">
         <v>1.47</v>
@@ -3946,13 +3946,13 @@
         <v>1.67</v>
       </c>
       <c r="AE22">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
         <v>1.38</v>
       </c>
       <c r="AG22">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4230,10 +4230,10 @@
         <v>2.25</v>
       </c>
       <c r="Q24">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="R24">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S24">
         <v>1.42</v>
@@ -4245,7 +4245,7 @@
         <v>2.81</v>
       </c>
       <c r="V24">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -4254,28 +4254,28 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z24">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA24">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AB24">
         <v>1.69</v>
       </c>
       <c r="AC24">
-        <v>3.63</v>
+        <v>3.8</v>
       </c>
       <c r="AD24">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE24">
         <v>1.03</v>
       </c>
       <c r="AF24">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG24">
         <v>1.95</v>
@@ -4387,7 +4387,7 @@
         <v>1.35</v>
       </c>
       <c r="O25">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="P25">
         <v>5.9</v>
@@ -4396,7 +4396,7 @@
         <v>1.77</v>
       </c>
       <c r="R25">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="S25">
         <v>1.2</v>
@@ -4405,13 +4405,13 @@
         <v>4</v>
       </c>
       <c r="U25">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V25">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W25">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4429,19 +4429,19 @@
         <v>2.7</v>
       </c>
       <c r="AC25">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AD25">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE25">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF25">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG25">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="O26">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="P26">
         <v>6.9</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK26">
         <v>3.6</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,28 +4710,28 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.78</v>
+        <v>1.27</v>
       </c>
       <c r="O27">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="P27">
-        <v>2.04</v>
+        <v>5.3</v>
       </c>
       <c r="Q27">
-        <v>3.32</v>
+        <v>1.77</v>
       </c>
       <c r="R27">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="S27">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="T27">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U27">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="V27">
         <v>1.93</v>
@@ -4743,31 +4743,31 @@
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z27">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="AA27">
         <v>1.3</v>
       </c>
       <c r="AB27">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="AC27">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AD27">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AE27">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF27">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AG27">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK27">
-        <v>1.32</v>
+        <v>2.75</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="O28">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P28">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q28">
-        <v>1.77</v>
+        <v>2.54</v>
       </c>
       <c r="R28">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="S28">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T28">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="U28">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="V28">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="W28">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z28">
-        <v>7.3</v>
+        <v>5.95</v>
       </c>
       <c r="AA28">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AB28">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="AC28">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AD28">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="AE28">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF28">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG28">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AK28">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P29">
         <v>2.75</v>
       </c>
       <c r="Q29">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.44</v>
+        <v>2.89</v>
       </c>
       <c r="S29">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="T29">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="V29">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="W29">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="X29">
+        <v>1</v>
+      </c>
+      <c r="Y29">
         <v>1.01</v>
       </c>
-      <c r="Y29">
-        <v>1.07</v>
-      </c>
       <c r="Z29">
-        <v>5.95</v>
+        <v>8.5</v>
       </c>
       <c r="AA29">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AB29">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="AC29">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AD29">
-        <v>1.79</v>
+        <v>2.21</v>
       </c>
       <c r="AE29">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AF29">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AG29">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,61 +5199,61 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.84</v>
+        <v>2.78</v>
       </c>
       <c r="O30">
-        <v>3.95</v>
+        <v>3.77</v>
       </c>
       <c r="P30">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q30">
-        <v>2.18</v>
+        <v>3.32</v>
       </c>
       <c r="R30">
-        <v>2.93</v>
+        <v>2.53</v>
       </c>
       <c r="S30">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="T30">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="U30">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="V30">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="W30">
+        <v>1.25</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.02</v>
+      </c>
+      <c r="Z30">
+        <v>7.8</v>
+      </c>
+      <c r="AA30">
         <v>1.3</v>
       </c>
-      <c r="X30">
-        <v>1</v>
-      </c>
-      <c r="Y30">
-        <v>1.01</v>
-      </c>
-      <c r="Z30">
-        <v>8.5</v>
-      </c>
-      <c r="AA30">
-        <v>1.2</v>
-      </c>
       <c r="AB30">
-        <v>3.82</v>
+        <v>3.41</v>
       </c>
       <c r="AC30">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AD30">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AE30">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AF30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG30">
         <v>3.5</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.91</v>
+        <v>1.32</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>2.57</v>
       </c>
       <c r="Q32">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="R32">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="U32">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="V32">
+        <v>1.64</v>
+      </c>
+      <c r="W32">
+        <v>1.13</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.09</v>
+      </c>
+      <c r="Z32">
+        <v>5.4</v>
+      </c>
+      <c r="AA32">
         <v>1.47</v>
       </c>
-      <c r="W32">
-        <v>1.08</v>
-      </c>
-      <c r="X32">
-        <v>1.03</v>
-      </c>
-      <c r="Y32">
-        <v>1.19</v>
-      </c>
-      <c r="Z32">
-        <v>3.78</v>
-      </c>
-      <c r="AA32">
-        <v>1.76</v>
-      </c>
       <c r="AB32">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="AC32">
-        <v>2.83</v>
+        <v>2.17</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AK32">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>2.57</v>
+        <v>4.2</v>
       </c>
       <c r="Q33">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="R33">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="S33">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T33">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="U33">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="V33">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
+        <v>1.19</v>
+      </c>
+      <c r="Z33">
+        <v>3.78</v>
+      </c>
+      <c r="AA33">
+        <v>1.76</v>
+      </c>
+      <c r="AB33">
+        <v>1.99</v>
+      </c>
+      <c r="AC33">
+        <v>2.83</v>
+      </c>
+      <c r="AD33">
+        <v>1.33</v>
+      </c>
+      <c r="AE33">
         <v>1.09</v>
       </c>
-      <c r="Z33">
-        <v>5.4</v>
-      </c>
-      <c r="AA33">
-        <v>1.47</v>
-      </c>
-      <c r="AB33">
-        <v>2.63</v>
-      </c>
-      <c r="AC33">
-        <v>2.17</v>
-      </c>
-      <c r="AD33">
-        <v>1.64</v>
-      </c>
-      <c r="AE33">
-        <v>1.22</v>
-      </c>
       <c r="AF33">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O34">
         <v>3.4</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="O35">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="P35">
-        <v>2.87</v>
+        <v>2.55</v>
       </c>
       <c r="Q35">
-        <v>2.52</v>
+        <v>3.02</v>
       </c>
       <c r="R35">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="U35">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="V35">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="W35">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
+        <v>1.25</v>
+      </c>
+      <c r="Z35">
+        <v>3.7</v>
+      </c>
+      <c r="AA35">
+        <v>1.83</v>
+      </c>
+      <c r="AB35">
+        <v>1.91</v>
+      </c>
+      <c r="AC35">
+        <v>2.91</v>
+      </c>
+      <c r="AD35">
+        <v>1.33</v>
+      </c>
+      <c r="AE35">
         <v>1.11</v>
       </c>
-      <c r="Z35">
-        <v>6</v>
-      </c>
-      <c r="AA35">
-        <v>1.44</v>
-      </c>
-      <c r="AB35">
-        <v>2.8</v>
-      </c>
-      <c r="AC35">
-        <v>2.11</v>
-      </c>
-      <c r="AD35">
-        <v>1.73</v>
-      </c>
-      <c r="AE35">
-        <v>1.29</v>
-      </c>
       <c r="AF35">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.89</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="O37">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>1.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q37">
-        <v>3.26</v>
+        <v>2.52</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S37">
         <v>1.2</v>
@@ -6361,59 +6361,59 @@
         <v>4.2</v>
       </c>
       <c r="U37">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="W37">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA37">
+        <v>1.44</v>
+      </c>
+      <c r="AB37">
+        <v>2.8</v>
+      </c>
+      <c r="AC37">
+        <v>2.11</v>
+      </c>
+      <c r="AD37">
+        <v>1.73</v>
+      </c>
+      <c r="AE37">
+        <v>1.29</v>
+      </c>
+      <c r="AF37">
         <v>1.4</v>
       </c>
-      <c r="AB37">
-        <v>3</v>
-      </c>
-      <c r="AC37">
-        <v>1.91</v>
-      </c>
-      <c r="AD37">
-        <v>1.83</v>
-      </c>
-      <c r="AE37">
+      <c r="AG37">
+        <v>2.89</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.33</v>
       </c>
-      <c r="AF37">
-        <v>1.36</v>
-      </c>
-      <c r="AG37">
-        <v>3</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.2</v>
-      </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.51</v>
+        <v>3.1</v>
       </c>
       <c r="O38">
+        <v>4</v>
+      </c>
+      <c r="P38">
+        <v>1.95</v>
+      </c>
+      <c r="Q38">
+        <v>3.26</v>
+      </c>
+      <c r="R38">
+        <v>2.5</v>
+      </c>
+      <c r="S38">
+        <v>1.2</v>
+      </c>
+      <c r="T38">
         <v>4.2</v>
       </c>
-      <c r="P38">
-        <v>4.25</v>
-      </c>
-      <c r="Q38">
-        <v>2.24</v>
-      </c>
-      <c r="R38">
-        <v>2.19</v>
-      </c>
-      <c r="S38">
-        <v>1.3</v>
-      </c>
-      <c r="T38">
-        <v>3.05</v>
-      </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AA38">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AC38">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AD38">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE38">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>2.27</v>
+        <v>1.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.74</v>
+        <v>1.51</v>
       </c>
       <c r="O39">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P39">
-        <v>1.87</v>
+        <v>4.25</v>
       </c>
       <c r="Q39">
-        <v>3.88</v>
+        <v>2.24</v>
       </c>
       <c r="R39">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
       <c r="S39">
+        <v>1.3</v>
+      </c>
+      <c r="T39">
+        <v>3.05</v>
+      </c>
+      <c r="U39">
+        <v>2.4</v>
+      </c>
+      <c r="V39">
+        <v>1.5</v>
+      </c>
+      <c r="W39">
+        <v>1.1</v>
+      </c>
+      <c r="X39">
+        <v>1.03</v>
+      </c>
+      <c r="Y39">
+        <v>1.18</v>
+      </c>
+      <c r="Z39">
+        <v>4.5</v>
+      </c>
+      <c r="AA39">
+        <v>1.59</v>
+      </c>
+      <c r="AB39">
+        <v>2.3</v>
+      </c>
+      <c r="AC39">
+        <v>2.5</v>
+      </c>
+      <c r="AD39">
+        <v>1.5</v>
+      </c>
+      <c r="AE39">
+        <v>1.18</v>
+      </c>
+      <c r="AF39">
+        <v>1.6</v>
+      </c>
+      <c r="AG39">
+        <v>2.15</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.2</v>
       </c>
-      <c r="T39">
-        <v>4.2</v>
-      </c>
-      <c r="U39">
-        <v>2</v>
-      </c>
-      <c r="V39">
-        <v>1.79</v>
-      </c>
-      <c r="W39">
-        <v>1.17</v>
-      </c>
-      <c r="X39">
-        <v>1.02</v>
-      </c>
-      <c r="Y39">
-        <v>1.08</v>
-      </c>
-      <c r="Z39">
-        <v>7</v>
-      </c>
-      <c r="AA39">
-        <v>1.43</v>
-      </c>
-      <c r="AB39">
-        <v>2.9</v>
-      </c>
-      <c r="AC39">
-        <v>1.95</v>
-      </c>
-      <c r="AD39">
-        <v>1.8</v>
-      </c>
-      <c r="AE39">
-        <v>1.33</v>
-      </c>
-      <c r="AF39">
-        <v>1.4</v>
-      </c>
-      <c r="AG39">
-        <v>2.9</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.83</v>
-      </c>
       <c r="AK39">
-        <v>1.25</v>
+        <v>2.27</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>8</v>
+        <v>3.74</v>
       </c>
       <c r="O40">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
       <c r="P40">
-        <v>1.26</v>
+        <v>1.87</v>
       </c>
       <c r="Q40">
-        <v>8.140000000000001</v>
+        <v>3.88</v>
       </c>
       <c r="R40">
-        <v>2.71</v>
+        <v>2.47</v>
       </c>
       <c r="S40">
+        <v>1.2</v>
+      </c>
+      <c r="T40">
+        <v>4.2</v>
+      </c>
+      <c r="U40">
+        <v>2</v>
+      </c>
+      <c r="V40">
+        <v>1.79</v>
+      </c>
+      <c r="W40">
         <v>1.17</v>
       </c>
-      <c r="T40">
-        <v>4.5</v>
-      </c>
-      <c r="U40">
-        <v>2.02</v>
-      </c>
-      <c r="V40">
-        <v>1.84</v>
-      </c>
-      <c r="W40">
-        <v>1.2</v>
-      </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z40">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA40">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AB40">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AC40">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AD40">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AE40">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF40">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AG40">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>3.31</v>
+        <v>1.83</v>
       </c>
       <c r="AK40">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,61 +6992,61 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.33</v>
+        <v>8</v>
       </c>
       <c r="O41">
-        <v>3.44</v>
+        <v>6.25</v>
       </c>
       <c r="P41">
-        <v>2.55</v>
+        <v>1.26</v>
       </c>
       <c r="Q41">
-        <v>3.02</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.71</v>
       </c>
       <c r="S41">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T41">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="U41">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="V41">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="Z41">
-        <v>3.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA41">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="AB41">
-        <v>1.91</v>
+        <v>3.4</v>
       </c>
       <c r="AC41">
-        <v>2.91</v>
+        <v>1.87</v>
       </c>
       <c r="AD41">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AF41">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG41">
         <v>2.15</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.28</v>
+        <v>3.31</v>
       </c>
       <c r="AK41">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="AA42">
         <v>1.63</v>
@@ -7327,55 +7327,55 @@
         <v>1.82</v>
       </c>
       <c r="Q43">
-        <v>3.76</v>
+        <v>4.5</v>
       </c>
       <c r="R43">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U43">
-        <v>2.07</v>
+        <v>3.8</v>
       </c>
       <c r="V43">
-        <v>1.64</v>
+        <v>1.19</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA43">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="AB43">
-        <v>2.14</v>
+        <v>1.39</v>
       </c>
       <c r="AC43">
-        <v>2.65</v>
+        <v>5.35</v>
       </c>
       <c r="AD43">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>1.56</v>
+        <v>2.23</v>
       </c>
       <c r="AG43">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AK43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.69</v>
+        <v>2.37</v>
       </c>
       <c r="O44">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q44">
         <v>3.25</v>
@@ -7520,10 +7520,10 @@
         <v>3.98</v>
       </c>
       <c r="AA44">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB44">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC44">
         <v>2.56</v>
@@ -7538,7 +7538,7 @@
         <v>1.54</v>
       </c>
       <c r="AG44">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7807,16 +7807,16 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="O46">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P46">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="Q46">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R46">
         <v>2.4</v>
@@ -7846,10 +7846,10 @@
         <v>4.33</v>
       </c>
       <c r="AA46">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB46">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC46">
         <v>2.43</v>
@@ -7864,7 +7864,7 @@
         <v>1.67</v>
       </c>
       <c r="AG46">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7988,7 +7988,7 @@
         <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U47">
         <v>2.2</v>
@@ -8012,7 +8012,7 @@
         <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC47">
         <v>2.36</v>
@@ -8302,7 +8302,7 @@
         <v>4.5</v>
       </c>
       <c r="P49">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="Q49">
         <v>1.92</v>
@@ -8338,7 +8338,7 @@
         <v>1.3</v>
       </c>
       <c r="AB49">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AC49">
         <v>1.83</v>
@@ -8353,7 +8353,7 @@
         <v>1.36</v>
       </c>
       <c r="AG49">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8498,10 +8498,10 @@
         <v>6.32</v>
       </c>
       <c r="AA50">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB50">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC50">
         <v>2.01</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8646,10 +8646,10 @@
         <v>2</v>
       </c>
       <c r="V51">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W51">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X51">
         <v>0</v>
@@ -8676,10 +8676,10 @@
         <v>1.34</v>
       </c>
       <c r="AF51">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AG51">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>2.59</v>
       </c>
       <c r="S52">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
         <v>4</v>
@@ -8809,7 +8809,7 @@
         <v>2.06</v>
       </c>
       <c r="V52">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W52">
         <v>1.15</v>
@@ -8842,7 +8842,7 @@
         <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O61">
         <v>3.6</v>
@@ -10309,7 +10309,7 @@
         <v>1.33</v>
       </c>
       <c r="AG61">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P62">
         <v>3.65</v>
@@ -10626,7 +10626,7 @@
         <v>2.13</v>
       </c>
       <c r="AD63">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE63">
         <v>1.22</v>
@@ -10765,7 +10765,7 @@
         <v>1.94</v>
       </c>
       <c r="V64">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="W64">
         <v>1.25</v>
@@ -10958,7 +10958,7 @@
         <v>1.22</v>
       </c>
       <c r="AF65">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG65">
         <v>2.4</v>
@@ -11121,7 +11121,7 @@
         <v>1.28</v>
       </c>
       <c r="AF66">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AG66">
         <v>2.64</v>
@@ -11248,13 +11248,13 @@
         <v>1.25</v>
       </c>
       <c r="T67">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U67">
         <v>2.25</v>
       </c>
       <c r="V67">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W67">
         <v>1.15</v>
@@ -11263,25 +11263,25 @@
         <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z67">
         <v>4.75</v>
       </c>
       <c r="AA67">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB67">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC67">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AD67">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE67">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF67">
         <v>1.53</v>
@@ -11411,7 +11411,7 @@
         <v>1.17</v>
       </c>
       <c r="T68">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U68">
         <v>2.02</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O69">
         <v>4.33</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>2.57</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="U32">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
+        <v>1.19</v>
+      </c>
+      <c r="Z32">
+        <v>3.78</v>
+      </c>
+      <c r="AA32">
+        <v>1.76</v>
+      </c>
+      <c r="AB32">
+        <v>1.99</v>
+      </c>
+      <c r="AC32">
+        <v>2.83</v>
+      </c>
+      <c r="AD32">
+        <v>1.33</v>
+      </c>
+      <c r="AE32">
         <v>1.09</v>
       </c>
-      <c r="Z32">
-        <v>5.4</v>
-      </c>
-      <c r="AA32">
-        <v>1.47</v>
-      </c>
-      <c r="AB32">
-        <v>2.63</v>
-      </c>
-      <c r="AC32">
-        <v>2.17</v>
-      </c>
-      <c r="AD32">
-        <v>1.64</v>
-      </c>
-      <c r="AE32">
-        <v>1.22</v>
-      </c>
       <c r="AF32">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>4.2</v>
+        <v>2.57</v>
       </c>
       <c r="Q33">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="R33">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T33">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="U33">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="V33">
+        <v>1.64</v>
+      </c>
+      <c r="W33">
+        <v>1.13</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.09</v>
+      </c>
+      <c r="Z33">
+        <v>5.4</v>
+      </c>
+      <c r="AA33">
         <v>1.47</v>
       </c>
-      <c r="W33">
-        <v>1.08</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
-      <c r="Y33">
-        <v>1.19</v>
-      </c>
-      <c r="Z33">
-        <v>3.78</v>
-      </c>
-      <c r="AA33">
-        <v>1.76</v>
-      </c>
       <c r="AB33">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="AC33">
-        <v>2.83</v>
+        <v>2.17</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AK33">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="Q35">
-        <v>3.02</v>
+        <v>2.34</v>
       </c>
       <c r="R35">
         <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T35">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V35">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AB35">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AC35">
-        <v>2.91</v>
+        <v>2.68</v>
       </c>
       <c r="AD35">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AE35">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK35">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="P36">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="Q36">
-        <v>2.34</v>
+        <v>3.02</v>
       </c>
       <c r="R36">
         <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U36">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V36">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W36">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA36">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AB36">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AC36">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="AD36">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P37">
-        <v>2.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q37">
-        <v>2.52</v>
+        <v>3.26</v>
       </c>
       <c r="R37">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
         <v>1.2</v>
@@ -6361,43 +6361,43 @@
         <v>4.2</v>
       </c>
       <c r="U37">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V37">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="W37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AC37">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AD37">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE37">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF37">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG37">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>1.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q38">
-        <v>3.26</v>
+        <v>2.52</v>
       </c>
       <c r="R38">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="S38">
         <v>1.2</v>
@@ -6524,59 +6524,59 @@
         <v>4.2</v>
       </c>
       <c r="U38">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="W38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA38">
+        <v>1.44</v>
+      </c>
+      <c r="AB38">
+        <v>2.8</v>
+      </c>
+      <c r="AC38">
+        <v>2.11</v>
+      </c>
+      <c r="AD38">
+        <v>1.73</v>
+      </c>
+      <c r="AE38">
+        <v>1.29</v>
+      </c>
+      <c r="AF38">
         <v>1.4</v>
       </c>
-      <c r="AB38">
-        <v>3</v>
-      </c>
-      <c r="AC38">
-        <v>1.91</v>
-      </c>
-      <c r="AD38">
-        <v>1.83</v>
-      </c>
-      <c r="AE38">
+      <c r="AG38">
+        <v>2.89</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.33</v>
       </c>
-      <c r="AF38">
-        <v>1.36</v>
-      </c>
-      <c r="AG38">
-        <v>3</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.2</v>
-      </c>
       <c r="AK38">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7360,7 +7360,7 @@
         <v>2.6</v>
       </c>
       <c r="AB43">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AC43">
         <v>5.35</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="O8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P8">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1812,13 +1812,13 @@
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA9">
         <v>1.74</v>
       </c>
       <c r="AB9">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AC9">
         <v>2.88</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O10">
         <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="Q10">
         <v>2.7</v>
@@ -1954,49 +1954,49 @@
         <v>2.25</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC10">
         <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF10">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AG10">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2301,7 +2301,7 @@
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="AA12">
         <v>1.66</v>
@@ -2443,10 +2443,10 @@
         <v>2.48</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T13">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U13">
         <v>2.2</v>
@@ -2461,31 +2461,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AA13">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB13">
         <v>2.63</v>
       </c>
       <c r="AC13">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AD13">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE13">
         <v>1.25</v>
       </c>
       <c r="AF13">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG13">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -3261,16 +3261,16 @@
         <v>1.17</v>
       </c>
       <c r="T18">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="V18">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="W18">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="Q19">
-        <v>3.36</v>
+        <v>2</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="T19">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="V19">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>4.19</v>
+        <v>5.73</v>
       </c>
       <c r="AA19">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB19">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC19">
-        <v>2.52</v>
+        <v>1.79</v>
       </c>
       <c r="AD19">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.97</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="O20">
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>2.63</v>
+        <v>3.36</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U20">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
         <v>1.02</v>
@@ -3605,28 +3605,28 @@
         <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>4.3</v>
+        <v>4.19</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AB20">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="AC20">
-        <v>2.15</v>
+        <v>2.52</v>
       </c>
       <c r="AD20">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK20">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O21">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S21">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="V21">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="W21">
+        <v>1.08</v>
+      </c>
+      <c r="X21">
+        <v>1.02</v>
+      </c>
+      <c r="Y21">
+        <v>1.15</v>
+      </c>
+      <c r="Z21">
+        <v>4.3</v>
+      </c>
+      <c r="AA21">
+        <v>1.57</v>
+      </c>
+      <c r="AB21">
+        <v>2.14</v>
+      </c>
+      <c r="AC21">
+        <v>2.15</v>
+      </c>
+      <c r="AD21">
+        <v>1.45</v>
+      </c>
+      <c r="AE21">
         <v>1.14</v>
       </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>1.07</v>
-      </c>
-      <c r="Z21">
-        <v>5.59</v>
-      </c>
-      <c r="AA21">
-        <v>1.36</v>
-      </c>
-      <c r="AB21">
-        <v>2.25</v>
-      </c>
-      <c r="AC21">
-        <v>1.81</v>
-      </c>
-      <c r="AD21">
-        <v>1.69</v>
-      </c>
-      <c r="AE21">
-        <v>1.2</v>
-      </c>
       <c r="AF21">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG21">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>1.97</v>
+        <v>1.49</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3910,19 +3910,19 @@
         <v>2.41</v>
       </c>
       <c r="S22">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="U22">
         <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -4067,55 +4067,55 @@
         <v>3.25</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U23">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z23">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA23">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB23">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC23">
         <v>2.88</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
         <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG23">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4236,7 +4236,7 @@
         <v>2.01</v>
       </c>
       <c r="S24">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T24">
         <v>2.88</v>
@@ -4245,7 +4245,7 @@
         <v>2.81</v>
       </c>
       <c r="V24">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
         <v>1.06</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="O32">
+        <v>3.7</v>
+      </c>
+      <c r="P32">
+        <v>2.57</v>
+      </c>
+      <c r="Q32">
+        <v>2.54</v>
+      </c>
+      <c r="R32">
+        <v>2.32</v>
+      </c>
+      <c r="S32">
+        <v>1.2</v>
+      </c>
+      <c r="T32">
         <v>3.8</v>
       </c>
-      <c r="P32">
-        <v>4.2</v>
-      </c>
-      <c r="Q32">
-        <v>2.36</v>
-      </c>
-      <c r="R32">
-        <v>2.13</v>
-      </c>
-      <c r="S32">
-        <v>1.28</v>
-      </c>
-      <c r="T32">
-        <v>3.22</v>
-      </c>
       <c r="U32">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="V32">
+        <v>1.64</v>
+      </c>
+      <c r="W32">
+        <v>1.13</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.13</v>
+      </c>
+      <c r="Z32">
+        <v>6</v>
+      </c>
+      <c r="AA32">
         <v>1.47</v>
       </c>
-      <c r="W32">
-        <v>1.08</v>
-      </c>
-      <c r="X32">
-        <v>1.03</v>
-      </c>
-      <c r="Y32">
-        <v>1.19</v>
-      </c>
-      <c r="Z32">
-        <v>3.78</v>
-      </c>
-      <c r="AA32">
-        <v>1.76</v>
-      </c>
       <c r="AB32">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="AC32">
-        <v>2.83</v>
+        <v>2.2</v>
       </c>
       <c r="AD32">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AK32">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.37</v>
+        <v>1.74</v>
       </c>
       <c r="O33">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>2.57</v>
+        <v>4.2</v>
       </c>
       <c r="Q33">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="R33">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="S33">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="V33">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
+        <v>1.19</v>
+      </c>
+      <c r="Z33">
+        <v>3.78</v>
+      </c>
+      <c r="AA33">
+        <v>1.76</v>
+      </c>
+      <c r="AB33">
+        <v>1.99</v>
+      </c>
+      <c r="AC33">
+        <v>2.88</v>
+      </c>
+      <c r="AD33">
+        <v>1.4</v>
+      </c>
+      <c r="AE33">
         <v>1.09</v>
       </c>
-      <c r="Z33">
-        <v>5.4</v>
-      </c>
-      <c r="AA33">
-        <v>1.47</v>
-      </c>
-      <c r="AB33">
-        <v>2.63</v>
-      </c>
-      <c r="AC33">
-        <v>2.17</v>
-      </c>
-      <c r="AD33">
-        <v>1.64</v>
-      </c>
-      <c r="AE33">
-        <v>1.22</v>
-      </c>
       <c r="AF33">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5866,13 +5866,13 @@
         <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
         <v>1.37</v>
@@ -5881,7 +5881,7 @@
         <v>1.03</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
         <v>1.24</v>
@@ -5890,7 +5890,7 @@
         <v>3.34</v>
       </c>
       <c r="AA34">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AB34">
         <v>1.84</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.33</v>
+        <v>3.1</v>
       </c>
       <c r="O36">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="Q36">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
+        <v>1.2</v>
+      </c>
+      <c r="T36">
+        <v>4.2</v>
+      </c>
+      <c r="U36">
+        <v>2.04</v>
+      </c>
+      <c r="V36">
+        <v>1.82</v>
+      </c>
+      <c r="W36">
+        <v>1.2</v>
+      </c>
+      <c r="X36">
+        <v>1.02</v>
+      </c>
+      <c r="Y36">
+        <v>1.08</v>
+      </c>
+      <c r="Z36">
+        <v>7</v>
+      </c>
+      <c r="AA36">
+        <v>1.4</v>
+      </c>
+      <c r="AB36">
+        <v>3</v>
+      </c>
+      <c r="AC36">
+        <v>1.91</v>
+      </c>
+      <c r="AD36">
+        <v>1.83</v>
+      </c>
+      <c r="AE36">
+        <v>1.33</v>
+      </c>
+      <c r="AF36">
+        <v>1.36</v>
+      </c>
+      <c r="AG36">
+        <v>3</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>1.2</v>
+      </c>
+      <c r="AK36">
         <v>1.3</v>
-      </c>
-      <c r="T36">
-        <v>3.2</v>
-      </c>
-      <c r="U36">
-        <v>2.75</v>
-      </c>
-      <c r="V36">
-        <v>1.45</v>
-      </c>
-      <c r="W36">
-        <v>1.06</v>
-      </c>
-      <c r="X36">
-        <v>1.03</v>
-      </c>
-      <c r="Y36">
-        <v>1.25</v>
-      </c>
-      <c r="Z36">
-        <v>3.7</v>
-      </c>
-      <c r="AA36">
-        <v>1.83</v>
-      </c>
-      <c r="AB36">
-        <v>1.91</v>
-      </c>
-      <c r="AC36">
-        <v>2.91</v>
-      </c>
-      <c r="AD36">
-        <v>1.33</v>
-      </c>
-      <c r="AE36">
-        <v>1.11</v>
-      </c>
-      <c r="AF36">
-        <v>1.67</v>
-      </c>
-      <c r="AG36">
-        <v>2.15</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.28</v>
-      </c>
-      <c r="AK36">
-        <v>1.43</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="O37">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="P37">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="Q37">
-        <v>3.26</v>
+        <v>3.02</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="U37">
-        <v>2.04</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="W37">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="AA37">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AC37">
-        <v>1.91</v>
+        <v>2.91</v>
       </c>
       <c r="AD37">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -7170,7 +7170,7 @@
         <v>2.34</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
         <v>3.24</v>
@@ -7179,7 +7179,7 @@
         <v>2.38</v>
       </c>
       <c r="V42">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
         <v>1.11</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>2.13</v>
       </c>
       <c r="AK42">
         <v>1.16</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="O43">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="P43">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="Q43">
         <v>4.5</v>
       </c>
       <c r="R43">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="S43">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T43">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="U43">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="V43">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="W43">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y43">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Z43">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="AA43">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AB43">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC43">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="AD43">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AE43">
         <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AG43">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AK43">
         <v>1.2</v>
@@ -7517,22 +7517,22 @@
         <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>3.98</v>
+        <v>4.25</v>
       </c>
       <c r="AA44">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB44">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AC44">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AD44">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE44">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
         <v>1.54</v>
@@ -7816,13 +7816,13 @@
         <v>4.75</v>
       </c>
       <c r="Q46">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R46">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="T46">
         <v>3.5</v>
@@ -7843,13 +7843,13 @@
         <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA46">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC46">
         <v>2.43</v>
@@ -7861,10 +7861,10 @@
         <v>1.14</v>
       </c>
       <c r="AF46">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG46">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK46">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="O47">
         <v>3.76</v>
@@ -8136,7 +8136,7 @@
         <v>1.91</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
         <v>3.1</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK49">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,80 +10252,80 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.42</v>
+        <v>1.25</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>7.36</v>
       </c>
       <c r="P61">
-        <v>2.58</v>
+        <v>10.5</v>
       </c>
       <c r="Q61">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="R61">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T61">
-        <v>4.2</v>
+        <v>4.95</v>
       </c>
       <c r="U61">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="V61">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="W61">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X61">
         <v>0</v>
       </c>
       <c r="Y61">
+        <v>1.1</v>
+      </c>
+      <c r="Z61">
+        <v>6.8</v>
+      </c>
+      <c r="AA61">
+        <v>1.29</v>
+      </c>
+      <c r="AB61">
+        <v>3.5</v>
+      </c>
+      <c r="AC61">
+        <v>1.75</v>
+      </c>
+      <c r="AD61">
+        <v>2.07</v>
+      </c>
+      <c r="AE61">
+        <v>1.41</v>
+      </c>
+      <c r="AF61">
+        <v>1.62</v>
+      </c>
+      <c r="AG61">
+        <v>2.2</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
         <v>1.11</v>
       </c>
-      <c r="Z61">
-        <v>5.88</v>
-      </c>
-      <c r="AA61">
-        <v>1.44</v>
-      </c>
-      <c r="AB61">
-        <v>2.72</v>
-      </c>
-      <c r="AC61">
-        <v>2.11</v>
-      </c>
-      <c r="AD61">
-        <v>1.72</v>
-      </c>
-      <c r="AE61">
-        <v>1.29</v>
-      </c>
-      <c r="AF61">
-        <v>1.33</v>
-      </c>
-      <c r="AG61">
-        <v>2.8</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.2</v>
-      </c>
       <c r="AK61">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="O62">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="Q62">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="U62">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V62">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="W62">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X62">
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z62">
-        <v>5.04</v>
+        <v>5.88</v>
       </c>
       <c r="AA62">
+        <v>1.44</v>
+      </c>
+      <c r="AB62">
+        <v>2.72</v>
+      </c>
+      <c r="AC62">
+        <v>2.11</v>
+      </c>
+      <c r="AD62">
+        <v>1.72</v>
+      </c>
+      <c r="AE62">
+        <v>1.29</v>
+      </c>
+      <c r="AF62">
+        <v>1.33</v>
+      </c>
+      <c r="AG62">
+        <v>2.8</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>1.2</v>
+      </c>
+      <c r="AK62">
         <v>1.5</v>
-      </c>
-      <c r="AB62">
-        <v>2.4</v>
-      </c>
-      <c r="AC62">
-        <v>2.37</v>
-      </c>
-      <c r="AD62">
-        <v>1.59</v>
-      </c>
-      <c r="AE62">
-        <v>1.23</v>
-      </c>
-      <c r="AF62">
-        <v>1.44</v>
-      </c>
-      <c r="AG62">
-        <v>2.43</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.22</v>
-      </c>
-      <c r="AK62">
-        <v>1.8</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
+        <v>1.95</v>
+      </c>
+      <c r="O63">
+        <v>3.65</v>
+      </c>
+      <c r="P63">
+        <v>3.65</v>
+      </c>
+      <c r="Q63">
+        <v>2.26</v>
+      </c>
+      <c r="R63">
+        <v>2.5</v>
+      </c>
+      <c r="S63">
+        <v>1.25</v>
+      </c>
+      <c r="T63">
+        <v>3.75</v>
+      </c>
+      <c r="U63">
+        <v>2.25</v>
+      </c>
+      <c r="V63">
+        <v>1.6</v>
+      </c>
+      <c r="W63">
+        <v>1.13</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>1.17</v>
+      </c>
+      <c r="Z63">
+        <v>5.04</v>
+      </c>
+      <c r="AA63">
+        <v>1.5</v>
+      </c>
+      <c r="AB63">
+        <v>2.4</v>
+      </c>
+      <c r="AC63">
         <v>2.37</v>
       </c>
-      <c r="O63">
-        <v>3.5</v>
-      </c>
-      <c r="P63">
-        <v>2.45</v>
-      </c>
-      <c r="Q63">
-        <v>2.74</v>
-      </c>
-      <c r="R63">
-        <v>2.36</v>
-      </c>
-      <c r="S63">
-        <v>1.2</v>
-      </c>
-      <c r="T63">
-        <v>4</v>
-      </c>
-      <c r="U63">
-        <v>2.15</v>
-      </c>
-      <c r="V63">
-        <v>1.65</v>
-      </c>
-      <c r="W63">
-        <v>1.18</v>
-      </c>
-      <c r="X63">
-        <v>0</v>
-      </c>
-      <c r="Y63">
-        <v>1.15</v>
-      </c>
-      <c r="Z63">
-        <v>4.95</v>
-      </c>
-      <c r="AA63">
-        <v>1.47</v>
-      </c>
-      <c r="AB63">
-        <v>2.63</v>
-      </c>
-      <c r="AC63">
-        <v>2.13</v>
-      </c>
       <c r="AD63">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AE63">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF63">
         <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK63">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,80 +10741,80 @@
         </is>
       </c>
       <c r="N64">
+        <v>2.37</v>
+      </c>
+      <c r="O64">
+        <v>3.5</v>
+      </c>
+      <c r="P64">
+        <v>2.45</v>
+      </c>
+      <c r="Q64">
+        <v>2.61</v>
+      </c>
+      <c r="R64">
+        <v>2.36</v>
+      </c>
+      <c r="S64">
+        <v>1.2</v>
+      </c>
+      <c r="T64">
+        <v>4</v>
+      </c>
+      <c r="U64">
+        <v>2.15</v>
+      </c>
+      <c r="V64">
+        <v>1.65</v>
+      </c>
+      <c r="W64">
+        <v>1.18</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>1.15</v>
+      </c>
+      <c r="Z64">
+        <v>4.95</v>
+      </c>
+      <c r="AA64">
+        <v>1.47</v>
+      </c>
+      <c r="AB64">
+        <v>2.63</v>
+      </c>
+      <c r="AC64">
+        <v>2.13</v>
+      </c>
+      <c r="AD64">
+        <v>1.65</v>
+      </c>
+      <c r="AE64">
+        <v>1.22</v>
+      </c>
+      <c r="AF64">
+        <v>1.44</v>
+      </c>
+      <c r="AG64">
+        <v>2.62</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
         <v>1.25</v>
       </c>
-      <c r="O64">
-        <v>7.36</v>
-      </c>
-      <c r="P64">
-        <v>10.5</v>
-      </c>
-      <c r="Q64">
-        <v>1.55</v>
-      </c>
-      <c r="R64">
-        <v>2.82</v>
-      </c>
-      <c r="S64">
-        <v>1.11</v>
-      </c>
-      <c r="T64">
-        <v>4.95</v>
-      </c>
-      <c r="U64">
-        <v>1.94</v>
-      </c>
-      <c r="V64">
-        <v>1.91</v>
-      </c>
-      <c r="W64">
-        <v>1.25</v>
-      </c>
-      <c r="X64">
-        <v>0</v>
-      </c>
-      <c r="Y64">
-        <v>1.1</v>
-      </c>
-      <c r="Z64">
-        <v>6.8</v>
-      </c>
-      <c r="AA64">
-        <v>1.29</v>
-      </c>
-      <c r="AB64">
-        <v>3.5</v>
-      </c>
-      <c r="AC64">
-        <v>1.75</v>
-      </c>
-      <c r="AD64">
-        <v>2.07</v>
-      </c>
-      <c r="AE64">
-        <v>1.41</v>
-      </c>
-      <c r="AF64">
-        <v>1.62</v>
-      </c>
-      <c r="AG64">
-        <v>2.2</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.11</v>
-      </c>
       <c r="AK64">
-        <v>3.8</v>
+        <v>1.54</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>1.95</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P66">
         <v>3.48</v>
@@ -11236,7 +11236,7 @@
         <v>3.68</v>
       </c>
       <c r="P67">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q67">
         <v>2.44</v>
@@ -11559,7 +11559,7 @@
         <v>1.44</v>
       </c>
       <c r="O69">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="P69">
         <v>6</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -964,13 +964,13 @@
         <v>1.45</v>
       </c>
       <c r="O4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P4">
         <v>4.4</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="R4">
         <v>2.25</v>
@@ -982,10 +982,10 @@
         <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W4">
         <v>1.12</v>
@@ -997,16 +997,16 @@
         <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="AA4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB4">
         <v>2.09</v>
       </c>
       <c r="AC4">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="AD4">
         <v>1.36</v>
@@ -1018,7 +1018,7 @@
         <v>1.68</v>
       </c>
       <c r="AG4">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1287,34 +1287,34 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P6">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="S6">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="U6">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V6">
         <v>1.69</v>
       </c>
       <c r="W6">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
         <v>1.02</v>
@@ -1326,19 +1326,19 @@
         <v>5.45</v>
       </c>
       <c r="AA6">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB6">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="AC6">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AD6">
         <v>1.68</v>
       </c>
       <c r="AE6">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF6">
         <v>1.4</v>
@@ -1788,7 +1788,7 @@
         <v>1.87</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="S9">
         <v>1.3</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AK9">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
         <v>3</v>
@@ -1951,37 +1951,37 @@
         <v>2.7</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="S10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U10">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V10">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC10">
         <v>2.88</v>
@@ -1990,13 +1990,13 @@
         <v>1.4</v>
       </c>
       <c r="AE10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AG10">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
         <v>1.57</v>
@@ -2437,10 +2437,10 @@
         <v>4.1</v>
       </c>
       <c r="Q13">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R13">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S13">
         <v>1.22</v>
@@ -2449,10 +2449,10 @@
         <v>3.75</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="V13">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="W13">
         <v>1.15</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
         <v>2.1</v>
@@ -2597,13 +2597,13 @@
         <v>3.95</v>
       </c>
       <c r="P14">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q14">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R14">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="S14">
         <v>1.24</v>
@@ -2639,7 +2639,7 @@
         <v>1.95</v>
       </c>
       <c r="AD14">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE14">
         <v>1.3</v>
@@ -2664,7 +2664,7 @@
         <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="O15">
         <v>6.3</v>
       </c>
       <c r="P15">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q15">
         <v>6.28</v>
       </c>
       <c r="R15">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S15">
         <v>1.2</v>
       </c>
       <c r="T15">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U15">
         <v>1.92</v>
@@ -2790,10 +2790,10 @@
         <v>1.07</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA15">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AB15">
         <v>2.82</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK15">
         <v>1.07</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q16">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="R16">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="S16">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T16">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="U16">
         <v>3.28</v>
@@ -2947,7 +2947,7 @@
         <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y16">
         <v>1.51</v>
@@ -2959,10 +2959,10 @@
         <v>2.49</v>
       </c>
       <c r="AB16">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AC16">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD16">
         <v>1.11</v>
@@ -2971,10 +2971,10 @@
         <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG16">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK16">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q17">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="R17">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="S17">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="T17">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U17">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="V17">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y17">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z17">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AA17">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB17">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC17">
-        <v>5.45</v>
+        <v>5.6</v>
       </c>
       <c r="AD17">
         <v>1.08</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AG17">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,34 +3243,34 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="O18">
+        <v>3.9</v>
+      </c>
+      <c r="P18">
         <v>3.7</v>
       </c>
-      <c r="P18">
-        <v>2.95</v>
-      </c>
       <c r="Q18">
-        <v>2.61</v>
+        <v>2</v>
       </c>
       <c r="R18">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="V18">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="W18">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,28 +3279,28 @@
         <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>5.85</v>
+        <v>5.73</v>
       </c>
       <c r="AA18">
         <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AC18">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AD18">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AE18">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG18">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.17</v>
       </c>
       <c r="AK18">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="O19">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>2</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
         <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>5.73</v>
+        <v>4.19</v>
       </c>
       <c r="AA19">
+        <v>1.63</v>
+      </c>
+      <c r="AB19">
+        <v>1.83</v>
+      </c>
+      <c r="AC19">
+        <v>2.52</v>
+      </c>
+      <c r="AD19">
+        <v>1.41</v>
+      </c>
+      <c r="AE19">
+        <v>1.13</v>
+      </c>
+      <c r="AF19">
+        <v>1.44</v>
+      </c>
+      <c r="AG19">
+        <v>2.3</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.09</v>
+      </c>
+      <c r="AK19">
         <v>1.36</v>
-      </c>
-      <c r="AB19">
-        <v>2.3</v>
-      </c>
-      <c r="AC19">
-        <v>1.79</v>
-      </c>
-      <c r="AD19">
-        <v>1.72</v>
-      </c>
-      <c r="AE19">
-        <v>1.2</v>
-      </c>
-      <c r="AF19">
-        <v>1.4</v>
-      </c>
-      <c r="AG19">
-        <v>2.7</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.17</v>
-      </c>
-      <c r="AK19">
-        <v>1.97</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="O20">
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q20">
-        <v>3.36</v>
+        <v>2.63</v>
       </c>
       <c r="R20">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U20">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
         <v>1.02</v>
@@ -3605,28 +3605,28 @@
         <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>4.19</v>
+        <v>4.3</v>
       </c>
       <c r="AA20">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AC20">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="AD20">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q21">
+        <v>2.61</v>
+      </c>
+      <c r="R21">
         <v>2.63</v>
       </c>
-      <c r="R21">
-        <v>2.25</v>
-      </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U21">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="V21">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>4.3</v>
+        <v>5.85</v>
       </c>
       <c r="AA21">
+        <v>1.36</v>
+      </c>
+      <c r="AB21">
+        <v>3.1</v>
+      </c>
+      <c r="AC21">
+        <v>1.89</v>
+      </c>
+      <c r="AD21">
+        <v>1.78</v>
+      </c>
+      <c r="AE21">
+        <v>1.31</v>
+      </c>
+      <c r="AF21">
+        <v>1.36</v>
+      </c>
+      <c r="AG21">
+        <v>2.91</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>1.17</v>
+      </c>
+      <c r="AK21">
         <v>1.57</v>
-      </c>
-      <c r="AB21">
-        <v>2.14</v>
-      </c>
-      <c r="AC21">
-        <v>2.15</v>
-      </c>
-      <c r="AD21">
-        <v>1.45</v>
-      </c>
-      <c r="AE21">
-        <v>1.14</v>
-      </c>
-      <c r="AF21">
-        <v>1.5</v>
-      </c>
-      <c r="AG21">
-        <v>2.05</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.21</v>
-      </c>
-      <c r="AK21">
-        <v>1.49</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="O23">
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q23">
         <v>2.4</v>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,16 +4387,16 @@
         <v>1.35</v>
       </c>
       <c r="O25">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P25">
-        <v>5.9</v>
+        <v>6.75</v>
       </c>
       <c r="Q25">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="R25">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="S25">
         <v>1.2</v>
@@ -4405,7 +4405,7 @@
         <v>4</v>
       </c>
       <c r="U25">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="V25">
         <v>1.75</v>
@@ -4429,10 +4429,10 @@
         <v>2.7</v>
       </c>
       <c r="AC25">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AD25">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE25">
         <v>1.3</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="O26">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="P26">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="Q26">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="R26">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="S26">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T26">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="U26">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="V26">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="W26">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.01</v>
       </c>
       <c r="Z26">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA26">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AB26">
-        <v>3.76</v>
+        <v>3.92</v>
       </c>
       <c r="AC26">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AD26">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AE26">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AF26">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK26">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="O27">
         <v>4.6</v>
@@ -4722,7 +4722,7 @@
         <v>1.77</v>
       </c>
       <c r="R27">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="S27">
         <v>1.17</v>
@@ -4734,7 +4734,7 @@
         <v>1.79</v>
       </c>
       <c r="V27">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="W27">
         <v>1.25</v>
@@ -4749,7 +4749,7 @@
         <v>7.3</v>
       </c>
       <c r="AA27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB27">
         <v>3.5</v>
@@ -4894,10 +4894,10 @@
         <v>4.2</v>
       </c>
       <c r="U28">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V28">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="W28">
         <v>1.2</v>
@@ -4915,7 +4915,7 @@
         <v>1.4</v>
       </c>
       <c r="AB28">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AC28">
         <v>1.94</v>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O29">
         <v>3.9</v>
@@ -5048,7 +5048,7 @@
         <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="S29">
         <v>1.13</v>
@@ -5057,10 +5057,10 @@
         <v>5.5</v>
       </c>
       <c r="U29">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="V29">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="W29">
         <v>1.3</v>
@@ -5081,16 +5081,16 @@
         <v>3.82</v>
       </c>
       <c r="AC29">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AD29">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AE29">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AF29">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG29">
         <v>3.5</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="O30">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="Q30">
         <v>3.32</v>
@@ -5368,7 +5368,7 @@
         <v>3.65</v>
       </c>
       <c r="P31">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="Q31">
         <v>3.35</v>
@@ -5380,7 +5380,7 @@
         <v>1.12</v>
       </c>
       <c r="T31">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U31">
         <v>1.82</v>
@@ -5404,7 +5404,7 @@
         <v>1.26</v>
       </c>
       <c r="AB31">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AC31">
         <v>1.79</v>
@@ -5416,10 +5416,10 @@
         <v>1.38</v>
       </c>
       <c r="AF31">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AG31">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="O32">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>2.57</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T32">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U32">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="V32">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W32">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>3.78</v>
       </c>
       <c r="AA32">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AB32">
-        <v>2.63</v>
+        <v>1.99</v>
       </c>
       <c r="AC32">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AD32">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="AE32">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AF32">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG32">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AK32">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.74</v>
+        <v>2.37</v>
       </c>
       <c r="O33">
         <v>3.8</v>
       </c>
       <c r="P33">
-        <v>4.2</v>
+        <v>2.57</v>
       </c>
       <c r="Q33">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="R33">
-        <v>2.13</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="U33">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="V33">
+        <v>1.64</v>
+      </c>
+      <c r="W33">
+        <v>1.13</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.13</v>
+      </c>
+      <c r="Z33">
+        <v>6</v>
+      </c>
+      <c r="AA33">
         <v>1.47</v>
       </c>
-      <c r="W33">
-        <v>1.08</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
-      <c r="Y33">
-        <v>1.19</v>
-      </c>
-      <c r="Z33">
-        <v>3.78</v>
-      </c>
-      <c r="AA33">
-        <v>1.76</v>
-      </c>
       <c r="AB33">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="AC33">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AD33">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AF33">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AK33">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,7 +5854,7 @@
         <v>2.25</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="P34">
         <v>2.97</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O35">
         <v>3.5</v>
       </c>
       <c r="P35">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="Q35">
-        <v>2.34</v>
+        <v>3.02</v>
       </c>
       <c r="R35">
         <v>2.3</v>
       </c>
       <c r="S35">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U35">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V35">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA35">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AB35">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AC35">
-        <v>2.68</v>
+        <v>2.93</v>
       </c>
       <c r="AD35">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AE35">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF35">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.1</v>
+        <v>3.74</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q36">
-        <v>3.26</v>
+        <v>3.88</v>
       </c>
       <c r="R36">
         <v>2.5</v>
@@ -6198,13 +6198,13 @@
         <v>4.2</v>
       </c>
       <c r="U36">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V36">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="W36">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X36">
         <v>1.02</v>
@@ -6216,41 +6216,41 @@
         <v>7</v>
       </c>
       <c r="AA36">
+        <v>1.45</v>
+      </c>
+      <c r="AB36">
+        <v>2.82</v>
+      </c>
+      <c r="AC36">
+        <v>2</v>
+      </c>
+      <c r="AD36">
+        <v>1.75</v>
+      </c>
+      <c r="AE36">
+        <v>1.29</v>
+      </c>
+      <c r="AF36">
         <v>1.4</v>
       </c>
-      <c r="AB36">
-        <v>3</v>
-      </c>
-      <c r="AC36">
-        <v>1.91</v>
-      </c>
-      <c r="AD36">
+      <c r="AG36">
+        <v>2.9</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.83</v>
       </c>
-      <c r="AE36">
-        <v>1.33</v>
-      </c>
-      <c r="AF36">
-        <v>1.36</v>
-      </c>
-      <c r="AG36">
-        <v>3</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.2</v>
-      </c>
       <c r="AK36">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,65 +6340,65 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="O37">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="Q37">
-        <v>3.02</v>
+        <v>2.36</v>
       </c>
       <c r="R37">
+        <v>2.38</v>
+      </c>
+      <c r="S37">
+        <v>1.33</v>
+      </c>
+      <c r="T37">
+        <v>3.4</v>
+      </c>
+      <c r="U37">
+        <v>2.4</v>
+      </c>
+      <c r="V37">
+        <v>1.5</v>
+      </c>
+      <c r="W37">
+        <v>1.1</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.2</v>
+      </c>
+      <c r="Z37">
+        <v>4.2</v>
+      </c>
+      <c r="AA37">
+        <v>1.72</v>
+      </c>
+      <c r="AB37">
+        <v>2.17</v>
+      </c>
+      <c r="AC37">
+        <v>2.68</v>
+      </c>
+      <c r="AD37">
+        <v>1.47</v>
+      </c>
+      <c r="AE37">
+        <v>1.14</v>
+      </c>
+      <c r="AF37">
+        <v>1.6</v>
+      </c>
+      <c r="AG37">
         <v>2.3</v>
       </c>
-      <c r="S37">
-        <v>1.3</v>
-      </c>
-      <c r="T37">
-        <v>3.2</v>
-      </c>
-      <c r="U37">
-        <v>2.75</v>
-      </c>
-      <c r="V37">
-        <v>1.45</v>
-      </c>
-      <c r="W37">
-        <v>1.06</v>
-      </c>
-      <c r="X37">
-        <v>1.03</v>
-      </c>
-      <c r="Y37">
-        <v>1.25</v>
-      </c>
-      <c r="Z37">
-        <v>3.7</v>
-      </c>
-      <c r="AA37">
-        <v>1.83</v>
-      </c>
-      <c r="AB37">
-        <v>1.91</v>
-      </c>
-      <c r="AC37">
-        <v>2.91</v>
-      </c>
-      <c r="AD37">
-        <v>1.33</v>
-      </c>
-      <c r="AE37">
-        <v>1.11</v>
-      </c>
-      <c r="AF37">
-        <v>1.67</v>
-      </c>
-      <c r="AG37">
-        <v>2.15</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK37">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P38">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="Q38">
-        <v>2.52</v>
+        <v>3.26</v>
       </c>
       <c r="R38">
-        <v>2.67</v>
+        <v>2.48</v>
       </c>
       <c r="S38">
         <v>1.2</v>
       </c>
       <c r="T38">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="U38">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V38">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="W38">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA38">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AC38">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AD38">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE38">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF38">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG38">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.51</v>
+        <v>2.11</v>
       </c>
       <c r="O39">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P39">
-        <v>4.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q39">
-        <v>2.24</v>
+        <v>2.49</v>
       </c>
       <c r="R39">
-        <v>2.19</v>
+        <v>2.64</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>3.05</v>
+        <v>4.05</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="W39">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AA39">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AB39">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AC39">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="AD39">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AE39">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AF39">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AG39">
-        <v>2.15</v>
+        <v>2.89</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
-        <v>2.27</v>
+        <v>1.72</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>3.74</v>
+        <v>1.51</v>
       </c>
       <c r="O40">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P40">
-        <v>1.87</v>
+        <v>4.25</v>
       </c>
       <c r="Q40">
-        <v>3.88</v>
+        <v>2.21</v>
       </c>
       <c r="R40">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
       <c r="S40">
+        <v>1.3</v>
+      </c>
+      <c r="T40">
+        <v>3.42</v>
+      </c>
+      <c r="U40">
+        <v>2.4</v>
+      </c>
+      <c r="V40">
+        <v>1.56</v>
+      </c>
+      <c r="W40">
+        <v>1.11</v>
+      </c>
+      <c r="X40">
+        <v>1.03</v>
+      </c>
+      <c r="Y40">
+        <v>1.18</v>
+      </c>
+      <c r="Z40">
+        <v>4.5</v>
+      </c>
+      <c r="AA40">
+        <v>1.59</v>
+      </c>
+      <c r="AB40">
+        <v>2.3</v>
+      </c>
+      <c r="AC40">
+        <v>2.5</v>
+      </c>
+      <c r="AD40">
+        <v>1.5</v>
+      </c>
+      <c r="AE40">
+        <v>1.18</v>
+      </c>
+      <c r="AF40">
+        <v>1.6</v>
+      </c>
+      <c r="AG40">
+        <v>2.15</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.2</v>
       </c>
-      <c r="T40">
-        <v>4.2</v>
-      </c>
-      <c r="U40">
-        <v>2</v>
-      </c>
-      <c r="V40">
-        <v>1.79</v>
-      </c>
-      <c r="W40">
-        <v>1.17</v>
-      </c>
-      <c r="X40">
-        <v>1.02</v>
-      </c>
-      <c r="Y40">
-        <v>1.08</v>
-      </c>
-      <c r="Z40">
-        <v>7</v>
-      </c>
-      <c r="AA40">
-        <v>1.43</v>
-      </c>
-      <c r="AB40">
-        <v>2.9</v>
-      </c>
-      <c r="AC40">
-        <v>1.95</v>
-      </c>
-      <c r="AD40">
-        <v>1.8</v>
-      </c>
-      <c r="AE40">
-        <v>1.33</v>
-      </c>
-      <c r="AF40">
-        <v>1.4</v>
-      </c>
-      <c r="AG40">
-        <v>2.9</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.83</v>
-      </c>
       <c r="AK40">
-        <v>1.25</v>
+        <v>2.27</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O41">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="P41">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q41">
-        <v>8.140000000000001</v>
+        <v>7.83</v>
       </c>
       <c r="R41">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="S41">
         <v>1.17</v>
@@ -7013,7 +7013,7 @@
         <v>4.5</v>
       </c>
       <c r="U41">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="V41">
         <v>1.84</v>
@@ -7031,16 +7031,16 @@
         <v>7.5</v>
       </c>
       <c r="AA41">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AB41">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AC41">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AD41">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AE41">
         <v>1.36</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="AK41">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>4.6</v>
       </c>
       <c r="O42">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P42">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q42">
         <v>4.88</v>
@@ -7191,7 +7191,7 @@
         <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="AA42">
         <v>1.63</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="O46">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P46">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="Q46">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R46">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="S46">
         <v>1.23</v>
@@ -7837,50 +7837,50 @@
         <v>1.13</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
         <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AA46">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB46">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC46">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AD46">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE46">
+        <v>1.18</v>
+      </c>
+      <c r="AF46">
+        <v>1.67</v>
+      </c>
+      <c r="AG46">
+        <v>2.02</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.14</v>
       </c>
-      <c r="AF46">
-        <v>1.69</v>
-      </c>
-      <c r="AG46">
-        <v>2.03</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.13</v>
-      </c>
       <c r="AK46">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7994,16 +7994,16 @@
         <v>2.2</v>
       </c>
       <c r="V47">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W47">
         <v>1.13</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z47">
         <v>5.1</v>
@@ -8015,13 +8015,13 @@
         <v>2.45</v>
       </c>
       <c r="AC47">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AD47">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF47">
         <v>1.5</v>
@@ -8043,7 +8043,7 @@
         <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8139,13 +8139,13 @@
         <v>3.6</v>
       </c>
       <c r="P48">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q48">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="R48">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="S48">
         <v>1.2</v>
@@ -8163,25 +8163,25 @@
         <v>1.17</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z48">
         <v>5.54</v>
       </c>
       <c r="AA48">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB48">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AC48">
         <v>2.24</v>
       </c>
       <c r="AD48">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE48">
         <v>1.21</v>
@@ -8190,7 +8190,7 @@
         <v>1.44</v>
       </c>
       <c r="AG48">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8335,10 +8335,10 @@
         <v>8</v>
       </c>
       <c r="AA49">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB49">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AC49">
         <v>1.83</v>
@@ -8465,7 +8465,7 @@
         <v>3.9</v>
       </c>
       <c r="P50">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="Q50">
         <v>2.4</v>
@@ -8474,10 +8474,10 @@
         <v>2.68</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T50">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U50">
         <v>1.95</v>
@@ -8486,7 +8486,7 @@
         <v>1.76</v>
       </c>
       <c r="W50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X50">
         <v>0</v>
@@ -8631,22 +8631,22 @@
         <v>2.85</v>
       </c>
       <c r="Q51">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="R51">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="S51">
         <v>1.17</v>
       </c>
       <c r="T51">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="U51">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V51">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W51">
         <v>1.2</v>
@@ -8655,19 +8655,19 @@
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z51">
-        <v>6.16</v>
+        <v>6.5</v>
       </c>
       <c r="AA51">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB51">
         <v>2.83</v>
       </c>
       <c r="AC51">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AD51">
         <v>1.81</v>
@@ -8806,7 +8806,7 @@
         <v>4</v>
       </c>
       <c r="U52">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="V52">
         <v>1.67</v>
@@ -8815,10 +8815,10 @@
         <v>1.15</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
         <v>5.38</v>
@@ -10267,7 +10267,7 @@
         <v>2.85</v>
       </c>
       <c r="S61">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="T61">
         <v>4.95</v>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
         <v>2.58</v>
@@ -10454,7 +10454,7 @@
         <v>5.88</v>
       </c>
       <c r="AA62">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB62">
         <v>2.72</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O63">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="P63">
         <v>3.65</v>
@@ -10620,7 +10620,7 @@
         <v>1.5</v>
       </c>
       <c r="AB63">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC63">
         <v>2.37</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O64">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Q64">
         <v>2.61</v>
@@ -10777,7 +10777,7 @@
         <v>1.15</v>
       </c>
       <c r="Z64">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA64">
         <v>1.47</v>
@@ -10904,10 +10904,10 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="P65">
         <v>3</v>
@@ -10916,7 +10916,7 @@
         <v>2.65</v>
       </c>
       <c r="R65">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S65">
         <v>1.25</v>
@@ -10925,7 +10925,7 @@
         <v>3.5</v>
       </c>
       <c r="U65">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="V65">
         <v>1.56</v>
@@ -11399,13 +11399,13 @@
         <v>3.7</v>
       </c>
       <c r="P68">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="Q68">
         <v>2.33</v>
       </c>
       <c r="R68">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="S68">
         <v>1.17</v>
@@ -11441,7 +11441,7 @@
         <v>2.02</v>
       </c>
       <c r="AD68">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE68">
         <v>1.35</v>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK68">
         <v>1.75</v>
@@ -11583,7 +11583,7 @@
         <v>1.59</v>
       </c>
       <c r="W69">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X69">
         <v>0</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AK69">
         <v>2.7</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>4.01</v>
+        <v>2.99</v>
       </c>
       <c r="O2">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="P2">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Q2">
         <v>3.7</v>
@@ -653,7 +653,7 @@
         <v>1.34</v>
       </c>
       <c r="T2">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
         <v>2.65</v>
@@ -662,10 +662,10 @@
         <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
         <v>1.29</v>
@@ -677,7 +677,7 @@
         <v>1.93</v>
       </c>
       <c r="AB2">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AC2">
         <v>3.25</v>
@@ -686,13 +686,13 @@
         <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AK2">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="O4">
         <v>3.7</v>
       </c>
       <c r="P4">
-        <v>4.4</v>
+        <v>4.77</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
         <v>1.3</v>
@@ -1009,7 +1009,7 @@
         <v>2.82</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE4">
         <v>1.1</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="O9">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="P9">
-        <v>6.1</v>
+        <v>6.13</v>
       </c>
       <c r="Q9">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R9">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="U9">
         <v>2.63</v>
@@ -1818,7 +1818,7 @@
         <v>1.74</v>
       </c>
       <c r="AB9">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AC9">
         <v>2.88</v>
@@ -1849,7 +1849,7 @@
         <v>1.14</v>
       </c>
       <c r="AK9">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1984,10 +1984,10 @@
         <v>1.93</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AD10">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE10">
         <v>1.1</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q18">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="V18">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>5.73</v>
+        <v>4.3</v>
       </c>
       <c r="AA18">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AD18">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.97</v>
+        <v>1.49</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="Q19">
-        <v>3.36</v>
+        <v>2.61</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>4.19</v>
+        <v>5.85</v>
       </c>
       <c r="AA19">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB19">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="AC19">
-        <v>2.52</v>
+        <v>1.89</v>
       </c>
       <c r="AD19">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF19">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="P20">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="Q20">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="V20">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>4.3</v>
+        <v>5.73</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AC20">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AD20">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG20">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>1.49</v>
+        <v>1.97</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
+        <v>2.05</v>
+      </c>
+      <c r="O21">
+        <v>3.55</v>
+      </c>
+      <c r="P21">
+        <v>2.96</v>
+      </c>
+      <c r="Q21">
+        <v>2.46</v>
+      </c>
+      <c r="R21">
+        <v>2.41</v>
+      </c>
+      <c r="S21">
+        <v>1.2</v>
+      </c>
+      <c r="T21">
+        <v>4</v>
+      </c>
+      <c r="U21">
         <v>2.1</v>
       </c>
-      <c r="O21">
-        <v>3.7</v>
-      </c>
-      <c r="P21">
-        <v>2.68</v>
-      </c>
-      <c r="Q21">
-        <v>2.61</v>
-      </c>
-      <c r="R21">
-        <v>2.63</v>
-      </c>
-      <c r="S21">
+      <c r="V21">
+        <v>1.67</v>
+      </c>
+      <c r="W21">
         <v>1.17</v>
       </c>
-      <c r="T21">
-        <v>3.1</v>
-      </c>
-      <c r="U21">
-        <v>1.75</v>
-      </c>
-      <c r="V21">
-        <v>1.59</v>
-      </c>
-      <c r="W21">
-        <v>1.2</v>
-      </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>5.85</v>
+        <v>3.6</v>
       </c>
       <c r="AA21">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AB21">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AC21">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="AD21">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AE21">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AF21">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG21">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
+        <v>2.7</v>
+      </c>
+      <c r="O22">
+        <v>3.4</v>
+      </c>
+      <c r="P22">
+        <v>2.21</v>
+      </c>
+      <c r="Q22">
+        <v>3.36</v>
+      </c>
+      <c r="R22">
         <v>2.05</v>
       </c>
-      <c r="O22">
-        <v>3.55</v>
-      </c>
-      <c r="P22">
-        <v>2.96</v>
-      </c>
-      <c r="Q22">
-        <v>2.46</v>
-      </c>
-      <c r="R22">
-        <v>2.41</v>
-      </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="V22">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
-        <v>3.6</v>
+        <v>4.19</v>
       </c>
       <c r="AA22">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AB22">
-        <v>2.59</v>
+        <v>1.83</v>
       </c>
       <c r="AC22">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="AD22">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
         <v>2.3</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="AK22">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4094,13 +4094,13 @@
         <v>1.19</v>
       </c>
       <c r="Z23">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA23">
         <v>1.69</v>
       </c>
       <c r="AB23">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC23">
         <v>2.88</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O24">
         <v>3.1</v>
@@ -4230,7 +4230,7 @@
         <v>2.25</v>
       </c>
       <c r="Q24">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="R24">
         <v>2.01</v>
@@ -4294,7 +4294,7 @@
         <v>1.25</v>
       </c>
       <c r="AK24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="O27">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q27">
-        <v>1.77</v>
+        <v>2.54</v>
       </c>
       <c r="R27">
-        <v>3.02</v>
+        <v>2.44</v>
       </c>
       <c r="S27">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T27">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="U27">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="V27">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="W27">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z27">
-        <v>7.3</v>
+        <v>5.95</v>
       </c>
       <c r="AA27">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AB27">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AC27">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AD27">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="AE27">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF27">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AG27">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AK27">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.03</v>
+        <v>3.05</v>
       </c>
       <c r="O28">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P28">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q28">
-        <v>2.54</v>
+        <v>3.32</v>
       </c>
       <c r="R28">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="S28">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="T28">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="U28">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="V28">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="W28">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Z28">
-        <v>5.95</v>
+        <v>7.8</v>
       </c>
       <c r="AA28">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AB28">
-        <v>2.88</v>
+        <v>3.41</v>
       </c>
       <c r="AC28">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AD28">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="AE28">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AF28">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AG28">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.86</v>
+        <v>1.4</v>
       </c>
       <c r="O29">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="P29">
+        <v>5.3</v>
+      </c>
+      <c r="Q29">
+        <v>1.77</v>
+      </c>
+      <c r="R29">
+        <v>3.02</v>
+      </c>
+      <c r="S29">
+        <v>1.17</v>
+      </c>
+      <c r="T29">
+        <v>4.6</v>
+      </c>
+      <c r="U29">
+        <v>1.79</v>
+      </c>
+      <c r="V29">
+        <v>1.91</v>
+      </c>
+      <c r="W29">
+        <v>1.25</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>1.03</v>
+      </c>
+      <c r="Z29">
+        <v>7.3</v>
+      </c>
+      <c r="AA29">
+        <v>1.29</v>
+      </c>
+      <c r="AB29">
+        <v>3.5</v>
+      </c>
+      <c r="AC29">
+        <v>1.72</v>
+      </c>
+      <c r="AD29">
+        <v>1.97</v>
+      </c>
+      <c r="AE29">
+        <v>1.4</v>
+      </c>
+      <c r="AF29">
+        <v>1.4</v>
+      </c>
+      <c r="AG29">
+        <v>2.7</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.09</v>
+      </c>
+      <c r="AK29">
         <v>2.75</v>
-      </c>
-      <c r="Q29">
-        <v>2.2</v>
-      </c>
-      <c r="R29">
-        <v>2.91</v>
-      </c>
-      <c r="S29">
-        <v>1.13</v>
-      </c>
-      <c r="T29">
-        <v>5.5</v>
-      </c>
-      <c r="U29">
-        <v>1.74</v>
-      </c>
-      <c r="V29">
-        <v>2.04</v>
-      </c>
-      <c r="W29">
-        <v>1.3</v>
-      </c>
-      <c r="X29">
-        <v>1</v>
-      </c>
-      <c r="Y29">
-        <v>1.01</v>
-      </c>
-      <c r="Z29">
-        <v>8.5</v>
-      </c>
-      <c r="AA29">
-        <v>1.25</v>
-      </c>
-      <c r="AB29">
-        <v>3.82</v>
-      </c>
-      <c r="AC29">
-        <v>1.57</v>
-      </c>
-      <c r="AD29">
-        <v>2.17</v>
-      </c>
-      <c r="AE29">
-        <v>1.55</v>
-      </c>
-      <c r="AF29">
-        <v>1.25</v>
-      </c>
-      <c r="AG29">
-        <v>3.5</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.2</v>
-      </c>
-      <c r="AK29">
-        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,58 +5199,58 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.05</v>
+        <v>1.86</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P30">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="Q30">
-        <v>3.32</v>
+        <v>2.2</v>
       </c>
       <c r="R30">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="S30">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="T30">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="U30">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="V30">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="W30">
+        <v>1.3</v>
+      </c>
+      <c r="X30">
+        <v>1</v>
+      </c>
+      <c r="Y30">
+        <v>1.01</v>
+      </c>
+      <c r="Z30">
+        <v>8.5</v>
+      </c>
+      <c r="AA30">
         <v>1.25</v>
       </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.02</v>
-      </c>
-      <c r="Z30">
-        <v>7.8</v>
-      </c>
-      <c r="AA30">
-        <v>1.3</v>
-      </c>
       <c r="AB30">
-        <v>3.41</v>
+        <v>3.82</v>
       </c>
       <c r="AC30">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AD30">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AE30">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AF30">
         <v>1.25</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5525,34 +5525,34 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O32">
         <v>3.8</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q32">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="R32">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S32">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U32">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V32">
         <v>1.47</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X32">
         <v>1.03</v>
@@ -5570,10 +5570,10 @@
         <v>1.99</v>
       </c>
       <c r="AC32">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AD32">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE32">
         <v>1.09</v>
@@ -5694,7 +5694,7 @@
         <v>3.8</v>
       </c>
       <c r="P33">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="Q33">
         <v>2.54</v>
@@ -5854,7 +5854,7 @@
         <v>2.25</v>
       </c>
       <c r="O34">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
         <v>2.97</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P35">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="Q35">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="S35">
+        <v>1.2</v>
+      </c>
+      <c r="T35">
+        <v>3.94</v>
+      </c>
+      <c r="U35">
+        <v>2.04</v>
+      </c>
+      <c r="V35">
+        <v>1.82</v>
+      </c>
+      <c r="W35">
+        <v>1.21</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.08</v>
+      </c>
+      <c r="Z35">
+        <v>7</v>
+      </c>
+      <c r="AA35">
+        <v>1.4</v>
+      </c>
+      <c r="AB35">
+        <v>3</v>
+      </c>
+      <c r="AC35">
+        <v>2</v>
+      </c>
+      <c r="AD35">
+        <v>1.83</v>
+      </c>
+      <c r="AE35">
+        <v>1.33</v>
+      </c>
+      <c r="AF35">
         <v>1.36</v>
       </c>
-      <c r="T35">
-        <v>3.1</v>
-      </c>
-      <c r="U35">
-        <v>2.75</v>
-      </c>
-      <c r="V35">
-        <v>1.43</v>
-      </c>
-      <c r="W35">
-        <v>1.06</v>
-      </c>
-      <c r="X35">
-        <v>1.03</v>
-      </c>
-      <c r="Y35">
-        <v>1.25</v>
-      </c>
-      <c r="Z35">
-        <v>3.7</v>
-      </c>
-      <c r="AA35">
-        <v>1.83</v>
-      </c>
-      <c r="AB35">
-        <v>1.91</v>
-      </c>
-      <c r="AC35">
-        <v>2.93</v>
-      </c>
-      <c r="AD35">
-        <v>1.33</v>
-      </c>
-      <c r="AE35">
-        <v>1.11</v>
-      </c>
-      <c r="AF35">
-        <v>1.67</v>
-      </c>
       <c r="AG35">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
+        <v>1.2</v>
+      </c>
+      <c r="AK35">
         <v>1.3</v>
-      </c>
-      <c r="AK35">
-        <v>1.43</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.74</v>
+        <v>2.6</v>
       </c>
       <c r="O36">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="Q36">
-        <v>3.88</v>
+        <v>3.02</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="U36">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="V36">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="W36">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="AA36">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AB36">
-        <v>2.82</v>
+        <v>1.91</v>
       </c>
       <c r="AC36">
-        <v>2</v>
+        <v>2.93</v>
       </c>
       <c r="AD36">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="AF36">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.1</v>
+        <v>3.74</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>3.05</v>
+        <v>1.88</v>
       </c>
       <c r="Q37">
-        <v>2.36</v>
+        <v>3.88</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="U37">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="W37">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AA37">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AB37">
-        <v>2.17</v>
+        <v>2.82</v>
       </c>
       <c r="AC37">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="AD37">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AF37">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.23</v>
+        <v>1.83</v>
       </c>
       <c r="AK37">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="Q38">
-        <v>3.26</v>
+        <v>2.36</v>
       </c>
       <c r="R38">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
+        <v>1.33</v>
+      </c>
+      <c r="T38">
+        <v>3.4</v>
+      </c>
+      <c r="U38">
+        <v>2.4</v>
+      </c>
+      <c r="V38">
+        <v>1.5</v>
+      </c>
+      <c r="W38">
+        <v>1.1</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
         <v>1.2</v>
       </c>
-      <c r="T38">
-        <v>3.94</v>
-      </c>
-      <c r="U38">
-        <v>2.04</v>
-      </c>
-      <c r="V38">
-        <v>1.82</v>
-      </c>
-      <c r="W38">
-        <v>1.21</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.08</v>
-      </c>
       <c r="Z38">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AA38">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB38">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AC38">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="AD38">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AE38">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7158,7 +7158,7 @@
         <v>4.6</v>
       </c>
       <c r="O42">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P42">
         <v>1.7</v>
@@ -7330,7 +7330,7 @@
         <v>4.5</v>
       </c>
       <c r="R43">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S43">
         <v>1.5</v>
@@ -7348,25 +7348,25 @@
         <v>1.04</v>
       </c>
       <c r="X43">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y43">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z43">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AA43">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="AB43">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC43">
         <v>5.5</v>
       </c>
       <c r="AD43">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AE43">
         <v>1.01</v>
@@ -7375,7 +7375,7 @@
         <v>2.2</v>
       </c>
       <c r="AG43">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AK43">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7653,25 +7653,25 @@
         <v>1.95</v>
       </c>
       <c r="Q45">
-        <v>3.56</v>
+        <v>3.77</v>
       </c>
       <c r="R45">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T45">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U45">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V45">
         <v>1.67</v>
       </c>
       <c r="W45">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X45">
         <v>1.02</v>
@@ -7680,7 +7680,7 @@
         <v>1.07</v>
       </c>
       <c r="Z45">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AA45">
         <v>1.4</v>
@@ -7689,13 +7689,13 @@
         <v>2.56</v>
       </c>
       <c r="AC45">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD45">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE45">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF45">
         <v>1.4</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK45">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8009,7 +8009,7 @@
         <v>5.1</v>
       </c>
       <c r="AA47">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB47">
         <v>2.45</v>
@@ -8160,7 +8160,7 @@
         <v>1.6</v>
       </c>
       <c r="W48">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8206,7 +8206,7 @@
         <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8465,19 +8465,19 @@
         <v>3.9</v>
       </c>
       <c r="P50">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Q50">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R50">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="S50">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U50">
         <v>1.95</v>
@@ -8495,7 +8495,7 @@
         <v>1.06</v>
       </c>
       <c r="Z50">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="AA50">
         <v>1.36</v>
@@ -8504,13 +8504,13 @@
         <v>3.1</v>
       </c>
       <c r="AC50">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD50">
         <v>1.83</v>
       </c>
       <c r="AE50">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AF50">
         <v>1.36</v>
@@ -8695,7 +8695,7 @@
         <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10261,10 +10261,10 @@
         <v>10.5</v>
       </c>
       <c r="Q61">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="R61">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="S61">
         <v>1.17</v>
@@ -10285,10 +10285,10 @@
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AA61">
         <v>1.29</v>
@@ -10297,16 +10297,16 @@
         <v>3.5</v>
       </c>
       <c r="AC61">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AD61">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AE61">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF61">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG61">
         <v>2.2</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="O62">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q62">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="R62">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="S62">
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V62">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W62">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z62">
-        <v>5.88</v>
+        <v>4.9</v>
       </c>
       <c r="AA62">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB62">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AC62">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AD62">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AE62">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AK62">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.91</v>
+        <v>2.41</v>
       </c>
       <c r="O63">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="P63">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="Q63">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="R63">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S63">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T63">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="U63">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="V63">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="W63">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X63">
         <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z63">
-        <v>5.04</v>
+        <v>5.88</v>
       </c>
       <c r="AA63">
+        <v>1.45</v>
+      </c>
+      <c r="AB63">
+        <v>2.72</v>
+      </c>
+      <c r="AC63">
+        <v>2.06</v>
+      </c>
+      <c r="AD63">
+        <v>1.76</v>
+      </c>
+      <c r="AE63">
+        <v>1.29</v>
+      </c>
+      <c r="AF63">
+        <v>1.36</v>
+      </c>
+      <c r="AG63">
+        <v>2.8</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
+        <v>1.2</v>
+      </c>
+      <c r="AK63">
         <v>1.5</v>
-      </c>
-      <c r="AB63">
-        <v>2.55</v>
-      </c>
-      <c r="AC63">
-        <v>2.37</v>
-      </c>
-      <c r="AD63">
-        <v>1.59</v>
-      </c>
-      <c r="AE63">
-        <v>1.23</v>
-      </c>
-      <c r="AF63">
-        <v>1.44</v>
-      </c>
-      <c r="AG63">
-        <v>2.43</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.26</v>
-      </c>
-      <c r="AK63">
-        <v>1.8</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q64">
-        <v>2.61</v>
+        <v>2.33</v>
       </c>
       <c r="R64">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T64">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U64">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="V64">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W64">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z64">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA64">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AB64">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AC64">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="AD64">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AE64">
         <v>1.22</v>
       </c>
       <c r="AF64">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG64">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10910,19 +10910,19 @@
         <v>3.73</v>
       </c>
       <c r="P65">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q65">
         <v>2.65</v>
       </c>
       <c r="R65">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S65">
         <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U65">
         <v>2.3</v>
@@ -10934,7 +10934,7 @@
         <v>1.14</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
         <v>1.18</v>
@@ -10955,13 +10955,13 @@
         <v>1.54</v>
       </c>
       <c r="AE65">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
         <v>1.53</v>
       </c>
       <c r="AG65">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>3.48</v>
       </c>
       <c r="Q66">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="R66">
         <v>2.41</v>
@@ -11097,13 +11097,13 @@
         <v>1.17</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AA66">
         <v>1.48</v>
@@ -11112,19 +11112,19 @@
         <v>2.64</v>
       </c>
       <c r="AC66">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AD66">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE66">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF66">
         <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK66">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,10 +11239,10 @@
         <v>2.87</v>
       </c>
       <c r="Q67">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R67">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="S67">
         <v>1.25</v>
@@ -11254,19 +11254,19 @@
         <v>2.25</v>
       </c>
       <c r="V67">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W67">
         <v>1.15</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA67">
         <v>1.57</v>
@@ -11275,7 +11275,7 @@
         <v>2.38</v>
       </c>
       <c r="AC67">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AD67">
         <v>1.5</v>
@@ -11284,7 +11284,7 @@
         <v>1.2</v>
       </c>
       <c r="AF67">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG67">
         <v>2.4</v>
@@ -11402,34 +11402,34 @@
         <v>3</v>
       </c>
       <c r="Q68">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="R68">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S68">
         <v>1.17</v>
       </c>
       <c r="T68">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U68">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="V68">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="W68">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X68">
         <v>0</v>
       </c>
       <c r="Y68">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>6.42</v>
+        <v>6.5</v>
       </c>
       <c r="AA68">
         <v>1.36</v>
@@ -11438,19 +11438,19 @@
         <v>3.1</v>
       </c>
       <c r="AC68">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AD68">
         <v>1.8</v>
       </c>
       <c r="AE68">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF68">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG68">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
         <v>1.75</v>
@@ -11586,10 +11586,10 @@
         <v>1.15</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z69">
         <v>4.92</v>
@@ -11601,16 +11601,16 @@
         <v>2.43</v>
       </c>
       <c r="AC69">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="AD69">
         <v>1.53</v>
       </c>
       <c r="AE69">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF69">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG69">
         <v>2.05</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -653,7 +653,7 @@
         <v>1.34</v>
       </c>
       <c r="T2">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U2">
         <v>2.65</v>
@@ -677,7 +677,7 @@
         <v>1.93</v>
       </c>
       <c r="AB2">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AC2">
         <v>3.25</v>
@@ -807,19 +807,19 @@
         <v>2.05</v>
       </c>
       <c r="Q3">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="R3">
         <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="U3">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V3">
         <v>1.4</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="O6">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
+        <v>3.02</v>
+      </c>
+      <c r="Q6">
+        <v>2.7</v>
+      </c>
+      <c r="R6">
+        <v>2.16</v>
+      </c>
+      <c r="S6">
+        <v>1.3</v>
+      </c>
+      <c r="T6">
+        <v>3</v>
+      </c>
+      <c r="U6">
+        <v>2.62</v>
+      </c>
+      <c r="V6">
+        <v>1.44</v>
+      </c>
+      <c r="W6">
+        <v>1.09</v>
+      </c>
+      <c r="X6">
+        <v>1.03</v>
+      </c>
+      <c r="Y6">
+        <v>1.22</v>
+      </c>
+      <c r="Z6">
+        <v>3.5</v>
+      </c>
+      <c r="AA6">
+        <v>1.75</v>
+      </c>
+      <c r="AB6">
+        <v>1.93</v>
+      </c>
+      <c r="AC6">
         <v>3.1</v>
       </c>
-      <c r="Q6">
-        <v>2.49</v>
-      </c>
-      <c r="R6">
-        <v>2.59</v>
-      </c>
-      <c r="S6">
+      <c r="AD6">
+        <v>1.36</v>
+      </c>
+      <c r="AE6">
+        <v>1.1</v>
+      </c>
+      <c r="AF6">
+        <v>1.63</v>
+      </c>
+      <c r="AG6">
+        <v>2.09</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.22</v>
       </c>
-      <c r="T6">
-        <v>3.9</v>
-      </c>
-      <c r="U6">
-        <v>2.12</v>
-      </c>
-      <c r="V6">
-        <v>1.69</v>
-      </c>
-      <c r="W6">
-        <v>1.17</v>
-      </c>
-      <c r="X6">
-        <v>1.02</v>
-      </c>
-      <c r="Y6">
-        <v>1.08</v>
-      </c>
-      <c r="Z6">
-        <v>5.45</v>
-      </c>
-      <c r="AA6">
-        <v>1.44</v>
-      </c>
-      <c r="AB6">
-        <v>2.73</v>
-      </c>
-      <c r="AC6">
-        <v>2.11</v>
-      </c>
-      <c r="AD6">
-        <v>1.68</v>
-      </c>
-      <c r="AE6">
-        <v>1.3</v>
-      </c>
-      <c r="AF6">
-        <v>1.4</v>
-      </c>
-      <c r="AG6">
-        <v>2.73</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.21</v>
-      </c>
       <c r="AK6">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,68 +1446,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
-        <v>4.99</v>
+        <v>1.85</v>
       </c>
       <c r="O7">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="P7">
-        <v>1.63</v>
+        <v>3.1</v>
       </c>
       <c r="Q7">
-        <v>6.05</v>
+        <v>2.48</v>
       </c>
       <c r="R7">
-        <v>2.01</v>
+        <v>2.59</v>
       </c>
       <c r="S7">
+        <v>1.22</v>
+      </c>
+      <c r="T7">
+        <v>3.9</v>
+      </c>
+      <c r="U7">
+        <v>2.12</v>
+      </c>
+      <c r="V7">
+        <v>1.7</v>
+      </c>
+      <c r="W7">
+        <v>1.17</v>
+      </c>
+      <c r="X7">
+        <v>1.02</v>
+      </c>
+      <c r="Y7">
+        <v>1.08</v>
+      </c>
+      <c r="Z7">
+        <v>5.45</v>
+      </c>
+      <c r="AA7">
+        <v>1.44</v>
+      </c>
+      <c r="AB7">
+        <v>2.73</v>
+      </c>
+      <c r="AC7">
+        <v>2.11</v>
+      </c>
+      <c r="AD7">
+        <v>1.68</v>
+      </c>
+      <c r="AE7">
+        <v>1.3</v>
+      </c>
+      <c r="AF7">
         <v>1.4</v>
       </c>
-      <c r="T7">
-        <v>2.54</v>
-      </c>
-      <c r="U7">
-        <v>3.29</v>
-      </c>
-      <c r="V7">
-        <v>1.27</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>1.4</v>
-      </c>
-      <c r="Z7">
-        <v>2.65</v>
-      </c>
-      <c r="AA7">
-        <v>2.37</v>
-      </c>
-      <c r="AB7">
-        <v>1.49</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>2.29</v>
-      </c>
       <c r="AG7">
-        <v>1.52</v>
+        <v>2.73</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-14 10:30:00</t>
+          <t>2026-10-14 10:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G8">
@@ -1609,35 +1609,35 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8">
-        <v>1.55</v>
+        <v>4.99</v>
       </c>
       <c r="O8">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="P8">
-        <v>4.9</v>
+        <v>1.63</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W8">
         <v>0</v>
@@ -1646,16 +1646,16 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1667,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-14 11:00:00</t>
+          <t>2026-10-14 10:30:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="O9">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P9">
-        <v>6.13</v>
+        <v>4.9</v>
       </c>
       <c r="Q9">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>6.13</v>
       </c>
       <c r="Q10">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="R10">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U10">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V10">
         <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
         <v>1.03</v>
@@ -1975,28 +1975,28 @@
         <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB10">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="AG10">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>2.62</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-14 12:00:00</t>
+          <t>2026-10-14 11:00:00</t>
         </is>
       </c>
     </row>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,80 +3243,80 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="Q18">
+        <v>2.61</v>
+      </c>
+      <c r="R18">
         <v>2.63</v>
       </c>
-      <c r="R18">
-        <v>2.25</v>
-      </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>4.3</v>
+        <v>5.85</v>
       </c>
       <c r="AA18">
+        <v>1.36</v>
+      </c>
+      <c r="AB18">
+        <v>3.1</v>
+      </c>
+      <c r="AC18">
+        <v>1.89</v>
+      </c>
+      <c r="AD18">
+        <v>1.78</v>
+      </c>
+      <c r="AE18">
+        <v>1.31</v>
+      </c>
+      <c r="AF18">
+        <v>1.36</v>
+      </c>
+      <c r="AG18">
+        <v>2.91</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.17</v>
+      </c>
+      <c r="AK18">
         <v>1.57</v>
-      </c>
-      <c r="AB18">
-        <v>2.14</v>
-      </c>
-      <c r="AC18">
-        <v>2.15</v>
-      </c>
-      <c r="AD18">
-        <v>1.45</v>
-      </c>
-      <c r="AE18">
-        <v>1.14</v>
-      </c>
-      <c r="AF18">
-        <v>1.5</v>
-      </c>
-      <c r="AG18">
-        <v>2.05</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.21</v>
-      </c>
-      <c r="AK18">
-        <v>1.49</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.68</v>
+        <v>2.21</v>
       </c>
       <c r="Q19">
-        <v>2.61</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>5.85</v>
+        <v>4.19</v>
       </c>
       <c r="AA19">
+        <v>1.63</v>
+      </c>
+      <c r="AB19">
+        <v>1.83</v>
+      </c>
+      <c r="AC19">
+        <v>2.52</v>
+      </c>
+      <c r="AD19">
+        <v>1.41</v>
+      </c>
+      <c r="AE19">
+        <v>1.13</v>
+      </c>
+      <c r="AF19">
+        <v>1.44</v>
+      </c>
+      <c r="AG19">
+        <v>2.3</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.09</v>
+      </c>
+      <c r="AK19">
         <v>1.36</v>
-      </c>
-      <c r="AB19">
-        <v>3.1</v>
-      </c>
-      <c r="AC19">
-        <v>1.89</v>
-      </c>
-      <c r="AD19">
-        <v>1.78</v>
-      </c>
-      <c r="AE19">
-        <v>1.31</v>
-      </c>
-      <c r="AF19">
-        <v>1.36</v>
-      </c>
-      <c r="AG19">
-        <v>2.91</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.17</v>
-      </c>
-      <c r="AK19">
-        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="O20">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q20">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U20">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="V20">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>5.73</v>
+        <v>4.3</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="AC20">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AD20">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AE20">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AF20">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>1.97</v>
+        <v>1.49</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,80 +3732,80 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="O21">
-        <v>3.55</v>
+        <v>4.25</v>
       </c>
       <c r="P21">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="Q21">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="R21">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U21">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="V21">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W21">
+        <v>1.13</v>
+      </c>
+      <c r="X21">
+        <v>1.01</v>
+      </c>
+      <c r="Y21">
+        <v>1.07</v>
+      </c>
+      <c r="Z21">
+        <v>5.73</v>
+      </c>
+      <c r="AA21">
+        <v>1.36</v>
+      </c>
+      <c r="AB21">
+        <v>2.3</v>
+      </c>
+      <c r="AC21">
+        <v>1.79</v>
+      </c>
+      <c r="AD21">
+        <v>1.72</v>
+      </c>
+      <c r="AE21">
+        <v>1.2</v>
+      </c>
+      <c r="AF21">
+        <v>1.4</v>
+      </c>
+      <c r="AG21">
+        <v>2.7</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.17</v>
       </c>
-      <c r="X21">
-        <v>1.02</v>
-      </c>
-      <c r="Y21">
-        <v>1.08</v>
-      </c>
-      <c r="Z21">
-        <v>3.6</v>
-      </c>
-      <c r="AA21">
-        <v>1.47</v>
-      </c>
-      <c r="AB21">
-        <v>2.59</v>
-      </c>
-      <c r="AC21">
-        <v>2.04</v>
-      </c>
-      <c r="AD21">
-        <v>1.67</v>
-      </c>
-      <c r="AE21">
-        <v>1.28</v>
-      </c>
-      <c r="AF21">
-        <v>1.38</v>
-      </c>
-      <c r="AG21">
-        <v>2.3</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ21">
-        <v>1.25</v>
-      </c>
       <c r="AK21">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P22">
-        <v>2.21</v>
+        <v>2.96</v>
       </c>
       <c r="Q22">
-        <v>3.36</v>
+        <v>2.46</v>
       </c>
       <c r="R22">
-        <v>2.05</v>
+        <v>2.41</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U22">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>4.19</v>
+        <v>3.6</v>
       </c>
       <c r="AA22">
-        <v>1.63</v>
+        <v>1.47</v>
       </c>
       <c r="AB22">
-        <v>1.83</v>
+        <v>2.59</v>
       </c>
       <c r="AC22">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="AD22">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AE22">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AG22">
         <v>2.3</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>2.7</v>
       </c>
       <c r="AC25">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AD25">
         <v>1.74</v>
@@ -4457,7 +4457,7 @@
         <v>1.17</v>
       </c>
       <c r="AK25">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4571,13 +4571,13 @@
         <v>1.66</v>
       </c>
       <c r="V26">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="W26">
         <v>1.32</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26">
         <v>1.01</v>
@@ -4713,10 +4713,10 @@
         <v>2.03</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P27">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="Q27">
         <v>2.54</v>
@@ -4894,7 +4894,7 @@
         <v>4.8</v>
       </c>
       <c r="U28">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V28">
         <v>1.93</v>
@@ -4915,7 +4915,7 @@
         <v>1.3</v>
       </c>
       <c r="AB28">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="AC28">
         <v>1.74</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,65 +5036,65 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="O29">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="P29">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q29">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="S29">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T29">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="U29">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="V29">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="W29">
+        <v>1.3</v>
+      </c>
+      <c r="X29">
+        <v>1</v>
+      </c>
+      <c r="Y29">
+        <v>1.01</v>
+      </c>
+      <c r="Z29">
+        <v>8.5</v>
+      </c>
+      <c r="AA29">
         <v>1.25</v>
       </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>1.03</v>
-      </c>
-      <c r="Z29">
-        <v>7.3</v>
-      </c>
-      <c r="AA29">
-        <v>1.29</v>
-      </c>
       <c r="AB29">
+        <v>3.82</v>
+      </c>
+      <c r="AC29">
+        <v>1.57</v>
+      </c>
+      <c r="AD29">
+        <v>2.17</v>
+      </c>
+      <c r="AE29">
+        <v>1.55</v>
+      </c>
+      <c r="AF29">
+        <v>1.25</v>
+      </c>
+      <c r="AG29">
         <v>3.5</v>
       </c>
-      <c r="AC29">
-        <v>1.72</v>
-      </c>
-      <c r="AD29">
-        <v>1.97</v>
-      </c>
-      <c r="AE29">
-        <v>1.4</v>
-      </c>
-      <c r="AF29">
-        <v>1.4</v>
-      </c>
-      <c r="AG29">
-        <v>2.7</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AK29">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.86</v>
+        <v>1.4</v>
       </c>
       <c r="O30">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="P30">
+        <v>5.3</v>
+      </c>
+      <c r="Q30">
+        <v>1.78</v>
+      </c>
+      <c r="R30">
+        <v>2.88</v>
+      </c>
+      <c r="S30">
+        <v>1.17</v>
+      </c>
+      <c r="T30">
+        <v>4.6</v>
+      </c>
+      <c r="U30">
+        <v>1.79</v>
+      </c>
+      <c r="V30">
+        <v>1.91</v>
+      </c>
+      <c r="W30">
+        <v>1.25</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.03</v>
+      </c>
+      <c r="Z30">
+        <v>7.3</v>
+      </c>
+      <c r="AA30">
+        <v>1.29</v>
+      </c>
+      <c r="AB30">
+        <v>3.5</v>
+      </c>
+      <c r="AC30">
+        <v>1.72</v>
+      </c>
+      <c r="AD30">
+        <v>1.97</v>
+      </c>
+      <c r="AE30">
+        <v>1.4</v>
+      </c>
+      <c r="AF30">
+        <v>1.4</v>
+      </c>
+      <c r="AG30">
+        <v>2.7</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.09</v>
+      </c>
+      <c r="AK30">
         <v>2.75</v>
-      </c>
-      <c r="Q30">
-        <v>2.2</v>
-      </c>
-      <c r="R30">
-        <v>2.91</v>
-      </c>
-      <c r="S30">
-        <v>1.13</v>
-      </c>
-      <c r="T30">
-        <v>5.5</v>
-      </c>
-      <c r="U30">
-        <v>1.74</v>
-      </c>
-      <c r="V30">
-        <v>2.04</v>
-      </c>
-      <c r="W30">
-        <v>1.3</v>
-      </c>
-      <c r="X30">
-        <v>1</v>
-      </c>
-      <c r="Y30">
-        <v>1.01</v>
-      </c>
-      <c r="Z30">
-        <v>8.5</v>
-      </c>
-      <c r="AA30">
-        <v>1.25</v>
-      </c>
-      <c r="AB30">
-        <v>3.82</v>
-      </c>
-      <c r="AC30">
-        <v>1.57</v>
-      </c>
-      <c r="AD30">
-        <v>2.17</v>
-      </c>
-      <c r="AE30">
-        <v>1.55</v>
-      </c>
-      <c r="AF30">
-        <v>1.25</v>
-      </c>
-      <c r="AG30">
-        <v>3.5</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.2</v>
-      </c>
-      <c r="AK30">
-        <v>1.85</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="O31">
         <v>3.65</v>
@@ -5371,13 +5371,13 @@
         <v>1.99</v>
       </c>
       <c r="Q31">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="R31">
         <v>2.51</v>
       </c>
       <c r="S31">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="T31">
         <v>4.5</v>
@@ -5407,7 +5407,7 @@
         <v>3.4</v>
       </c>
       <c r="AC31">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AD31">
         <v>1.98</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="O32">
         <v>3.8</v>
       </c>
       <c r="P32">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="Q32">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="R32">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="S32">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T32">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U32">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="V32">
+        <v>1.64</v>
+      </c>
+      <c r="W32">
+        <v>1.13</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.13</v>
+      </c>
+      <c r="Z32">
+        <v>6</v>
+      </c>
+      <c r="AA32">
         <v>1.47</v>
       </c>
-      <c r="W32">
-        <v>1.07</v>
-      </c>
-      <c r="X32">
-        <v>1.03</v>
-      </c>
-      <c r="Y32">
-        <v>1.19</v>
-      </c>
-      <c r="Z32">
-        <v>3.78</v>
-      </c>
-      <c r="AA32">
-        <v>1.76</v>
-      </c>
       <c r="AB32">
-        <v>1.99</v>
+        <v>2.63</v>
       </c>
       <c r="AC32">
-        <v>2.99</v>
+        <v>2.2</v>
       </c>
       <c r="AD32">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="AE32">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AF32">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG32">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AK32">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.37</v>
+        <v>1.75</v>
       </c>
       <c r="O33">
         <v>3.8</v>
       </c>
       <c r="P33">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="Q33">
-        <v>2.54</v>
+        <v>2.28</v>
       </c>
       <c r="R33">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="S33">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="V33">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>3.78</v>
       </c>
       <c r="AA33">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AB33">
-        <v>2.63</v>
+        <v>1.99</v>
       </c>
       <c r="AC33">
-        <v>2.2</v>
+        <v>2.99</v>
       </c>
       <c r="AD33">
-        <v>1.64</v>
+        <v>1.39</v>
       </c>
       <c r="AE33">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AK33">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="Q35">
-        <v>3.26</v>
+        <v>2.36</v>
       </c>
       <c r="R35">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>3.4</v>
+      </c>
+      <c r="U35">
+        <v>2.4</v>
+      </c>
+      <c r="V35">
+        <v>1.5</v>
+      </c>
+      <c r="W35">
+        <v>1.1</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
         <v>1.2</v>
       </c>
-      <c r="T35">
-        <v>3.94</v>
-      </c>
-      <c r="U35">
-        <v>2.04</v>
-      </c>
-      <c r="V35">
-        <v>1.82</v>
-      </c>
-      <c r="W35">
-        <v>1.21</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.08</v>
-      </c>
       <c r="Z35">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB35">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AC35">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="AD35">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AE35">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,55 +6340,55 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.74</v>
+        <v>2.11</v>
       </c>
       <c r="O37">
         <v>3.9</v>
       </c>
       <c r="P37">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q37">
-        <v>3.88</v>
+        <v>2.49</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="S37">
         <v>1.2</v>
       </c>
       <c r="T37">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="U37">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="V37">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA37">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB37">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AC37">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AD37">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE37">
         <v>1.29</v>
@@ -6397,7 +6397,7 @@
         <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AK37">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.1</v>
+        <v>3.74</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>3.05</v>
+        <v>1.88</v>
       </c>
       <c r="Q38">
-        <v>2.36</v>
+        <v>3.88</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AA38">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="AB38">
-        <v>2.17</v>
+        <v>2.82</v>
       </c>
       <c r="AC38">
-        <v>2.68</v>
+        <v>2</v>
       </c>
       <c r="AD38">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AE38">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>1.83</v>
       </c>
       <c r="AK38">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.11</v>
+        <v>3.1</v>
       </c>
       <c r="O39">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P39">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q39">
-        <v>2.49</v>
+        <v>3.26</v>
       </c>
       <c r="R39">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="S39">
         <v>1.2</v>
       </c>
       <c r="T39">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="U39">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="V39">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="W39">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA39">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AC39">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AD39">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE39">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF39">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG39">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P62">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q62">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="R62">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="S62">
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U62">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V62">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z62">
-        <v>4.9</v>
+        <v>5.88</v>
       </c>
       <c r="AA62">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AB62">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="AC62">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AD62">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AE62">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF62">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG62">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK62">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,80 +10578,80 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="O63">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q63">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="R63">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="S63">
         <v>1.2</v>
       </c>
       <c r="T63">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U63">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V63">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="W63">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z63">
-        <v>5.88</v>
+        <v>4.9</v>
       </c>
       <c r="AA63">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB63">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AC63">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AD63">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AE63">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF63">
+        <v>1.44</v>
+      </c>
+      <c r="AG63">
+        <v>2.62</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ63">
         <v>1.36</v>
       </c>
-      <c r="AG63">
-        <v>2.8</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ63">
-        <v>1.2</v>
-      </c>
       <c r="AK63">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,31 +11230,31 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="O67">
-        <v>3.68</v>
+        <v>4.8</v>
       </c>
       <c r="P67">
-        <v>2.87</v>
+        <v>6</v>
       </c>
       <c r="Q67">
-        <v>2.46</v>
+        <v>1.88</v>
       </c>
       <c r="R67">
-        <v>2.23</v>
+        <v>2.69</v>
       </c>
       <c r="S67">
         <v>1.25</v>
       </c>
       <c r="T67">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U67">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="V67">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="W67">
         <v>1.15</v>
@@ -11266,28 +11266,28 @@
         <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="AA67">
         <v>1.57</v>
       </c>
       <c r="AB67">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AC67">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AD67">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE67">
         <v>1.2</v>
       </c>
       <c r="AF67">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AK67">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="O68">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P68">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q68">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="R68">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="S68">
+        <v>1.25</v>
+      </c>
+      <c r="T68">
+        <v>3.5</v>
+      </c>
+      <c r="U68">
+        <v>2.25</v>
+      </c>
+      <c r="V68">
+        <v>1.55</v>
+      </c>
+      <c r="W68">
+        <v>1.15</v>
+      </c>
+      <c r="X68">
+        <v>1.01</v>
+      </c>
+      <c r="Y68">
         <v>1.17</v>
       </c>
-      <c r="T68">
-        <v>4.5</v>
-      </c>
-      <c r="U68">
-        <v>1.94</v>
-      </c>
-      <c r="V68">
-        <v>1.88</v>
-      </c>
-      <c r="W68">
-        <v>1.22</v>
-      </c>
-      <c r="X68">
-        <v>0</v>
-      </c>
-      <c r="Y68">
-        <v>1.1</v>
-      </c>
       <c r="Z68">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AA68">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB68">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AC68">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="AD68">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AE68">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AF68">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG68">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,80 +11556,80 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="O69">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="P69">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q69">
+        <v>2.32</v>
+      </c>
+      <c r="R69">
+        <v>2.5</v>
+      </c>
+      <c r="S69">
+        <v>1.17</v>
+      </c>
+      <c r="T69">
+        <v>4.5</v>
+      </c>
+      <c r="U69">
+        <v>1.94</v>
+      </c>
+      <c r="V69">
         <v>1.88</v>
       </c>
-      <c r="R69">
-        <v>2.69</v>
-      </c>
-      <c r="S69">
+      <c r="W69">
+        <v>1.22</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>1.1</v>
+      </c>
+      <c r="Z69">
+        <v>6.5</v>
+      </c>
+      <c r="AA69">
+        <v>1.36</v>
+      </c>
+      <c r="AB69">
+        <v>3.1</v>
+      </c>
+      <c r="AC69">
+        <v>1.9</v>
+      </c>
+      <c r="AD69">
+        <v>1.8</v>
+      </c>
+      <c r="AE69">
+        <v>1.36</v>
+      </c>
+      <c r="AF69">
+        <v>1.36</v>
+      </c>
+      <c r="AG69">
+        <v>3.1</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
         <v>1.25</v>
       </c>
-      <c r="T69">
-        <v>3.8</v>
-      </c>
-      <c r="U69">
-        <v>2.32</v>
-      </c>
-      <c r="V69">
-        <v>1.59</v>
-      </c>
-      <c r="W69">
-        <v>1.15</v>
-      </c>
-      <c r="X69">
-        <v>1.01</v>
-      </c>
-      <c r="Y69">
-        <v>1.17</v>
-      </c>
-      <c r="Z69">
-        <v>4.92</v>
-      </c>
-      <c r="AA69">
-        <v>1.57</v>
-      </c>
-      <c r="AB69">
-        <v>2.43</v>
-      </c>
-      <c r="AC69">
-        <v>2.45</v>
-      </c>
-      <c r="AD69">
-        <v>1.53</v>
-      </c>
-      <c r="AE69">
-        <v>1.2</v>
-      </c>
-      <c r="AF69">
+      <c r="AK69">
         <v>1.75</v>
-      </c>
-      <c r="AG69">
-        <v>2.05</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.14</v>
-      </c>
-      <c r="AK69">
-        <v>2.7</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.99</v>
+        <v>3.76</v>
       </c>
       <c r="O2">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="P2">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q2">
         <v>3.7</v>
@@ -677,7 +677,7 @@
         <v>1.93</v>
       </c>
       <c r="AB2">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC2">
         <v>3.25</v>
@@ -689,10 +689,10 @@
         <v>1.13</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.57</v>
       </c>
       <c r="AK2">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,7 +807,7 @@
         <v>2.05</v>
       </c>
       <c r="Q3">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R3">
         <v>2.1</v>
@@ -967,13 +967,13 @@
         <v>3.7</v>
       </c>
       <c r="P4">
-        <v>4.77</v>
+        <v>4.4</v>
       </c>
       <c r="Q4">
         <v>2.18</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
         <v>1.3</v>
@@ -1163,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC5">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>4.9</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="O10">
         <v>4.05</v>
@@ -1948,7 +1948,7 @@
         <v>6.13</v>
       </c>
       <c r="Q10">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R10">
         <v>2.3</v>
@@ -2261,17 +2261,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N12">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O12">
         <v>3.4</v>
       </c>
       <c r="P12">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="Q12">
         <v>2.62</v>
@@ -2289,7 +2289,7 @@
         <v>2.5</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
         <v>1.07</v>
@@ -2298,10 +2298,10 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="AA12">
         <v>1.66</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="Q18">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="R18">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="V18">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>5.85</v>
+        <v>4.3</v>
       </c>
       <c r="AA18">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="AD18">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AE18">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
+        <v>2.1</v>
+      </c>
+      <c r="O19">
+        <v>3.7</v>
+      </c>
+      <c r="P19">
         <v>2.7</v>
       </c>
-      <c r="O19">
-        <v>3.4</v>
-      </c>
-      <c r="P19">
-        <v>2.21</v>
-      </c>
       <c r="Q19">
-        <v>3.36</v>
+        <v>2.61</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z19">
-        <v>4.19</v>
+        <v>5.85</v>
       </c>
       <c r="AA19">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB19">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="AC19">
-        <v>2.52</v>
+        <v>1.89</v>
       </c>
       <c r="AD19">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF19">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="P20">
+        <v>4.05</v>
+      </c>
+      <c r="Q20">
+        <v>1.95</v>
+      </c>
+      <c r="R20">
+        <v>2.3</v>
+      </c>
+      <c r="S20">
+        <v>1.2</v>
+      </c>
+      <c r="T20">
+        <v>3</v>
+      </c>
+      <c r="U20">
+        <v>1.8</v>
+      </c>
+      <c r="V20">
+        <v>1.71</v>
+      </c>
+      <c r="W20">
+        <v>1.13</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.07</v>
+      </c>
+      <c r="Z20">
+        <v>3.75</v>
+      </c>
+      <c r="AA20">
+        <v>1.37</v>
+      </c>
+      <c r="AB20">
+        <v>2.3</v>
+      </c>
+      <c r="AC20">
+        <v>1.8</v>
+      </c>
+      <c r="AD20">
+        <v>1.74</v>
+      </c>
+      <c r="AE20">
+        <v>1.2</v>
+      </c>
+      <c r="AF20">
+        <v>1.4</v>
+      </c>
+      <c r="AG20">
         <v>2.62</v>
       </c>
-      <c r="Q20">
-        <v>2.63</v>
-      </c>
-      <c r="R20">
-        <v>2.25</v>
-      </c>
-      <c r="S20">
-        <v>1.25</v>
-      </c>
-      <c r="T20">
-        <v>3.5</v>
-      </c>
-      <c r="U20">
-        <v>1.98</v>
-      </c>
-      <c r="V20">
-        <v>1.53</v>
-      </c>
-      <c r="W20">
-        <v>1.08</v>
-      </c>
-      <c r="X20">
-        <v>1.02</v>
-      </c>
-      <c r="Y20">
-        <v>1.15</v>
-      </c>
-      <c r="Z20">
-        <v>4.3</v>
-      </c>
-      <c r="AA20">
-        <v>1.57</v>
-      </c>
-      <c r="AB20">
-        <v>2.14</v>
-      </c>
-      <c r="AC20">
-        <v>2.15</v>
-      </c>
-      <c r="AD20">
-        <v>1.45</v>
-      </c>
-      <c r="AE20">
-        <v>1.14</v>
-      </c>
-      <c r="AF20">
-        <v>1.5</v>
-      </c>
-      <c r="AG20">
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>1.06</v>
+      </c>
+      <c r="AK20">
         <v>2.05</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.21</v>
-      </c>
-      <c r="AK20">
-        <v>1.49</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,65 +3732,65 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="O21">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q21">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
         <v>1.2</v>
       </c>
       <c r="T21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="V21">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W21">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>5.73</v>
+        <v>3.6</v>
       </c>
       <c r="AA21">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AB21">
+        <v>2.56</v>
+      </c>
+      <c r="AC21">
+        <v>1.84</v>
+      </c>
+      <c r="AD21">
+        <v>1.52</v>
+      </c>
+      <c r="AE21">
+        <v>1.29</v>
+      </c>
+      <c r="AF21">
+        <v>1.3</v>
+      </c>
+      <c r="AG21">
         <v>2.3</v>
       </c>
-      <c r="AC21">
-        <v>1.79</v>
-      </c>
-      <c r="AD21">
-        <v>1.72</v>
-      </c>
-      <c r="AE21">
-        <v>1.2</v>
-      </c>
-      <c r="AF21">
-        <v>1.4</v>
-      </c>
-      <c r="AG21">
-        <v>2.7</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
+        <v>2.7</v>
+      </c>
+      <c r="O22">
+        <v>3.4</v>
+      </c>
+      <c r="P22">
+        <v>2.21</v>
+      </c>
+      <c r="Q22">
+        <v>3.36</v>
+      </c>
+      <c r="R22">
         <v>2.05</v>
       </c>
-      <c r="O22">
-        <v>3.55</v>
-      </c>
-      <c r="P22">
-        <v>2.96</v>
-      </c>
-      <c r="Q22">
-        <v>2.46</v>
-      </c>
-      <c r="R22">
-        <v>2.41</v>
-      </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="U22">
-        <v>2.1</v>
+        <v>2.51</v>
       </c>
       <c r="V22">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
-        <v>3.6</v>
+        <v>4.23</v>
       </c>
       <c r="AA22">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="AB22">
-        <v>2.59</v>
+        <v>2.1</v>
       </c>
       <c r="AC22">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="AD22">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AF22">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
         <v>2.3</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK22">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O24">
         <v>3.1</v>
       </c>
       <c r="P24">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q24">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="R24">
         <v>2.01</v>
       </c>
       <c r="S24">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T24">
         <v>2.88</v>
       </c>
       <c r="U24">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="V24">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z24">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB24">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AC24">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="AD24">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AK24">
         <v>1.33</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="O29">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="P29">
+        <v>5.3</v>
+      </c>
+      <c r="Q29">
+        <v>1.78</v>
+      </c>
+      <c r="R29">
+        <v>2.88</v>
+      </c>
+      <c r="S29">
+        <v>1.17</v>
+      </c>
+      <c r="T29">
+        <v>4.6</v>
+      </c>
+      <c r="U29">
+        <v>1.79</v>
+      </c>
+      <c r="V29">
+        <v>1.91</v>
+      </c>
+      <c r="W29">
+        <v>1.25</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>1.03</v>
+      </c>
+      <c r="Z29">
+        <v>7.3</v>
+      </c>
+      <c r="AA29">
+        <v>1.29</v>
+      </c>
+      <c r="AB29">
+        <v>3.5</v>
+      </c>
+      <c r="AC29">
+        <v>1.72</v>
+      </c>
+      <c r="AD29">
+        <v>1.97</v>
+      </c>
+      <c r="AE29">
+        <v>1.4</v>
+      </c>
+      <c r="AF29">
+        <v>1.4</v>
+      </c>
+      <c r="AG29">
+        <v>2.7</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.09</v>
+      </c>
+      <c r="AK29">
         <v>2.75</v>
-      </c>
-      <c r="Q29">
-        <v>2.2</v>
-      </c>
-      <c r="R29">
-        <v>2.91</v>
-      </c>
-      <c r="S29">
-        <v>1.15</v>
-      </c>
-      <c r="T29">
-        <v>5.5</v>
-      </c>
-      <c r="U29">
-        <v>1.68</v>
-      </c>
-      <c r="V29">
-        <v>2.04</v>
-      </c>
-      <c r="W29">
-        <v>1.3</v>
-      </c>
-      <c r="X29">
-        <v>1</v>
-      </c>
-      <c r="Y29">
-        <v>1.01</v>
-      </c>
-      <c r="Z29">
-        <v>8.5</v>
-      </c>
-      <c r="AA29">
-        <v>1.25</v>
-      </c>
-      <c r="AB29">
-        <v>3.82</v>
-      </c>
-      <c r="AC29">
-        <v>1.57</v>
-      </c>
-      <c r="AD29">
-        <v>2.17</v>
-      </c>
-      <c r="AE29">
-        <v>1.55</v>
-      </c>
-      <c r="AF29">
-        <v>1.25</v>
-      </c>
-      <c r="AG29">
-        <v>3.5</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.2</v>
-      </c>
-      <c r="AK29">
-        <v>1.85</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,65 +5199,65 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="O30">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="P30">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q30">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="R30">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="S30">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T30">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="U30">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="V30">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="W30">
+        <v>1.3</v>
+      </c>
+      <c r="X30">
+        <v>1</v>
+      </c>
+      <c r="Y30">
+        <v>1.01</v>
+      </c>
+      <c r="Z30">
+        <v>8.5</v>
+      </c>
+      <c r="AA30">
         <v>1.25</v>
       </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.03</v>
-      </c>
-      <c r="Z30">
-        <v>7.3</v>
-      </c>
-      <c r="AA30">
-        <v>1.29</v>
-      </c>
       <c r="AB30">
+        <v>3.82</v>
+      </c>
+      <c r="AC30">
+        <v>1.57</v>
+      </c>
+      <c r="AD30">
+        <v>2.17</v>
+      </c>
+      <c r="AE30">
+        <v>1.55</v>
+      </c>
+      <c r="AF30">
+        <v>1.25</v>
+      </c>
+      <c r="AG30">
         <v>3.5</v>
       </c>
-      <c r="AC30">
-        <v>1.72</v>
-      </c>
-      <c r="AD30">
-        <v>1.97</v>
-      </c>
-      <c r="AE30">
-        <v>1.4</v>
-      </c>
-      <c r="AF30">
-        <v>1.4</v>
-      </c>
-      <c r="AG30">
-        <v>2.7</v>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AK30">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="Q32">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="R32">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="T32">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>2.15</v>
+        <v>2.84</v>
       </c>
       <c r="V32">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="W32">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y32">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="AA32">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="AB32">
-        <v>2.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC32">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
-        <v>1.64</v>
+        <v>1.34</v>
       </c>
       <c r="AE32">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AK32">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P33">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="Q33">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R33">
         <v>2.14</v>
@@ -5712,7 +5712,7 @@
         <v>2.6</v>
       </c>
       <c r="V33">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
         <v>1.07</v>
@@ -5721,25 +5721,25 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="AA33">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB33">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC33">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="AD33">
         <v>1.39</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
         <v>1.7</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,65 +5851,65 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>2.97</v>
+        <v>2.42</v>
       </c>
       <c r="Q34">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="U34">
+        <v>2.18</v>
+      </c>
+      <c r="V34">
+        <v>1.67</v>
+      </c>
+      <c r="W34">
+        <v>1.13</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.13</v>
+      </c>
+      <c r="Z34">
+        <v>6</v>
+      </c>
+      <c r="AA34">
+        <v>1.47</v>
+      </c>
+      <c r="AB34">
+        <v>2.65</v>
+      </c>
+      <c r="AC34">
+        <v>2.21</v>
+      </c>
+      <c r="AD34">
+        <v>1.64</v>
+      </c>
+      <c r="AE34">
+        <v>1.25</v>
+      </c>
+      <c r="AF34">
+        <v>1.44</v>
+      </c>
+      <c r="AG34">
         <v>2.62</v>
       </c>
-      <c r="V34">
-        <v>1.37</v>
-      </c>
-      <c r="W34">
-        <v>1.03</v>
-      </c>
-      <c r="X34">
-        <v>1.04</v>
-      </c>
-      <c r="Y34">
-        <v>1.24</v>
-      </c>
-      <c r="Z34">
-        <v>3.34</v>
-      </c>
-      <c r="AA34">
-        <v>1.94</v>
-      </c>
-      <c r="AB34">
-        <v>1.84</v>
-      </c>
-      <c r="AC34">
-        <v>3.2</v>
-      </c>
-      <c r="AD34">
-        <v>1.33</v>
-      </c>
-      <c r="AE34">
-        <v>1.06</v>
-      </c>
-      <c r="AF34">
-        <v>1.75</v>
-      </c>
-      <c r="AG34">
-        <v>1.95</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.27</v>
+        <v>1.46</v>
       </c>
       <c r="AK34">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P35">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="Q35">
-        <v>2.36</v>
+        <v>3.26</v>
       </c>
       <c r="R35">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="S35">
+        <v>1.2</v>
+      </c>
+      <c r="T35">
+        <v>3.94</v>
+      </c>
+      <c r="U35">
+        <v>2.04</v>
+      </c>
+      <c r="V35">
+        <v>1.82</v>
+      </c>
+      <c r="W35">
+        <v>1.21</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.08</v>
+      </c>
+      <c r="Z35">
+        <v>7</v>
+      </c>
+      <c r="AA35">
+        <v>1.4</v>
+      </c>
+      <c r="AB35">
+        <v>3</v>
+      </c>
+      <c r="AC35">
+        <v>2</v>
+      </c>
+      <c r="AD35">
+        <v>1.83</v>
+      </c>
+      <c r="AE35">
         <v>1.33</v>
       </c>
-      <c r="T35">
-        <v>3.4</v>
-      </c>
-      <c r="U35">
-        <v>2.4</v>
-      </c>
-      <c r="V35">
-        <v>1.5</v>
-      </c>
-      <c r="W35">
-        <v>1.1</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
+      <c r="AF35">
+        <v>1.36</v>
+      </c>
+      <c r="AG35">
+        <v>3</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.2</v>
       </c>
-      <c r="Z35">
-        <v>4.2</v>
-      </c>
-      <c r="AA35">
-        <v>1.72</v>
-      </c>
-      <c r="AB35">
-        <v>2.17</v>
-      </c>
-      <c r="AC35">
-        <v>2.68</v>
-      </c>
-      <c r="AD35">
-        <v>1.47</v>
-      </c>
-      <c r="AE35">
-        <v>1.14</v>
-      </c>
-      <c r="AF35">
-        <v>1.6</v>
-      </c>
-      <c r="AG35">
-        <v>2.3</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.23</v>
-      </c>
       <c r="AK35">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,55 +6340,55 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.11</v>
+        <v>3.74</v>
       </c>
       <c r="O37">
         <v>3.9</v>
       </c>
       <c r="P37">
-        <v>2.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q37">
-        <v>2.49</v>
+        <v>3.88</v>
       </c>
       <c r="R37">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
         <v>1.2</v>
       </c>
       <c r="T37">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="U37">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="W37">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB37">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AC37">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AD37">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE37">
         <v>1.29</v>
@@ -6397,7 +6397,7 @@
         <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AK37">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.74</v>
+        <v>2.1</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>1.88</v>
+        <v>3.05</v>
       </c>
       <c r="Q38">
-        <v>3.88</v>
+        <v>2.36</v>
       </c>
       <c r="R38">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
+        <v>1.33</v>
+      </c>
+      <c r="T38">
+        <v>3.4</v>
+      </c>
+      <c r="U38">
+        <v>2.4</v>
+      </c>
+      <c r="V38">
+        <v>1.5</v>
+      </c>
+      <c r="W38">
+        <v>1.1</v>
+      </c>
+      <c r="X38">
+        <v>1.01</v>
+      </c>
+      <c r="Y38">
         <v>1.2</v>
       </c>
-      <c r="T38">
+      <c r="Z38">
         <v>4.2</v>
       </c>
-      <c r="U38">
-        <v>2</v>
-      </c>
-      <c r="V38">
-        <v>1.79</v>
-      </c>
-      <c r="W38">
-        <v>1.17</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.08</v>
-      </c>
-      <c r="Z38">
-        <v>7</v>
-      </c>
       <c r="AA38">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AB38">
-        <v>2.82</v>
+        <v>2.17</v>
       </c>
       <c r="AC38">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="AD38">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AE38">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P39">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q39">
-        <v>3.26</v>
+        <v>2.49</v>
       </c>
       <c r="R39">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="S39">
         <v>1.2</v>
       </c>
       <c r="T39">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="U39">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="V39">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="W39">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA39">
+        <v>1.44</v>
+      </c>
+      <c r="AB39">
+        <v>2.8</v>
+      </c>
+      <c r="AC39">
+        <v>2.11</v>
+      </c>
+      <c r="AD39">
+        <v>1.73</v>
+      </c>
+      <c r="AE39">
+        <v>1.29</v>
+      </c>
+      <c r="AF39">
         <v>1.4</v>
       </c>
-      <c r="AB39">
-        <v>3</v>
-      </c>
-      <c r="AC39">
-        <v>2</v>
-      </c>
-      <c r="AD39">
-        <v>1.83</v>
-      </c>
-      <c r="AE39">
+      <c r="AG39">
+        <v>2.89</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.33</v>
       </c>
-      <c r="AF39">
-        <v>1.36</v>
-      </c>
-      <c r="AG39">
-        <v>3</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.2</v>
-      </c>
       <c r="AK39">
-        <v>1.3</v>
+        <v>1.72</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AA42">
         <v>1.63</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AK42">
         <v>1.16</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="O43">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P43">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q43">
         <v>4.5</v>
@@ -7333,13 +7333,13 @@
         <v>1.72</v>
       </c>
       <c r="S43">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="T43">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U43">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V43">
         <v>1.25</v>
@@ -7351,16 +7351,16 @@
         <v>1.08</v>
       </c>
       <c r="Y43">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z43">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AA43">
-        <v>2.61</v>
+        <v>2.43</v>
       </c>
       <c r="AB43">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC43">
         <v>5.5</v>
@@ -7372,7 +7372,7 @@
         <v>1.01</v>
       </c>
       <c r="AF43">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG43">
         <v>1.73</v>
@@ -7391,7 +7391,7 @@
         <v>1.36</v>
       </c>
       <c r="AK43">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7487,7 +7487,7 @@
         <v>3.4</v>
       </c>
       <c r="P44">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q44">
         <v>3.25</v>
@@ -7535,7 +7535,7 @@
         <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG44">
         <v>2.3</v>
@@ -7554,7 +7554,7 @@
         <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.96</v>
+        <v>3.33</v>
       </c>
       <c r="O45">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P45">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Q45">
         <v>3.77</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
         <v>2.32</v>
@@ -8160,7 +8160,7 @@
         <v>1.6</v>
       </c>
       <c r="W48">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8335,7 +8335,7 @@
         <v>8</v>
       </c>
       <c r="AA49">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB49">
         <v>3.38</v>
@@ -8462,13 +8462,13 @@
         <v>1.95</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="P50">
-        <v>2.87</v>
+        <v>2.68</v>
       </c>
       <c r="Q50">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R50">
         <v>2.67</v>
@@ -8492,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z50">
         <v>6.3</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8661,7 +8661,7 @@
         <v>6.5</v>
       </c>
       <c r="AA51">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB51">
         <v>2.83</v>
@@ -8797,7 +8797,7 @@
         <v>2.38</v>
       </c>
       <c r="R52">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8806,7 +8806,7 @@
         <v>4</v>
       </c>
       <c r="U52">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="V52">
         <v>1.67</v>
@@ -8821,22 +8821,22 @@
         <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>5.38</v>
+        <v>5.26</v>
       </c>
       <c r="AA52">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB52">
         <v>2.63</v>
       </c>
       <c r="AC52">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AD52">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE52">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF52">
         <v>1.44</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.25</v>
+        <v>2.41</v>
       </c>
       <c r="O61">
-        <v>7.36</v>
+        <v>3.75</v>
       </c>
       <c r="P61">
-        <v>10.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q61">
-        <v>1.51</v>
+        <v>2.9</v>
       </c>
       <c r="R61">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="U61">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="V61">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="W61">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="X61">
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>8</v>
+        <v>5.88</v>
       </c>
       <c r="AA61">
+        <v>1.45</v>
+      </c>
+      <c r="AB61">
+        <v>2.72</v>
+      </c>
+      <c r="AC61">
+        <v>2.06</v>
+      </c>
+      <c r="AD61">
+        <v>1.76</v>
+      </c>
+      <c r="AE61">
         <v>1.29</v>
       </c>
-      <c r="AB61">
-        <v>3.5</v>
-      </c>
-      <c r="AC61">
-        <v>1.8</v>
-      </c>
-      <c r="AD61">
-        <v>2</v>
-      </c>
-      <c r="AE61">
-        <v>1.4</v>
-      </c>
       <c r="AF61">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AG61">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>3.8</v>
+        <v>1.53</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="O62">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P62">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q62">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="R62">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="S62">
         <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V62">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="W62">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z62">
-        <v>5.88</v>
+        <v>4.9</v>
       </c>
       <c r="AA62">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB62">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="AC62">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AD62">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AE62">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF62">
+        <v>1.44</v>
+      </c>
+      <c r="AG62">
+        <v>2.62</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.36</v>
       </c>
-      <c r="AG62">
-        <v>2.8</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.2</v>
-      </c>
       <c r="AK62">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,65 +10578,65 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="O63">
-        <v>3.6</v>
+        <v>7.36</v>
       </c>
       <c r="P63">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q63">
-        <v>2.82</v>
+        <v>1.51</v>
       </c>
       <c r="R63">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S63">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T63">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="U63">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="V63">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="W63">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y63">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z63">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AA63">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AB63">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AC63">
+        <v>1.8</v>
+      </c>
+      <c r="AD63">
+        <v>2</v>
+      </c>
+      <c r="AE63">
+        <v>1.4</v>
+      </c>
+      <c r="AF63">
+        <v>1.6</v>
+      </c>
+      <c r="AG63">
         <v>2.2</v>
       </c>
-      <c r="AD63">
-        <v>1.65</v>
-      </c>
-      <c r="AE63">
-        <v>1.22</v>
-      </c>
-      <c r="AF63">
-        <v>1.44</v>
-      </c>
-      <c r="AG63">
-        <v>2.62</v>
-      </c>
       <c r="AH63" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AK63">
-        <v>1.58</v>
+        <v>3.8</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q64">
         <v>2.33</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="O65">
         <v>3.73</v>
@@ -10913,16 +10913,16 @@
         <v>2.9</v>
       </c>
       <c r="Q65">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="R65">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S65">
         <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U65">
         <v>2.3</v>
@@ -10937,22 +10937,22 @@
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z65">
-        <v>4.76</v>
+        <v>4.69</v>
       </c>
       <c r="AA65">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AB65">
         <v>2.3</v>
       </c>
       <c r="AC65">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AD65">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE65">
         <v>1.2</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O66">
         <v>3.8</v>
@@ -11399,7 +11399,7 @@
         <v>3.68</v>
       </c>
       <c r="P68">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="Q68">
         <v>2.46</v>
@@ -11417,7 +11417,7 @@
         <v>2.25</v>
       </c>
       <c r="V68">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W68">
         <v>1.15</v>
@@ -11629,7 +11629,7 @@
         <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="O4">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P4">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="Q4">
         <v>2.18</v>
@@ -982,7 +982,7 @@
         <v>3.2</v>
       </c>
       <c r="U4">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="V4">
         <v>1.48</v>
@@ -997,19 +997,19 @@
         <v>1.17</v>
       </c>
       <c r="Z4">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="AA4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB4">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC4">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AD4">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AE4">
         <v>1.1</v>
@@ -1124,43 +1124,43 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA5">
         <v>2.05</v>
@@ -1169,19 +1169,19 @@
         <v>1.75</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="O6">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="Q6">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="R6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S6">
         <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="V6">
         <v>1.44</v>
@@ -1320,22 +1320,22 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA6">
         <v>1.75</v>
       </c>
       <c r="AB6">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC6">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
         <v>1.1</v>
@@ -1360,7 +1360,7 @@
         <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,25 +1450,25 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O7">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q7">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="R7">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="S7">
         <v>1.22</v>
       </c>
       <c r="T7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U7">
         <v>2.12</v>
@@ -1489,7 +1489,7 @@
         <v>5.45</v>
       </c>
       <c r="AA7">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB7">
         <v>2.73</v>
@@ -1945,7 +1945,7 @@
         <v>4.05</v>
       </c>
       <c r="P10">
-        <v>6.13</v>
+        <v>6.67</v>
       </c>
       <c r="Q10">
         <v>1.91</v>
@@ -1954,7 +1954,7 @@
         <v>2.3</v>
       </c>
       <c r="S10">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T10">
         <v>3.18</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O13">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R13">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="S13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T13">
         <v>3.75</v>
       </c>
       <c r="U13">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="V13">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA13">
+        <v>1.57</v>
+      </c>
+      <c r="AB13">
+        <v>2.55</v>
+      </c>
+      <c r="AC13">
+        <v>2.38</v>
+      </c>
+      <c r="AD13">
+        <v>1.57</v>
+      </c>
+      <c r="AE13">
+        <v>1.22</v>
+      </c>
+      <c r="AF13">
         <v>1.53</v>
       </c>
-      <c r="AB13">
-        <v>2.63</v>
-      </c>
-      <c r="AC13">
-        <v>2.2</v>
-      </c>
-      <c r="AD13">
-        <v>1.65</v>
-      </c>
-      <c r="AE13">
-        <v>1.25</v>
-      </c>
-      <c r="AF13">
-        <v>1.5</v>
-      </c>
       <c r="AG13">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O16">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P16">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q16">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="R16">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="S16">
         <v>1.5</v>
@@ -2950,47 +2950,47 @@
         <v>1.08</v>
       </c>
       <c r="Y16">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Z16">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="AA16">
-        <v>2.49</v>
+        <v>2.64</v>
       </c>
       <c r="AB16">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC16">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AD16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE16">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AF16">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AG16">
+        <v>1.6</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.16</v>
+      </c>
+      <c r="AK16">
         <v>1.65</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.21</v>
-      </c>
-      <c r="AK16">
-        <v>1.56</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3095,22 +3095,22 @@
         <v>1.75</v>
       </c>
       <c r="S17">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="T17">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U17">
         <v>3.92</v>
       </c>
       <c r="V17">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y17">
         <v>1.55</v>
@@ -3119,22 +3119,22 @@
         <v>2.24</v>
       </c>
       <c r="AA17">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB17">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC17">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD17">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AE17">
         <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AG17">
         <v>1.55</v>
@@ -3153,7 +3153,7 @@
         <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="P18">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="Q18">
-        <v>2.63</v>
+        <v>1.87</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="AA18">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AC18">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AD18">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AF18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>1.49</v>
+        <v>2.24</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q19">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>5.85</v>
+        <v>4.3</v>
       </c>
       <c r="AA19">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC19">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AD19">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AE19">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,65 +3569,65 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="O20">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="P20">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="Q20">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S20">
         <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z20">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA20">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
+        <v>2.56</v>
+      </c>
+      <c r="AC20">
+        <v>1.84</v>
+      </c>
+      <c r="AD20">
+        <v>1.52</v>
+      </c>
+      <c r="AE20">
+        <v>1.29</v>
+      </c>
+      <c r="AF20">
+        <v>1.3</v>
+      </c>
+      <c r="AG20">
         <v>2.3</v>
       </c>
-      <c r="AC20">
-        <v>1.8</v>
-      </c>
-      <c r="AD20">
-        <v>1.74</v>
-      </c>
-      <c r="AE20">
-        <v>1.2</v>
-      </c>
-      <c r="AF20">
-        <v>1.4</v>
-      </c>
-      <c r="AG20">
-        <v>2.62</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="O21">
         <v>3.7</v>
       </c>
       <c r="P21">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="Q21">
-        <v>2.37</v>
+        <v>2.61</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="S21">
+        <v>1.17</v>
+      </c>
+      <c r="T21">
+        <v>3.1</v>
+      </c>
+      <c r="U21">
+        <v>1.75</v>
+      </c>
+      <c r="V21">
+        <v>1.59</v>
+      </c>
+      <c r="W21">
         <v>1.2</v>
-      </c>
-      <c r="T21">
-        <v>4</v>
-      </c>
-      <c r="U21">
-        <v>2.1</v>
-      </c>
-      <c r="V21">
-        <v>1.67</v>
-      </c>
-      <c r="W21">
-        <v>1.17</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>3.6</v>
+        <v>5.85</v>
       </c>
       <c r="AA21">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AB21">
-        <v>2.56</v>
+        <v>3.1</v>
       </c>
       <c r="AC21">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AD21">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AE21">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF21">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG21">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3901,7 +3901,7 @@
         <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="Q22">
         <v>3.36</v>
@@ -3913,7 +3913,7 @@
         <v>1.3</v>
       </c>
       <c r="T22">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
         <v>2.51</v>
@@ -3928,7 +3928,7 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z22">
         <v>4.23</v>
@@ -4227,7 +4227,7 @@
         <v>3.1</v>
       </c>
       <c r="P24">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="Q24">
         <v>3.26</v>
@@ -4236,7 +4236,7 @@
         <v>2.01</v>
       </c>
       <c r="S24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
         <v>2.88</v>
@@ -4245,7 +4245,7 @@
         <v>2.65</v>
       </c>
       <c r="V24">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W24">
         <v>1.07</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O25">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="P25">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q25">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="R25">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S25">
+        <v>1.18</v>
+      </c>
+      <c r="T25">
+        <v>4.2</v>
+      </c>
+      <c r="U25">
+        <v>1.91</v>
+      </c>
+      <c r="V25">
+        <v>1.8</v>
+      </c>
+      <c r="W25">
         <v>1.2</v>
-      </c>
-      <c r="T25">
-        <v>4</v>
-      </c>
-      <c r="U25">
-        <v>2.03</v>
-      </c>
-      <c r="V25">
-        <v>1.75</v>
-      </c>
-      <c r="W25">
-        <v>1.18</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z25">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="AA25">
+        <v>1.34</v>
+      </c>
+      <c r="AB25">
+        <v>3.2</v>
+      </c>
+      <c r="AC25">
+        <v>1.82</v>
+      </c>
+      <c r="AD25">
+        <v>1.85</v>
+      </c>
+      <c r="AE25">
         <v>1.36</v>
       </c>
-      <c r="AB25">
-        <v>2.7</v>
-      </c>
-      <c r="AC25">
-        <v>1.95</v>
-      </c>
-      <c r="AD25">
-        <v>1.74</v>
-      </c>
-      <c r="AE25">
-        <v>1.3</v>
-      </c>
       <c r="AF25">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AK25">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O26">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>7.5</v>
       </c>
       <c r="Q26">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="R26">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="S26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="T26">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="U26">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V26">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="W26">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
         <v>1</v>
       </c>
-      <c r="Y26">
-        <v>1.01</v>
-      </c>
       <c r="Z26">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA26">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AB26">
-        <v>3.92</v>
+        <v>4.4</v>
       </c>
       <c r="AC26">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AD26">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="AE26">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AF26">
         <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK26">
         <v>4</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="O27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="Q27">
         <v>2.54</v>
@@ -4725,19 +4725,19 @@
         <v>2.44</v>
       </c>
       <c r="S27">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T27">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="U27">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V27">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="W27">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X27">
         <v>1.01</v>
@@ -4752,7 +4752,7 @@
         <v>1.4</v>
       </c>
       <c r="AB27">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AC27">
         <v>1.94</v>
@@ -4761,7 +4761,7 @@
         <v>1.79</v>
       </c>
       <c r="AE27">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF27">
         <v>1.33</v>
@@ -4879,7 +4879,7 @@
         <v>3.7</v>
       </c>
       <c r="P28">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q28">
         <v>3.32</v>
@@ -4891,16 +4891,16 @@
         <v>1.11</v>
       </c>
       <c r="T28">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="U28">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="V28">
         <v>1.93</v>
       </c>
       <c r="W28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="O29">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="P29">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q29">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="R29">
         <v>2.88</v>
       </c>
       <c r="S29">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T29">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="U29">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="V29">
+        <v>2.08</v>
+      </c>
+      <c r="W29">
+        <v>1.3</v>
+      </c>
+      <c r="X29">
+        <v>1</v>
+      </c>
+      <c r="Y29">
+        <v>1.01</v>
+      </c>
+      <c r="Z29">
+        <v>8.5</v>
+      </c>
+      <c r="AA29">
+        <v>1.25</v>
+      </c>
+      <c r="AB29">
+        <v>3.82</v>
+      </c>
+      <c r="AC29">
+        <v>1.57</v>
+      </c>
+      <c r="AD29">
+        <v>2.17</v>
+      </c>
+      <c r="AE29">
+        <v>1.55</v>
+      </c>
+      <c r="AF29">
+        <v>1.25</v>
+      </c>
+      <c r="AG29">
+        <v>3.5</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.22</v>
+      </c>
+      <c r="AK29">
         <v>1.91</v>
-      </c>
-      <c r="W29">
-        <v>1.25</v>
-      </c>
-      <c r="X29">
-        <v>1.01</v>
-      </c>
-      <c r="Y29">
-        <v>1.03</v>
-      </c>
-      <c r="Z29">
-        <v>7.3</v>
-      </c>
-      <c r="AA29">
-        <v>1.29</v>
-      </c>
-      <c r="AB29">
-        <v>3.5</v>
-      </c>
-      <c r="AC29">
-        <v>1.72</v>
-      </c>
-      <c r="AD29">
-        <v>1.97</v>
-      </c>
-      <c r="AE29">
-        <v>1.4</v>
-      </c>
-      <c r="AF29">
-        <v>1.4</v>
-      </c>
-      <c r="AG29">
-        <v>2.7</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.09</v>
-      </c>
-      <c r="AK29">
-        <v>2.75</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="O30">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="P30">
+        <v>5.3</v>
+      </c>
+      <c r="Q30">
+        <v>1.78</v>
+      </c>
+      <c r="R30">
+        <v>2.9</v>
+      </c>
+      <c r="S30">
+        <v>1.17</v>
+      </c>
+      <c r="T30">
+        <v>4.6</v>
+      </c>
+      <c r="U30">
+        <v>1.79</v>
+      </c>
+      <c r="V30">
+        <v>1.91</v>
+      </c>
+      <c r="W30">
+        <v>1.25</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.03</v>
+      </c>
+      <c r="Z30">
+        <v>7.3</v>
+      </c>
+      <c r="AA30">
+        <v>1.29</v>
+      </c>
+      <c r="AB30">
+        <v>3.5</v>
+      </c>
+      <c r="AC30">
+        <v>1.72</v>
+      </c>
+      <c r="AD30">
+        <v>1.97</v>
+      </c>
+      <c r="AE30">
+        <v>1.4</v>
+      </c>
+      <c r="AF30">
+        <v>1.4</v>
+      </c>
+      <c r="AG30">
+        <v>2.7</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.09</v>
+      </c>
+      <c r="AK30">
         <v>2.75</v>
-      </c>
-      <c r="Q30">
-        <v>2.2</v>
-      </c>
-      <c r="R30">
-        <v>2.91</v>
-      </c>
-      <c r="S30">
-        <v>1.15</v>
-      </c>
-      <c r="T30">
-        <v>5.5</v>
-      </c>
-      <c r="U30">
-        <v>1.68</v>
-      </c>
-      <c r="V30">
-        <v>2.04</v>
-      </c>
-      <c r="W30">
-        <v>1.3</v>
-      </c>
-      <c r="X30">
-        <v>1</v>
-      </c>
-      <c r="Y30">
-        <v>1.01</v>
-      </c>
-      <c r="Z30">
-        <v>8.5</v>
-      </c>
-      <c r="AA30">
-        <v>1.25</v>
-      </c>
-      <c r="AB30">
-        <v>3.82</v>
-      </c>
-      <c r="AC30">
-        <v>1.57</v>
-      </c>
-      <c r="AD30">
-        <v>2.17</v>
-      </c>
-      <c r="AE30">
-        <v>1.55</v>
-      </c>
-      <c r="AF30">
-        <v>1.25</v>
-      </c>
-      <c r="AG30">
-        <v>3.5</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.2</v>
-      </c>
-      <c r="AK30">
-        <v>1.85</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="O31">
         <v>3.65</v>
       </c>
       <c r="P31">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q31">
         <v>3.36</v>
@@ -5377,7 +5377,7 @@
         <v>2.51</v>
       </c>
       <c r="S31">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="T31">
         <v>4.5</v>
@@ -5407,7 +5407,7 @@
         <v>3.4</v>
       </c>
       <c r="AC31">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AD31">
         <v>1.98</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AK32">
         <v>1.59</v>
@@ -5700,7 +5700,7 @@
         <v>2.26</v>
       </c>
       <c r="R33">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
         <v>1.3</v>
@@ -5860,7 +5860,7 @@
         <v>2.42</v>
       </c>
       <c r="Q34">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R34">
         <v>2.32</v>
@@ -5872,10 +5872,10 @@
         <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="V34">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W34">
         <v>1.13</v>
@@ -5893,10 +5893,10 @@
         <v>1.47</v>
       </c>
       <c r="AB34">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AC34">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="AD34">
         <v>1.64</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="O35">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="Q35">
-        <v>3.26</v>
+        <v>2.36</v>
       </c>
       <c r="R35">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S35">
+        <v>1.33</v>
+      </c>
+      <c r="T35">
+        <v>3.4</v>
+      </c>
+      <c r="U35">
+        <v>2.4</v>
+      </c>
+      <c r="V35">
+        <v>1.5</v>
+      </c>
+      <c r="W35">
+        <v>1.1</v>
+      </c>
+      <c r="X35">
+        <v>1.01</v>
+      </c>
+      <c r="Y35">
         <v>1.2</v>
       </c>
-      <c r="T35">
-        <v>3.94</v>
-      </c>
-      <c r="U35">
-        <v>2.04</v>
-      </c>
-      <c r="V35">
-        <v>1.82</v>
-      </c>
-      <c r="W35">
-        <v>1.21</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.08</v>
-      </c>
       <c r="Z35">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AA35">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB35">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AC35">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="AD35">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AE35">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF35">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>1.3</v>
+        <v>1.77</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,80 +6177,80 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="Q36">
-        <v>3.02</v>
+        <v>2.49</v>
       </c>
       <c r="R36">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
-        <v>3.1</v>
+        <v>4.05</v>
       </c>
       <c r="U36">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="V36">
-        <v>1.43</v>
+        <v>1.71</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="Z36">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="AA36">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="AC36">
-        <v>2.93</v>
+        <v>2.11</v>
       </c>
       <c r="AD36">
+        <v>1.73</v>
+      </c>
+      <c r="AE36">
+        <v>1.29</v>
+      </c>
+      <c r="AF36">
+        <v>1.4</v>
+      </c>
+      <c r="AG36">
+        <v>2.89</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.33</v>
       </c>
-      <c r="AE36">
-        <v>1.11</v>
-      </c>
-      <c r="AF36">
-        <v>1.67</v>
-      </c>
-      <c r="AG36">
-        <v>2.15</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.3</v>
-      </c>
       <c r="AK36">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O38">
         <v>3.5</v>
       </c>
       <c r="P38">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="Q38">
-        <v>2.36</v>
+        <v>3.02</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
+        <v>1.36</v>
+      </c>
+      <c r="T38">
+        <v>3.1</v>
+      </c>
+      <c r="U38">
+        <v>2.75</v>
+      </c>
+      <c r="V38">
+        <v>1.43</v>
+      </c>
+      <c r="W38">
+        <v>1.06</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.25</v>
+      </c>
+      <c r="Z38">
+        <v>3.7</v>
+      </c>
+      <c r="AA38">
+        <v>1.83</v>
+      </c>
+      <c r="AB38">
+        <v>1.91</v>
+      </c>
+      <c r="AC38">
+        <v>2.93</v>
+      </c>
+      <c r="AD38">
         <v>1.33</v>
       </c>
-      <c r="T38">
-        <v>3.4</v>
-      </c>
-      <c r="U38">
-        <v>2.4</v>
-      </c>
-      <c r="V38">
-        <v>1.5</v>
-      </c>
-      <c r="W38">
-        <v>1.1</v>
-      </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.2</v>
-      </c>
-      <c r="Z38">
-        <v>4.2</v>
-      </c>
-      <c r="AA38">
-        <v>1.72</v>
-      </c>
-      <c r="AB38">
-        <v>2.17</v>
-      </c>
-      <c r="AC38">
-        <v>2.68</v>
-      </c>
-      <c r="AD38">
-        <v>1.47</v>
-      </c>
       <c r="AE38">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF38">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.77</v>
+        <v>1.43</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.11</v>
+        <v>3.1</v>
       </c>
       <c r="O39">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P39">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q39">
-        <v>2.49</v>
+        <v>3.26</v>
       </c>
       <c r="R39">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="S39">
         <v>1.2</v>
       </c>
       <c r="T39">
-        <v>4.05</v>
+        <v>3.94</v>
       </c>
       <c r="U39">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="V39">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="W39">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA39">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AC39">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AD39">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE39">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF39">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG39">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="O42">
         <v>4.05</v>
       </c>
       <c r="P42">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q42">
         <v>4.88</v>
@@ -7170,7 +7170,7 @@
         <v>2.34</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
         <v>3.24</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AK42">
         <v>1.16</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P44">
         <v>2.2</v>
       </c>
       <c r="Q44">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R44">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S44">
         <v>1.3</v>
@@ -7502,43 +7502,43 @@
         <v>3.25</v>
       </c>
       <c r="U44">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="V44">
         <v>1.5</v>
       </c>
       <c r="W44">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="AA44">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB44">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AC44">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AD44">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AE44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG44">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z45">
         <v>5.3</v>
@@ -7849,13 +7849,13 @@
         <v>1.62</v>
       </c>
       <c r="AB46">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AC46">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD46">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE46">
         <v>1.18</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK46">
         <v>2.32</v>
@@ -7979,22 +7979,22 @@
         <v>2.75</v>
       </c>
       <c r="Q47">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="R47">
-        <v>2.21</v>
+        <v>2.31</v>
       </c>
       <c r="S47">
         <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U47">
         <v>2.2</v>
       </c>
       <c r="V47">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W47">
         <v>1.13</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="O48">
         <v>3.6</v>
@@ -8154,7 +8154,7 @@
         <v>4</v>
       </c>
       <c r="U48">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="V48">
         <v>1.6</v>
@@ -8166,25 +8166,25 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z48">
-        <v>5.54</v>
+        <v>5.61</v>
       </c>
       <c r="AA48">
         <v>1.5</v>
       </c>
       <c r="AB48">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="AC48">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AD48">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE48">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF48">
         <v>1.44</v>
@@ -8206,7 +8206,7 @@
         <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="O49">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P49">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q49">
         <v>1.92</v>
@@ -8311,7 +8311,7 @@
         <v>2.75</v>
       </c>
       <c r="S49">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T49">
         <v>4.8</v>
@@ -8329,28 +8329,28 @@
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z49">
-        <v>8</v>
+        <v>6.91</v>
       </c>
       <c r="AA49">
         <v>1.3</v>
       </c>
       <c r="AB49">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AC49">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AD49">
         <v>2.05</v>
       </c>
       <c r="AE49">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AF49">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG49">
         <v>2.7</v>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK49">
         <v>2.46</v>
@@ -8462,16 +8462,16 @@
         <v>1.95</v>
       </c>
       <c r="O50">
-        <v>3.88</v>
+        <v>3.93</v>
       </c>
       <c r="P50">
-        <v>2.68</v>
+        <v>2.95</v>
       </c>
       <c r="Q50">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="R50">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="S50">
         <v>1.2</v>
@@ -8483,7 +8483,7 @@
         <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W50">
         <v>1.22</v>
@@ -8492,10 +8492,10 @@
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z50">
-        <v>6.3</v>
+        <v>6.33</v>
       </c>
       <c r="AA50">
         <v>1.36</v>
@@ -8504,13 +8504,13 @@
         <v>3.1</v>
       </c>
       <c r="AC50">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD50">
         <v>1.83</v>
       </c>
       <c r="AE50">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF50">
         <v>1.36</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O51">
         <v>3.92</v>
       </c>
       <c r="P51">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="Q51">
         <v>2.65</v>
@@ -8640,13 +8640,13 @@
         <v>1.17</v>
       </c>
       <c r="T51">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U51">
         <v>1.95</v>
       </c>
       <c r="V51">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W51">
         <v>1.2</v>
@@ -8797,7 +8797,7 @@
         <v>2.38</v>
       </c>
       <c r="R52">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8821,7 +8821,7 @@
         <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>5.26</v>
+        <v>5.5</v>
       </c>
       <c r="AA52">
         <v>1.5</v>
@@ -8830,13 +8830,13 @@
         <v>2.63</v>
       </c>
       <c r="AC52">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AD52">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE52">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF52">
         <v>1.44</v>
@@ -10261,7 +10261,7 @@
         <v>2.58</v>
       </c>
       <c r="Q61">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="R61">
         <v>2.5</v>
@@ -10424,7 +10424,7 @@
         <v>2.6</v>
       </c>
       <c r="Q62">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="R62">
         <v>2.36</v>
@@ -10439,7 +10439,7 @@
         <v>2.1</v>
       </c>
       <c r="V62">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W62">
         <v>1.18</v>
@@ -10605,7 +10605,7 @@
         <v>1.91</v>
       </c>
       <c r="W63">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X63">
         <v>0</v>
@@ -10632,7 +10632,7 @@
         <v>1.4</v>
       </c>
       <c r="AF63">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG63">
         <v>2.2</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="Q64">
         <v>2.33</v>
@@ -10765,7 +10765,7 @@
         <v>2.25</v>
       </c>
       <c r="V64">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W64">
         <v>1.13</v>
@@ -10780,7 +10780,7 @@
         <v>5.5</v>
       </c>
       <c r="AA64">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB64">
         <v>2.45</v>
@@ -10789,16 +10789,16 @@
         <v>2.38</v>
       </c>
       <c r="AD64">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF64">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG64">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK64">
         <v>1.75</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="O65">
-        <v>3.73</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="Q65">
-        <v>2.66</v>
+        <v>2.27</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T65">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="V65">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>4.69</v>
+        <v>6</v>
       </c>
       <c r="AA65">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AB65">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="AC65">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AD65">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AE65">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF65">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK65">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O66">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="P66">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="Q66">
-        <v>2.27</v>
+        <v>2.66</v>
       </c>
       <c r="R66">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U66">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V66">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="W66">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z66">
-        <v>6</v>
+        <v>4.69</v>
       </c>
       <c r="AA66">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AB66">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="AC66">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD66">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AE66">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF66">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG66">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK66">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11242,7 +11242,7 @@
         <v>1.88</v>
       </c>
       <c r="R67">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="S67">
         <v>1.25</v>
@@ -11251,7 +11251,7 @@
         <v>3.8</v>
       </c>
       <c r="U67">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V67">
         <v>1.59</v>
@@ -11284,7 +11284,7 @@
         <v>1.2</v>
       </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG67">
         <v>2.05</v>
@@ -11399,7 +11399,7 @@
         <v>3.68</v>
       </c>
       <c r="P68">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="Q68">
         <v>2.46</v>
@@ -11417,7 +11417,7 @@
         <v>2.25</v>
       </c>
       <c r="V68">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W68">
         <v>1.15</v>
@@ -11426,25 +11426,25 @@
         <v>1.01</v>
       </c>
       <c r="Y68">
+        <v>1.2</v>
+      </c>
+      <c r="Z68">
+        <v>4.5</v>
+      </c>
+      <c r="AA68">
+        <v>1.6</v>
+      </c>
+      <c r="AB68">
+        <v>2.3</v>
+      </c>
+      <c r="AC68">
+        <v>2.63</v>
+      </c>
+      <c r="AD68">
+        <v>1.47</v>
+      </c>
+      <c r="AE68">
         <v>1.17</v>
-      </c>
-      <c r="Z68">
-        <v>5</v>
-      </c>
-      <c r="AA68">
-        <v>1.57</v>
-      </c>
-      <c r="AB68">
-        <v>2.38</v>
-      </c>
-      <c r="AC68">
-        <v>2.55</v>
-      </c>
-      <c r="AD68">
-        <v>1.5</v>
-      </c>
-      <c r="AE68">
-        <v>1.2</v>
       </c>
       <c r="AF68">
         <v>1.5</v>
@@ -11559,7 +11559,7 @@
         <v>2</v>
       </c>
       <c r="O69">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="P69">
         <v>3</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -638,7 +638,7 @@
         <v>3.76</v>
       </c>
       <c r="O2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
         <v>1.85</v>
@@ -647,7 +647,7 @@
         <v>3.7</v>
       </c>
       <c r="R2">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
         <v>1.34</v>
@@ -659,13 +659,13 @@
         <v>2.65</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.29</v>
@@ -677,7 +677,7 @@
         <v>1.93</v>
       </c>
       <c r="AB2">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC2">
         <v>3.25</v>
@@ -686,13 +686,13 @@
         <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF2">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AG2">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G3">
@@ -794,69 +794,69 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N3">
-        <v>3.34</v>
+        <v>1.56</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P3">
+        <v>4.8</v>
+      </c>
+      <c r="Q3">
+        <v>2.18</v>
+      </c>
+      <c r="R3">
+        <v>2.25</v>
+      </c>
+      <c r="S3">
+        <v>1.3</v>
+      </c>
+      <c r="T3">
+        <v>3.2</v>
+      </c>
+      <c r="U3">
+        <v>2.61</v>
+      </c>
+      <c r="V3">
+        <v>1.48</v>
+      </c>
+      <c r="W3">
+        <v>1.12</v>
+      </c>
+      <c r="X3">
+        <v>1.02</v>
+      </c>
+      <c r="Y3">
+        <v>1.17</v>
+      </c>
+      <c r="Z3">
+        <v>4.03</v>
+      </c>
+      <c r="AA3">
+        <v>1.74</v>
+      </c>
+      <c r="AB3">
+        <v>2.1</v>
+      </c>
+      <c r="AC3">
+        <v>2.84</v>
+      </c>
+      <c r="AD3">
+        <v>1.47</v>
+      </c>
+      <c r="AE3">
+        <v>1.1</v>
+      </c>
+      <c r="AF3">
+        <v>1.68</v>
+      </c>
+      <c r="AG3">
         <v>2.05</v>
       </c>
-      <c r="Q3">
-        <v>3.75</v>
-      </c>
-      <c r="R3">
-        <v>2.1</v>
-      </c>
-      <c r="S3">
-        <v>1.33</v>
-      </c>
-      <c r="T3">
-        <v>2.85</v>
-      </c>
-      <c r="U3">
-        <v>2.7</v>
-      </c>
-      <c r="V3">
-        <v>1.4</v>
-      </c>
-      <c r="W3">
-        <v>1.02</v>
-      </c>
-      <c r="X3">
-        <v>1.04</v>
-      </c>
-      <c r="Y3">
-        <v>1.27</v>
-      </c>
-      <c r="Z3">
-        <v>3.14</v>
-      </c>
-      <c r="AA3">
-        <v>1.98</v>
-      </c>
-      <c r="AB3">
-        <v>1.74</v>
-      </c>
-      <c r="AC3">
-        <v>3.42</v>
-      </c>
-      <c r="AD3">
-        <v>1.33</v>
-      </c>
-      <c r="AE3">
-        <v>1.04</v>
-      </c>
-      <c r="AF3">
-        <v>1.75</v>
-      </c>
-      <c r="AG3">
-        <v>1.92</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-10-14 08:00:00</t>
+          <t>2026-10-14 08:30:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="O4">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q4">
-        <v>2.18</v>
+        <v>2.57</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
+        <v>1.35</v>
+      </c>
+      <c r="T4">
+        <v>2.98</v>
+      </c>
+      <c r="U4">
+        <v>2.67</v>
+      </c>
+      <c r="V4">
+        <v>1.43</v>
+      </c>
+      <c r="W4">
+        <v>1.08</v>
+      </c>
+      <c r="X4">
+        <v>1.01</v>
+      </c>
+      <c r="Y4">
+        <v>1.29</v>
+      </c>
+      <c r="Z4">
+        <v>3.4</v>
+      </c>
+      <c r="AA4">
+        <v>1.85</v>
+      </c>
+      <c r="AB4">
+        <v>1.95</v>
+      </c>
+      <c r="AC4">
+        <v>3.3</v>
+      </c>
+      <c r="AD4">
         <v>1.3</v>
       </c>
-      <c r="T4">
-        <v>3.2</v>
-      </c>
-      <c r="U4">
-        <v>2.61</v>
-      </c>
-      <c r="V4">
-        <v>1.48</v>
-      </c>
-      <c r="W4">
-        <v>1.12</v>
-      </c>
-      <c r="X4">
-        <v>1.02</v>
-      </c>
-      <c r="Y4">
-        <v>1.17</v>
-      </c>
-      <c r="Z4">
-        <v>4.03</v>
-      </c>
-      <c r="AA4">
-        <v>1.74</v>
-      </c>
-      <c r="AB4">
-        <v>2.1</v>
-      </c>
-      <c r="AC4">
-        <v>2.84</v>
-      </c>
-      <c r="AD4">
-        <v>1.47</v>
-      </c>
       <c r="AE4">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG4">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK4">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-10-14 08:30:00</t>
+          <t>2026-10-14 10:00:00</t>
         </is>
       </c>
     </row>
@@ -1082,22 +1082,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="O5">
+        <v>3.4</v>
+      </c>
+      <c r="P5">
         <v>3.1</v>
       </c>
-      <c r="P5">
-        <v>2.8</v>
-      </c>
       <c r="Q5">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="R5">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="S5">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA5">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AB5">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AC5">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE5">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,80 +1287,80 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q6">
-        <v>2.54</v>
+        <v>2.49</v>
       </c>
       <c r="R6">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="S6">
+        <v>1.22</v>
+      </c>
+      <c r="T6">
+        <v>3.85</v>
+      </c>
+      <c r="U6">
+        <v>2.12</v>
+      </c>
+      <c r="V6">
+        <v>1.7</v>
+      </c>
+      <c r="W6">
+        <v>1.17</v>
+      </c>
+      <c r="X6">
+        <v>1.02</v>
+      </c>
+      <c r="Y6">
+        <v>1.08</v>
+      </c>
+      <c r="Z6">
+        <v>5.45</v>
+      </c>
+      <c r="AA6">
+        <v>1.45</v>
+      </c>
+      <c r="AB6">
+        <v>2.73</v>
+      </c>
+      <c r="AC6">
+        <v>2.11</v>
+      </c>
+      <c r="AD6">
+        <v>1.68</v>
+      </c>
+      <c r="AE6">
         <v>1.3</v>
       </c>
-      <c r="T6">
-        <v>3.2</v>
-      </c>
-      <c r="U6">
-        <v>2.63</v>
-      </c>
-      <c r="V6">
-        <v>1.44</v>
-      </c>
-      <c r="W6">
-        <v>1.09</v>
-      </c>
-      <c r="X6">
-        <v>1.03</v>
-      </c>
-      <c r="Y6">
+      <c r="AF6">
+        <v>1.4</v>
+      </c>
+      <c r="AG6">
+        <v>2.73</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6">
         <v>1.21</v>
       </c>
-      <c r="Z6">
-        <v>3.58</v>
-      </c>
-      <c r="AA6">
-        <v>1.75</v>
-      </c>
-      <c r="AB6">
-        <v>2</v>
-      </c>
-      <c r="AC6">
-        <v>2.88</v>
-      </c>
-      <c r="AD6">
-        <v>1.4</v>
-      </c>
-      <c r="AE6">
-        <v>1.1</v>
-      </c>
-      <c r="AF6">
-        <v>1.63</v>
-      </c>
-      <c r="AG6">
-        <v>2.09</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.22</v>
-      </c>
       <c r="AK6">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,68 +1446,68 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7">
-        <v>1.91</v>
+        <v>4.99</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="P7">
-        <v>3.2</v>
+        <v>1.63</v>
       </c>
       <c r="Q7">
-        <v>2.49</v>
+        <v>6.05</v>
       </c>
       <c r="R7">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="S7">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>3.85</v>
+        <v>2.54</v>
       </c>
       <c r="U7">
-        <v>2.12</v>
+        <v>3.29</v>
       </c>
       <c r="V7">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="W7">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="Z7">
-        <v>5.45</v>
+        <v>2.65</v>
       </c>
       <c r="AA7">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
       <c r="AB7">
-        <v>2.73</v>
+        <v>1.49</v>
       </c>
       <c r="AC7">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1.4</v>
+        <v>2.29</v>
       </c>
       <c r="AG7">
-        <v>2.73</v>
+        <v>1.52</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-14 10:00:00</t>
+          <t>2026-10-14 10:30:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Minerva Punjab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G8">
@@ -1609,68 +1609,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8">
-        <v>4.99</v>
+        <v>1.55</v>
       </c>
       <c r="O8">
-        <v>3.36</v>
+        <v>3.9</v>
       </c>
       <c r="P8">
-        <v>1.63</v>
+        <v>4.6</v>
       </c>
       <c r="Q8">
-        <v>6.05</v>
+        <v>2.1</v>
       </c>
       <c r="R8">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>2.54</v>
+        <v>2.99</v>
       </c>
       <c r="U8">
-        <v>3.29</v>
+        <v>2.48</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>2.65</v>
+        <v>3.78</v>
       </c>
       <c r="AA8">
-        <v>2.37</v>
+        <v>1.71</v>
       </c>
       <c r="AB8">
-        <v>1.49</v>
+        <v>1.98</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="AG8">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-14 10:30:00</t>
+          <t>2026-10-14 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Minerva Punjab</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="O9">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P9">
-        <v>4.9</v>
+        <v>6.13</v>
       </c>
       <c r="Q9">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="R9">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.3</v>
       </c>
       <c r="T9">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U9">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="V9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA9">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB9">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="AC9">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD9">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AG9">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK9">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G10">
@@ -1935,68 +1935,68 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.44</v>
+        <v>3.02</v>
       </c>
       <c r="O10">
-        <v>4.05</v>
+        <v>3.3</v>
       </c>
       <c r="P10">
-        <v>6.67</v>
+        <v>2.05</v>
       </c>
       <c r="Q10">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="R10">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S10">
         <v>1.3</v>
       </c>
       <c r="T10">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
         <v>2.63</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
         <v>1.11</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="AA10">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AB10">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC10">
         <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AG10">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>2.62</v>
+        <v>1.29</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,61 +2105,61 @@
         <v>2.05</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
-        <v>3.25</v>
+        <v>3.57</v>
       </c>
       <c r="Q11">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="R11">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="S11">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="T11">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U11">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W11">
         <v>1.05</v>
       </c>
       <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>1.31</v>
+      </c>
+      <c r="Z11">
+        <v>2.92</v>
+      </c>
+      <c r="AA11">
+        <v>2</v>
+      </c>
+      <c r="AB11">
+        <v>1.8</v>
+      </c>
+      <c r="AC11">
+        <v>3.8</v>
+      </c>
+      <c r="AD11">
+        <v>1.22</v>
+      </c>
+      <c r="AE11">
         <v>1.04</v>
       </c>
-      <c r="Y11">
-        <v>1.38</v>
-      </c>
-      <c r="Z11">
-        <v>2.62</v>
-      </c>
-      <c r="AA11">
-        <v>2.29</v>
-      </c>
-      <c r="AB11">
-        <v>1.57</v>
-      </c>
-      <c r="AC11">
-        <v>4.1</v>
-      </c>
-      <c r="AD11">
-        <v>1.16</v>
-      </c>
-      <c r="AE11">
-        <v>1.01</v>
-      </c>
       <c r="AF11">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AG11">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2594,16 +2594,16 @@
         <v>3.3</v>
       </c>
       <c r="O14">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P14">
         <v>2</v>
       </c>
       <c r="Q14">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R14">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="S14">
         <v>1.24</v>
@@ -2612,7 +2612,7 @@
         <v>4</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V14">
         <v>1.7</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK14">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,7 +2757,7 @@
         <v>8.5</v>
       </c>
       <c r="O15">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>1.28</v>
@@ -2766,10 +2766,10 @@
         <v>6.28</v>
       </c>
       <c r="R15">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T15">
         <v>4.5</v>
@@ -2781,7 +2781,7 @@
         <v>1.83</v>
       </c>
       <c r="W15">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,7 +2793,7 @@
         <v>7.5</v>
       </c>
       <c r="AA15">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AB15">
         <v>2.82</v>
@@ -2805,7 +2805,7 @@
         <v>1.93</v>
       </c>
       <c r="AE15">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF15">
         <v>1.67</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK15">
         <v>1.07</v>
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O16">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P16">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q16">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="R16">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="S16">
         <v>1.5</v>
       </c>
       <c r="T16">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="U16">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="V16">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y16">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Z16">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AA16">
-        <v>2.64</v>
+        <v>2.71</v>
       </c>
       <c r="AB16">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AC16">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD16">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AE16">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AG16">
+        <v>1.57</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.18</v>
+      </c>
+      <c r="AK16">
         <v>1.6</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.16</v>
-      </c>
-      <c r="AK16">
-        <v>1.65</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
         <v>2.75</v>
       </c>
       <c r="P17">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Q17">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S17">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="T17">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="U17">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="V17">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W17">
         <v>1.02</v>
@@ -3113,22 +3113,22 @@
         <v>1.1</v>
       </c>
       <c r="Y17">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Z17">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AA17">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AB17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC17">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AD17">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE17">
         <v>1.01</v>
@@ -3137,7 +3137,7 @@
         <v>2.2</v>
       </c>
       <c r="AG17">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,65 +3243,65 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.55</v>
+        <v>2.17</v>
       </c>
       <c r="O18">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
-        <v>4.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q18">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="R18">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AA18">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
+        <v>2.14</v>
+      </c>
+      <c r="AC18">
+        <v>2.2</v>
+      </c>
+      <c r="AD18">
+        <v>1.45</v>
+      </c>
+      <c r="AE18">
+        <v>1.14</v>
+      </c>
+      <c r="AF18">
+        <v>1.5</v>
+      </c>
+      <c r="AG18">
         <v>2.3</v>
       </c>
-      <c r="AC18">
-        <v>1.8</v>
-      </c>
-      <c r="AD18">
-        <v>1.74</v>
-      </c>
-      <c r="AE18">
-        <v>1.26</v>
-      </c>
-      <c r="AF18">
-        <v>1.44</v>
-      </c>
-      <c r="AG18">
-        <v>2.5</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>2.24</v>
+        <v>1.49</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,61 +3406,61 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="O19">
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>2.51</v>
       </c>
       <c r="V19">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z19">
-        <v>4.3</v>
+        <v>4.23</v>
       </c>
       <c r="AA19">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AB19">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="AD19">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
         <v>2.3</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK19">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="O20">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="P20">
+        <v>4.55</v>
+      </c>
+      <c r="Q20">
+        <v>1.95</v>
+      </c>
+      <c r="R20">
+        <v>2.38</v>
+      </c>
+      <c r="S20">
+        <v>1.17</v>
+      </c>
+      <c r="T20">
         <v>3</v>
       </c>
-      <c r="Q20">
-        <v>2.37</v>
-      </c>
-      <c r="R20">
-        <v>2.4</v>
-      </c>
-      <c r="S20">
-        <v>1.2</v>
-      </c>
-      <c r="T20">
-        <v>4</v>
-      </c>
       <c r="U20">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="V20">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="W20">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AC20">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AD20">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="AE20">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AF20">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK20">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
+        <v>1.93</v>
+      </c>
+      <c r="O21">
+        <v>3.65</v>
+      </c>
+      <c r="P21">
+        <v>3</v>
+      </c>
+      <c r="Q21">
+        <v>2.37</v>
+      </c>
+      <c r="R21">
+        <v>2.4</v>
+      </c>
+      <c r="S21">
+        <v>1.2</v>
+      </c>
+      <c r="T21">
+        <v>4</v>
+      </c>
+      <c r="U21">
         <v>2.1</v>
       </c>
-      <c r="O21">
-        <v>3.7</v>
-      </c>
-      <c r="P21">
-        <v>2.67</v>
-      </c>
-      <c r="Q21">
-        <v>2.61</v>
-      </c>
-      <c r="R21">
-        <v>2.63</v>
-      </c>
-      <c r="S21">
+      <c r="V21">
+        <v>1.67</v>
+      </c>
+      <c r="W21">
         <v>1.17</v>
-      </c>
-      <c r="T21">
-        <v>3.1</v>
-      </c>
-      <c r="U21">
-        <v>1.75</v>
-      </c>
-      <c r="V21">
-        <v>1.59</v>
-      </c>
-      <c r="W21">
-        <v>1.2</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>5.85</v>
+        <v>3.6</v>
       </c>
       <c r="AA21">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB21">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AC21">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="AD21">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AE21">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF21">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG21">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="O22">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="P22">
-        <v>2.22</v>
+        <v>2.67</v>
       </c>
       <c r="Q22">
-        <v>3.36</v>
+        <v>2.61</v>
       </c>
       <c r="R22">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U22">
-        <v>2.51</v>
+        <v>1.75</v>
       </c>
       <c r="V22">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z22">
-        <v>4.23</v>
+        <v>5.85</v>
       </c>
       <c r="AA22">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="AB22">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="AC22">
-        <v>2.52</v>
+        <v>1.89</v>
       </c>
       <c r="AD22">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AE22">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF22">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG22">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4248,7 +4248,7 @@
         <v>1.4</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
         <v>1.04</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="O29">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="P29">
+        <v>5.3</v>
+      </c>
+      <c r="Q29">
+        <v>1.78</v>
+      </c>
+      <c r="R29">
+        <v>2.9</v>
+      </c>
+      <c r="S29">
+        <v>1.17</v>
+      </c>
+      <c r="T29">
+        <v>4.6</v>
+      </c>
+      <c r="U29">
+        <v>1.79</v>
+      </c>
+      <c r="V29">
+        <v>1.91</v>
+      </c>
+      <c r="W29">
+        <v>1.25</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>1.03</v>
+      </c>
+      <c r="Z29">
+        <v>7.3</v>
+      </c>
+      <c r="AA29">
+        <v>1.29</v>
+      </c>
+      <c r="AB29">
+        <v>3.5</v>
+      </c>
+      <c r="AC29">
+        <v>1.72</v>
+      </c>
+      <c r="AD29">
+        <v>1.97</v>
+      </c>
+      <c r="AE29">
+        <v>1.4</v>
+      </c>
+      <c r="AF29">
+        <v>1.4</v>
+      </c>
+      <c r="AG29">
+        <v>2.7</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>1.09</v>
+      </c>
+      <c r="AK29">
         <v>2.75</v>
-      </c>
-      <c r="Q29">
-        <v>2.15</v>
-      </c>
-      <c r="R29">
-        <v>2.88</v>
-      </c>
-      <c r="S29">
-        <v>1.15</v>
-      </c>
-      <c r="T29">
-        <v>5.5</v>
-      </c>
-      <c r="U29">
-        <v>1.68</v>
-      </c>
-      <c r="V29">
-        <v>2.08</v>
-      </c>
-      <c r="W29">
-        <v>1.3</v>
-      </c>
-      <c r="X29">
-        <v>1</v>
-      </c>
-      <c r="Y29">
-        <v>1.01</v>
-      </c>
-      <c r="Z29">
-        <v>8.5</v>
-      </c>
-      <c r="AA29">
-        <v>1.25</v>
-      </c>
-      <c r="AB29">
-        <v>3.82</v>
-      </c>
-      <c r="AC29">
-        <v>1.57</v>
-      </c>
-      <c r="AD29">
-        <v>2.17</v>
-      </c>
-      <c r="AE29">
-        <v>1.55</v>
-      </c>
-      <c r="AF29">
-        <v>1.25</v>
-      </c>
-      <c r="AG29">
-        <v>3.5</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.22</v>
-      </c>
-      <c r="AK29">
-        <v>1.91</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="O30">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="P30">
-        <v>5.3</v>
+        <v>2.75</v>
       </c>
       <c r="Q30">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="R30">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="S30">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T30">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="U30">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="V30">
+        <v>2.08</v>
+      </c>
+      <c r="W30">
+        <v>1.3</v>
+      </c>
+      <c r="X30">
+        <v>1</v>
+      </c>
+      <c r="Y30">
+        <v>1.01</v>
+      </c>
+      <c r="Z30">
+        <v>8.5</v>
+      </c>
+      <c r="AA30">
+        <v>1.25</v>
+      </c>
+      <c r="AB30">
+        <v>3.82</v>
+      </c>
+      <c r="AC30">
+        <v>1.57</v>
+      </c>
+      <c r="AD30">
+        <v>2.17</v>
+      </c>
+      <c r="AE30">
+        <v>1.55</v>
+      </c>
+      <c r="AF30">
+        <v>1.25</v>
+      </c>
+      <c r="AG30">
+        <v>3.5</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>1.22</v>
+      </c>
+      <c r="AK30">
         <v>1.91</v>
-      </c>
-      <c r="W30">
-        <v>1.25</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.03</v>
-      </c>
-      <c r="Z30">
-        <v>7.3</v>
-      </c>
-      <c r="AA30">
-        <v>1.29</v>
-      </c>
-      <c r="AB30">
-        <v>3.5</v>
-      </c>
-      <c r="AC30">
-        <v>1.72</v>
-      </c>
-      <c r="AD30">
-        <v>1.97</v>
-      </c>
-      <c r="AE30">
-        <v>1.4</v>
-      </c>
-      <c r="AF30">
-        <v>1.4</v>
-      </c>
-      <c r="AG30">
-        <v>2.7</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.09</v>
-      </c>
-      <c r="AK30">
-        <v>2.75</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5528,16 +5528,16 @@
         <v>2.25</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P32">
-        <v>2.97</v>
+        <v>3.11</v>
       </c>
       <c r="Q32">
         <v>2.57</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S32">
         <v>1.35</v>
@@ -5549,10 +5549,10 @@
         <v>2.84</v>
       </c>
       <c r="V32">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X32">
         <v>1.04</v>
@@ -5567,13 +5567,13 @@
         <v>1.94</v>
       </c>
       <c r="AB32">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC32">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AD32">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AE32">
         <v>1.06</v>
@@ -5598,7 +5598,7 @@
         <v>1.23</v>
       </c>
       <c r="AK32">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O33">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P33">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q33">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R33">
         <v>2.1</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
         <v>2.6</v>
@@ -5724,22 +5724,22 @@
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="AA33">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AB33">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AC33">
         <v>3.1</v>
       </c>
       <c r="AD33">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
         <v>1.7</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK33">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>1.64</v>
       </c>
       <c r="AE34">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF34">
         <v>1.44</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O35">
         <v>3.5</v>
       </c>
       <c r="P35">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="Q35">
         <v>2.36</v>
       </c>
       <c r="R35">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
         <v>1.33</v>
@@ -6041,7 +6041,7 @@
         <v>1.5</v>
       </c>
       <c r="W35">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
         <v>1.01</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6189,7 +6189,7 @@
         <v>2.49</v>
       </c>
       <c r="R36">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="S36">
         <v>1.2</v>
@@ -6201,7 +6201,7 @@
         <v>2.13</v>
       </c>
       <c r="V36">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W36">
         <v>1.18</v>
@@ -6222,7 +6222,7 @@
         <v>2.8</v>
       </c>
       <c r="AC36">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD36">
         <v>1.73</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
         <v>1.72</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.74</v>
+        <v>2.6</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>1.88</v>
+        <v>2.55</v>
       </c>
       <c r="Q37">
-        <v>3.88</v>
+        <v>3.02</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S37">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="U37">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="V37">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
+        <v>1.25</v>
+      </c>
+      <c r="Z37">
+        <v>3.7</v>
+      </c>
+      <c r="AA37">
+        <v>1.83</v>
+      </c>
+      <c r="AB37">
+        <v>1.91</v>
+      </c>
+      <c r="AC37">
+        <v>2.91</v>
+      </c>
+      <c r="AD37">
+        <v>1.34</v>
+      </c>
+      <c r="AE37">
         <v>1.08</v>
       </c>
-      <c r="Z37">
-        <v>7</v>
-      </c>
-      <c r="AA37">
-        <v>1.45</v>
-      </c>
-      <c r="AB37">
-        <v>2.82</v>
-      </c>
-      <c r="AC37">
-        <v>2</v>
-      </c>
-      <c r="AD37">
-        <v>1.75</v>
-      </c>
-      <c r="AE37">
-        <v>1.29</v>
-      </c>
       <c r="AF37">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG37">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AK37">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.6</v>
+        <v>3.72</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="Q38">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="U38">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AA38">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="AB38">
-        <v>1.91</v>
+        <v>2.82</v>
       </c>
       <c r="AC38">
-        <v>2.93</v>
+        <v>2</v>
       </c>
       <c r="AD38">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="AF38">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
+        <v>1.8</v>
+      </c>
+      <c r="AK38">
         <v>1.3</v>
-      </c>
-      <c r="AK38">
-        <v>1.43</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,16 +6669,16 @@
         <v>3.1</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P39">
         <v>2.05</v>
       </c>
       <c r="Q39">
-        <v>3.26</v>
+        <v>3.51</v>
       </c>
       <c r="R39">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6690,13 +6690,13 @@
         <v>2.04</v>
       </c>
       <c r="V39">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="W39">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
         <v>1.08</v>
@@ -6832,19 +6832,19 @@
         <v>1.51</v>
       </c>
       <c r="O40">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P40">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="Q40">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="R40">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T40">
         <v>3.42</v>
@@ -6853,7 +6853,7 @@
         <v>2.4</v>
       </c>
       <c r="V40">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W40">
         <v>1.11</v>
@@ -6868,10 +6868,10 @@
         <v>4.5</v>
       </c>
       <c r="AA40">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AB40">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AC40">
         <v>2.5</v>
@@ -6883,7 +6883,7 @@
         <v>1.18</v>
       </c>
       <c r="AF40">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
         <v>2.15</v>
@@ -6902,7 +6902,7 @@
         <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,7 +7001,7 @@
         <v>1.3</v>
       </c>
       <c r="Q41">
-        <v>7.83</v>
+        <v>6.5</v>
       </c>
       <c r="R41">
         <v>2.72</v>
@@ -7034,7 +7034,7 @@
         <v>1.35</v>
       </c>
       <c r="AB41">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="AC41">
         <v>1.83</v>
@@ -7043,7 +7043,7 @@
         <v>1.91</v>
       </c>
       <c r="AE41">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF41">
         <v>1.65</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="O42">
         <v>4.05</v>
@@ -7170,7 +7170,7 @@
         <v>2.34</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
         <v>3.24</v>
@@ -7182,7 +7182,7 @@
         <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
         <v>1.03</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O43">
         <v>2.75</v>
       </c>
       <c r="P43">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q43">
         <v>4.5</v>
@@ -7336,7 +7336,7 @@
         <v>1.56</v>
       </c>
       <c r="T43">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="U43">
         <v>3.4</v>
@@ -7357,13 +7357,13 @@
         <v>2.56</v>
       </c>
       <c r="AA43">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AB43">
         <v>1.44</v>
       </c>
       <c r="AC43">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD43">
         <v>1.13</v>
@@ -7375,7 +7375,7 @@
         <v>2.1</v>
       </c>
       <c r="AG43">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.36</v>
       </c>
       <c r="AK43">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7502,7 +7502,7 @@
         <v>3.25</v>
       </c>
       <c r="U44">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="V44">
         <v>1.5</v>
@@ -7511,19 +7511,19 @@
         <v>1.1</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
         <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.23</v>
+        <v>4.14</v>
       </c>
       <c r="AA44">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB44">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AC44">
         <v>2.7</v>
@@ -7532,13 +7532,13 @@
         <v>1.44</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK44">
         <v>1.44</v>
@@ -7665,7 +7665,7 @@
         <v>4</v>
       </c>
       <c r="U45">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="V45">
         <v>1.67</v>
@@ -8335,7 +8335,7 @@
         <v>6.91</v>
       </c>
       <c r="AA49">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB49">
         <v>3.34</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O50">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="P50">
-        <v>2.95</v>
+        <v>3.12</v>
       </c>
       <c r="Q50">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="R50">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="S50">
         <v>1.2</v>
@@ -8492,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
         <v>6.33</v>
@@ -8513,10 +8513,10 @@
         <v>1.35</v>
       </c>
       <c r="AF50">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG50">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>3.75</v>
       </c>
       <c r="P61">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="Q61">
         <v>2.53</v>
@@ -10267,16 +10267,16 @@
         <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T61">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="U61">
         <v>2</v>
       </c>
       <c r="V61">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="W61">
         <v>1.2</v>
@@ -10285,28 +10285,28 @@
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>5.88</v>
+        <v>5.83</v>
       </c>
       <c r="AA61">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AB61">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="AC61">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AD61">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE61">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AF61">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG61">
         <v>2.8</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AK61">
         <v>1.53</v>
@@ -10424,7 +10424,7 @@
         <v>2.6</v>
       </c>
       <c r="Q62">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R62">
         <v>2.36</v>
@@ -10593,16 +10593,16 @@
         <v>2.9</v>
       </c>
       <c r="S63">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T63">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="U63">
         <v>1.89</v>
       </c>
       <c r="V63">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="W63">
         <v>1.27</v>
@@ -10617,7 +10617,7 @@
         <v>8</v>
       </c>
       <c r="AA63">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB63">
         <v>3.4</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="O64">
         <v>3.6</v>
       </c>
       <c r="P64">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="Q64">
         <v>2.33</v>
@@ -10765,7 +10765,7 @@
         <v>2.25</v>
       </c>
       <c r="V64">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W64">
         <v>1.13</v>
@@ -10774,10 +10774,10 @@
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z64">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA64">
         <v>1.56</v>
@@ -10792,7 +10792,7 @@
         <v>1.59</v>
       </c>
       <c r="AE64">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF64">
         <v>1.5</v>
@@ -10814,7 +10814,7 @@
         <v>1.23</v>
       </c>
       <c r="AK64">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="P65">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="Q65">
-        <v>2.27</v>
+        <v>2.66</v>
       </c>
       <c r="R65">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S65">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U65">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V65">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z65">
-        <v>6</v>
+        <v>4.74</v>
       </c>
       <c r="AA65">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AB65">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AC65">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD65">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AE65">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG65">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="O66">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="P66">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="Q66">
-        <v>2.66</v>
+        <v>2.27</v>
       </c>
       <c r="R66">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T66">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U66">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="V66">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="W66">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>4.69</v>
+        <v>6</v>
       </c>
       <c r="AA66">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AB66">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AC66">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AD66">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AE66">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF66">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11396,31 +11396,31 @@
         <v>2.15</v>
       </c>
       <c r="O68">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
         <v>3</v>
       </c>
       <c r="Q68">
-        <v>2.46</v>
+        <v>2.67</v>
       </c>
       <c r="R68">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T68">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U68">
         <v>2.25</v>
       </c>
       <c r="V68">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W68">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X68">
         <v>1.01</v>
@@ -11432,7 +11432,7 @@
         <v>4.5</v>
       </c>
       <c r="AA68">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AB68">
         <v>2.3</v>
@@ -11466,7 +11466,7 @@
         <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11559,7 +11559,7 @@
         <v>2</v>
       </c>
       <c r="O69">
-        <v>3.83</v>
+        <v>3.93</v>
       </c>
       <c r="P69">
         <v>3</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -638,10 +638,10 @@
         <v>3.76</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
         <v>3.7</v>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="O3">
         <v>3.75</v>
@@ -819,7 +819,7 @@
         <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="V3">
         <v>1.48</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="O4">
         <v>3.4</v>
@@ -976,28 +976,28 @@
         <v>2.24</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="U4">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA4">
         <v>1.85</v>
@@ -1006,13 +1006,13 @@
         <v>1.95</v>
       </c>
       <c r="AC4">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="AD4">
         <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
         <v>1.7</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1130,7 +1130,7 @@
         <v>3.4</v>
       </c>
       <c r="P5">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q5">
         <v>2.54</v>
@@ -1154,7 +1154,7 @@
         <v>1.09</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
         <v>1.21</v>
@@ -1166,13 +1166,13 @@
         <v>1.75</v>
       </c>
       <c r="AB5">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AC5">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AD5">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AE5">
         <v>1.1</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
       <c r="O7">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P7">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q7">
         <v>6.05</v>
@@ -1631,16 +1631,16 @@
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.03</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="O9">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P9">
-        <v>6.13</v>
+        <v>6.75</v>
       </c>
       <c r="Q9">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R9">
         <v>2.3</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="O10">
         <v>3.3</v>
       </c>
       <c r="P10">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -1978,16 +1978,16 @@
         <v>3.68</v>
       </c>
       <c r="AA10">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AB10">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AC10">
         <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
         <v>1.09</v>
@@ -1996,7 +1996,7 @@
         <v>1.6</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="O12">
         <v>3.4</v>
       </c>
       <c r="P12">
-        <v>3.12</v>
+        <v>3.27</v>
       </c>
       <c r="Q12">
         <v>2.62</v>
@@ -2301,7 +2301,7 @@
         <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="AA12">
         <v>1.66</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O13">
         <v>3.75</v>
       </c>
       <c r="P13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q13">
         <v>2.15</v>
@@ -2443,10 +2443,10 @@
         <v>2.36</v>
       </c>
       <c r="S13">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U13">
         <v>2.15</v>
@@ -2470,7 +2470,7 @@
         <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC13">
         <v>2.38</v>
@@ -2597,25 +2597,25 @@
         <v>4</v>
       </c>
       <c r="P14">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q14">
         <v>3.75</v>
       </c>
       <c r="R14">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="S14">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
         <v>4</v>
       </c>
       <c r="U14">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V14">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W14">
         <v>1.17</v>
@@ -2633,7 +2633,7 @@
         <v>1.4</v>
       </c>
       <c r="AB14">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="AC14">
         <v>1.95</v>
@@ -2648,7 +2648,7 @@
         <v>1.36</v>
       </c>
       <c r="AG14">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>8.5</v>
+        <v>7.75</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Q15">
-        <v>6.28</v>
+        <v>7.95</v>
       </c>
       <c r="R15">
         <v>2.88</v>
@@ -2775,10 +2775,10 @@
         <v>4.5</v>
       </c>
       <c r="U15">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="V15">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="W15">
         <v>1.23</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AK15">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="O16">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P16">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q16">
         <v>2.85</v>
@@ -2932,7 +2932,7 @@
         <v>1.78</v>
       </c>
       <c r="S16">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="T16">
         <v>2.19</v>
@@ -2962,10 +2962,10 @@
         <v>1.41</v>
       </c>
       <c r="AC16">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD16">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AE16">
         <v>1.04</v>
@@ -3086,22 +3086,22 @@
         <v>2.75</v>
       </c>
       <c r="P17">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="Q17">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R17">
         <v>1.74</v>
       </c>
       <c r="S17">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="T17">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="U17">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="V17">
         <v>1.17</v>
@@ -3110,7 +3110,7 @@
         <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
         <v>1.56</v>
@@ -3119,13 +3119,13 @@
         <v>2.22</v>
       </c>
       <c r="AA17">
-        <v>2.74</v>
+        <v>2.3</v>
       </c>
       <c r="AB17">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC17">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AD17">
         <v>1.13</v>
@@ -3134,10 +3134,10 @@
         <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG17">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="O18">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="P18">
-        <v>2.62</v>
+        <v>4.7</v>
       </c>
       <c r="Q18">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="AC18">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AD18">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AF18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG18">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK18">
-        <v>1.49</v>
+        <v>2.28</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,61 +3406,61 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.7</v>
+        <v>1.93</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q19">
-        <v>3.36</v>
+        <v>2.26</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="S19">
+        <v>1.2</v>
+      </c>
+      <c r="T19">
+        <v>4</v>
+      </c>
+      <c r="U19">
+        <v>2.1</v>
+      </c>
+      <c r="V19">
+        <v>1.67</v>
+      </c>
+      <c r="W19">
+        <v>1.17</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>1.08</v>
+      </c>
+      <c r="Z19">
+        <v>3.6</v>
+      </c>
+      <c r="AA19">
+        <v>1.33</v>
+      </c>
+      <c r="AB19">
+        <v>2.56</v>
+      </c>
+      <c r="AC19">
+        <v>1.84</v>
+      </c>
+      <c r="AD19">
+        <v>1.52</v>
+      </c>
+      <c r="AE19">
         <v>1.3</v>
       </c>
-      <c r="T19">
-        <v>3.3</v>
-      </c>
-      <c r="U19">
-        <v>2.51</v>
-      </c>
-      <c r="V19">
-        <v>1.5</v>
-      </c>
-      <c r="W19">
-        <v>1.13</v>
-      </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
-        <v>1.16</v>
-      </c>
-      <c r="Z19">
-        <v>4.23</v>
-      </c>
-      <c r="AA19">
-        <v>1.63</v>
-      </c>
-      <c r="AB19">
-        <v>2.1</v>
-      </c>
-      <c r="AC19">
-        <v>2.52</v>
-      </c>
-      <c r="AD19">
-        <v>1.41</v>
-      </c>
-      <c r="AE19">
-        <v>1.13</v>
-      </c>
       <c r="AF19">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG19">
         <v>2.3</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,65 +3569,65 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="O20">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>4.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q20">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="R20">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T20">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U20">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="V20">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
+        <v>2.14</v>
+      </c>
+      <c r="AC20">
+        <v>2.2</v>
+      </c>
+      <c r="AD20">
+        <v>1.45</v>
+      </c>
+      <c r="AE20">
+        <v>1.14</v>
+      </c>
+      <c r="AF20">
+        <v>1.5</v>
+      </c>
+      <c r="AG20">
         <v>2.3</v>
       </c>
-      <c r="AC20">
-        <v>1.8</v>
-      </c>
-      <c r="AD20">
-        <v>1.74</v>
-      </c>
-      <c r="AE20">
-        <v>1.26</v>
-      </c>
-      <c r="AF20">
-        <v>1.44</v>
-      </c>
-      <c r="AG20">
-        <v>2.5</v>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="O21">
         <v>3.65</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="Q21">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="S21">
         <v>1.2</v>
@@ -3753,43 +3753,43 @@
         <v>4</v>
       </c>
       <c r="U21">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="V21">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z21">
-        <v>3.6</v>
+        <v>5.85</v>
       </c>
       <c r="AA21">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AB21">
-        <v>2.56</v>
+        <v>3.2</v>
       </c>
       <c r="AC21">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AD21">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AE21">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AF21">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG21">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK21">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="O22">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>2.67</v>
+        <v>2.19</v>
       </c>
       <c r="Q22">
-        <v>2.61</v>
+        <v>3.39</v>
       </c>
       <c r="R22">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="S22">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U22">
-        <v>1.75</v>
+        <v>2.52</v>
       </c>
       <c r="V22">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="W22">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="Z22">
-        <v>5.85</v>
+        <v>4.23</v>
       </c>
       <c r="AA22">
+        <v>1.63</v>
+      </c>
+      <c r="AB22">
+        <v>1.83</v>
+      </c>
+      <c r="AC22">
+        <v>2.52</v>
+      </c>
+      <c r="AD22">
+        <v>1.41</v>
+      </c>
+      <c r="AE22">
+        <v>1.13</v>
+      </c>
+      <c r="AF22">
+        <v>1.44</v>
+      </c>
+      <c r="AG22">
+        <v>2.3</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.09</v>
+      </c>
+      <c r="AK22">
         <v>1.36</v>
-      </c>
-      <c r="AB22">
-        <v>3.1</v>
-      </c>
-      <c r="AC22">
-        <v>1.89</v>
-      </c>
-      <c r="AD22">
-        <v>1.78</v>
-      </c>
-      <c r="AE22">
-        <v>1.31</v>
-      </c>
-      <c r="AF22">
-        <v>1.36</v>
-      </c>
-      <c r="AG22">
-        <v>2.91</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.17</v>
-      </c>
-      <c r="AK22">
-        <v>1.57</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P23">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q23">
         <v>2.4</v>
@@ -4076,7 +4076,7 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
         <v>2.45</v>
@@ -4115,7 +4115,7 @@
         <v>1.63</v>
       </c>
       <c r="AG23">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>3.1</v>
       </c>
       <c r="P24">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q24">
         <v>3.26</v>
@@ -4266,7 +4266,7 @@
         <v>1.79</v>
       </c>
       <c r="AC24">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AD24">
         <v>1.3</v>
@@ -4278,7 +4278,7 @@
         <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>2.25</v>
       </c>
       <c r="O32">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
         <v>3.11</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
         <v>1.67</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O33">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q33">
         <v>2.2</v>
@@ -5724,7 +5724,7 @@
         <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="AA33">
         <v>1.76</v>
@@ -5761,7 +5761,7 @@
         <v>1.16</v>
       </c>
       <c r="AK33">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="O34">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P34">
         <v>2.42</v>
@@ -5872,10 +5872,10 @@
         <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="V34">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="W34">
         <v>1.13</v>
@@ -5896,13 +5896,13 @@
         <v>2.6</v>
       </c>
       <c r="AC34">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AD34">
         <v>1.64</v>
       </c>
       <c r="AE34">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AF34">
         <v>1.44</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
+        <v>2.11</v>
+      </c>
+      <c r="O35">
+        <v>3.9</v>
+      </c>
+      <c r="P35">
+        <v>3.1</v>
+      </c>
+      <c r="Q35">
+        <v>2.49</v>
+      </c>
+      <c r="R35">
+        <v>2.65</v>
+      </c>
+      <c r="S35">
+        <v>1.2</v>
+      </c>
+      <c r="T35">
+        <v>4.05</v>
+      </c>
+      <c r="U35">
+        <v>2.13</v>
+      </c>
+      <c r="V35">
+        <v>1.69</v>
+      </c>
+      <c r="W35">
+        <v>1.18</v>
+      </c>
+      <c r="X35">
+        <v>1.02</v>
+      </c>
+      <c r="Y35">
+        <v>1.11</v>
+      </c>
+      <c r="Z35">
+        <v>6</v>
+      </c>
+      <c r="AA35">
+        <v>1.44</v>
+      </c>
+      <c r="AB35">
+        <v>2.8</v>
+      </c>
+      <c r="AC35">
         <v>2.05</v>
       </c>
-      <c r="O35">
-        <v>3.5</v>
-      </c>
-      <c r="P35">
-        <v>3.4</v>
-      </c>
-      <c r="Q35">
-        <v>2.36</v>
-      </c>
-      <c r="R35">
-        <v>2.3</v>
-      </c>
-      <c r="S35">
-        <v>1.33</v>
-      </c>
-      <c r="T35">
-        <v>3.4</v>
-      </c>
-      <c r="U35">
-        <v>2.4</v>
-      </c>
-      <c r="V35">
-        <v>1.5</v>
-      </c>
-      <c r="W35">
-        <v>1.12</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
+      <c r="AD35">
+        <v>1.73</v>
+      </c>
+      <c r="AE35">
+        <v>1.29</v>
+      </c>
+      <c r="AF35">
+        <v>1.4</v>
+      </c>
+      <c r="AG35">
+        <v>2.89</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.2</v>
       </c>
-      <c r="Z35">
-        <v>4.2</v>
-      </c>
-      <c r="AA35">
+      <c r="AK35">
         <v>1.72</v>
-      </c>
-      <c r="AB35">
-        <v>2.17</v>
-      </c>
-      <c r="AC35">
-        <v>2.68</v>
-      </c>
-      <c r="AD35">
-        <v>1.47</v>
-      </c>
-      <c r="AE35">
-        <v>1.14</v>
-      </c>
-      <c r="AF35">
-        <v>1.6</v>
-      </c>
-      <c r="AG35">
-        <v>2.3</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.25</v>
-      </c>
-      <c r="AK35">
-        <v>1.81</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="O36">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="Q36">
-        <v>2.49</v>
+        <v>3.02</v>
       </c>
       <c r="R36">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="S36">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>4.05</v>
+        <v>3.1</v>
       </c>
       <c r="U36">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="V36">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="W36">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="AA36">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AB36">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC36">
-        <v>2.05</v>
+        <v>2.91</v>
       </c>
       <c r="AD36">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AE36">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AF36">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.89</v>
+        <v>2.2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK36">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P37">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q37">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="R37">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T37">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="U37">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AA37">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="AB37">
-        <v>1.91</v>
+        <v>2.81</v>
       </c>
       <c r="AC37">
-        <v>2.91</v>
+        <v>2</v>
       </c>
       <c r="AD37">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AE37">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AF37">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
+        <v>1.8</v>
+      </c>
+      <c r="AK37">
         <v>1.3</v>
-      </c>
-      <c r="AK37">
-        <v>1.43</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,25 +6503,25 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.72</v>
+        <v>3.15</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P38">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="Q38">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="U38">
         <v>2</v>
@@ -6530,10 +6530,10 @@
         <v>1.75</v>
       </c>
       <c r="W38">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
         <v>1.08</v>
@@ -6542,25 +6542,25 @@
         <v>7</v>
       </c>
       <c r="AA38">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AC38">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD38">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE38">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF38">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG38">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="O39">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="Q39">
-        <v>3.51</v>
+        <v>2.36</v>
       </c>
       <c r="R39">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB39">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AC39">
-        <v>2</v>
+        <v>2.68</v>
       </c>
       <c r="AD39">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="AE39">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AG39">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>3.42</v>
       </c>
       <c r="U40">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V40">
         <v>1.57</v>
@@ -6902,7 +6902,7 @@
         <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7043,7 +7043,7 @@
         <v>1.91</v>
       </c>
       <c r="AE41">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF41">
         <v>1.65</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="AK41">
         <v>1.05</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O42">
         <v>4.05</v>
@@ -7170,7 +7170,7 @@
         <v>2.34</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T42">
         <v>3.24</v>
@@ -7182,7 +7182,7 @@
         <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X42">
         <v>1.03</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="AK42">
         <v>1.16</v>
@@ -7321,10 +7321,10 @@
         <v>3.6</v>
       </c>
       <c r="O43">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P43">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q43">
         <v>4.5</v>
@@ -7333,10 +7333,10 @@
         <v>1.72</v>
       </c>
       <c r="S43">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T43">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="U43">
         <v>3.4</v>
@@ -7354,7 +7354,7 @@
         <v>1.46</v>
       </c>
       <c r="Z43">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AA43">
         <v>2.42</v>
@@ -7375,7 +7375,7 @@
         <v>2.1</v>
       </c>
       <c r="AG43">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AK43">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,16 +7481,16 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="O44">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="P44">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q44">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="R44">
         <v>2.25</v>
@@ -7502,7 +7502,7 @@
         <v>3.25</v>
       </c>
       <c r="U44">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="V44">
         <v>1.5</v>
@@ -7511,13 +7511,13 @@
         <v>1.1</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
         <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="AA44">
         <v>1.7</v>
@@ -7532,10 +7532,10 @@
         <v>1.44</v>
       </c>
       <c r="AE44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG44">
         <v>2.3</v>
@@ -7554,7 +7554,7 @@
         <v>1.57</v>
       </c>
       <c r="AK44">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="O45">
         <v>3.8</v>
@@ -7656,7 +7656,7 @@
         <v>3.77</v>
       </c>
       <c r="R45">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S45">
         <v>1.2</v>
@@ -7665,7 +7665,7 @@
         <v>4</v>
       </c>
       <c r="U45">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="V45">
         <v>1.67</v>
@@ -7677,7 +7677,7 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z45">
         <v>5.3</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
         <v>2.32</v>
@@ -8329,10 +8329,10 @@
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z49">
-        <v>6.91</v>
+        <v>8</v>
       </c>
       <c r="AA49">
         <v>1.33</v>
@@ -8341,19 +8341,19 @@
         <v>3.34</v>
       </c>
       <c r="AC49">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AD49">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AE49">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AF49">
         <v>1.4</v>
       </c>
       <c r="AG49">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK49">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8462,16 +8462,16 @@
         <v>1.88</v>
       </c>
       <c r="O50">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="P50">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="Q50">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="R50">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="S50">
         <v>1.2</v>
@@ -8625,16 +8625,16 @@
         <v>2.15</v>
       </c>
       <c r="O51">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="P51">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="Q51">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="R51">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="S51">
         <v>1.17</v>
@@ -8643,13 +8643,13 @@
         <v>4.4</v>
       </c>
       <c r="U51">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V51">
         <v>1.8</v>
       </c>
       <c r="W51">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X51">
         <v>0</v>
@@ -8667,13 +8667,13 @@
         <v>2.83</v>
       </c>
       <c r="AC51">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD51">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AE51">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AF51">
         <v>1.36</v>
@@ -8797,7 +8797,7 @@
         <v>2.38</v>
       </c>
       <c r="R52">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8806,10 +8806,10 @@
         <v>4</v>
       </c>
       <c r="U52">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="V52">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W52">
         <v>1.15</v>
@@ -8821,22 +8821,22 @@
         <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>5.5</v>
+        <v>5.22</v>
       </c>
       <c r="AA52">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AB52">
         <v>2.63</v>
       </c>
       <c r="AC52">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AD52">
         <v>1.61</v>
       </c>
       <c r="AE52">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AF52">
         <v>1.44</v>
@@ -10261,7 +10261,7 @@
         <v>2.59</v>
       </c>
       <c r="Q61">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="R61">
         <v>2.5</v>
@@ -10270,7 +10270,7 @@
         <v>1.22</v>
       </c>
       <c r="T61">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U61">
         <v>2</v>
@@ -10279,31 +10279,31 @@
         <v>1.69</v>
       </c>
       <c r="W61">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>0</v>
       </c>
       <c r="Y61">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>5.83</v>
+        <v>5.81</v>
       </c>
       <c r="AA61">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB61">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="AC61">
         <v>2.13</v>
       </c>
       <c r="AD61">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE61">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF61">
         <v>1.4</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,65 +10415,65 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="O62">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="P62">
-        <v>2.6</v>
+        <v>8</v>
       </c>
       <c r="Q62">
-        <v>2.8</v>
+        <v>1.51</v>
       </c>
       <c r="R62">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T62">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U62">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="V62">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="W62">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z62">
-        <v>4.9</v>
+        <v>6.95</v>
       </c>
       <c r="AA62">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AB62">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="AC62">
+        <v>1.73</v>
+      </c>
+      <c r="AD62">
+        <v>2</v>
+      </c>
+      <c r="AE62">
+        <v>1.42</v>
+      </c>
+      <c r="AF62">
+        <v>1.6</v>
+      </c>
+      <c r="AG62">
         <v>2.2</v>
       </c>
-      <c r="AD62">
-        <v>1.65</v>
-      </c>
-      <c r="AE62">
-        <v>1.22</v>
-      </c>
-      <c r="AF62">
-        <v>1.44</v>
-      </c>
-      <c r="AG62">
-        <v>2.62</v>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AK62">
-        <v>1.58</v>
+        <v>4.2</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="O63">
-        <v>7.36</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q63">
-        <v>1.51</v>
+        <v>2.53</v>
       </c>
       <c r="R63">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="S63">
+        <v>1.2</v>
+      </c>
+      <c r="T63">
+        <v>4</v>
+      </c>
+      <c r="U63">
+        <v>2.1</v>
+      </c>
+      <c r="V63">
+        <v>1.68</v>
+      </c>
+      <c r="W63">
         <v>1.18</v>
       </c>
-      <c r="T63">
-        <v>5</v>
-      </c>
-      <c r="U63">
-        <v>1.89</v>
-      </c>
-      <c r="V63">
-        <v>1.85</v>
-      </c>
-      <c r="W63">
-        <v>1.27</v>
-      </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z63">
-        <v>8</v>
+        <v>4.9</v>
       </c>
       <c r="AA63">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AB63">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC63">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD63">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AE63">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AF63">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AG63">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AK63">
-        <v>3.8</v>
+        <v>1.56</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10750,7 +10750,7 @@
         <v>3.25</v>
       </c>
       <c r="Q64">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="R64">
         <v>2.5</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK64">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="O65">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="P65">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="Q65">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T65">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="V65">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>4.74</v>
+        <v>6</v>
       </c>
       <c r="AA65">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="AB65">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AC65">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AD65">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AE65">
+        <v>1.29</v>
+      </c>
+      <c r="AF65">
+        <v>1.44</v>
+      </c>
+      <c r="AG65">
+        <v>2.7</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
         <v>1.2</v>
       </c>
-      <c r="AF65">
-        <v>1.53</v>
-      </c>
-      <c r="AG65">
-        <v>2.55</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.33</v>
-      </c>
       <c r="AK65">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.88</v>
+        <v>2.19</v>
       </c>
       <c r="O66">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P66">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="Q66">
-        <v>2.27</v>
+        <v>2.66</v>
       </c>
       <c r="R66">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="S66">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U66">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V66">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="W66">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z66">
-        <v>6</v>
+        <v>4.74</v>
       </c>
       <c r="AA66">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="AB66">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AC66">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD66">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AE66">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF66">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG66">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AK66">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11251,7 +11251,7 @@
         <v>3.8</v>
       </c>
       <c r="U67">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="V67">
         <v>1.59</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O68">
         <v>3.6</v>
       </c>
       <c r="P68">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q68">
         <v>2.67</v>
@@ -11414,10 +11414,10 @@
         <v>3.4</v>
       </c>
       <c r="U68">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="V68">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W68">
         <v>1.12</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="O69">
-        <v>3.93</v>
+        <v>3.92</v>
       </c>
       <c r="P69">
         <v>3</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2">
@@ -822,7 +822,7 @@
         <v>2.39</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W3">
         <v>1.12</v>
@@ -834,19 +834,19 @@
         <v>1.17</v>
       </c>
       <c r="Z3">
-        <v>4.03</v>
+        <v>4.04</v>
       </c>
       <c r="AA3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AB3">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC3">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="AD3">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
         <v>1.1</v>
@@ -871,7 +871,7 @@
         <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,16 +970,16 @@
         <v>3.1</v>
       </c>
       <c r="Q4">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="S4">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U4">
         <v>2.5</v>
@@ -1003,7 +1003,7 @@
         <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC4">
         <v>2.97</v>
@@ -1015,10 +1015,10 @@
         <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
@@ -1459,22 +1459,22 @@
         <v>1.62</v>
       </c>
       <c r="Q7">
-        <v>6.05</v>
+        <v>7.01</v>
       </c>
       <c r="R7">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="S7">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T7">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="U7">
-        <v>3.29</v>
+        <v>3.19</v>
       </c>
       <c r="V7">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1483,32 +1483,32 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z7">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AA7">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="AB7">
+        <v>1.52</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>2.38</v>
+      </c>
+      <c r="AG7">
         <v>1.49</v>
       </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>2.29</v>
-      </c>
-      <c r="AG7">
-        <v>1.52</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O9">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P9">
-        <v>6.75</v>
+        <v>6.13</v>
       </c>
       <c r="Q9">
         <v>1.93</v>
@@ -1935,23 +1935,23 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N10">
         <v>3.25</v>
       </c>
       <c r="O10">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q10">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R10">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="S10">
         <v>1.3</v>
@@ -1972,28 +1972,28 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="AA10">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AC10">
         <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE10">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG10">
         <v>2.2</v>
@@ -2012,7 +2012,7 @@
         <v>1.22</v>
       </c>
       <c r="AK10">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
         <v>3.57</v>
@@ -2277,7 +2277,7 @@
         <v>2.62</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2301,7 +2301,7 @@
         <v>1.23</v>
       </c>
       <c r="Z12">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="AA12">
         <v>1.66</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AK12">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>3.75</v>
       </c>
       <c r="P13">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
         <v>2.15</v>
@@ -2443,19 +2443,19 @@
         <v>2.36</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="T13">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="U13">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="V13">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W13">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2932,7 +2932,7 @@
         <v>1.78</v>
       </c>
       <c r="S16">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="T16">
         <v>2.19</v>
@@ -3134,10 +3134,10 @@
         <v>1.01</v>
       </c>
       <c r="AF17">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,65 +3243,65 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="O18">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>4.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q18">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="R18">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AA18">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
+        <v>2.14</v>
+      </c>
+      <c r="AC18">
+        <v>2.2</v>
+      </c>
+      <c r="AD18">
+        <v>1.45</v>
+      </c>
+      <c r="AE18">
+        <v>1.14</v>
+      </c>
+      <c r="AF18">
+        <v>1.5</v>
+      </c>
+      <c r="AG18">
         <v>2.3</v>
       </c>
-      <c r="AC18">
-        <v>2.07</v>
-      </c>
-      <c r="AD18">
-        <v>1.75</v>
-      </c>
-      <c r="AE18">
-        <v>1.26</v>
-      </c>
-      <c r="AF18">
-        <v>1.44</v>
-      </c>
-      <c r="AG18">
-        <v>2.5</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>2.28</v>
+        <v>1.49</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="P19">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="Q19">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="R19">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="S19">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U19">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="V19">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB19">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AC19">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="AD19">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AE19">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF19">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AK19">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,61 +3569,61 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="Q20">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="S20">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T20">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="V20">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="W20">
+        <v>1.17</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
         <v>1.08</v>
       </c>
-      <c r="X20">
-        <v>1.02</v>
-      </c>
-      <c r="Y20">
-        <v>1.15</v>
-      </c>
       <c r="Z20">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="AC20">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AD20">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AE20">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG20">
         <v>2.3</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4097,7 +4097,7 @@
         <v>4.1</v>
       </c>
       <c r="AA23">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB23">
         <v>2</v>
@@ -4230,10 +4230,10 @@
         <v>2.3</v>
       </c>
       <c r="Q24">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="R24">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S24">
         <v>1.4</v>
@@ -4260,10 +4260,10 @@
         <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB24">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC24">
         <v>3.24</v>
@@ -5528,7 +5528,7 @@
         <v>2.25</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P32">
         <v>3.11</v>
@@ -5546,7 +5546,7 @@
         <v>3</v>
       </c>
       <c r="U32">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="V32">
         <v>1.36</v>
@@ -5567,13 +5567,13 @@
         <v>1.94</v>
       </c>
       <c r="AB32">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AC32">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AD32">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE32">
         <v>1.06</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK32">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
+        <v>3.6</v>
+      </c>
+      <c r="P33">
+        <v>2.41</v>
+      </c>
+      <c r="Q33">
+        <v>2.61</v>
+      </c>
+      <c r="R33">
+        <v>2.3</v>
+      </c>
+      <c r="S33">
+        <v>1.2</v>
+      </c>
+      <c r="T33">
         <v>3.8</v>
       </c>
-      <c r="P33">
-        <v>4.6</v>
-      </c>
-      <c r="Q33">
-        <v>2.2</v>
-      </c>
-      <c r="R33">
-        <v>2.1</v>
-      </c>
-      <c r="S33">
-        <v>1.29</v>
-      </c>
-      <c r="T33">
-        <v>3.3</v>
-      </c>
       <c r="U33">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="V33">
+        <v>1.66</v>
+      </c>
+      <c r="W33">
+        <v>1.13</v>
+      </c>
+      <c r="X33">
+        <v>1.01</v>
+      </c>
+      <c r="Y33">
+        <v>1.13</v>
+      </c>
+      <c r="Z33">
+        <v>6</v>
+      </c>
+      <c r="AA33">
+        <v>1.47</v>
+      </c>
+      <c r="AB33">
+        <v>2.62</v>
+      </c>
+      <c r="AC33">
+        <v>2.23</v>
+      </c>
+      <c r="AD33">
+        <v>1.64</v>
+      </c>
+      <c r="AE33">
+        <v>1.25</v>
+      </c>
+      <c r="AF33">
         <v>1.44</v>
       </c>
-      <c r="W33">
-        <v>1.07</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
-      <c r="Y33">
-        <v>1.22</v>
-      </c>
-      <c r="Z33">
-        <v>4</v>
-      </c>
-      <c r="AA33">
-        <v>1.76</v>
-      </c>
-      <c r="AB33">
-        <v>1.99</v>
-      </c>
-      <c r="AC33">
-        <v>3.1</v>
-      </c>
-      <c r="AD33">
-        <v>1.36</v>
-      </c>
-      <c r="AE33">
-        <v>1.09</v>
-      </c>
-      <c r="AF33">
-        <v>1.7</v>
-      </c>
       <c r="AG33">
-        <v>2.05</v>
+        <v>2.62</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="AK33">
-        <v>2.15</v>
+        <v>1.54</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="O34">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>2.42</v>
+        <v>4.6</v>
       </c>
       <c r="Q34">
-        <v>2.56</v>
+        <v>2.21</v>
       </c>
       <c r="R34">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="V34">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>4.05</v>
       </c>
       <c r="AA34">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AB34">
-        <v>2.6</v>
+        <v>1.99</v>
       </c>
       <c r="AC34">
-        <v>2.23</v>
+        <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AF34">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="AK34">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="O35">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
+        <v>2.55</v>
+      </c>
+      <c r="Q35">
+        <v>3.02</v>
+      </c>
+      <c r="R35">
+        <v>2.32</v>
+      </c>
+      <c r="S35">
+        <v>1.36</v>
+      </c>
+      <c r="T35">
         <v>3.1</v>
       </c>
-      <c r="Q35">
-        <v>2.49</v>
-      </c>
-      <c r="R35">
-        <v>2.65</v>
-      </c>
-      <c r="S35">
-        <v>1.2</v>
-      </c>
-      <c r="T35">
-        <v>4.05</v>
-      </c>
       <c r="U35">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="V35">
-        <v>1.69</v>
+        <v>1.43</v>
       </c>
       <c r="W35">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="Z35">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="AA35">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AB35">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="AC35">
-        <v>2.05</v>
+        <v>2.91</v>
       </c>
       <c r="AD35">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="AE35">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AG35">
-        <v>2.89</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK35">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>2.55</v>
+        <v>1.87</v>
       </c>
       <c r="Q36">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="R36">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="U36">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="V36">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z36">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AA36">
-        <v>1.83</v>
+        <v>1.39</v>
       </c>
       <c r="AB36">
-        <v>1.91</v>
+        <v>2.81</v>
       </c>
       <c r="AC36">
-        <v>2.91</v>
+        <v>2</v>
       </c>
       <c r="AD36">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AE36">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AG36">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="AK36">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="O37">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P37">
-        <v>1.87</v>
+        <v>3.4</v>
       </c>
       <c r="Q37">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S37">
+        <v>1.33</v>
+      </c>
+      <c r="T37">
+        <v>3.4</v>
+      </c>
+      <c r="U37">
+        <v>2.4</v>
+      </c>
+      <c r="V37">
+        <v>1.5</v>
+      </c>
+      <c r="W37">
+        <v>1.12</v>
+      </c>
+      <c r="X37">
+        <v>1.01</v>
+      </c>
+      <c r="Y37">
+        <v>1.2</v>
+      </c>
+      <c r="Z37">
+        <v>4.2</v>
+      </c>
+      <c r="AA37">
+        <v>1.72</v>
+      </c>
+      <c r="AB37">
+        <v>2.17</v>
+      </c>
+      <c r="AC37">
+        <v>2.68</v>
+      </c>
+      <c r="AD37">
+        <v>1.47</v>
+      </c>
+      <c r="AE37">
+        <v>1.14</v>
+      </c>
+      <c r="AF37">
+        <v>1.6</v>
+      </c>
+      <c r="AG37">
+        <v>2.3</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.25</v>
       </c>
-      <c r="T37">
-        <v>3.45</v>
-      </c>
-      <c r="U37">
-        <v>2</v>
-      </c>
-      <c r="V37">
-        <v>1.75</v>
-      </c>
-      <c r="W37">
-        <v>1.17</v>
-      </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.08</v>
-      </c>
-      <c r="Z37">
-        <v>7</v>
-      </c>
-      <c r="AA37">
-        <v>1.39</v>
-      </c>
-      <c r="AB37">
-        <v>2.81</v>
-      </c>
-      <c r="AC37">
-        <v>2</v>
-      </c>
-      <c r="AD37">
-        <v>1.8</v>
-      </c>
-      <c r="AE37">
-        <v>1.29</v>
-      </c>
-      <c r="AF37">
-        <v>1.4</v>
-      </c>
-      <c r="AG37">
-        <v>2.9</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.8</v>
-      </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.15</v>
+        <v>2.11</v>
       </c>
       <c r="O38">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>3.5</v>
+        <v>2.49</v>
       </c>
       <c r="R38">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="S38">
         <v>1.2</v>
       </c>
       <c r="T38">
-        <v>3.94</v>
+        <v>4.05</v>
       </c>
       <c r="U38">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="V38">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="W38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA38">
+        <v>1.44</v>
+      </c>
+      <c r="AB38">
+        <v>2.8</v>
+      </c>
+      <c r="AC38">
+        <v>2.05</v>
+      </c>
+      <c r="AD38">
+        <v>1.73</v>
+      </c>
+      <c r="AE38">
+        <v>1.29</v>
+      </c>
+      <c r="AF38">
         <v>1.4</v>
       </c>
-      <c r="AB38">
-        <v>3</v>
-      </c>
-      <c r="AC38">
-        <v>1.91</v>
-      </c>
-      <c r="AD38">
-        <v>1.83</v>
-      </c>
-      <c r="AE38">
-        <v>1.33</v>
-      </c>
-      <c r="AF38">
-        <v>1.36</v>
-      </c>
       <c r="AG38">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.05</v>
+        <v>3.15</v>
       </c>
       <c r="O39">
+        <v>4.1</v>
+      </c>
+      <c r="P39">
+        <v>2.08</v>
+      </c>
+      <c r="Q39">
         <v>3.5</v>
       </c>
-      <c r="P39">
-        <v>3.4</v>
-      </c>
-      <c r="Q39">
-        <v>2.36</v>
-      </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
+        <v>1.08</v>
+      </c>
+      <c r="Z39">
+        <v>7</v>
+      </c>
+      <c r="AA39">
+        <v>1.4</v>
+      </c>
+      <c r="AB39">
+        <v>3</v>
+      </c>
+      <c r="AC39">
+        <v>1.91</v>
+      </c>
+      <c r="AD39">
+        <v>1.83</v>
+      </c>
+      <c r="AE39">
+        <v>1.33</v>
+      </c>
+      <c r="AF39">
+        <v>1.36</v>
+      </c>
+      <c r="AG39">
+        <v>3</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.2</v>
       </c>
-      <c r="Z39">
-        <v>4.2</v>
-      </c>
-      <c r="AA39">
-        <v>1.72</v>
-      </c>
-      <c r="AB39">
-        <v>2.17</v>
-      </c>
-      <c r="AC39">
-        <v>2.68</v>
-      </c>
-      <c r="AD39">
-        <v>1.47</v>
-      </c>
-      <c r="AE39">
-        <v>1.14</v>
-      </c>
-      <c r="AF39">
-        <v>1.6</v>
-      </c>
-      <c r="AG39">
-        <v>2.3</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.25</v>
-      </c>
       <c r="AK39">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         <v>4.05</v>
       </c>
       <c r="P42">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="Q42">
         <v>4.88</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="AK42">
         <v>1.16</v>
@@ -7321,16 +7321,16 @@
         <v>3.6</v>
       </c>
       <c r="O43">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="P43">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q43">
         <v>4.5</v>
       </c>
       <c r="R43">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S43">
         <v>1.5</v>
@@ -7357,7 +7357,7 @@
         <v>2.53</v>
       </c>
       <c r="AA43">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AB43">
         <v>1.44</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AK43">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AL43">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -638,10 +638,10 @@
         <v>3.76</v>
       </c>
       <c r="O2">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Q2">
         <v>3.7</v>
@@ -659,13 +659,13 @@
         <v>2.65</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
         <v>1.11</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.29</v>
@@ -686,7 +686,7 @@
         <v>1.29</v>
       </c>
       <c r="AE2">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
         <v>1.64</v>
@@ -813,16 +813,16 @@
         <v>2.25</v>
       </c>
       <c r="S3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U3">
         <v>2.39</v>
       </c>
       <c r="V3">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
         <v>1.12</v>
@@ -834,19 +834,19 @@
         <v>1.17</v>
       </c>
       <c r="Z3">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="AA3">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AB3">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AC3">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AD3">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
         <v>1.1</v>
@@ -871,7 +871,7 @@
         <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>3.1</v>
       </c>
       <c r="Q4">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="R4">
         <v>2.07</v>
@@ -979,13 +979,13 @@
         <v>1.35</v>
       </c>
       <c r="T4">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="U4">
         <v>2.5</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
         <v>1.1</v>
@@ -1003,7 +1003,7 @@
         <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
         <v>2.97</v>
@@ -1130,7 +1130,7 @@
         <v>3.4</v>
       </c>
       <c r="P5">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Q5">
         <v>2.54</v>
@@ -1166,7 +1166,7 @@
         <v>1.75</v>
       </c>
       <c r="AB5">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AC5">
         <v>2.38</v>
@@ -1287,46 +1287,46 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q6">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="S6">
         <v>1.22</v>
       </c>
       <c r="T6">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U6">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="V6">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="W6">
         <v>1.17</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.08</v>
       </c>
       <c r="Z6">
-        <v>5.45</v>
+        <v>5.55</v>
       </c>
       <c r="AA6">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB6">
         <v>2.73</v>
@@ -1335,7 +1335,7 @@
         <v>2.11</v>
       </c>
       <c r="AD6">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE6">
         <v>1.3</v>
@@ -1344,7 +1344,7 @@
         <v>1.4</v>
       </c>
       <c r="AG6">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK6">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.9</v>
+        <v>6.55</v>
       </c>
       <c r="O7">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P7">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="Q7">
-        <v>7.01</v>
+        <v>7.17</v>
       </c>
       <c r="R7">
         <v>2.07</v>
@@ -1483,13 +1483,13 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z7">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="AA7">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AB7">
         <v>1.52</v>
@@ -1504,10 +1504,10 @@
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AG7">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1613,55 +1613,55 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="O8">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q8">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T8">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="U8">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z8">
-        <v>3.78</v>
+        <v>3.34</v>
       </c>
       <c r="AA8">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="AB8">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AC8">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="AD8">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE8">
         <v>1.1</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK8">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1779,10 +1779,10 @@
         <v>1.44</v>
       </c>
       <c r="O9">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P9">
-        <v>6.13</v>
+        <v>6</v>
       </c>
       <c r="Q9">
         <v>1.93</v>
@@ -1794,7 +1794,7 @@
         <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="U9">
         <v>2.63</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK9">
         <v>2.62</v>
@@ -1942,16 +1942,16 @@
         <v>3.25</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P10">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="Q10">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="R10">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S10">
         <v>1.3</v>
@@ -1966,31 +1966,31 @@
         <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AA10">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AD10">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF10">
         <v>1.62</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>2</v>
       </c>
       <c r="O11">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
         <v>3.57</v>
@@ -2141,10 +2141,10 @@
         <v>2.92</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB11">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
         <v>3.8</v>
@@ -2274,10 +2274,10 @@
         <v>3.27</v>
       </c>
       <c r="Q12">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
         <v>1.36</v>
@@ -2286,37 +2286,37 @@
         <v>2.88</v>
       </c>
       <c r="U12">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>4.13</v>
+        <v>4.76</v>
       </c>
       <c r="AA12">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB12">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AC12">
-        <v>2.59</v>
+        <v>2.43</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
         <v>1.65</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK12">
         <v>1.67</v>
@@ -2431,31 +2431,31 @@
         <v>1.67</v>
       </c>
       <c r="O13">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
         <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="R13">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T13">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="U13">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="V13">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X13">
         <v>1.01</v>
@@ -2594,16 +2594,16 @@
         <v>3.3</v>
       </c>
       <c r="O14">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P14">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q14">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R14">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="S14">
         <v>1.2</v>
@@ -2612,10 +2612,10 @@
         <v>4</v>
       </c>
       <c r="U14">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V14">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W14">
         <v>1.17</v>
@@ -2630,16 +2630,16 @@
         <v>7</v>
       </c>
       <c r="AA14">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB14">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="AC14">
         <v>1.95</v>
       </c>
       <c r="AD14">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE14">
         <v>1.3</v>
@@ -2648,7 +2648,7 @@
         <v>1.36</v>
       </c>
       <c r="AG14">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>1.31</v>
       </c>
       <c r="Q15">
-        <v>7.95</v>
+        <v>7.8</v>
       </c>
       <c r="R15">
         <v>2.88</v>
@@ -2772,13 +2772,13 @@
         <v>1.19</v>
       </c>
       <c r="T15">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="V15">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W15">
         <v>1.23</v>
@@ -2811,7 +2811,7 @@
         <v>1.67</v>
       </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P18">
-        <v>2.62</v>
+        <v>2.19</v>
       </c>
       <c r="Q18">
-        <v>2.6</v>
+        <v>3.41</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z18">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AA18">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AB18">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="AC18">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="AD18">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE18">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG18">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AK18">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="O19">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="P19">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q19">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="R19">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="S19">
+        <v>1.2</v>
+      </c>
+      <c r="T19">
+        <v>4</v>
+      </c>
+      <c r="U19">
+        <v>2.1</v>
+      </c>
+      <c r="V19">
+        <v>1.67</v>
+      </c>
+      <c r="W19">
         <v>1.17</v>
-      </c>
-      <c r="T19">
-        <v>3</v>
-      </c>
-      <c r="U19">
-        <v>1.79</v>
-      </c>
-      <c r="V19">
-        <v>1.75</v>
-      </c>
-      <c r="W19">
-        <v>1.13</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z19">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA19">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB19">
+        <v>2.56</v>
+      </c>
+      <c r="AC19">
+        <v>1.85</v>
+      </c>
+      <c r="AD19">
+        <v>1.52</v>
+      </c>
+      <c r="AE19">
+        <v>1.3</v>
+      </c>
+      <c r="AF19">
+        <v>1.3</v>
+      </c>
+      <c r="AG19">
         <v>2.3</v>
       </c>
-      <c r="AC19">
-        <v>2.07</v>
-      </c>
-      <c r="AD19">
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.25</v>
+      </c>
+      <c r="AK19">
         <v>1.75</v>
-      </c>
-      <c r="AE19">
-        <v>1.26</v>
-      </c>
-      <c r="AF19">
-        <v>1.44</v>
-      </c>
-      <c r="AG19">
-        <v>2.5</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.16</v>
-      </c>
-      <c r="AK19">
-        <v>2.28</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.93</v>
+        <v>1.55</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="P20">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q20">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="R20">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="S20">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U20">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="V20">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="W20">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Z20">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AC20">
+        <v>1.74</v>
+      </c>
+      <c r="AD20">
         <v>1.84</v>
       </c>
-      <c r="AD20">
-        <v>1.52</v>
-      </c>
       <c r="AE20">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF20">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK20">
-        <v>1.75</v>
+        <v>2.24</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
+        <v>2.35</v>
+      </c>
+      <c r="O21">
+        <v>3.6</v>
+      </c>
+      <c r="P21">
+        <v>2.7</v>
+      </c>
+      <c r="Q21">
+        <v>2.6</v>
+      </c>
+      <c r="R21">
+        <v>2.25</v>
+      </c>
+      <c r="S21">
+        <v>1.25</v>
+      </c>
+      <c r="T21">
+        <v>3.5</v>
+      </c>
+      <c r="U21">
+        <v>2</v>
+      </c>
+      <c r="V21">
+        <v>1.53</v>
+      </c>
+      <c r="W21">
+        <v>1.07</v>
+      </c>
+      <c r="X21">
+        <v>1.02</v>
+      </c>
+      <c r="Y21">
+        <v>1.15</v>
+      </c>
+      <c r="Z21">
+        <v>4.3</v>
+      </c>
+      <c r="AA21">
+        <v>1.57</v>
+      </c>
+      <c r="AB21">
+        <v>2.14</v>
+      </c>
+      <c r="AC21">
         <v>2.2</v>
       </c>
-      <c r="O21">
-        <v>3.65</v>
-      </c>
-      <c r="P21">
-        <v>2.68</v>
-      </c>
-      <c r="Q21">
-        <v>2.36</v>
-      </c>
-      <c r="R21">
-        <v>2.65</v>
-      </c>
-      <c r="S21">
-        <v>1.2</v>
-      </c>
-      <c r="T21">
-        <v>4</v>
-      </c>
-      <c r="U21">
-        <v>2.04</v>
-      </c>
-      <c r="V21">
-        <v>1.78</v>
-      </c>
-      <c r="W21">
-        <v>1.2</v>
-      </c>
-      <c r="X21">
-        <v>1.01</v>
-      </c>
-      <c r="Y21">
-        <v>1.07</v>
-      </c>
-      <c r="Z21">
-        <v>5.85</v>
-      </c>
-      <c r="AA21">
-        <v>1.3</v>
-      </c>
-      <c r="AB21">
-        <v>3.2</v>
-      </c>
-      <c r="AC21">
-        <v>1.89</v>
-      </c>
       <c r="AD21">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="AE21">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AF21">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AG21">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
-        <v>2.19</v>
+        <v>2.74</v>
       </c>
       <c r="Q22">
-        <v>3.39</v>
+        <v>2.47</v>
       </c>
       <c r="R22">
-        <v>2.05</v>
+        <v>2.67</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="U22">
-        <v>2.52</v>
+        <v>1.75</v>
       </c>
       <c r="V22">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="Z22">
-        <v>4.23</v>
+        <v>5.9</v>
       </c>
       <c r="AA22">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AB22">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="AC22">
-        <v>2.52</v>
+        <v>1.88</v>
       </c>
       <c r="AD22">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AE22">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="AF22">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG22">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O23">
+        <v>3.3</v>
+      </c>
+      <c r="P23">
         <v>3.35</v>
       </c>
-      <c r="P23">
-        <v>3.5</v>
-      </c>
       <c r="Q23">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
         <v>1.3</v>
@@ -4079,10 +4079,10 @@
         <v>3.25</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
         <v>1.08</v>
@@ -4091,16 +4091,16 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA23">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC23">
         <v>2.88</v>
@@ -4112,7 +4112,7 @@
         <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
         <v>2.15</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK23">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,25 +4230,25 @@
         <v>2.3</v>
       </c>
       <c r="Q24">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U24">
         <v>2.65</v>
       </c>
       <c r="V24">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1.04</v>
@@ -4260,19 +4260,19 @@
         <v>3.28</v>
       </c>
       <c r="AA24">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB24">
         <v>1.78</v>
       </c>
       <c r="AC24">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="AD24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF24">
         <v>1.7</v>
@@ -4294,7 +4294,7 @@
         <v>1.52</v>
       </c>
       <c r="AK24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,10 +4387,10 @@
         <v>1.25</v>
       </c>
       <c r="O25">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="P25">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="Q25">
         <v>1.59</v>
@@ -4423,7 +4423,7 @@
         <v>8</v>
       </c>
       <c r="AA25">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AB25">
         <v>3.2</v>
@@ -4547,19 +4547,19 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="O26">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="P26">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="R26">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="S26">
         <v>1.07</v>
@@ -4713,13 +4713,13 @@
         <v>2.04</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P27">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="Q27">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="R27">
         <v>2.44</v>
@@ -4734,7 +4734,7 @@
         <v>1.96</v>
       </c>
       <c r="V27">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="W27">
         <v>1.18</v>
@@ -4746,16 +4746,16 @@
         <v>1.07</v>
       </c>
       <c r="Z27">
-        <v>5.95</v>
+        <v>6.25</v>
       </c>
       <c r="AA27">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB27">
         <v>2.9</v>
       </c>
       <c r="AC27">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD27">
         <v>1.79</v>
@@ -4876,28 +4876,28 @@
         <v>3.05</v>
       </c>
       <c r="O28">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P28">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q28">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="R28">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="S28">
         <v>1.11</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="U28">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V28">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W28">
         <v>1.26</v>
@@ -4915,7 +4915,7 @@
         <v>1.3</v>
       </c>
       <c r="AB28">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AC28">
         <v>1.74</v>
@@ -4927,10 +4927,10 @@
         <v>1.41</v>
       </c>
       <c r="AF28">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AG28">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="AK28">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5039,16 +5039,16 @@
         <v>1.4</v>
       </c>
       <c r="O29">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P29">
         <v>5.3</v>
       </c>
       <c r="Q29">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R29">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="S29">
         <v>1.17</v>
@@ -5057,10 +5057,10 @@
         <v>4.6</v>
       </c>
       <c r="U29">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="V29">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W29">
         <v>1.25</v>
@@ -5075,7 +5075,7 @@
         <v>7.3</v>
       </c>
       <c r="AA29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB29">
         <v>3.5</v>
@@ -5093,7 +5093,7 @@
         <v>1.4</v>
       </c>
       <c r="AG29">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O30">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="P30">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="Q30">
         <v>2.15</v>
@@ -5220,10 +5220,10 @@
         <v>5.5</v>
       </c>
       <c r="U30">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V30">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="W30">
         <v>1.3</v>
@@ -5232,25 +5232,25 @@
         <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Z30">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA30">
         <v>1.25</v>
       </c>
       <c r="AB30">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="AC30">
         <v>1.57</v>
       </c>
       <c r="AD30">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AE30">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AF30">
         <v>1.25</v>
@@ -5272,7 +5272,7 @@
         <v>1.22</v>
       </c>
       <c r="AK30">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,19 +5362,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="O31">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="P31">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q31">
-        <v>3.36</v>
+        <v>3.02</v>
       </c>
       <c r="R31">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S31">
         <v>1.12</v>
@@ -5386,7 +5386,7 @@
         <v>1.82</v>
       </c>
       <c r="V31">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="W31">
         <v>1.24</v>
@@ -5401,25 +5401,25 @@
         <v>7.3</v>
       </c>
       <c r="AA31">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AB31">
         <v>3.4</v>
       </c>
       <c r="AC31">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AD31">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AE31">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AF31">
         <v>1.3</v>
       </c>
       <c r="AG31">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AK31">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,58 +5525,58 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
         <v>3.45</v>
       </c>
       <c r="P32">
-        <v>3.11</v>
+        <v>2.99</v>
       </c>
       <c r="Q32">
-        <v>2.57</v>
+        <v>2.72</v>
       </c>
       <c r="R32">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="S32">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
         <v>3</v>
       </c>
       <c r="U32">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="V32">
         <v>1.36</v>
       </c>
       <c r="W32">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA32">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AB32">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AC32">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF32">
         <v>1.75</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK32">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P33">
-        <v>2.41</v>
+        <v>4.9</v>
       </c>
       <c r="Q33">
-        <v>2.61</v>
+        <v>2.23</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S33">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="T33">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="U33">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="V33">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>3.84</v>
       </c>
       <c r="AA33">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="AB33">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="AC33">
-        <v>2.23</v>
+        <v>3.1</v>
       </c>
       <c r="AD33">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AF33">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AG33">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="AK33">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="O34">
+        <v>3.9</v>
+      </c>
+      <c r="P34">
+        <v>2.41</v>
+      </c>
+      <c r="Q34">
+        <v>2.96</v>
+      </c>
+      <c r="R34">
+        <v>2.37</v>
+      </c>
+      <c r="S34">
+        <v>1.22</v>
+      </c>
+      <c r="T34">
         <v>3.8</v>
       </c>
-      <c r="P34">
-        <v>4.6</v>
-      </c>
-      <c r="Q34">
-        <v>2.21</v>
-      </c>
-      <c r="R34">
-        <v>2.1</v>
-      </c>
-      <c r="S34">
-        <v>1.29</v>
-      </c>
-      <c r="T34">
-        <v>3.3</v>
-      </c>
       <c r="U34">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="V34">
+        <v>1.67</v>
+      </c>
+      <c r="W34">
+        <v>1.12</v>
+      </c>
+      <c r="X34">
+        <v>1.01</v>
+      </c>
+      <c r="Y34">
+        <v>1.13</v>
+      </c>
+      <c r="Z34">
+        <v>6</v>
+      </c>
+      <c r="AA34">
+        <v>1.47</v>
+      </c>
+      <c r="AB34">
+        <v>2.64</v>
+      </c>
+      <c r="AC34">
+        <v>2.26</v>
+      </c>
+      <c r="AD34">
+        <v>1.63</v>
+      </c>
+      <c r="AE34">
+        <v>1.25</v>
+      </c>
+      <c r="AF34">
         <v>1.44</v>
       </c>
-      <c r="W34">
-        <v>1.07</v>
-      </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.22</v>
-      </c>
-      <c r="Z34">
-        <v>4.05</v>
-      </c>
-      <c r="AA34">
-        <v>1.76</v>
-      </c>
-      <c r="AB34">
-        <v>1.99</v>
-      </c>
-      <c r="AC34">
-        <v>3.1</v>
-      </c>
-      <c r="AD34">
-        <v>1.36</v>
-      </c>
-      <c r="AE34">
-        <v>1.09</v>
-      </c>
-      <c r="AF34">
-        <v>1.75</v>
-      </c>
       <c r="AG34">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="AK34">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,10 +6023,10 @@
         <v>2.55</v>
       </c>
       <c r="Q35">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="R35">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="S35">
         <v>1.36</v>
@@ -6044,7 +6044,7 @@
         <v>1.06</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
         <v>1.25</v>
@@ -6059,10 +6059,10 @@
         <v>1.91</v>
       </c>
       <c r="AC35">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AD35">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE35">
         <v>1.08</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P36">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -6198,7 +6198,7 @@
         <v>3.45</v>
       </c>
       <c r="U36">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="V36">
         <v>1.75</v>
@@ -6216,10 +6216,10 @@
         <v>7</v>
       </c>
       <c r="AA36">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="AC36">
         <v>2</v>
@@ -6250,7 +6250,7 @@
         <v>1.8</v>
       </c>
       <c r="AK36">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.05</v>
+        <v>3.15</v>
       </c>
       <c r="O37">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
+        <v>1.95</v>
+      </c>
+      <c r="Q37">
         <v>3.4</v>
       </c>
-      <c r="Q37">
-        <v>2.36</v>
-      </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T37">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="U37">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z37">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="AA37">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AB37">
-        <v>2.17</v>
+        <v>3.2</v>
       </c>
       <c r="AC37">
-        <v>2.68</v>
+        <v>1.87</v>
       </c>
       <c r="AD37">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AF37">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AG37">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,13 +6512,13 @@
         <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="R38">
         <v>2.65</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
         <v>4.05</v>
@@ -6576,7 +6576,7 @@
         <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.15</v>
+        <v>2.05</v>
       </c>
       <c r="O39">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>2.08</v>
+        <v>3.4</v>
       </c>
       <c r="Q39">
-        <v>3.5</v>
+        <v>2.36</v>
       </c>
       <c r="R39">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="U39">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="V39">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="W39">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z39">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AA39">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB39">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="AC39">
-        <v>1.91</v>
+        <v>2.68</v>
       </c>
       <c r="AD39">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AE39">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AG39">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="O40">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P40">
-        <v>4.35</v>
+        <v>4.95</v>
       </c>
       <c r="Q40">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R40">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S40">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T40">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U40">
         <v>2.3</v>
@@ -6856,37 +6856,37 @@
         <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X40">
         <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z40">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA40">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AB40">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AC40">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD40">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE40">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF40">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG40">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>5.8</v>
       </c>
       <c r="P41">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q41">
         <v>6.5</v>
       </c>
       <c r="R41">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="S41">
         <v>1.17</v>
       </c>
       <c r="T41">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U41">
         <v>1.85</v>
       </c>
       <c r="V41">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W41">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7031,16 +7031,16 @@
         <v>7.5</v>
       </c>
       <c r="AA41">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB41">
-        <v>3.19</v>
+        <v>3.33</v>
       </c>
       <c r="AC41">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD41">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AE41">
         <v>1.36</v>
@@ -7049,7 +7049,7 @@
         <v>1.65</v>
       </c>
       <c r="AG41">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O42">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q42">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="R42">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="S42">
         <v>1.32</v>
       </c>
       <c r="T42">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="U42">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W42">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
         <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z42">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AA42">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AB42">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AC42">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AD42">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE42">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AG42">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AK42">
         <v>1.16</v>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O43">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P43">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q43">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="R43">
         <v>1.71</v>
@@ -7351,22 +7351,22 @@
         <v>1.08</v>
       </c>
       <c r="Y43">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z43">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="AA43">
         <v>2.55</v>
       </c>
       <c r="AB43">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AC43">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AD43">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE43">
         <v>1.01</v>
@@ -7375,7 +7375,7 @@
         <v>2.1</v>
       </c>
       <c r="AG43">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK43">
         <v>1.25</v>
@@ -7481,28 +7481,28 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="O44">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
         <v>2.35</v>
       </c>
       <c r="Q44">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="R44">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="S44">
         <v>1.3</v>
       </c>
       <c r="T44">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U44">
-        <v>2.33</v>
+        <v>2.54</v>
       </c>
       <c r="V44">
         <v>1.5</v>
@@ -7517,25 +7517,25 @@
         <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="AA44">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB44">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AC44">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AD44">
         <v>1.44</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG44">
         <v>2.3</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AK44">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O45">
         <v>3.8</v>
@@ -7656,7 +7656,7 @@
         <v>3.77</v>
       </c>
       <c r="R45">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="S45">
         <v>1.2</v>
@@ -7665,7 +7665,7 @@
         <v>4</v>
       </c>
       <c r="U45">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="V45">
         <v>1.67</v>
@@ -7674,7 +7674,7 @@
         <v>1.2</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
         <v>1.1</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="O46">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P46">
         <v>4.85</v>
@@ -7837,7 +7837,7 @@
         <v>1.13</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
         <v>1.14</v>
@@ -7846,19 +7846,19 @@
         <v>4.3</v>
       </c>
       <c r="AA46">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB46">
         <v>2.18</v>
       </c>
       <c r="AC46">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="AD46">
         <v>1.44</v>
       </c>
       <c r="AE46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF46">
         <v>1.67</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="O47">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="P47">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q47">
-        <v>2.46</v>
+        <v>2.69</v>
       </c>
       <c r="R47">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="S47">
         <v>1.25</v>
@@ -8006,16 +8006,16 @@
         <v>1.14</v>
       </c>
       <c r="Z47">
-        <v>5.1</v>
+        <v>5.21</v>
       </c>
       <c r="AA47">
         <v>1.57</v>
       </c>
       <c r="AB47">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="AC47">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD47">
         <v>1.57</v>
@@ -8043,7 +8043,7 @@
         <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O48">
         <v>3.6</v>
@@ -8145,7 +8145,7 @@
         <v>2.43</v>
       </c>
       <c r="R48">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="S48">
         <v>1.2</v>
@@ -8154,10 +8154,10 @@
         <v>4</v>
       </c>
       <c r="U48">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="V48">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="W48">
         <v>1.14</v>
@@ -8166,31 +8166,31 @@
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z48">
-        <v>5.61</v>
+        <v>6.21</v>
       </c>
       <c r="AA48">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB48">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="AC48">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AD48">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AE48">
         <v>1.25</v>
       </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG48">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O49">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P49">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q49">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R49">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S49">
         <v>1.15</v>
       </c>
       <c r="T49">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U49">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V49">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="W49">
         <v>1.22</v>
@@ -8335,16 +8335,16 @@
         <v>8</v>
       </c>
       <c r="AA49">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB49">
-        <v>3.34</v>
+        <v>3.19</v>
       </c>
       <c r="AC49">
         <v>1.8</v>
       </c>
       <c r="AD49">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AE49">
         <v>1.4</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK49">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="O50">
-        <v>3.93</v>
+        <v>4.15</v>
       </c>
       <c r="P50">
-        <v>3.11</v>
+        <v>3.53</v>
       </c>
       <c r="Q50">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="R50">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T50">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="U50">
         <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="W50">
         <v>1.22</v>
@@ -8492,25 +8492,25 @@
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z50">
-        <v>6.33</v>
+        <v>7.22</v>
       </c>
       <c r="AA50">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB50">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AC50">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AD50">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AE50">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AF50">
         <v>1.4</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O51">
         <v>3.8</v>
       </c>
       <c r="P51">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="Q51">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="R51">
-        <v>2.67</v>
+        <v>2.51</v>
       </c>
       <c r="S51">
         <v>1.17</v>
       </c>
       <c r="T51">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U51">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="V51">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W51">
         <v>1.17</v>
@@ -8661,19 +8661,19 @@
         <v>6.5</v>
       </c>
       <c r="AA51">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB51">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AC51">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD51">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AE51">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF51">
         <v>1.36</v>
@@ -8695,7 +8695,7 @@
         <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O52">
         <v>3.9</v>
@@ -8794,10 +8794,10 @@
         <v>3.5</v>
       </c>
       <c r="Q52">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R52">
-        <v>2.56</v>
+        <v>2.61</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8806,10 +8806,10 @@
         <v>4</v>
       </c>
       <c r="U52">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="V52">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W52">
         <v>1.15</v>
@@ -8821,22 +8821,22 @@
         <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>5.22</v>
+        <v>5.59</v>
       </c>
       <c r="AA52">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB52">
         <v>2.63</v>
       </c>
       <c r="AC52">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AD52">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE52">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF52">
         <v>1.44</v>
@@ -10252,22 +10252,22 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="O61">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="Q61">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S61">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
         <v>3.9</v>
@@ -10276,10 +10276,10 @@
         <v>2</v>
       </c>
       <c r="V61">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W61">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X61">
         <v>0</v>
@@ -10288,28 +10288,28 @@
         <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>5.81</v>
+        <v>6.43</v>
       </c>
       <c r="AA61">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB61">
-        <v>2.6</v>
+        <v>2.87</v>
       </c>
       <c r="AC61">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AD61">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AE61">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF61">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG61">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AK61">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O62">
         <v>7.8</v>
       </c>
       <c r="P62">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Q62">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R62">
-        <v>2.9</v>
+        <v>3.07</v>
       </c>
       <c r="S62">
         <v>1.17</v>
@@ -10436,7 +10436,7 @@
         <v>5</v>
       </c>
       <c r="U62">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V62">
         <v>1.91</v>
@@ -10463,13 +10463,13 @@
         <v>1.73</v>
       </c>
       <c r="AD62">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE62">
         <v>1.42</v>
       </c>
       <c r="AF62">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG62">
         <v>2.2</v>
@@ -10578,19 +10578,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="O63">
         <v>3.6</v>
       </c>
       <c r="P63">
+        <v>2.8</v>
+      </c>
+      <c r="Q63">
         <v>2.6</v>
       </c>
-      <c r="Q63">
-        <v>2.53</v>
-      </c>
       <c r="R63">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="S63">
         <v>1.2</v>
@@ -10602,7 +10602,7 @@
         <v>2.1</v>
       </c>
       <c r="V63">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W63">
         <v>1.18</v>
@@ -10614,7 +10614,7 @@
         <v>1.13</v>
       </c>
       <c r="Z63">
-        <v>4.9</v>
+        <v>5.05</v>
       </c>
       <c r="AA63">
         <v>1.47</v>
@@ -10629,7 +10629,7 @@
         <v>1.65</v>
       </c>
       <c r="AE63">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF63">
         <v>1.44</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK63">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,31 +10741,31 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P64">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="Q64">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="R64">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S64">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
         <v>3.75</v>
       </c>
       <c r="U64">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V64">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W64">
         <v>1.13</v>
@@ -10774,22 +10774,22 @@
         <v>1.01</v>
       </c>
       <c r="Y64">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z64">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA64">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB64">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AC64">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD64">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="AE64">
         <v>1.22</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK64">
         <v>1.85</v>
@@ -10904,19 +10904,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="O65">
         <v>3.9</v>
       </c>
       <c r="P65">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="Q65">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="R65">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="S65">
         <v>1.2</v>
@@ -10943,25 +10943,25 @@
         <v>6</v>
       </c>
       <c r="AA65">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB65">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AC65">
         <v>2.2</v>
       </c>
       <c r="AD65">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE65">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF65">
         <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK65">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="O66">
         <v>3.6</v>
       </c>
       <c r="P66">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Q66">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="R66">
         <v>2.3</v>
@@ -11085,13 +11085,13 @@
         <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U66">
         <v>2.3</v>
       </c>
       <c r="V66">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W66">
         <v>1.14</v>
@@ -11103,7 +11103,7 @@
         <v>1.19</v>
       </c>
       <c r="Z66">
-        <v>4.74</v>
+        <v>4.82</v>
       </c>
       <c r="AA66">
         <v>1.64</v>
@@ -11112,10 +11112,10 @@
         <v>2.25</v>
       </c>
       <c r="AC66">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AD66">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE66">
         <v>1.2</v>
@@ -11124,7 +11124,7 @@
         <v>1.53</v>
       </c>
       <c r="AG66">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.33</v>
       </c>
       <c r="AK66">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11236,13 +11236,13 @@
         <v>4.8</v>
       </c>
       <c r="P67">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Q67">
         <v>1.88</v>
       </c>
       <c r="R67">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="S67">
         <v>1.25</v>
@@ -11251,7 +11251,7 @@
         <v>3.8</v>
       </c>
       <c r="U67">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="V67">
         <v>1.59</v>
@@ -11263,25 +11263,25 @@
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>4.92</v>
+        <v>5.25</v>
       </c>
       <c r="AA67">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB67">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="AC67">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD67">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE67">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF67">
         <v>1.7</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P68">
         <v>2.95</v>
@@ -11417,7 +11417,7 @@
         <v>2.38</v>
       </c>
       <c r="V68">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W68">
         <v>1.12</v>
@@ -11559,13 +11559,13 @@
         <v>2.02</v>
       </c>
       <c r="O69">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="P69">
         <v>3</v>
       </c>
       <c r="Q69">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R69">
         <v>2.5</v>
@@ -11574,16 +11574,16 @@
         <v>1.17</v>
       </c>
       <c r="T69">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="U69">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="V69">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="W69">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X69">
         <v>0</v>
@@ -11604,7 +11604,7 @@
         <v>1.9</v>
       </c>
       <c r="AD69">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE69">
         <v>1.36</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -627,11 +627,11 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -701,7 +701,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,26 +775,26 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,12 +859,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "42", "46", "65"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47", "72"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         <v>2</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q4">
         <v>2.59</v>
@@ -982,13 +982,13 @@
         <v>2.97</v>
       </c>
       <c r="U4">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V4">
         <v>1.43</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.01</v>
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
         <v>3.1</v>
       </c>
       <c r="Q5">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="R5">
         <v>2.18</v>
@@ -1151,16 +1151,16 @@
         <v>1.44</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z5">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA5">
         <v>1.75</v>
@@ -1175,13 +1175,13 @@
         <v>1.29</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG5">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1264,130 +1264,130 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="O6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P6">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="S6">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U6">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="V6">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="W6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z6">
-        <v>5.55</v>
+        <v>5.9</v>
       </c>
       <c r="AA6">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB6">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="AC6">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="AD6">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AE6">
+        <v>1.34</v>
+      </c>
+      <c r="AF6">
+        <v>1.36</v>
+      </c>
+      <c r="AG6">
+        <v>2.88</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>["13", "32", "57", "68", "73", "89"]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>["56"]</t>
+        </is>
+      </c>
+      <c r="AJ6">
+        <v>1.18</v>
+      </c>
+      <c r="AK6">
+        <v>1.9</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>10</v>
+      </c>
+      <c r="AN6">
+        <v>2</v>
+      </c>
+      <c r="AO6">
+        <v>17</v>
+      </c>
+      <c r="AP6">
+        <v>11</v>
+      </c>
+      <c r="AQ6">
+        <v>2.28</v>
+      </c>
+      <c r="AR6">
         <v>1.3</v>
       </c>
-      <c r="AF6">
-        <v>1.4</v>
-      </c>
-      <c r="AG6">
-        <v>2.62</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6">
-        <v>1.19</v>
-      </c>
-      <c r="AK6">
-        <v>1.88</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>-1</v>
-      </c>
-      <c r="AN6">
-        <v>-1</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>-1</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
       <c r="AS6">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>6.55</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="Q7">
-        <v>7.17</v>
+        <v>6.8</v>
       </c>
       <c r="R7">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T7">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U7">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="V7">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z7">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="AA7">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AB7">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF7">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="AG7">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q8">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R8">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="S8">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T8">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="U8">
         <v>2.7</v>
       </c>
       <c r="V8">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
         <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="AA8">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB8">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AD8">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF8">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG8">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O9">
         <v>4.2</v>
@@ -1785,7 +1785,7 @@
         <v>6</v>
       </c>
       <c r="Q9">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R9">
         <v>2.3</v>
@@ -1794,46 +1794,46 @@
         <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="U9">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
         <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA9">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AB9">
         <v>1.98</v>
       </c>
       <c r="AC9">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AD9">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE9">
         <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG9">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.15</v>
       </c>
       <c r="AK9">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="N10">
+        <v>2.76</v>
+      </c>
+      <c r="O10">
         <v>3.25</v>
-      </c>
-      <c r="O10">
-        <v>3.5</v>
       </c>
       <c r="P10">
         <v>1.86</v>
       </c>
       <c r="Q10">
-        <v>3.54</v>
+        <v>3.23</v>
       </c>
       <c r="R10">
         <v>2.16</v>
@@ -1969,22 +1969,22 @@
         <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z10">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AA10">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB10">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC10">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD10">
         <v>1.37</v>
@@ -1993,7 +1993,7 @@
         <v>1.09</v>
       </c>
       <c r="AF10">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG10">
         <v>2.2</v>
@@ -2012,7 +2012,7 @@
         <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O11">
         <v>3.2</v>
@@ -2114,19 +2114,19 @@
         <v>2.6</v>
       </c>
       <c r="R11">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S11">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U11">
         <v>3</v>
       </c>
       <c r="V11">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
         <v>1.05</v>
@@ -2135,16 +2135,16 @@
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z11">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AA11">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC11">
         <v>3.8</v>
@@ -2153,10 +2153,10 @@
         <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
         <v>1.85</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="Q12">
         <v>2.5</v>
@@ -2292,7 +2292,7 @@
         <v>1.56</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2304,13 +2304,13 @@
         <v>4.76</v>
       </c>
       <c r="AA12">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AB12">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AC12">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AD12">
         <v>1.3</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
         <v>1.67</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="O13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P13">
         <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="R13">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T13">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U13">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="V13">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="W13">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z13">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA13">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB13">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AC13">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AD13">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AE13">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF13">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AG13">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK13">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,49 +2917,49 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="O16">
-        <v>2.75</v>
+        <v>2.87</v>
       </c>
       <c r="P16">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="Q16">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="R16">
         <v>1.78</v>
       </c>
       <c r="S16">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T16">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="U16">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="V16">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W16">
         <v>1.04</v>
       </c>
       <c r="X16">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y16">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Z16">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AA16">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="AB16">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AC16">
         <v>3.6</v>
@@ -2968,7 +2968,7 @@
         <v>1.08</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF16">
         <v>2.25</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK16">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O17">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="Q17">
         <v>2.92</v>
@@ -3098,7 +3098,7 @@
         <v>1.5</v>
       </c>
       <c r="T17">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U17">
         <v>3.95</v>
@@ -3110,7 +3110,7 @@
         <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y17">
         <v>1.56</v>
@@ -3131,7 +3131,7 @@
         <v>1.13</v>
       </c>
       <c r="AE17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
         <v>2.25</v>
@@ -3153,7 +3153,7 @@
         <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="O18">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="P18">
-        <v>2.19</v>
+        <v>3.15</v>
       </c>
       <c r="Q18">
-        <v>3.41</v>
+        <v>2.41</v>
       </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="S18">
+        <v>1.2</v>
+      </c>
+      <c r="T18">
+        <v>4</v>
+      </c>
+      <c r="U18">
+        <v>2.1</v>
+      </c>
+      <c r="V18">
+        <v>1.67</v>
+      </c>
+      <c r="W18">
+        <v>1.17</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>1.08</v>
+      </c>
+      <c r="Z18">
+        <v>3.6</v>
+      </c>
+      <c r="AA18">
+        <v>1.33</v>
+      </c>
+      <c r="AB18">
+        <v>2.56</v>
+      </c>
+      <c r="AC18">
+        <v>1.85</v>
+      </c>
+      <c r="AD18">
+        <v>1.52</v>
+      </c>
+      <c r="AE18">
         <v>1.3</v>
       </c>
-      <c r="T18">
-        <v>3.3</v>
-      </c>
-      <c r="U18">
-        <v>2.53</v>
-      </c>
-      <c r="V18">
-        <v>1.52</v>
-      </c>
-      <c r="W18">
-        <v>1.13</v>
-      </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
-      <c r="Y18">
-        <v>1.16</v>
-      </c>
-      <c r="Z18">
-        <v>4.35</v>
-      </c>
-      <c r="AA18">
-        <v>1.63</v>
-      </c>
-      <c r="AB18">
-        <v>1.83</v>
-      </c>
-      <c r="AC18">
-        <v>2.52</v>
-      </c>
-      <c r="AD18">
-        <v>1.41</v>
-      </c>
-      <c r="AE18">
-        <v>1.13</v>
-      </c>
       <c r="AF18">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,61 +3406,61 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="O19">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="Q19">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U19">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA19">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="AC19">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD19">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AE19">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
         <v>2.3</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK19">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="O20">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="P20">
-        <v>4.8</v>
+        <v>2.19</v>
       </c>
       <c r="Q20">
-        <v>1.96</v>
+        <v>3.4</v>
       </c>
       <c r="R20">
+        <v>2.05</v>
+      </c>
+      <c r="S20">
+        <v>1.3</v>
+      </c>
+      <c r="T20">
+        <v>3.3</v>
+      </c>
+      <c r="U20">
         <v>2.52</v>
       </c>
-      <c r="S20">
-        <v>1.17</v>
-      </c>
-      <c r="T20">
-        <v>3</v>
-      </c>
-      <c r="U20">
-        <v>1.78</v>
-      </c>
       <c r="V20">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="W20">
         <v>1.13</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="Z20">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="AB20">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AC20">
-        <v>1.74</v>
+        <v>2.52</v>
       </c>
       <c r="AD20">
-        <v>1.84</v>
+        <v>1.41</v>
       </c>
       <c r="AE20">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
         <v>1.44</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>2.24</v>
+        <v>1.4</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="P21">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>1.99</v>
       </c>
       <c r="R21">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U21">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="V21">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="Z21">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AB21">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="AC21">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AD21">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="AE21">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AF21">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AK21">
-        <v>1.49</v>
+        <v>2.34</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O22">
         <v>3.65</v>
@@ -4058,22 +4058,22 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O23">
         <v>3.3</v>
       </c>
       <c r="P23">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="Q23">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T23">
         <v>3.25</v>
@@ -4088,13 +4088,13 @@
         <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA23">
         <v>1.72</v>
@@ -4106,13 +4106,13 @@
         <v>2.88</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE23">
         <v>1.11</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG23">
         <v>2.15</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>2.3</v>
       </c>
       <c r="Q24">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="R24">
         <v>2.06</v>
@@ -4248,7 +4248,7 @@
         <v>1.41</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
         <v>1.04</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O25">
         <v>5.8</v>
       </c>
       <c r="P25">
-        <v>8.75</v>
+        <v>8.25</v>
       </c>
       <c r="Q25">
         <v>1.59</v>
@@ -4411,7 +4411,7 @@
         <v>1.8</v>
       </c>
       <c r="W25">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4423,25 +4423,25 @@
         <v>8</v>
       </c>
       <c r="AA25">
+        <v>1.36</v>
+      </c>
+      <c r="AB25">
+        <v>3.13</v>
+      </c>
+      <c r="AC25">
+        <v>1.83</v>
+      </c>
+      <c r="AD25">
+        <v>1.84</v>
+      </c>
+      <c r="AE25">
         <v>1.33</v>
       </c>
-      <c r="AB25">
-        <v>3.2</v>
-      </c>
-      <c r="AC25">
-        <v>1.82</v>
-      </c>
-      <c r="AD25">
-        <v>1.85</v>
-      </c>
-      <c r="AE25">
-        <v>1.36</v>
-      </c>
       <c r="AF25">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4550,19 +4550,19 @@
         <v>1.25</v>
       </c>
       <c r="O26">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="P26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R26">
-        <v>3.06</v>
+        <v>3.51</v>
       </c>
       <c r="S26">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="T26">
         <v>5.9</v>
@@ -4571,7 +4571,7 @@
         <v>1.64</v>
       </c>
       <c r="V26">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="W26">
         <v>1.33</v>
@@ -4586,7 +4586,7 @@
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AB26">
         <v>4.4</v>
@@ -4595,16 +4595,16 @@
         <v>1.55</v>
       </c>
       <c r="AD26">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="AE26">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AF26">
         <v>1.44</v>
       </c>
       <c r="AG26">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK26">
         <v>4</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="O27">
         <v>3.65</v>
@@ -4719,7 +4719,7 @@
         <v>2.8</v>
       </c>
       <c r="Q27">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R27">
         <v>2.44</v>
@@ -4731,7 +4731,7 @@
         <v>4.1</v>
       </c>
       <c r="U27">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V27">
         <v>1.78</v>
@@ -4746,7 +4746,7 @@
         <v>1.07</v>
       </c>
       <c r="Z27">
-        <v>6.25</v>
+        <v>6.35</v>
       </c>
       <c r="AA27">
         <v>1.36</v>
@@ -4755,7 +4755,7 @@
         <v>2.9</v>
       </c>
       <c r="AC27">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AD27">
         <v>1.79</v>
@@ -4767,7 +4767,7 @@
         <v>1.33</v>
       </c>
       <c r="AG27">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4873,34 +4873,34 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O28">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
         <v>1.94</v>
       </c>
       <c r="Q28">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="R28">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="S28">
         <v>1.11</v>
       </c>
       <c r="T28">
-        <v>4.8</v>
+        <v>5.05</v>
       </c>
       <c r="U28">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V28">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="W28">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X28">
         <v>1.01</v>
@@ -4909,28 +4909,28 @@
         <v>1.02</v>
       </c>
       <c r="Z28">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AA28">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AB28">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AC28">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AD28">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AE28">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF28">
         <v>1.29</v>
       </c>
       <c r="AG28">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.85</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5042,58 +5042,58 @@
         <v>4.8</v>
       </c>
       <c r="P29">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="Q29">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R29">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="S29">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T29">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="U29">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="V29">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="W29">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z29">
-        <v>7.3</v>
+        <v>7.26</v>
       </c>
       <c r="AA29">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AB29">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AC29">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="AD29">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AE29">
         <v>1.4</v>
       </c>
       <c r="AF29">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG29">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK29">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="O30">
         <v>4.1</v>
       </c>
       <c r="P30">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q30">
         <v>2.15</v>
@@ -5220,7 +5220,7 @@
         <v>5.5</v>
       </c>
       <c r="U30">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V30">
         <v>2.05</v>
@@ -5229,7 +5229,7 @@
         <v>1.3</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.05</v>
@@ -5238,22 +5238,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AA30">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AB30">
         <v>3.7</v>
       </c>
       <c r="AC30">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AD30">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AE30">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AF30">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AG30">
         <v>3.5</v>
@@ -5368,58 +5368,58 @@
         <v>3.85</v>
       </c>
       <c r="P31">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q31">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="R31">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S31">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T31">
         <v>4.5</v>
       </c>
       <c r="U31">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="V31">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="W31">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Z31">
-        <v>7.3</v>
+        <v>7.21</v>
       </c>
       <c r="AA31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB31">
         <v>3.4</v>
       </c>
       <c r="AC31">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AD31">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AE31">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF31">
         <v>1.3</v>
       </c>
       <c r="AG31">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.8</v>
       </c>
       <c r="AK31">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.15</v>
+        <v>2.11</v>
       </c>
       <c r="O37">
         <v>3.9</v>
       </c>
       <c r="P37">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q37">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="R37">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="S37">
+        <v>1.22</v>
+      </c>
+      <c r="T37">
+        <v>4.05</v>
+      </c>
+      <c r="U37">
+        <v>2.13</v>
+      </c>
+      <c r="V37">
+        <v>1.69</v>
+      </c>
+      <c r="W37">
+        <v>1.18</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
+        <v>1.11</v>
+      </c>
+      <c r="Z37">
+        <v>6</v>
+      </c>
+      <c r="AA37">
+        <v>1.44</v>
+      </c>
+      <c r="AB37">
+        <v>2.8</v>
+      </c>
+      <c r="AC37">
+        <v>2.05</v>
+      </c>
+      <c r="AD37">
+        <v>1.73</v>
+      </c>
+      <c r="AE37">
+        <v>1.29</v>
+      </c>
+      <c r="AF37">
+        <v>1.4</v>
+      </c>
+      <c r="AG37">
+        <v>2.89</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.2</v>
       </c>
-      <c r="T37">
-        <v>4.2</v>
-      </c>
-      <c r="U37">
-        <v>2</v>
-      </c>
-      <c r="V37">
-        <v>1.75</v>
-      </c>
-      <c r="W37">
-        <v>1.22</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.07</v>
-      </c>
-      <c r="Z37">
-        <v>7.5</v>
-      </c>
-      <c r="AA37">
-        <v>1.35</v>
-      </c>
-      <c r="AB37">
-        <v>3.2</v>
-      </c>
-      <c r="AC37">
-        <v>1.87</v>
-      </c>
-      <c r="AD37">
-        <v>1.87</v>
-      </c>
-      <c r="AE37">
-        <v>1.36</v>
-      </c>
-      <c r="AF37">
-        <v>1.36</v>
-      </c>
-      <c r="AG37">
-        <v>3</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.22</v>
-      </c>
       <c r="AK37">
-        <v>1.31</v>
+        <v>1.74</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q38">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="R38">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="U38">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="V38">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="W38">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="Z38">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AA38">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AB38">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="AC38">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="AD38">
-        <v>1.73</v>
+        <v>1.46</v>
       </c>
       <c r="AE38">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF38">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AG38">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.05</v>
+        <v>3.15</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="P39">
+        <v>1.95</v>
+      </c>
+      <c r="Q39">
         <v>3.4</v>
       </c>
-      <c r="Q39">
-        <v>2.36</v>
-      </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="U39">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="V39">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="W39">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z39">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="AA39">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="AB39">
-        <v>2.17</v>
+        <v>3.2</v>
       </c>
       <c r="AC39">
-        <v>2.68</v>
+        <v>1.87</v>
       </c>
       <c r="AD39">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AF39">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AG39">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>1.81</v>
+        <v>1.31</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="O43">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P43">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q43">
         <v>3.9</v>
       </c>
       <c r="R43">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="S43">
         <v>1.5</v>
@@ -7354,7 +7354,7 @@
         <v>1.47</v>
       </c>
       <c r="Z43">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AA43">
         <v>2.55</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AK43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P44">
         <v>2.35</v>
       </c>
       <c r="Q44">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="R44">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="S44">
         <v>1.3</v>
@@ -7502,43 +7502,43 @@
         <v>3.2</v>
       </c>
       <c r="U44">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="V44">
         <v>1.5</v>
       </c>
       <c r="W44">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>4.17</v>
+        <v>3.98</v>
       </c>
       <c r="AA44">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AB44">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="AC44">
-        <v>2.76</v>
+        <v>2.91</v>
       </c>
       <c r="AD44">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF44">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG44">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="O45">
         <v>3.8</v>
@@ -7656,7 +7656,7 @@
         <v>3.77</v>
       </c>
       <c r="R45">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="S45">
         <v>1.2</v>
@@ -7665,7 +7665,7 @@
         <v>4</v>
       </c>
       <c r="U45">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="V45">
         <v>1.67</v>
@@ -7807,22 +7807,22 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="O46">
         <v>4.15</v>
       </c>
       <c r="P46">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
       </c>
       <c r="R46">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="S46">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
         <v>3.5</v>
@@ -7837,34 +7837,34 @@
         <v>1.13</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
         <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>4.3</v>
+        <v>4.45</v>
       </c>
       <c r="AA46">
         <v>1.6</v>
       </c>
       <c r="AB46">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AC46">
         <v>2.51</v>
       </c>
       <c r="AD46">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE46">
         <v>1.2</v>
       </c>
       <c r="AF46">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG46">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK46">
         <v>2.32</v>
@@ -7976,7 +7976,7 @@
         <v>3.72</v>
       </c>
       <c r="P47">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q47">
         <v>2.69</v>
@@ -8157,7 +8157,7 @@
         <v>2.11</v>
       </c>
       <c r="V48">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W48">
         <v>1.14</v>
@@ -8184,7 +8184,7 @@
         <v>1.76</v>
       </c>
       <c r="AE48">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF48">
         <v>1.4</v>
@@ -8299,10 +8299,10 @@
         <v>1.5</v>
       </c>
       <c r="O49">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="P49">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q49">
         <v>1.94</v>
@@ -8465,7 +8465,7 @@
         <v>4.15</v>
       </c>
       <c r="P50">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="Q50">
         <v>2.1</v>
@@ -8532,7 +8532,7 @@
         <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O51">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="P51">
         <v>2.77</v>
@@ -8788,16 +8788,16 @@
         <v>1.85</v>
       </c>
       <c r="O52">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P52">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q52">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R52">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8824,7 +8824,7 @@
         <v>5.59</v>
       </c>
       <c r="AA52">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB52">
         <v>2.63</v>
@@ -8833,7 +8833,7 @@
         <v>2.22</v>
       </c>
       <c r="AD52">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE52">
         <v>1.28</v>
@@ -8842,7 +8842,7 @@
         <v>1.44</v>
       </c>
       <c r="AG52">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10255,13 +10255,13 @@
         <v>2.55</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="Q61">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="R61">
         <v>2.45</v>
@@ -10288,7 +10288,7 @@
         <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>6.43</v>
+        <v>6.42</v>
       </c>
       <c r="AA61">
         <v>1.43</v>
@@ -10421,10 +10421,10 @@
         <v>7.8</v>
       </c>
       <c r="P62">
-        <v>8.5</v>
+        <v>8.59</v>
       </c>
       <c r="Q62">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R62">
         <v>3.07</v>
@@ -10581,10 +10581,10 @@
         <v>2.15</v>
       </c>
       <c r="O63">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -10744,7 +10744,7 @@
         <v>1.85</v>
       </c>
       <c r="O64">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P64">
         <v>3.75</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="O65">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="P65">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="Q65">
-        <v>2.34</v>
+        <v>2.59</v>
       </c>
       <c r="R65">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="S65">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U65">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V65">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z65">
-        <v>6</v>
+        <v>4.82</v>
       </c>
       <c r="AA65">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="AB65">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AC65">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AD65">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AE65">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF65">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG65">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="P66">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Q66">
-        <v>2.59</v>
+        <v>2.34</v>
       </c>
       <c r="R66">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T66">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U66">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="V66">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="W66">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>4.82</v>
+        <v>6</v>
       </c>
       <c r="AA66">
-        <v>1.64</v>
+        <v>1.48</v>
       </c>
       <c r="AB66">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AC66">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="AD66">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AE66">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF66">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK66">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,10 +11239,10 @@
         <v>5.75</v>
       </c>
       <c r="Q67">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R67">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="S67">
         <v>1.25</v>
@@ -11251,7 +11251,7 @@
         <v>3.8</v>
       </c>
       <c r="U67">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V67">
         <v>1.59</v>
@@ -11266,13 +11266,13 @@
         <v>1.14</v>
       </c>
       <c r="Z67">
-        <v>5.25</v>
+        <v>5.26</v>
       </c>
       <c r="AA67">
         <v>1.55</v>
       </c>
       <c r="AB67">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AC67">
         <v>2.38</v>
@@ -11399,7 +11399,7 @@
         <v>3.65</v>
       </c>
       <c r="P68">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="Q68">
         <v>2.67</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="O69">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="P69">
         <v>3</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -957,7 +957,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "37"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1116,11 +1116,11 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "90+5"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "87"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2091,14 +2091,14 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["74"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2594,61 +2594,61 @@
         <v>3.3</v>
       </c>
       <c r="O14">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P14">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="Q14">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R14">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="S14">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T14">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U14">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="V14">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="W14">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z14">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="AA14">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="AC14">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AD14">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AE14">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG14">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.62</v>
       </c>
       <c r="AK14">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>7.75</v>
+        <v>6.25</v>
       </c>
       <c r="O15">
-        <v>6</v>
+        <v>4.94</v>
       </c>
       <c r="P15">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="Q15">
-        <v>7.8</v>
+        <v>5.61</v>
       </c>
       <c r="R15">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="U15">
-        <v>1.99</v>
+        <v>2.32</v>
       </c>
       <c r="V15">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
-        <v>7.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA15">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AB15">
-        <v>2.82</v>
+        <v>2.27</v>
       </c>
       <c r="AC15">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="AD15">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AE15">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AF15">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
+        <v>1.14</v>
+      </c>
+      <c r="AK15">
         <v>1.1</v>
-      </c>
-      <c r="AK15">
-        <v>1.08</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>2.5</v>
+      </c>
+      <c r="O18">
+        <v>3.46</v>
+      </c>
+      <c r="P18">
+        <v>2.5</v>
+      </c>
+      <c r="Q18">
+        <v>2.63</v>
+      </c>
+      <c r="R18">
+        <v>2.3</v>
+      </c>
+      <c r="S18">
+        <v>1.25</v>
+      </c>
+      <c r="T18">
+        <v>3.5</v>
+      </c>
+      <c r="U18">
         <v>1.98</v>
       </c>
-      <c r="O18">
-        <v>3.65</v>
-      </c>
-      <c r="P18">
-        <v>3.15</v>
-      </c>
-      <c r="Q18">
-        <v>2.41</v>
-      </c>
-      <c r="R18">
-        <v>2.4</v>
-      </c>
-      <c r="S18">
-        <v>1.2</v>
-      </c>
-      <c r="T18">
-        <v>4</v>
-      </c>
-      <c r="U18">
-        <v>2.1</v>
-      </c>
       <c r="V18">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA18">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AB18">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AD18">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AE18">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AF18">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK18">
-        <v>1.75</v>
+        <v>1.46</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G19">
@@ -3409,77 +3409,77 @@
         <v>2.35</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P19">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="T19">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="V19">
+        <v>1.59</v>
+      </c>
+      <c r="W19">
+        <v>1.18</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>1.07</v>
+      </c>
+      <c r="Z19">
+        <v>5.9</v>
+      </c>
+      <c r="AA19">
+        <v>1.33</v>
+      </c>
+      <c r="AB19">
+        <v>3</v>
+      </c>
+      <c r="AC19">
+        <v>1.88</v>
+      </c>
+      <c r="AD19">
+        <v>1.79</v>
+      </c>
+      <c r="AE19">
+        <v>1.31</v>
+      </c>
+      <c r="AF19">
+        <v>1.36</v>
+      </c>
+      <c r="AG19">
+        <v>2.5</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>1.17</v>
+      </c>
+      <c r="AK19">
         <v>1.53</v>
-      </c>
-      <c r="W19">
-        <v>1.08</v>
-      </c>
-      <c r="X19">
-        <v>1.02</v>
-      </c>
-      <c r="Y19">
-        <v>1.15</v>
-      </c>
-      <c r="Z19">
-        <v>4.3</v>
-      </c>
-      <c r="AA19">
-        <v>1.57</v>
-      </c>
-      <c r="AB19">
-        <v>2.14</v>
-      </c>
-      <c r="AC19">
-        <v>2.2</v>
-      </c>
-      <c r="AD19">
-        <v>1.45</v>
-      </c>
-      <c r="AE19">
-        <v>1.14</v>
-      </c>
-      <c r="AF19">
-        <v>1.5</v>
-      </c>
-      <c r="AG19">
-        <v>2.3</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.21</v>
-      </c>
-      <c r="AK19">
-        <v>1.49</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O20">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
         <v>2.19</v>
       </c>
       <c r="Q20">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="R20">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S20">
         <v>1.3</v>
       </c>
       <c r="T20">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>4.35</v>
+        <v>4.12</v>
       </c>
       <c r="AA20">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AB20">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AC20">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AD20">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3753,10 +3753,10 @@
         <v>3.1</v>
       </c>
       <c r="U21">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V21">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W21">
         <v>1.14</v>
@@ -3768,19 +3768,19 @@
         <v>1.05</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>1.33</v>
       </c>
       <c r="AB21">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AC21">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD21">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE21">
         <v>1.28</v>
@@ -3789,7 +3789,7 @@
         <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="P22">
-        <v>2.74</v>
+        <v>3.57</v>
       </c>
       <c r="Q22">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="R22">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="S22">
+        <v>1.2</v>
+      </c>
+      <c r="T22">
+        <v>4</v>
+      </c>
+      <c r="U22">
+        <v>2.1</v>
+      </c>
+      <c r="V22">
+        <v>1.67</v>
+      </c>
+      <c r="W22">
         <v>1.17</v>
-      </c>
-      <c r="T22">
-        <v>4.2</v>
-      </c>
-      <c r="U22">
-        <v>1.75</v>
-      </c>
-      <c r="V22">
-        <v>1.59</v>
-      </c>
-      <c r="W22">
-        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z22">
-        <v>5.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA22">
         <v>1.33</v>
       </c>
       <c r="AB22">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="AC22">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AD22">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF22">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AG22">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P23">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="Q23">
         <v>2.63</v>
@@ -4088,7 +4088,7 @@
         <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.2</v>
@@ -4224,7 +4224,7 @@
         <v>2.88</v>
       </c>
       <c r="O24">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P24">
         <v>2.3</v>
@@ -4251,10 +4251,10 @@
         <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
         <v>3.28</v>
@@ -4266,19 +4266,19 @@
         <v>1.78</v>
       </c>
       <c r="AC24">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AD24">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE24">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF24">
         <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="O25">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="P25">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="R25">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="S25">
         <v>1.18</v>
       </c>
       <c r="T25">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U25">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="V25">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W25">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>6.55</v>
       </c>
       <c r="AA25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB25">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="AC25">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AD25">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AE25">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF25">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AK25">
-        <v>3.68</v>
+        <v>3.88</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,19 +4550,19 @@
         <v>1.25</v>
       </c>
       <c r="O26">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="P26">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q26">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="R26">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="S26">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="T26">
         <v>5.9</v>
@@ -4571,13 +4571,13 @@
         <v>1.64</v>
       </c>
       <c r="V26">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="W26">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y26">
         <v>1</v>
@@ -4589,19 +4589,19 @@
         <v>1.21</v>
       </c>
       <c r="AB26">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AC26">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD26">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AE26">
         <v>1.57</v>
       </c>
       <c r="AF26">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG26">
         <v>2.58</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AK26">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         <v>3.65</v>
       </c>
       <c r="P27">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q27">
         <v>2.38</v>
@@ -4728,7 +4728,7 @@
         <v>1.18</v>
       </c>
       <c r="T27">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U27">
         <v>1.97</v>
@@ -4746,25 +4746,25 @@
         <v>1.07</v>
       </c>
       <c r="Z27">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="AA27">
         <v>1.36</v>
       </c>
       <c r="AB27">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AC27">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AD27">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AE27">
         <v>1.3</v>
       </c>
       <c r="AF27">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AG27">
         <v>2.9</v>
@@ -4873,28 +4873,28 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P28">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Q28">
         <v>3.56</v>
       </c>
       <c r="R28">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S28">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="T28">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="U28">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V28">
         <v>1.95</v>
@@ -4915,10 +4915,10 @@
         <v>1.23</v>
       </c>
       <c r="AB28">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="AC28">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AD28">
         <v>2.08</v>
@@ -4927,10 +4927,10 @@
         <v>1.43</v>
       </c>
       <c r="AF28">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AG28">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5042,7 +5042,7 @@
         <v>4.8</v>
       </c>
       <c r="P29">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="Q29">
         <v>1.82</v>
@@ -5060,7 +5060,7 @@
         <v>1.98</v>
       </c>
       <c r="V29">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W29">
         <v>1.22</v>
@@ -5069,31 +5069,31 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z29">
-        <v>7.26</v>
+        <v>7.5</v>
       </c>
       <c r="AA29">
+        <v>1.35</v>
+      </c>
+      <c r="AB29">
+        <v>3.1</v>
+      </c>
+      <c r="AC29">
+        <v>1.85</v>
+      </c>
+      <c r="AD29">
+        <v>1.88</v>
+      </c>
+      <c r="AE29">
         <v>1.34</v>
       </c>
-      <c r="AB29">
-        <v>3.28</v>
-      </c>
-      <c r="AC29">
-        <v>1.82</v>
-      </c>
-      <c r="AD29">
-        <v>1.85</v>
-      </c>
-      <c r="AE29">
-        <v>1.4</v>
-      </c>
       <c r="AF29">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG29">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.13</v>
       </c>
       <c r="AK29">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>2.15</v>
       </c>
       <c r="R30">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S30">
         <v>1.15</v>
@@ -5220,10 +5220,10 @@
         <v>5.5</v>
       </c>
       <c r="U30">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V30">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="W30">
         <v>1.3</v>
@@ -5232,7 +5232,7 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z30">
         <v>8.199999999999999</v>
@@ -5241,19 +5241,19 @@
         <v>1.22</v>
       </c>
       <c r="AB30">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="AC30">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AD30">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AE30">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF30">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG30">
         <v>3.5</v>
@@ -5368,16 +5368,16 @@
         <v>3.85</v>
       </c>
       <c r="P31">
-        <v>1.96</v>
+        <v>2.03</v>
       </c>
       <c r="Q31">
-        <v>3.04</v>
+        <v>3.49</v>
       </c>
       <c r="R31">
         <v>2.54</v>
       </c>
       <c r="S31">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T31">
         <v>4.5</v>
@@ -5386,7 +5386,7 @@
         <v>1.86</v>
       </c>
       <c r="V31">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="W31">
         <v>1.22</v>
@@ -5395,22 +5395,22 @@
         <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z31">
-        <v>7.21</v>
+        <v>7.5</v>
       </c>
       <c r="AA31">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AB31">
         <v>3.4</v>
       </c>
       <c r="AC31">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AD31">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AE31">
         <v>1.36</v>
@@ -5419,7 +5419,7 @@
         <v>1.3</v>
       </c>
       <c r="AG31">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.8</v>
       </c>
       <c r="AK31">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5546,7 +5546,7 @@
         <v>3</v>
       </c>
       <c r="U32">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="V32">
         <v>1.36</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AK32">
         <v>1.59</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O33">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Q33">
         <v>2.23</v>
@@ -5703,10 +5703,10 @@
         <v>2.19</v>
       </c>
       <c r="S33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T33">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U33">
         <v>2.6</v>
@@ -5721,16 +5721,16 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
         <v>3.84</v>
       </c>
       <c r="AA33">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB33">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AC33">
         <v>3.1</v>
@@ -5739,7 +5739,7 @@
         <v>1.36</v>
       </c>
       <c r="AE33">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF33">
         <v>1.75</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK33">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,13 +5854,13 @@
         <v>2.45</v>
       </c>
       <c r="O34">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P34">
         <v>2.41</v>
       </c>
       <c r="Q34">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="R34">
         <v>2.37</v>
@@ -5872,28 +5872,28 @@
         <v>3.8</v>
       </c>
       <c r="U34">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="V34">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB34">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="AC34">
         <v>2.26</v>
@@ -5902,13 +5902,13 @@
         <v>1.63</v>
       </c>
       <c r="AE34">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF34">
         <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AK34">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,10 +6023,10 @@
         <v>2.55</v>
       </c>
       <c r="Q35">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="R35">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
         <v>1.36</v>
@@ -6035,37 +6035,37 @@
         <v>3.1</v>
       </c>
       <c r="U35">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z35">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="AA35">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AB35">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AC35">
-        <v>2.86</v>
+        <v>3.08</v>
       </c>
       <c r="AD35">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
         <v>1.67</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AK35">
         <v>1.5</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="O36">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P36">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q36">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R36">
         <v>2.38</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T36">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="U36">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="V36">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W36">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA36">
         <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="AC36">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD36">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE36">
         <v>1.29</v>
       </c>
       <c r="AF36">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG36">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AK36">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.11</v>
+        <v>3.15</v>
       </c>
       <c r="O37">
         <v>3.9</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q37">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="R37">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T37">
         <v>4.05</v>
       </c>
       <c r="U37">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="V37">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="W37">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AB37">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AC37">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AD37">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AE37">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF37">
+        <v>1.33</v>
+      </c>
+      <c r="AG37">
+        <v>3.04</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>1.67</v>
+      </c>
+      <c r="AK37">
         <v>1.4</v>
-      </c>
-      <c r="AG37">
-        <v>2.89</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.2</v>
-      </c>
-      <c r="AK37">
-        <v>1.74</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6509,49 +6509,49 @@
         <v>3.5</v>
       </c>
       <c r="P38">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q38">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="R38">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T38">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U38">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V38">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W38">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z38">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA38">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AB38">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="AC38">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="AD38">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AE38">
         <v>1.14</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK38">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="O39">
         <v>3.9</v>
       </c>
       <c r="P39">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="Q39">
-        <v>3.4</v>
+        <v>2.54</v>
       </c>
       <c r="R39">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S39">
         <v>1.2</v>
@@ -6687,28 +6687,28 @@
         <v>4.2</v>
       </c>
       <c r="U39">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V39">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W39">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z39">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="AA39">
         <v>1.35</v>
       </c>
       <c r="AB39">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AC39">
         <v>1.87</v>
@@ -6723,7 +6723,7 @@
         <v>1.36</v>
       </c>
       <c r="AG39">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.31</v>
+        <v>1.73</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,49 +6829,49 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="O40">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P40">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="Q40">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R40">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T40">
         <v>3.5</v>
       </c>
       <c r="U40">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V40">
         <v>1.57</v>
       </c>
       <c r="W40">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X40">
         <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z40">
         <v>5</v>
       </c>
       <c r="AA40">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AB40">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="AC40">
         <v>2.38</v>
@@ -6883,7 +6883,7 @@
         <v>1.2</v>
       </c>
       <c r="AF40">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
         <v>2.24</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O41">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="P41">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Q41">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="R41">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="S41">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T41">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="U41">
         <v>1.85</v>
       </c>
       <c r="V41">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="W41">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7031,25 +7031,25 @@
         <v>7.5</v>
       </c>
       <c r="AA41">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB41">
-        <v>3.33</v>
+        <v>3.08</v>
       </c>
       <c r="AC41">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AD41">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AE41">
         <v>1.36</v>
       </c>
       <c r="AF41">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AG41">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="AK41">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O42">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P42">
         <v>1.73</v>
       </c>
       <c r="Q42">
-        <v>4.94</v>
+        <v>5.09</v>
       </c>
       <c r="R42">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S42">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T42">
-        <v>3.12</v>
+        <v>2.96</v>
       </c>
       <c r="U42">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="V42">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W42">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="AA42">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AB42">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AC42">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AD42">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF42">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="AG42">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>2.21</v>
       </c>
       <c r="AK42">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="O43">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P43">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q43">
         <v>3.9</v>
       </c>
       <c r="R43">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="S43">
         <v>1.5</v>
@@ -7345,31 +7345,31 @@
         <v>1.25</v>
       </c>
       <c r="W43">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X43">
         <v>1.08</v>
       </c>
       <c r="Y43">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z43">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="AA43">
         <v>2.55</v>
       </c>
       <c r="AB43">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AC43">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD43">
         <v>1.12</v>
       </c>
       <c r="AE43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF43">
         <v>2.1</v>
@@ -7391,7 +7391,7 @@
         <v>1.51</v>
       </c>
       <c r="AK43">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7496,7 +7496,7 @@
         <v>2.34</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
         <v>3.2</v>
@@ -7508,13 +7508,13 @@
         <v>1.5</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X44">
         <v>1.03</v>
       </c>
       <c r="Y44">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z44">
         <v>3.98</v>
@@ -7532,13 +7532,13 @@
         <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF44">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.53</v>
       </c>
       <c r="AK44">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7665,7 +7665,7 @@
         <v>4</v>
       </c>
       <c r="U45">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="V45">
         <v>1.67</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.18</v>
+        <v>1.83</v>
       </c>
       <c r="AK45">
         <v>1.25</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="O46">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P46">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
@@ -7831,7 +7831,7 @@
         <v>2.25</v>
       </c>
       <c r="V46">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W46">
         <v>1.13</v>
@@ -7852,7 +7852,7 @@
         <v>2.24</v>
       </c>
       <c r="AC46">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AD46">
         <v>1.45</v>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
         <v>2.32</v>
@@ -8006,19 +8006,19 @@
         <v>1.14</v>
       </c>
       <c r="Z47">
-        <v>5.21</v>
+        <v>5.25</v>
       </c>
       <c r="AA47">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB47">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="AC47">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD47">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE47">
         <v>1.22</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
         <v>1.57</v>
@@ -8136,7 +8136,7 @@
         <v>2</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
         <v>3.4</v>
@@ -8145,22 +8145,22 @@
         <v>2.43</v>
       </c>
       <c r="R48">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="S48">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U48">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="V48">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8169,28 +8169,28 @@
         <v>1.1</v>
       </c>
       <c r="Z48">
-        <v>6.21</v>
+        <v>5.55</v>
       </c>
       <c r="AA48">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AB48">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AC48">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AD48">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AE48">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF48">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG48">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8302,16 +8302,16 @@
         <v>4.4</v>
       </c>
       <c r="P49">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Q49">
         <v>1.94</v>
       </c>
       <c r="R49">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S49">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T49">
         <v>4.5</v>
@@ -8320,40 +8320,40 @@
         <v>1.91</v>
       </c>
       <c r="V49">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="W49">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z49">
-        <v>8</v>
+        <v>7.18</v>
       </c>
       <c r="AA49">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB49">
-        <v>3.19</v>
+        <v>2.92</v>
       </c>
       <c r="AC49">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AD49">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="AE49">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AF49">
         <v>1.4</v>
       </c>
       <c r="AG49">
-        <v>2.88</v>
+        <v>2.58</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK49">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O50">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="P50">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="Q50">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="S50">
         <v>1.18</v>
       </c>
       <c r="T50">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="U50">
         <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="W50">
         <v>1.22</v>
@@ -8492,47 +8492,47 @@
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z50">
-        <v>7.22</v>
+        <v>7.45</v>
       </c>
       <c r="AA50">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AB50">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AC50">
+        <v>1.84</v>
+      </c>
+      <c r="AD50">
+        <v>2.05</v>
+      </c>
+      <c r="AE50">
+        <v>1.44</v>
+      </c>
+      <c r="AF50">
+        <v>1.36</v>
+      </c>
+      <c r="AG50">
+        <v>2.9</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ50">
+        <v>1.25</v>
+      </c>
+      <c r="AK50">
         <v>1.91</v>
-      </c>
-      <c r="AD50">
-        <v>1.96</v>
-      </c>
-      <c r="AE50">
-        <v>1.41</v>
-      </c>
-      <c r="AF50">
-        <v>1.4</v>
-      </c>
-      <c r="AG50">
-        <v>2.8</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ50">
-        <v>1.2</v>
-      </c>
-      <c r="AK50">
-        <v>2.1</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,22 +8622,22 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="O51">
-        <v>3.72</v>
+        <v>3.87</v>
       </c>
       <c r="P51">
         <v>2.77</v>
       </c>
       <c r="Q51">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="R51">
         <v>2.51</v>
       </c>
       <c r="S51">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T51">
         <v>4.2</v>
@@ -8649,37 +8649,37 @@
         <v>1.75</v>
       </c>
       <c r="W51">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X51">
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z51">
-        <v>6.5</v>
+        <v>6.79</v>
       </c>
       <c r="AA51">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB51">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AC51">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD51">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE51">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF51">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG51">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK51">
         <v>1.59</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="O52">
         <v>3.8</v>
       </c>
       <c r="P52">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="Q52">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R52">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8812,31 +8812,31 @@
         <v>1.67</v>
       </c>
       <c r="W52">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z52">
-        <v>5.59</v>
+        <v>6.35</v>
       </c>
       <c r="AA52">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB52">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AC52">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="AD52">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE52">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF52">
         <v>1.44</v>
@@ -8858,7 +8858,7 @@
         <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10258,28 +10258,28 @@
         <v>3.7</v>
       </c>
       <c r="P61">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="Q61">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="R61">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
         <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="U61">
         <v>2</v>
       </c>
       <c r="V61">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X61">
         <v>0</v>
@@ -10288,19 +10288,19 @@
         <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>6.42</v>
+        <v>6.37</v>
       </c>
       <c r="AA61">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB61">
         <v>2.87</v>
       </c>
       <c r="AC61">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AD61">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AE61">
         <v>1.33</v>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AK61">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10436,7 +10436,7 @@
         <v>5</v>
       </c>
       <c r="U62">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V62">
         <v>1.91</v>
@@ -10451,25 +10451,25 @@
         <v>1.07</v>
       </c>
       <c r="Z62">
-        <v>6.95</v>
+        <v>8.5</v>
       </c>
       <c r="AA62">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AB62">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AC62">
         <v>1.73</v>
       </c>
       <c r="AD62">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE62">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AF62">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG62">
         <v>2.2</v>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O63">
         <v>3.5</v>
       </c>
       <c r="P63">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="Q63">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="R63">
         <v>2.42</v>
@@ -10632,10 +10632,10 @@
         <v>1.23</v>
       </c>
       <c r="AF63">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG63">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,19 +10741,19 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O64">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P64">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="Q64">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="R64">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S64">
         <v>1.22</v>
@@ -10768,7 +10768,7 @@
         <v>1.65</v>
       </c>
       <c r="W64">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
         <v>1.01</v>
@@ -10789,16 +10789,16 @@
         <v>2.3</v>
       </c>
       <c r="AD64">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AE64">
         <v>1.22</v>
       </c>
       <c r="AF64">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG64">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10904,25 +10904,25 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="O65">
+        <v>3.7</v>
+      </c>
+      <c r="P65">
         <v>3.5</v>
       </c>
-      <c r="P65">
-        <v>3.1</v>
-      </c>
       <c r="Q65">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="R65">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S65">
         <v>1.25</v>
       </c>
       <c r="T65">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U65">
         <v>2.3</v>
@@ -10931,7 +10931,7 @@
         <v>1.57</v>
       </c>
       <c r="W65">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X65">
         <v>1.01</v>
@@ -10940,19 +10940,19 @@
         <v>1.19</v>
       </c>
       <c r="Z65">
-        <v>4.82</v>
+        <v>4.99</v>
       </c>
       <c r="AA65">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB65">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC65">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AD65">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE65">
         <v>1.2</v>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK65">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11070,10 +11070,10 @@
         <v>1.97</v>
       </c>
       <c r="O66">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P66">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="Q66">
         <v>2.34</v>
@@ -11112,7 +11112,7 @@
         <v>2.7</v>
       </c>
       <c r="AC66">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AD66">
         <v>1.66</v>
@@ -11124,7 +11124,7 @@
         <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11233,16 +11233,16 @@
         <v>1.44</v>
       </c>
       <c r="O67">
-        <v>4.8</v>
+        <v>4.84</v>
       </c>
       <c r="P67">
         <v>5.75</v>
       </c>
       <c r="Q67">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="R67">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="S67">
         <v>1.25</v>
@@ -11251,43 +11251,43 @@
         <v>3.8</v>
       </c>
       <c r="U67">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="V67">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="W67">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>5.26</v>
+        <v>5.57</v>
       </c>
       <c r="AA67">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AB67">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="AC67">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD67">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AE67">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF67">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AG67">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.14</v>
       </c>
       <c r="AK67">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,16 +11393,16 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O68">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P68">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="Q68">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="R68">
         <v>2.25</v>
@@ -11432,10 +11432,10 @@
         <v>4.5</v>
       </c>
       <c r="AA68">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB68">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC68">
         <v>2.63</v>
@@ -11447,10 +11447,10 @@
         <v>1.17</v>
       </c>
       <c r="AF68">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG68">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="O69">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="P69">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q69">
         <v>2.34</v>
@@ -11577,7 +11577,7 @@
         <v>4.33</v>
       </c>
       <c r="U69">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V69">
         <v>1.83</v>
@@ -11629,7 +11629,7 @@
         <v>1.25</v>
       </c>
       <c r="AK69">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AL69">
         <v>0</v>

--- a/jogos_2026-10-14.xlsx
+++ b/jogos_2026-10-14.xlsx
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,26 +2405,26 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "90+3"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,26 +2568,26 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "52", "81"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "90+3"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "74", "77"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "24", "37", "51", "66", "72"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -2913,17 +2913,17 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O16">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="P16">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="Q16">
         <v>2.71</v>
@@ -2938,16 +2938,16 @@
         <v>2.17</v>
       </c>
       <c r="U16">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="V16">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
         <v>1.53</v>
@@ -2956,34 +2956,34 @@
         <v>2.29</v>
       </c>
       <c r="AA16">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="AB16">
         <v>1.39</v>
       </c>
       <c r="AC16">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD16">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE16">
         <v>1.01</v>
       </c>
       <c r="AF16">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG16">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3060,57 +3060,57 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O17">
         <v>2.8</v>
       </c>
       <c r="P17">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="Q17">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="R17">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S17">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="T17">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="U17">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="V17">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W17">
         <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
         <v>1.56</v>
@@ -3119,25 +3119,25 @@
         <v>2.22</v>
       </c>
       <c r="AA17">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AB17">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AD17">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF17">
         <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3146,41 +3146,41 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "75"]</t>
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "51", "77"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3374,22 +3374,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Sonnenhof Großaspach</t>
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -3398,115 +3398,115 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="O19">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="P19">
-        <v>2.74</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>2.47</v>
+        <v>1.99</v>
       </c>
       <c r="R19">
-        <v>2.71</v>
+        <v>2.46</v>
       </c>
       <c r="S19">
         <v>1.17</v>
       </c>
       <c r="T19">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="U19">
         <v>1.75</v>
       </c>
       <c r="V19">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="W19">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z19">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>1.33</v>
       </c>
       <c r="AB19">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AC19">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AD19">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AE19">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AF19">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "11"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["70", "88"]</t>
         </is>
       </c>
       <c r="AJ19">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AK19">
-        <v>1.53</v>
+        <v>2.34</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3537,19 +3537,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -3561,72 +3561,72 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.78</v>
       </c>
       <c r="P20">
-        <v>2.19</v>
+        <v>3.57</v>
       </c>
       <c r="Q20">
-        <v>3.24</v>
+        <v>2.27</v>
       </c>
       <c r="R20">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="S20">
+        <v>1.2</v>
+      </c>
+      <c r="T20">
+        <v>4</v>
+      </c>
+      <c r="U20">
+        <v>2.1</v>
+      </c>
+      <c r="V20">
+        <v>1.67</v>
+      </c>
+      <c r="W20">
+        <v>1.17</v>
+      </c>
+      <c r="X20">
+        <v>1.01</v>
+      </c>
+      <c r="Y20">
+        <v>1.09</v>
+      </c>
+      <c r="Z20">
+        <v>3.6</v>
+      </c>
+      <c r="AA20">
+        <v>1.33</v>
+      </c>
+      <c r="AB20">
+        <v>2.56</v>
+      </c>
+      <c r="AC20">
+        <v>1.83</v>
+      </c>
+      <c r="AD20">
+        <v>1.65</v>
+      </c>
+      <c r="AE20">
         <v>1.3</v>
       </c>
-      <c r="T20">
-        <v>3.25</v>
-      </c>
-      <c r="U20">
-        <v>2.62</v>
-      </c>
-      <c r="V20">
-        <v>1.49</v>
-      </c>
-      <c r="W20">
-        <v>1.11</v>
-      </c>
-      <c r="X20">
-        <v>1.03</v>
-      </c>
-      <c r="Y20">
-        <v>1.18</v>
-      </c>
-      <c r="Z20">
-        <v>4.12</v>
-      </c>
-      <c r="AA20">
-        <v>1.69</v>
-      </c>
-      <c r="AB20">
-        <v>2.1</v>
-      </c>
-      <c r="AC20">
-        <v>2.7</v>
-      </c>
-      <c r="AD20">
-        <v>1.36</v>
-      </c>
-      <c r="AE20">
-        <v>1.11</v>
-      </c>
       <c r="AF20">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3635,41 +3635,41 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "64", "88"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK20">
-        <v>1.37</v>
+        <v>1.91</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3700,19 +3700,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sonnenhof Großaspach</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -3721,118 +3721,118 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>5</v>
+        <v>2.19</v>
       </c>
       <c r="Q21">
-        <v>1.99</v>
+        <v>3.24</v>
       </c>
       <c r="R21">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="S21">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
-        <v>1.75</v>
+        <v>2.62</v>
       </c>
       <c r="V21">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>4.12</v>
       </c>
       <c r="AA21">
-        <v>1.33</v>
+        <v>1.69</v>
       </c>
       <c r="AB21">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AC21">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="AD21">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65", "90+3"]</t>
         </is>
       </c>
       <c r="AJ21">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="AK21">
-        <v>2.34</v>
+        <v>1.37</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3863,139 +3863,139 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22">
         <v>0</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="O22">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
-        <v>3.57</v>
+        <v>2.74</v>
       </c>
       <c r="Q22">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="R22">
-        <v>2.39</v>
+        <v>2.71</v>
       </c>
       <c r="S22">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U22">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="V22">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="W22">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z22">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="AA22">
         <v>1.33</v>
       </c>
       <c r="AB22">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="AC22">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AD22">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AE22">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF22">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AG22">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66", "73"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "43"]</t>
         </is>
       </c>
       <c r="AJ22">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AL22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4201,23 +4201,23 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K24">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "24", "37", "53"]</t>
         </is>
       </c>
       <c r="AJ24">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4352,139 +4352,139 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25">
         <v>0</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O25">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="P25">
+        <v>7.5</v>
+      </c>
+      <c r="Q25">
+        <v>1.57</v>
+      </c>
+      <c r="R25">
+        <v>3.1</v>
+      </c>
+      <c r="S25">
+        <v>1.13</v>
+      </c>
+      <c r="T25">
+        <v>5.9</v>
+      </c>
+      <c r="U25">
+        <v>1.64</v>
+      </c>
+      <c r="V25">
+        <v>2.16</v>
+      </c>
+      <c r="W25">
+        <v>1.34</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1</v>
+      </c>
+      <c r="Z25">
         <v>9</v>
       </c>
-      <c r="Q25">
-        <v>1.56</v>
-      </c>
-      <c r="R25">
-        <v>2.94</v>
-      </c>
-      <c r="S25">
-        <v>1.18</v>
-      </c>
-      <c r="T25">
-        <v>4.4</v>
-      </c>
-      <c r="U25">
-        <v>1.85</v>
-      </c>
-      <c r="V25">
-        <v>1.83</v>
-      </c>
-      <c r="W25">
+      <c r="AA25">
         <v>1.21</v>
       </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.1</v>
-      </c>
-      <c r="Z25">
-        <v>6.55</v>
-      </c>
-      <c r="AA25">
-        <v>1.33</v>
-      </c>
       <c r="AB25">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="AC25">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="AD25">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="AE25">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="AG25">
+        <v>2.58</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>["45", "59", "81"]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>1.08</v>
+      </c>
+      <c r="AK25">
+        <v>3.78</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>5</v>
+      </c>
+      <c r="AN25">
+        <v>2</v>
+      </c>
+      <c r="AO25">
+        <v>17</v>
+      </c>
+      <c r="AP25">
+        <v>4</v>
+      </c>
+      <c r="AQ25">
         <v>2.05</v>
       </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ25">
-        <v>1.03</v>
-      </c>
-      <c r="AK25">
-        <v>3.88</v>
-      </c>
-      <c r="AL25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>-1</v>
-      </c>
-      <c r="AN25">
-        <v>-1</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>-1</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
       <c r="AR25">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4515,22 +4515,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4539,115 +4539,115 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O26">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R26">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="S26">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="T26">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="U26">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="V26">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="W26">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>1.1</v>
+      </c>
+      <c r="Z26">
+        <v>6.55</v>
+      </c>
+      <c r="AA26">
+        <v>1.33</v>
+      </c>
+      <c r="AB26">
+        <v>3.3</v>
+      </c>
+      <c r="AC26">
+        <v>1.87</v>
+      </c>
+      <c r="AD26">
+        <v>1.95</v>
+      </c>
+      <c r="AE26">
+        <v>1.35</v>
+      </c>
+      <c r="AF26">
+        <v>1.67</v>
+      </c>
+      <c r="AG26">
+        <v>2.05</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>["42"]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>["64"]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>1.03</v>
+      </c>
+      <c r="AK26">
+        <v>3.88</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>5</v>
+      </c>
+      <c r="AN26">
         <v>1</v>
       </c>
-      <c r="Y26">
-        <v>1</v>
-      </c>
-      <c r="Z26">
-        <v>9</v>
-      </c>
-      <c r="AA26">
-        <v>1.21</v>
-      </c>
-      <c r="AB26">
-        <v>4.35</v>
-      </c>
-      <c r="AC26">
-        <v>1.57</v>
-      </c>
-      <c r="AD26">
-        <v>2.41</v>
-      </c>
-      <c r="AE26">
-        <v>1.57</v>
-      </c>
-      <c r="AF26">
-        <v>1.45</v>
-      </c>
-      <c r="AG26">
-        <v>2.58</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.08</v>
-      </c>
-      <c r="AK26">
-        <v>3.78</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>-1</v>
-      </c>
-      <c r="AN26">
-        <v>-1</v>
-      </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4853,13 +4853,13 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5004,139 +5004,139 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="O29">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="P29">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q29">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="R29">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S29">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T29">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="U29">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="V29">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="W29">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Z29">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA29">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AB29">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AC29">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AD29">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="AE29">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AF29">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="AG29">
-        <v>2.53</v>
+        <v>3.5</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "18", "31", "42", "79"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88"]</t>
         </is>
       </c>
       <c r="AJ29">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>2.74</v>
+        <v>1.95</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5167,139 +5167,139 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="O30">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="P30">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="Q30">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="R30">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S30">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="T30">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="U30">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="V30">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="W30">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X30">
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Z30">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AA30">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AB30">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AC30">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AD30">
-        <v>2.22</v>
+        <v>1.88</v>
       </c>
       <c r="AE30">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AF30">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AG30">
-        <v>3.5</v>
+        <v>2.53</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "47", "62", "84"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AJ30">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK30">
-        <v>1.95</v>
+        <v>2.74</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5339,13 +5339,13 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -5354,11 +5354,11 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+6"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AJ31">
@@ -5441,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O32">
         <v>3.45</v>
@@ -5546,7 +5546,7 @@
         <v>3</v>
       </c>
       <c r="U32">
-        <v>2.65</v>
+        <v>2.91</v>
       </c>
       <c r="V32">
         <v>1.36</v>
@@ -5582,7 +5582,7 @@
         <v>1.75</v>
       </c>
       <c r="AG32">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK32">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P33">
-        <v>4.7</v>
+        <v>2.43</v>
       </c>
       <c r="Q33">
-        <v>2.23</v>
+        <v>2.97</v>
       </c>
       <c r="R33">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="V33">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X33">
         <v>1.03</v>
       </c>
       <c r="Y33">
+        <v>1.18</v>
+      </c>
+      <c r="Z33">
+        <v>4.75</v>
+      </c>
+      <c r="AA33">
+        <v>1.53</v>
+      </c>
+      <c r="AB33">
+        <v>2.45</v>
+      </c>
+      <c r="AC33">
+        <v>2.26</v>
+      </c>
+      <c r="AD33">
+        <v>1.63</v>
+      </c>
+      <c r="AE33">
+        <v>1.2</v>
+      </c>
+      <c r="AF33">
+        <v>1.44</v>
+      </c>
+      <c r="AG33">
+        <v>2.5</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
         <v>1.25</v>
       </c>
-      <c r="Z33">
-        <v>3.84</v>
-      </c>
-      <c r="AA33">
-        <v>1.83</v>
-      </c>
-      <c r="AB33">
-        <v>1.91</v>
-      </c>
-      <c r="AC33">
-        <v>3.1</v>
-      </c>
-      <c r="AD33">
-        <v>1.36</v>
-      </c>
-      <c r="AE33">
-        <v>1.07</v>
-      </c>
-      <c r="AF33">
-        <v>1.75</v>
-      </c>
-      <c r="AG33">
-        <v>1.95</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.15</v>
-      </c>
       <c r="AK33">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="O34">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>2.41</v>
+        <v>4.7</v>
       </c>
       <c r="Q34">
-        <v>3.02</v>
+        <v>2.15</v>
       </c>
       <c r="R34">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="V34">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="Z34">
-        <v>5</v>
+        <v>3.77</v>
       </c>
       <c r="AA34">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AB34">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AC34">
-        <v>2.26</v>
+        <v>3.25</v>
       </c>
       <c r="AD34">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AG34">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="AK34">
-        <v>1.52</v>
+        <v>2.16</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.15</v>
+        <v>2</v>
       </c>
       <c r="O37">
         <v>3.9</v>
       </c>
       <c r="P37">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q37">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="R37">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
+        <v>1.2</v>
+      </c>
+      <c r="T37">
+        <v>4.2</v>
+      </c>
+      <c r="U37">
+        <v>2.02</v>
+      </c>
+      <c r="V37">
+        <v>1.73</v>
+      </c>
+      <c r="W37">
         <v>1.21</v>
-      </c>
-      <c r="T37">
-        <v>4.05</v>
-      </c>
-      <c r="U37">
-        <v>1.9</v>
-      </c>
-      <c r="V37">
-        <v>1.75</v>
-      </c>
-      <c r="W37">
-        <v>1.22</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z37">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="AA37">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AB37">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AC37">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AD37">
         <v>1.87</v>
       </c>
       <c r="AE37">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF37">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG37">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.67</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="O39">
         <v>3.9</v>
       </c>
       <c r="P39">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q39">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="R39">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T39">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="U39">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="V39">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W39">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z39">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="AA39">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AB39">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC39">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AD39">
         <v>1.87</v>
       </c>
       <c r="AE39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF39">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG39">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.67</v>
       </c>
       <c r="AK39">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7155,28 +7155,28 @@
         </is>
       </c>
       <c r="N42">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="O42">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P42">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Q42">
-        <v>5.09</v>
+        <v>5.26</v>
       </c>
       <c r="R42">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S42">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T42">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U42">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="V42">
         <v>1.4</v>
@@ -7185,34 +7185,34 @@
         <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
         <v>1.29</v>
       </c>
       <c r="Z42">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA42">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AB42">
         <v>1.9</v>
       </c>
       <c r="AC42">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD42">
         <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF42">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AG42">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AK42">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="Q65">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="R65">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T65">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U65">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="V65">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="W65">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
         <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z65">
-        <v>4.99</v>
+        <v>6</v>
       </c>
       <c r="AA65">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AB65">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AC65">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AD65">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AE65">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF65">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK65">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="O66">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="Q66">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="R66">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U66">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="V66">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="W66">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X66">
         <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z66">
-        <v>6</v>
+        <v>4.99</v>
       </c>
       <c r="AA66">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AB66">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC66">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AD66">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AE66">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF66">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG66">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AL66">
         <v>0</v>
